--- a/media/Levels/Level_5.xlsx
+++ b/media/Levels/Level_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71F39DD4-A09D-4452-8173-4C1AE9BD2B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508954F7-CD6B-46E1-A8CA-61D564C0ACD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="1">
   <si>
     <t xml:space="preserve"> </t>
     <phoneticPr fontId="1"/>
@@ -63,7 +63,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -100,6 +100,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -115,7 +121,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -132,6 +138,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -690,7 +699,7 @@
       <c r="BW1" s="1">
         <v>0</v>
       </c>
-      <c r="BX1" s="1">
+      <c r="BX1" s="6">
         <v>1</v>
       </c>
       <c r="BY1" s="1">
@@ -14704,8 +14713,8 @@
       <c r="BW150" s="1">
         <v>0</v>
       </c>
-      <c r="BX150" s="1" t="s">
-        <v>0</v>
+      <c r="BX150" s="6">
+        <v>1</v>
       </c>
       <c r="BY150" s="1">
         <v>0</v>

--- a/media/Levels/Level_5.xlsx
+++ b/media/Levels/Level_5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508954F7-CD6B-46E1-A8CA-61D564C0ACD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E19118-B94E-462C-AEDE-683B238226BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
+    <workbookView xWindow="3672" yWindow="84" windowWidth="13836" windowHeight="12156" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -923,6 +923,9 @@
       <c r="DC2" s="1">
         <v>0</v>
       </c>
+      <c r="DO2" s="1">
+        <v>0</v>
+      </c>
       <c r="DS2" s="1">
         <v>0</v>
       </c>
@@ -938,10 +941,13 @@
         <v>6</v>
       </c>
       <c r="BN3" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DC3" s="1">
         <v>3</v>
+      </c>
+      <c r="DO3" s="1">
+        <v>4</v>
       </c>
       <c r="DS3" s="1">
         <v>3</v>
@@ -961,6 +967,9 @@
         <v>0</v>
       </c>
       <c r="DC4" s="1">
+        <v>0</v>
+      </c>
+      <c r="DO4" s="1">
         <v>0</v>
       </c>
       <c r="DS4" s="1">
@@ -983,6 +992,9 @@
       <c r="DC5" s="1">
         <v>0</v>
       </c>
+      <c r="DO5" s="1">
+        <v>0</v>
+      </c>
       <c r="DS5" s="1">
         <v>0</v>
       </c>
@@ -998,10 +1010,13 @@
         <v>0</v>
       </c>
       <c r="BN6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DC6" s="1">
         <v>3</v>
+      </c>
+      <c r="DO6" s="1">
+        <v>4</v>
       </c>
       <c r="DS6" s="1">
         <v>3</v>
@@ -1023,6 +1038,9 @@
       <c r="DC7" s="1">
         <v>0</v>
       </c>
+      <c r="DO7" s="1">
+        <v>0</v>
+      </c>
       <c r="DS7" s="1">
         <v>0</v>
       </c>
@@ -1058,6 +1076,9 @@
       <c r="DC8" s="1">
         <v>0</v>
       </c>
+      <c r="DO8" s="1">
+        <v>0</v>
+      </c>
       <c r="DZ8" s="4">
         <v>0</v>
       </c>
@@ -1085,10 +1106,13 @@
         <v>0</v>
       </c>
       <c r="BN9" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DC9" s="1">
         <v>3</v>
+      </c>
+      <c r="DO9" s="1">
+        <v>4</v>
       </c>
       <c r="DZ9" s="4">
         <v>0</v>
@@ -1122,6 +1146,9 @@
       <c r="DC10" s="1">
         <v>0</v>
       </c>
+      <c r="DO10" s="1">
+        <v>0</v>
+      </c>
       <c r="DZ10" s="4">
         <v>0</v>
       </c>
@@ -1146,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN11" s="1">
         <v>0</v>
@@ -1247,13 +1274,13 @@
         <v>0</v>
       </c>
       <c r="BN12" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DC12" s="1">
         <v>3</v>
       </c>
       <c r="DO12" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS12" s="1">
         <v>3</v>
@@ -1380,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP14" s="3">
         <v>0</v>
@@ -1598,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="BN15" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CO15" s="3">
         <v>0</v>
@@ -1661,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="DO15" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS15" s="1">
         <v>3</v>
@@ -1674,6 +1701,21 @@
       <c r="A16" s="1">
         <v>0</v>
       </c>
+      <c r="Q16" s="4">
+        <v>0</v>
+      </c>
+      <c r="R16" s="4">
+        <v>0</v>
+      </c>
+      <c r="S16" s="4">
+        <v>0</v>
+      </c>
+      <c r="T16" s="4">
+        <v>0</v>
+      </c>
+      <c r="U16" s="4">
+        <v>0</v>
+      </c>
       <c r="X16" s="1">
         <v>0</v>
       </c>
@@ -1832,6 +1874,21 @@
       <c r="A17" s="1">
         <v>0</v>
       </c>
+      <c r="Q17" s="4">
+        <v>0</v>
+      </c>
+      <c r="R17" s="4">
+        <v>0</v>
+      </c>
+      <c r="S17" s="4">
+        <v>0</v>
+      </c>
+      <c r="T17" s="4">
+        <v>0</v>
+      </c>
+      <c r="U17" s="4">
+        <v>0</v>
+      </c>
       <c r="W17" s="1">
         <v>5</v>
       </c>
@@ -1851,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP17" s="3">
         <v>0</v>
@@ -2002,6 +2059,21 @@
       <c r="A18" s="1">
         <v>0</v>
       </c>
+      <c r="Q18" s="4">
+        <v>0</v>
+      </c>
+      <c r="R18" s="4">
+        <v>0</v>
+      </c>
+      <c r="S18" s="4">
+        <v>11</v>
+      </c>
+      <c r="T18" s="4">
+        <v>0</v>
+      </c>
+      <c r="U18" s="4">
+        <v>0</v>
+      </c>
       <c r="V18" s="1">
         <v>0</v>
       </c>
@@ -2147,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="DO18" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS18" s="1">
         <v>3</v>
@@ -2175,11 +2247,23 @@
       <c r="A19" s="1">
         <v>0</v>
       </c>
-      <c r="U19" s="1">
+      <c r="Q19" s="4">
+        <v>0</v>
+      </c>
+      <c r="R19" s="4">
+        <v>0</v>
+      </c>
+      <c r="S19" s="4">
+        <v>0</v>
+      </c>
+      <c r="T19" s="4">
+        <v>0</v>
+      </c>
+      <c r="U19" s="4">
         <v>0</v>
       </c>
       <c r="AC19" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI19" s="1">
         <v>0</v>
@@ -2348,29 +2432,26 @@
       <c r="A20" s="1">
         <v>0</v>
       </c>
-      <c r="N20" s="4">
-        <v>0</v>
-      </c>
-      <c r="O20" s="4">
-        <v>0</v>
-      </c>
-      <c r="P20" s="4">
-        <v>0</v>
-      </c>
       <c r="Q20" s="4">
         <v>0</v>
       </c>
       <c r="R20" s="4">
         <v>0</v>
       </c>
-      <c r="T20" s="1">
-        <v>5</v>
+      <c r="S20" s="4">
+        <v>0</v>
+      </c>
+      <c r="T20" s="4">
+        <v>0</v>
+      </c>
+      <c r="U20" s="4">
+        <v>0</v>
       </c>
       <c r="AC20" s="1">
         <v>0</v>
       </c>
       <c r="AI20" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP20" s="3">
         <v>0</v>
@@ -2536,24 +2617,6 @@
       <c r="A21" s="1">
         <v>0</v>
       </c>
-      <c r="N21" s="4">
-        <v>0</v>
-      </c>
-      <c r="O21" s="4">
-        <v>0</v>
-      </c>
-      <c r="P21" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="4">
-        <v>0</v>
-      </c>
-      <c r="R21" s="4">
-        <v>0</v>
-      </c>
-      <c r="S21" s="1">
-        <v>0</v>
-      </c>
       <c r="AC21" s="1">
         <v>0</v>
       </c>
@@ -2696,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="DO21" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS21" s="1">
         <v>3</v>
@@ -2739,23 +2802,8 @@
       <c r="A22" s="1">
         <v>0</v>
       </c>
-      <c r="N22" s="4">
-        <v>0</v>
-      </c>
-      <c r="O22" s="4">
-        <v>0</v>
-      </c>
-      <c r="P22" s="4">
-        <v>11</v>
-      </c>
-      <c r="Q22" s="4">
-        <v>0</v>
-      </c>
-      <c r="R22" s="4">
-        <v>0</v>
-      </c>
       <c r="AC22" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI22" s="1">
         <v>0</v>
@@ -2924,26 +2972,11 @@
       <c r="A23" s="1">
         <v>0</v>
       </c>
-      <c r="N23" s="4">
-        <v>0</v>
-      </c>
-      <c r="O23" s="4">
-        <v>0</v>
-      </c>
-      <c r="P23" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="4">
-        <v>0</v>
-      </c>
-      <c r="R23" s="4">
-        <v>0</v>
-      </c>
       <c r="AC23" s="1">
         <v>0</v>
       </c>
       <c r="AI23" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP23" s="3">
         <v>0</v>
@@ -3063,9 +3096,6 @@
         <v>0</v>
       </c>
       <c r="DH23" s="3">
-        <v>0</v>
-      </c>
-      <c r="DO23" s="1">
         <v>0</v>
       </c>
       <c r="DS23" s="1">
@@ -3094,21 +3124,21 @@
       <c r="A24" s="1">
         <v>0</v>
       </c>
-      <c r="N24" s="4">
-        <v>0</v>
-      </c>
-      <c r="O24" s="4">
-        <v>0</v>
-      </c>
-      <c r="P24" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="4">
-        <v>0</v>
-      </c>
       <c r="R24" s="4">
         <v>0</v>
       </c>
+      <c r="S24" s="4">
+        <v>0</v>
+      </c>
+      <c r="T24" s="4">
+        <v>0</v>
+      </c>
+      <c r="U24" s="4">
+        <v>0</v>
+      </c>
+      <c r="V24" s="4">
+        <v>0</v>
+      </c>
       <c r="AC24" s="1">
         <v>0</v>
       </c>
@@ -3175,6 +3205,24 @@
       <c r="BI24" s="3">
         <v>0</v>
       </c>
+      <c r="CI24" s="1">
+        <v>0</v>
+      </c>
+      <c r="CJ24" s="1">
+        <v>3</v>
+      </c>
+      <c r="CK24" s="1">
+        <v>0</v>
+      </c>
+      <c r="CL24" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM24" s="1">
+        <v>3</v>
+      </c>
+      <c r="CN24" s="1">
+        <v>0</v>
+      </c>
       <c r="CO24" s="3">
         <v>0</v>
       </c>
@@ -3234,9 +3282,6 @@
       </c>
       <c r="DH24" s="3">
         <v>0</v>
-      </c>
-      <c r="DO24" s="1">
-        <v>3</v>
       </c>
       <c r="DS24" s="1">
         <v>3</v>
@@ -3264,8 +3309,23 @@
       <c r="A25" s="1">
         <v>0</v>
       </c>
+      <c r="R25" s="4">
+        <v>0</v>
+      </c>
+      <c r="S25" s="4">
+        <v>0</v>
+      </c>
+      <c r="T25" s="4">
+        <v>0</v>
+      </c>
+      <c r="U25" s="4">
+        <v>0</v>
+      </c>
+      <c r="V25" s="4">
+        <v>0</v>
+      </c>
       <c r="AC25" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI25" s="1">
         <v>0</v>
@@ -3388,9 +3448,6 @@
         <v>0</v>
       </c>
       <c r="DH25" s="3">
-        <v>0</v>
-      </c>
-      <c r="DO25" s="1">
         <v>0</v>
       </c>
       <c r="DS25" s="1">
@@ -3419,11 +3476,26 @@
       <c r="A26" s="1">
         <v>0</v>
       </c>
+      <c r="R26" s="4">
+        <v>0</v>
+      </c>
+      <c r="S26" s="4">
+        <v>0</v>
+      </c>
+      <c r="T26" s="4">
+        <v>11</v>
+      </c>
+      <c r="U26" s="4">
+        <v>0</v>
+      </c>
+      <c r="V26" s="4">
+        <v>0</v>
+      </c>
       <c r="AC26" s="1">
         <v>0</v>
       </c>
       <c r="AI26" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP26" s="3">
         <v>0</v>
@@ -3546,9 +3618,6 @@
         <v>0</v>
       </c>
       <c r="DH26" s="3">
-        <v>0</v>
-      </c>
-      <c r="DO26" s="1">
         <v>0</v>
       </c>
       <c r="DS26" s="1">
@@ -3577,6 +3646,9 @@
       <c r="V27" s="4">
         <v>0</v>
       </c>
+      <c r="W27" s="1">
+        <v>0</v>
+      </c>
       <c r="Z27" s="4">
         <v>0</v>
       </c>
@@ -3656,7 +3728,7 @@
         <v>0</v>
       </c>
       <c r="BN27" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CO27" s="3">
         <v>0</v>
@@ -3717,9 +3789,6 @@
       </c>
       <c r="DH27" s="3">
         <v>0</v>
-      </c>
-      <c r="DO27" s="1">
-        <v>3</v>
       </c>
       <c r="DS27" s="1">
         <v>3</v>
@@ -3747,6 +3816,9 @@
       <c r="V28" s="4">
         <v>0</v>
       </c>
+      <c r="X28" s="1">
+        <v>6</v>
+      </c>
       <c r="Z28" s="4">
         <v>0</v>
       </c>
@@ -3886,9 +3958,6 @@
         <v>0</v>
       </c>
       <c r="DH28" s="3">
-        <v>0</v>
-      </c>
-      <c r="DO28" s="1">
         <v>0</v>
       </c>
       <c r="DS28" s="1">
@@ -3902,27 +3971,6 @@
       <c r="A29" s="1">
         <v>0</v>
       </c>
-      <c r="R29" s="4">
-        <v>0</v>
-      </c>
-      <c r="S29" s="4">
-        <v>0</v>
-      </c>
-      <c r="T29" s="4">
-        <v>11</v>
-      </c>
-      <c r="U29" s="4">
-        <v>0</v>
-      </c>
-      <c r="V29" s="4">
-        <v>0</v>
-      </c>
-      <c r="W29" s="1">
-        <v>0</v>
-      </c>
-      <c r="X29" s="1">
-        <v>3</v>
-      </c>
       <c r="Y29" s="1">
         <v>0</v>
       </c>
@@ -3942,7 +3990,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP29" s="3">
         <v>0</v>
@@ -4081,21 +4129,6 @@
       <c r="A30" s="1">
         <v>0</v>
       </c>
-      <c r="R30" s="4">
-        <v>0</v>
-      </c>
-      <c r="S30" s="4">
-        <v>0</v>
-      </c>
-      <c r="T30" s="4">
-        <v>0</v>
-      </c>
-      <c r="U30" s="4">
-        <v>0</v>
-      </c>
-      <c r="V30" s="4">
-        <v>0</v>
-      </c>
       <c r="Z30" s="4">
         <v>0</v>
       </c>
@@ -4184,7 +4217,7 @@
         <v>0</v>
       </c>
       <c r="BN30" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CF30" s="4">
         <v>0</v>
@@ -4262,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="DO30" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS30" s="1">
         <v>3</v>
@@ -4275,21 +4308,6 @@
       <c r="A31" s="1">
         <v>0</v>
       </c>
-      <c r="R31" s="4">
-        <v>0</v>
-      </c>
-      <c r="S31" s="4">
-        <v>0</v>
-      </c>
-      <c r="T31" s="4">
-        <v>0</v>
-      </c>
-      <c r="U31" s="4">
-        <v>0</v>
-      </c>
-      <c r="V31" s="4">
-        <v>0</v>
-      </c>
       <c r="Z31" s="4">
         <v>0</v>
       </c>
@@ -4553,10 +4571,10 @@
         <v>0</v>
       </c>
       <c r="BF33" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN33" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CF33" s="4">
         <v>0</v>
@@ -4634,7 +4652,7 @@
         <v>0</v>
       </c>
       <c r="DO33" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS33" s="1">
         <v>3</v>
@@ -4796,16 +4814,16 @@
         <v>0</v>
       </c>
       <c r="BF36" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN36" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CG36" s="1">
         <v>5</v>
       </c>
       <c r="DO36" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS36" s="1">
         <v>3</v>
@@ -4925,16 +4943,16 @@
         <v>0</v>
       </c>
       <c r="BF39" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN39" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CD39" s="1">
         <v>5</v>
       </c>
       <c r="DO39" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS39" s="1">
         <v>3</v>
@@ -4994,16 +5012,16 @@
         <v>0</v>
       </c>
       <c r="BF42" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN42" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CA42" s="1">
         <v>5</v>
       </c>
       <c r="DO42" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS42" s="1">
         <v>3</v>
@@ -5326,13 +5344,13 @@
         <v>0</v>
       </c>
       <c r="AG46" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BK46" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DY46" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET46" s="1">
         <v>0</v>
@@ -5557,13 +5575,13 @@
         <v>0</v>
       </c>
       <c r="AG49" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BK49" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DY49" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET49" s="1">
         <v>0</v>
@@ -5788,13 +5806,13 @@
         <v>0</v>
       </c>
       <c r="AG52" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BK52" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DY52" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="EF52" s="4">
         <v>0</v>
@@ -6064,13 +6082,13 @@
         <v>0</v>
       </c>
       <c r="AG55" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BK55" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DY55" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="EF55" s="4">
         <v>0</v>
@@ -6358,7 +6376,7 @@
         <v>0</v>
       </c>
       <c r="AG58" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN58" s="4">
         <v>0</v>
@@ -6376,7 +6394,7 @@
         <v>0</v>
       </c>
       <c r="BK58" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL58" s="1">
         <v>0</v>
@@ -6559,7 +6577,7 @@
         <v>0</v>
       </c>
       <c r="DY58" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET58" s="1">
         <v>0</v>
@@ -6803,10 +6821,10 @@
         <v>0</v>
       </c>
       <c r="DM60" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS60" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DY60" s="1">
         <v>0</v>
@@ -6880,7 +6898,7 @@
         <v>0</v>
       </c>
       <c r="AG61" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN61" s="4">
         <v>0</v>
@@ -6898,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="BK61" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DM61" s="1">
         <v>0</v>
@@ -6907,7 +6925,7 @@
         <v>0</v>
       </c>
       <c r="DY61" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET61" s="1">
         <v>0</v>
@@ -7067,10 +7085,10 @@
         <v>0</v>
       </c>
       <c r="DM63" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS63" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DY63" s="1">
         <v>0</v>
@@ -7144,10 +7162,10 @@
         <v>0</v>
       </c>
       <c r="AG64" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BK64" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DM64" s="1">
         <v>0</v>
@@ -7156,7 +7174,7 @@
         <v>0</v>
       </c>
       <c r="DY64" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET64" s="1">
         <v>0</v>
@@ -7376,10 +7394,10 @@
         <v>0</v>
       </c>
       <c r="DM66" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS66" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DY66" s="1">
         <v>0</v>
@@ -7392,14 +7410,14 @@
       <c r="A67" s="1">
         <v>0</v>
       </c>
-      <c r="Y67" s="1">
+      <c r="S67" s="1">
         <v>0</v>
       </c>
       <c r="AG67" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BK67" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BP67" s="3">
         <v>0</v>
@@ -7468,7 +7486,7 @@
         <v>0</v>
       </c>
       <c r="DY67" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET67" s="1">
         <v>0</v>
@@ -7478,8 +7496,8 @@
       <c r="A68" s="1">
         <v>0</v>
       </c>
-      <c r="X68" s="1">
-        <v>5</v>
+      <c r="S68" s="1">
+        <v>4</v>
       </c>
       <c r="AG68" s="1">
         <v>0</v>
@@ -7579,7 +7597,7 @@
       <c r="A69" s="1">
         <v>0</v>
       </c>
-      <c r="W69" s="1">
+      <c r="S69" s="1">
         <v>0</v>
       </c>
       <c r="AG69" s="1">
@@ -7649,10 +7667,10 @@
         <v>0</v>
       </c>
       <c r="DM69" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS69" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DY69" s="1">
         <v>0</v>
@@ -7680,17 +7698,14 @@
       <c r="A70" s="1">
         <v>0</v>
       </c>
-      <c r="B70" s="1">
-        <v>0</v>
-      </c>
-      <c r="V70" s="1">
+      <c r="S70" s="1">
         <v>0</v>
       </c>
       <c r="AG70" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BK70" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BP70" s="3">
         <v>0</v>
@@ -7759,7 +7774,7 @@
         <v>0</v>
       </c>
       <c r="DY70" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="EB70" s="4">
         <v>0</v>
@@ -7784,11 +7799,8 @@
       <c r="A71" s="1">
         <v>0</v>
       </c>
-      <c r="C71" s="1">
-        <v>6</v>
-      </c>
-      <c r="U71" s="1">
-        <v>5</v>
+      <c r="S71" s="1">
+        <v>4</v>
       </c>
       <c r="AG71" s="1">
         <v>0</v>
@@ -7957,10 +7969,7 @@
       <c r="A72" s="1">
         <v>0</v>
       </c>
-      <c r="D72" s="1">
-        <v>0</v>
-      </c>
-      <c r="T72" s="1">
+      <c r="S72" s="1">
         <v>0</v>
       </c>
       <c r="AG72" s="1">
@@ -8114,7 +8123,7 @@
         <v>0</v>
       </c>
       <c r="DS72" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DY72" s="1">
         <v>0</v>
@@ -8142,9 +8151,6 @@
       <c r="A73" s="1">
         <v>0</v>
       </c>
-      <c r="E73" s="1">
-        <v>0</v>
-      </c>
       <c r="S73" s="1">
         <v>0</v>
       </c>
@@ -8212,7 +8218,7 @@
         <v>0</v>
       </c>
       <c r="DY73" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET73" s="1">
         <v>0</v>
@@ -8221,9 +8227,6 @@
     <row r="74" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A74" s="1">
         <v>0</v>
-      </c>
-      <c r="F74" s="1">
-        <v>6</v>
       </c>
       <c r="R74" s="1">
         <v>5</v>
@@ -8302,9 +8305,6 @@
       <c r="A75" s="2">
         <v>2</v>
       </c>
-      <c r="G75" s="1">
-        <v>0</v>
-      </c>
       <c r="Q75" s="1">
         <v>0</v>
       </c>
@@ -8369,7 +8369,7 @@
         <v>0</v>
       </c>
       <c r="DS75" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY75" s="1">
         <v>0</v>
@@ -8382,9 +8382,6 @@
       <c r="A76" s="1">
         <v>0</v>
       </c>
-      <c r="H76" s="1">
-        <v>0</v>
-      </c>
       <c r="P76" s="1">
         <v>0</v>
       </c>
@@ -8449,10 +8446,10 @@
         <v>0</v>
       </c>
       <c r="DS76" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY76" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET76" s="1">
         <v>0</v>
@@ -8462,9 +8459,6 @@
       <c r="A77" s="1">
         <v>0</v>
       </c>
-      <c r="I77" s="1">
-        <v>6</v>
-      </c>
       <c r="O77" s="1">
         <v>5</v>
       </c>
@@ -8557,7 +8551,31 @@
       <c r="A78" s="1">
         <v>0</v>
       </c>
-      <c r="J78" s="1">
+      <c r="B78" s="1">
+        <v>0</v>
+      </c>
+      <c r="C78" s="1">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1">
+        <v>0</v>
+      </c>
+      <c r="E78" s="1">
+        <v>0</v>
+      </c>
+      <c r="F78" s="1">
+        <v>3</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0</v>
+      </c>
+      <c r="H78" s="5">
+        <v>0</v>
+      </c>
+      <c r="I78" s="5">
+        <v>7</v>
+      </c>
+      <c r="J78" s="5">
         <v>0</v>
       </c>
       <c r="K78" s="5">
@@ -8648,7 +8666,7 @@
         <v>0</v>
       </c>
       <c r="DS78" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY78" s="1">
         <v>0</v>
@@ -8737,10 +8755,10 @@
         <v>0</v>
       </c>
       <c r="DS79" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY79" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET79" s="1">
         <v>0</v>
@@ -9086,7 +9104,7 @@
         <v>0</v>
       </c>
       <c r="DS81" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY81" s="1">
         <v>0</v>
@@ -9100,10 +9118,10 @@
         <v>0</v>
       </c>
       <c r="AG82" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BK82" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BP82" s="3">
         <v>0</v>
@@ -9166,13 +9184,13 @@
         <v>0</v>
       </c>
       <c r="DM82" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS82" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY82" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET82" s="1">
         <v>0</v>
@@ -9338,7 +9356,7 @@
         <v>0</v>
       </c>
       <c r="DS84" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY84" s="1">
         <v>0</v>
@@ -9352,10 +9370,10 @@
         <v>0</v>
       </c>
       <c r="AG85" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BK85" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BP85" s="3">
         <v>0</v>
@@ -9421,13 +9439,13 @@
         <v>3</v>
       </c>
       <c r="DM85" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS85" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY85" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET85" s="1">
         <v>0</v>
@@ -9476,7 +9494,7 @@
         <v>0</v>
       </c>
       <c r="DS87" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY87" s="1">
         <v>0</v>
@@ -9490,19 +9508,19 @@
         <v>0</v>
       </c>
       <c r="AG88" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CJ88" s="1">
         <v>3</v>
       </c>
       <c r="DM88" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS88" s="1">
         <v>0</v>
       </c>
       <c r="DY88" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET88" s="1">
         <v>0</v>
@@ -9522,7 +9540,7 @@
         <v>0</v>
       </c>
       <c r="DS89" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY89" s="1">
         <v>0</v>
@@ -9545,7 +9563,7 @@
         <v>0</v>
       </c>
       <c r="DS90" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY90" s="1">
         <v>0</v>
@@ -9559,19 +9577,19 @@
         <v>0</v>
       </c>
       <c r="AG91" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CJ91" s="1">
         <v>3</v>
       </c>
       <c r="DM91" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS91" s="1">
         <v>0</v>
       </c>
       <c r="DY91" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET91" s="1">
         <v>0</v>
@@ -9594,7 +9612,7 @@
         <v>0</v>
       </c>
       <c r="DS92" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY92" s="1">
         <v>0</v>
@@ -9611,7 +9629,7 @@
         <v>0</v>
       </c>
       <c r="BK93" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL93" s="1">
         <v>0</v>
@@ -9731,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="DS93" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY93" s="1">
         <v>0</v>
@@ -9745,7 +9763,7 @@
         <v>0</v>
       </c>
       <c r="AG94" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BK94" s="1">
         <v>0</v>
@@ -9760,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="DY94" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET94" s="1">
         <v>0</v>
@@ -9773,8 +9791,11 @@
       <c r="AG95" s="1">
         <v>0</v>
       </c>
+      <c r="BK95" s="1">
+        <v>0</v>
+      </c>
       <c r="BR95" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CH95" s="1">
         <v>3</v>
@@ -9783,7 +9804,7 @@
         <v>0</v>
       </c>
       <c r="DS95" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY95" s="1">
         <v>0</v>
@@ -9799,6 +9820,9 @@
       <c r="AG96" s="1">
         <v>0</v>
       </c>
+      <c r="BK96" s="1">
+        <v>4</v>
+      </c>
       <c r="BR96" s="1">
         <v>0</v>
       </c>
@@ -9806,7 +9830,7 @@
         <v>0</v>
       </c>
       <c r="DS96" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY96" s="1">
         <v>0</v>
@@ -9820,7 +9844,10 @@
         <v>0</v>
       </c>
       <c r="AG97" s="1">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="BK97" s="1">
+        <v>0</v>
       </c>
       <c r="BP97" s="4">
         <v>0</v>
@@ -9856,7 +9883,22 @@
         <v>0</v>
       </c>
       <c r="DY97" s="1">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="EK97" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL97" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM97" s="4">
+        <v>0</v>
+      </c>
+      <c r="EN97" s="4">
+        <v>0</v>
+      </c>
+      <c r="EO97" s="4">
+        <v>0</v>
       </c>
       <c r="ET97" s="1">
         <v>0</v>
@@ -9869,6 +9911,9 @@
       <c r="AG98" s="1">
         <v>0</v>
       </c>
+      <c r="BK98" s="1">
+        <v>0</v>
+      </c>
       <c r="BP98" s="4">
         <v>0</v>
       </c>
@@ -9900,9 +9945,24 @@
         <v>0</v>
       </c>
       <c r="DS98" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY98" s="1">
+        <v>0</v>
+      </c>
+      <c r="EK98" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL98" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM98" s="4">
+        <v>0</v>
+      </c>
+      <c r="EN98" s="4">
+        <v>0</v>
+      </c>
+      <c r="EO98" s="4">
         <v>0</v>
       </c>
       <c r="ET98" s="1">
@@ -9916,6 +9976,9 @@
       <c r="AG99" s="1">
         <v>0</v>
       </c>
+      <c r="BK99" s="1">
+        <v>4</v>
+      </c>
       <c r="BP99" s="4">
         <v>0</v>
       </c>
@@ -9947,9 +10010,24 @@
         <v>0</v>
       </c>
       <c r="DS99" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY99" s="1">
+        <v>0</v>
+      </c>
+      <c r="EK99" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL99" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM99" s="4">
+        <v>11</v>
+      </c>
+      <c r="EN99" s="4">
+        <v>0</v>
+      </c>
+      <c r="EO99" s="4">
         <v>0</v>
       </c>
       <c r="ET99" s="1">
@@ -9961,7 +10039,10 @@
         <v>0</v>
       </c>
       <c r="AG100" s="1">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="BK100" s="1">
+        <v>0</v>
       </c>
       <c r="BP100" s="4">
         <v>0</v>
@@ -9997,7 +10078,22 @@
         <v>0</v>
       </c>
       <c r="DY100" s="1">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="EK100" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL100" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM100" s="4">
+        <v>0</v>
+      </c>
+      <c r="EN100" s="4">
+        <v>0</v>
+      </c>
+      <c r="EO100" s="4">
+        <v>0</v>
       </c>
       <c r="ET100" s="1">
         <v>0</v>
@@ -10041,9 +10137,24 @@
         <v>0</v>
       </c>
       <c r="DS101" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY101" s="1">
+        <v>0</v>
+      </c>
+      <c r="EK101" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL101" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM101" s="4">
+        <v>0</v>
+      </c>
+      <c r="EN101" s="4">
+        <v>0</v>
+      </c>
+      <c r="EO101" s="4">
         <v>0</v>
       </c>
       <c r="ET101" s="1">
@@ -10064,7 +10175,7 @@
         <v>0</v>
       </c>
       <c r="DS102" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY102" s="1">
         <v>0</v>
@@ -10078,10 +10189,10 @@
         <v>0</v>
       </c>
       <c r="AG103" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BR103" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CH103" s="1">
         <v>3</v>
@@ -10090,7 +10201,7 @@
         <v>0</v>
       </c>
       <c r="DY103" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET103" s="1">
         <v>0</v>
@@ -10110,7 +10221,7 @@
         <v>0</v>
       </c>
       <c r="DS104" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY104" s="1">
         <v>0</v>
@@ -10412,7 +10523,7 @@
         <v>0</v>
       </c>
       <c r="DS105" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY105" s="1">
         <v>0</v>
@@ -10441,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="DY106" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET106" s="1">
         <v>0</v>
@@ -10455,16 +10566,16 @@
         <v>5</v>
       </c>
       <c r="AX107" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BE107" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ107" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS107" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY107" s="1">
         <v>0</v>
@@ -10490,7 +10601,7 @@
         <v>0</v>
       </c>
       <c r="DS108" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY108" s="1">
         <v>0</v>
@@ -10516,7 +10627,7 @@
         <v>0</v>
       </c>
       <c r="DY109" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET109" s="1">
         <v>0</v>
@@ -10533,13 +10644,13 @@
         <v>5</v>
       </c>
       <c r="AX110" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ110" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS110" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY110" s="1">
         <v>0</v>
@@ -10552,6 +10663,9 @@
       <c r="A111" s="1">
         <v>0</v>
       </c>
+      <c r="O111" s="4">
+        <v>0</v>
+      </c>
       <c r="P111" s="4">
         <v>0</v>
       </c>
@@ -10564,9 +10678,6 @@
       <c r="S111" s="4">
         <v>0</v>
       </c>
-      <c r="T111" s="4">
-        <v>0</v>
-      </c>
       <c r="AX111" s="1">
         <v>0</v>
       </c>
@@ -10574,7 +10685,7 @@
         <v>0</v>
       </c>
       <c r="DS111" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY111" s="1">
         <v>0</v>
@@ -10587,6 +10698,9 @@
       <c r="A112" s="1">
         <v>0</v>
       </c>
+      <c r="O112" s="4">
+        <v>0</v>
+      </c>
       <c r="P112" s="4">
         <v>0</v>
       </c>
@@ -10599,9 +10713,6 @@
       <c r="S112" s="4">
         <v>0</v>
       </c>
-      <c r="T112" s="4">
-        <v>0</v>
-      </c>
       <c r="AX112" s="1">
         <v>0</v>
       </c>
@@ -10612,7 +10723,7 @@
         <v>0</v>
       </c>
       <c r="DY112" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET112" s="1">
         <v>0</v>
@@ -10622,29 +10733,29 @@
       <c r="A113" s="1">
         <v>0</v>
       </c>
+      <c r="O113" s="4">
+        <v>0</v>
+      </c>
       <c r="P113" s="4">
         <v>0</v>
       </c>
       <c r="Q113" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R113" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S113" s="4">
         <v>0</v>
       </c>
-      <c r="T113" s="4">
-        <v>0</v>
-      </c>
       <c r="AX113" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ113" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS113" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY113" s="1">
         <v>0</v>
@@ -10657,6 +10768,9 @@
       <c r="A114" s="1">
         <v>0</v>
       </c>
+      <c r="J114" s="4">
+        <v>0</v>
+      </c>
       <c r="K114" s="4">
         <v>0</v>
       </c>
@@ -10684,9 +10798,6 @@
       <c r="S114" s="4">
         <v>0</v>
       </c>
-      <c r="T114" s="4">
-        <v>0</v>
-      </c>
       <c r="AX114" s="1">
         <v>0</v>
       </c>
@@ -10697,7 +10808,7 @@
         <v>0</v>
       </c>
       <c r="DS114" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY114" s="1">
         <v>0</v>
@@ -10710,6 +10821,9 @@
       <c r="A115" s="1">
         <v>0</v>
       </c>
+      <c r="J115" s="4">
+        <v>0</v>
+      </c>
       <c r="K115" s="4">
         <v>0</v>
       </c>
@@ -10737,14 +10851,11 @@
       <c r="S115" s="4">
         <v>0</v>
       </c>
-      <c r="T115" s="4">
-        <v>0</v>
-      </c>
       <c r="AX115" s="1">
         <v>0</v>
       </c>
       <c r="BE115" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ115" s="1">
         <v>0</v>
@@ -10813,7 +10924,7 @@
         <v>0</v>
       </c>
       <c r="DY115" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET115" s="1">
         <v>0</v>
@@ -10823,32 +10934,32 @@
       <c r="A116" s="1">
         <v>0</v>
       </c>
+      <c r="J116" s="4">
+        <v>0</v>
+      </c>
       <c r="K116" s="4">
         <v>0</v>
       </c>
       <c r="L116" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M116" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N116" s="4">
         <v>0</v>
       </c>
-      <c r="O116" s="4">
-        <v>0</v>
-      </c>
-      <c r="T116" s="1">
+      <c r="S116" s="1">
         <v>0</v>
       </c>
       <c r="AX116" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BE116" s="1">
         <v>0</v>
       </c>
       <c r="BZ116" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK116" s="3">
         <v>0</v>
@@ -10911,7 +11022,7 @@
         <v>0</v>
       </c>
       <c r="DS116" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY116" s="1">
         <v>0</v>
@@ -10924,6 +11035,9 @@
       <c r="A117" s="1">
         <v>0</v>
       </c>
+      <c r="J117" s="4">
+        <v>0</v>
+      </c>
       <c r="K117" s="4">
         <v>0</v>
       </c>
@@ -10936,11 +11050,8 @@
       <c r="N117" s="4">
         <v>0</v>
       </c>
-      <c r="O117" s="4">
-        <v>0</v>
-      </c>
-      <c r="T117" s="1">
-        <v>3</v>
+      <c r="S117" s="1">
+        <v>4</v>
       </c>
       <c r="AX117" s="1">
         <v>0</v>
@@ -11012,7 +11123,7 @@
         <v>0</v>
       </c>
       <c r="DS117" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY117" s="1">
         <v>0</v>
@@ -11025,6 +11136,9 @@
       <c r="A118" s="1">
         <v>0</v>
       </c>
+      <c r="J118" s="4">
+        <v>0</v>
+      </c>
       <c r="K118" s="4">
         <v>0</v>
       </c>
@@ -11037,17 +11151,14 @@
       <c r="N118" s="4">
         <v>0</v>
       </c>
-      <c r="O118" s="4">
-        <v>0</v>
-      </c>
-      <c r="T118" s="1">
+      <c r="S118" s="1">
         <v>0</v>
       </c>
       <c r="AX118" s="1">
         <v>0</v>
       </c>
       <c r="BE118" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ118" s="1">
         <v>0</v>
@@ -11116,7 +11227,7 @@
         <v>0</v>
       </c>
       <c r="DY118" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET118" s="1">
         <v>0</v>
@@ -11126,6 +11237,9 @@
       <c r="A119" s="1">
         <v>0</v>
       </c>
+      <c r="F119" s="4">
+        <v>0</v>
+      </c>
       <c r="G119" s="4">
         <v>0</v>
       </c>
@@ -11138,10 +11252,7 @@
       <c r="J119" s="4">
         <v>0</v>
       </c>
-      <c r="K119" s="4">
-        <v>0</v>
-      </c>
-      <c r="T119" s="5">
+      <c r="S119" s="5">
         <v>0</v>
       </c>
       <c r="Y119" s="3">
@@ -11205,13 +11316,13 @@
         <v>0</v>
       </c>
       <c r="AX119" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BE119" s="1">
         <v>0</v>
       </c>
       <c r="BZ119" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CJ119" s="1">
         <v>0</v>
@@ -11277,7 +11388,7 @@
         <v>0</v>
       </c>
       <c r="DS119" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY119" s="1">
         <v>0</v>
@@ -11290,6 +11401,9 @@
       <c r="A120" s="1">
         <v>0</v>
       </c>
+      <c r="F120" s="4">
+        <v>0</v>
+      </c>
       <c r="G120" s="4">
         <v>0</v>
       </c>
@@ -11302,10 +11416,7 @@
       <c r="J120" s="4">
         <v>0</v>
       </c>
-      <c r="K120" s="4">
-        <v>0</v>
-      </c>
-      <c r="T120" s="5">
+      <c r="S120" s="5">
         <v>7</v>
       </c>
       <c r="Y120" s="3">
@@ -11447,9 +11558,24 @@
         <v>0</v>
       </c>
       <c r="DS120" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY120" s="1">
+        <v>0</v>
+      </c>
+      <c r="ED120" s="4">
+        <v>0</v>
+      </c>
+      <c r="EE120" s="4">
+        <v>0</v>
+      </c>
+      <c r="EF120" s="4">
+        <v>0</v>
+      </c>
+      <c r="EG120" s="4">
+        <v>0</v>
+      </c>
+      <c r="EH120" s="4">
         <v>0</v>
       </c>
       <c r="ET120" s="1">
@@ -11460,22 +11586,22 @@
       <c r="A121" s="1">
         <v>0</v>
       </c>
+      <c r="F121" s="4">
+        <v>0</v>
+      </c>
       <c r="G121" s="4">
         <v>0</v>
       </c>
       <c r="H121" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I121" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J121" s="4">
         <v>0</v>
       </c>
-      <c r="K121" s="4">
-        <v>0</v>
-      </c>
-      <c r="T121" s="5">
+      <c r="S121" s="5">
         <v>0</v>
       </c>
       <c r="Y121" s="3">
@@ -11617,7 +11743,22 @@
         <v>0</v>
       </c>
       <c r="DY121" s="1">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="ED121" s="4">
+        <v>0</v>
+      </c>
+      <c r="EE121" s="4">
+        <v>0</v>
+      </c>
+      <c r="EF121" s="4">
+        <v>0</v>
+      </c>
+      <c r="EG121" s="4">
+        <v>0</v>
+      </c>
+      <c r="EH121" s="4">
+        <v>0</v>
       </c>
       <c r="ET121" s="1">
         <v>0</v>
@@ -11627,6 +11768,9 @@
       <c r="A122" s="1">
         <v>0</v>
       </c>
+      <c r="F122" s="4">
+        <v>0</v>
+      </c>
       <c r="G122" s="4">
         <v>0</v>
       </c>
@@ -11639,10 +11783,7 @@
       <c r="J122" s="4">
         <v>0</v>
       </c>
-      <c r="K122" s="4">
-        <v>0</v>
-      </c>
-      <c r="T122" s="5">
+      <c r="S122" s="5">
         <v>0</v>
       </c>
       <c r="Y122" s="3">
@@ -11706,7 +11847,7 @@
         <v>0</v>
       </c>
       <c r="AX122" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC122" s="1">
         <v>5</v>
@@ -11715,7 +11856,7 @@
         <v>6</v>
       </c>
       <c r="BZ122" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CG122" s="1">
         <v>0</v>
@@ -11781,9 +11922,24 @@
         <v>0</v>
       </c>
       <c r="DS122" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY122" s="1">
+        <v>0</v>
+      </c>
+      <c r="ED122" s="4">
+        <v>0</v>
+      </c>
+      <c r="EE122" s="4">
+        <v>0</v>
+      </c>
+      <c r="EF122" s="4">
+        <v>11</v>
+      </c>
+      <c r="EG122" s="4">
+        <v>0</v>
+      </c>
+      <c r="EH122" s="4">
         <v>0</v>
       </c>
       <c r="ET122" s="1">
@@ -11794,6 +11950,9 @@
       <c r="A123" s="1">
         <v>0</v>
       </c>
+      <c r="F123" s="4">
+        <v>0</v>
+      </c>
       <c r="G123" s="4">
         <v>0</v>
       </c>
@@ -11806,10 +11965,7 @@
       <c r="J123" s="4">
         <v>0</v>
       </c>
-      <c r="K123" s="4">
-        <v>0</v>
-      </c>
-      <c r="T123" s="5">
+      <c r="S123" s="5">
         <v>7</v>
       </c>
       <c r="Y123" s="3">
@@ -11948,9 +12104,24 @@
         <v>0</v>
       </c>
       <c r="DS123" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY123" s="1">
+        <v>0</v>
+      </c>
+      <c r="ED123" s="4">
+        <v>0</v>
+      </c>
+      <c r="EE123" s="4">
+        <v>0</v>
+      </c>
+      <c r="EF123" s="4">
+        <v>0</v>
+      </c>
+      <c r="EG123" s="4">
+        <v>0</v>
+      </c>
+      <c r="EH123" s="4">
         <v>0</v>
       </c>
       <c r="ET123" s="1">
@@ -11961,10 +12132,10 @@
       <c r="A124" s="1">
         <v>0</v>
       </c>
-      <c r="J124" s="1">
-        <v>0</v>
-      </c>
-      <c r="T124" s="5">
+      <c r="I124" s="1">
+        <v>0</v>
+      </c>
+      <c r="S124" s="5">
         <v>0</v>
       </c>
       <c r="Y124" s="3">
@@ -12133,7 +12304,22 @@
         <v>0</v>
       </c>
       <c r="DY124" s="1">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="ED124" s="4">
+        <v>0</v>
+      </c>
+      <c r="EE124" s="4">
+        <v>0</v>
+      </c>
+      <c r="EF124" s="4">
+        <v>0</v>
+      </c>
+      <c r="EG124" s="4">
+        <v>0</v>
+      </c>
+      <c r="EH124" s="4">
+        <v>0</v>
       </c>
       <c r="ET124" s="1">
         <v>0</v>
@@ -12143,10 +12329,10 @@
       <c r="A125" s="1">
         <v>0</v>
       </c>
-      <c r="K125" s="1">
+      <c r="J125" s="1">
         <v>6</v>
       </c>
-      <c r="T125" s="1">
+      <c r="S125" s="1">
         <v>0</v>
       </c>
       <c r="Y125" s="3">
@@ -12210,7 +12396,7 @@
         <v>0</v>
       </c>
       <c r="AX125" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ125" s="1">
         <v>5</v>
@@ -12219,7 +12405,7 @@
         <v>6</v>
       </c>
       <c r="BZ125" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK125" s="3">
         <v>0</v>
@@ -12282,7 +12468,7 @@
         <v>0</v>
       </c>
       <c r="DS125" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY125" s="1">
         <v>0</v>
@@ -12295,11 +12481,11 @@
       <c r="A126" s="1">
         <v>0</v>
       </c>
-      <c r="L126" s="1">
-        <v>0</v>
-      </c>
-      <c r="T126" s="1">
-        <v>3</v>
+      <c r="K126" s="1">
+        <v>0</v>
+      </c>
+      <c r="S126" s="1">
+        <v>4</v>
       </c>
       <c r="Y126" s="3">
         <v>0</v>
@@ -12452,7 +12638,7 @@
         <v>0</v>
       </c>
       <c r="DS126" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY126" s="1">
         <v>0</v>
@@ -12465,10 +12651,10 @@
       <c r="A127" s="1">
         <v>0</v>
       </c>
-      <c r="M127" s="1">
-        <v>0</v>
-      </c>
-      <c r="T127" s="1">
+      <c r="L127" s="1">
+        <v>0</v>
+      </c>
+      <c r="S127" s="1">
         <v>0</v>
       </c>
       <c r="Y127" s="3">
@@ -12613,7 +12799,7 @@
         <v>0</v>
       </c>
       <c r="DY127" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET127" s="1">
         <v>0</v>
@@ -12623,9 +12809,12 @@
       <c r="A128" s="1">
         <v>0</v>
       </c>
-      <c r="N128" s="1">
+      <c r="M128" s="1">
         <v>6</v>
       </c>
+      <c r="O128" s="4">
+        <v>0</v>
+      </c>
       <c r="P128" s="4">
         <v>0</v>
       </c>
@@ -12636,9 +12825,6 @@
         <v>0</v>
       </c>
       <c r="S128" s="4">
-        <v>0</v>
-      </c>
-      <c r="T128" s="4">
         <v>0</v>
       </c>
       <c r="Y128" s="3">
@@ -12717,7 +12903,7 @@
         <v>0</v>
       </c>
       <c r="BZ128" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK128" s="3">
         <v>0</v>
@@ -12780,7 +12966,7 @@
         <v>0</v>
       </c>
       <c r="DS128" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY128" s="1">
         <v>0</v>
@@ -12793,7 +12979,10 @@
       <c r="A129" s="1">
         <v>0</v>
       </c>
-      <c r="O129" s="1">
+      <c r="N129" s="1">
+        <v>0</v>
+      </c>
+      <c r="O129" s="4">
         <v>0</v>
       </c>
       <c r="P129" s="4">
@@ -12806,9 +12995,6 @@
         <v>0</v>
       </c>
       <c r="S129" s="4">
-        <v>0</v>
-      </c>
-      <c r="T129" s="4">
         <v>0</v>
       </c>
       <c r="Y129" s="3">
@@ -12950,7 +13136,7 @@
         <v>0</v>
       </c>
       <c r="DS129" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY129" s="1">
         <v>0</v>
@@ -12963,21 +13149,21 @@
       <c r="A130" s="1">
         <v>0</v>
       </c>
+      <c r="O130" s="4">
+        <v>0</v>
+      </c>
       <c r="P130" s="4">
         <v>0</v>
       </c>
       <c r="Q130" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R130" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S130" s="4">
         <v>0</v>
       </c>
-      <c r="T130" s="4">
-        <v>0</v>
-      </c>
       <c r="Y130" s="3">
         <v>0</v>
       </c>
@@ -13120,7 +13306,7 @@
         <v>0</v>
       </c>
       <c r="DY130" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET130" s="1">
         <v>0</v>
@@ -13130,6 +13316,9 @@
       <c r="A131" s="1">
         <v>0</v>
       </c>
+      <c r="O131" s="4">
+        <v>0</v>
+      </c>
       <c r="P131" s="4">
         <v>0</v>
       </c>
@@ -13142,9 +13331,6 @@
       <c r="S131" s="4">
         <v>0</v>
       </c>
-      <c r="T131" s="4">
-        <v>0</v>
-      </c>
       <c r="Y131" s="3">
         <v>0</v>
       </c>
@@ -13221,7 +13407,7 @@
         <v>0</v>
       </c>
       <c r="BZ131" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK131" s="3">
         <v>0</v>
@@ -13284,7 +13470,7 @@
         <v>0</v>
       </c>
       <c r="DS131" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY131" s="1">
         <v>0</v>
@@ -13297,6 +13483,9 @@
       <c r="A132" s="1">
         <v>0</v>
       </c>
+      <c r="O132" s="4">
+        <v>0</v>
+      </c>
       <c r="P132" s="4">
         <v>0</v>
       </c>
@@ -13309,9 +13498,6 @@
       <c r="S132" s="4">
         <v>0</v>
       </c>
-      <c r="T132" s="4">
-        <v>0</v>
-      </c>
       <c r="Y132" s="3">
         <v>0</v>
       </c>
@@ -13439,7 +13625,7 @@
         <v>0</v>
       </c>
       <c r="DS132" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY132" s="1">
         <v>0</v>
@@ -13513,7 +13699,7 @@
         <v>0</v>
       </c>
       <c r="AX133" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY133" s="1">
         <v>0</v>
@@ -13606,7 +13792,7 @@
         <v>0</v>
       </c>
       <c r="DY133" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET133" s="1">
         <v>0</v>
@@ -13686,7 +13872,7 @@
         <v>5</v>
       </c>
       <c r="BZ134" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CE134" s="1">
         <v>0</v>
@@ -13752,7 +13938,7 @@
         <v>0</v>
       </c>
       <c r="DS134" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY134" s="1">
         <v>0</v>
@@ -13844,7 +14030,7 @@
         <v>0</v>
       </c>
       <c r="DS135" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY135" s="1">
         <v>0</v>
@@ -13918,7 +14104,7 @@
         <v>0</v>
       </c>
       <c r="AX136" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB136" s="1">
         <v>0</v>
@@ -13939,7 +14125,7 @@
         <v>0</v>
       </c>
       <c r="DY136" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET136" s="1">
         <v>0</v>
@@ -14019,7 +14205,7 @@
         <v>5</v>
       </c>
       <c r="BZ137" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CB137" s="1">
         <v>0</v>
@@ -14028,7 +14214,7 @@
         <v>0</v>
       </c>
       <c r="DS137" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY137" s="1">
         <v>0</v>
@@ -14120,7 +14306,7 @@
         <v>0</v>
       </c>
       <c r="DS138" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY138" s="1">
         <v>0</v>
@@ -14134,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="AX139" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BE139" s="1">
         <v>0</v>
@@ -14155,7 +14341,7 @@
         <v>0</v>
       </c>
       <c r="DY139" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET139" s="1">
         <v>0</v>
@@ -14223,7 +14409,7 @@
         <v>0</v>
       </c>
       <c r="DS140" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DY140" s="1">
         <v>0</v>
@@ -14258,7 +14444,7 @@
         <v>0</v>
       </c>
       <c r="DS141" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY141" s="1">
         <v>0</v>
@@ -14272,7 +14458,7 @@
         <v>0</v>
       </c>
       <c r="AX142" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK142" s="1">
         <v>5</v>
@@ -14346,8 +14532,11 @@
       <c r="DR142" s="1">
         <v>0</v>
       </c>
+      <c r="DS142" s="1">
+        <v>0</v>
+      </c>
       <c r="DY142" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET142" s="1">
         <v>0</v>
@@ -14422,13 +14611,13 @@
         <v>0</v>
       </c>
       <c r="AX145" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CH145" s="1">
         <v>5</v>
       </c>
       <c r="DY145" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="ET145" s="1">
         <v>0</v>
@@ -14473,13 +14662,13 @@
         <v>0</v>
       </c>
       <c r="AX148" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CE148" s="1">
         <v>5</v>
       </c>
       <c r="DY148" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="EQ148" s="1">
         <v>0</v>

--- a/media/Levels/Level_5.xlsx
+++ b/media/Levels/Level_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E19118-B94E-462C-AEDE-683B238226BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7EB12EC-BA92-4CCF-8AD8-D2257AEE576D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3672" yWindow="84" windowWidth="13836" windowHeight="12156" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -920,13 +920,10 @@
       <c r="BN2" s="1">
         <v>0</v>
       </c>
-      <c r="DC2" s="1">
+      <c r="CY2" s="1">
         <v>0</v>
       </c>
       <c r="DO2" s="1">
-        <v>0</v>
-      </c>
-      <c r="DS2" s="1">
         <v>0</v>
       </c>
       <c r="EP2" s="1">
@@ -943,14 +940,11 @@
       <c r="BN3" s="1">
         <v>4</v>
       </c>
-      <c r="DC3" s="1">
-        <v>3</v>
+      <c r="CY3" s="1">
+        <v>4</v>
       </c>
       <c r="DO3" s="1">
         <v>4</v>
-      </c>
-      <c r="DS3" s="1">
-        <v>3</v>
       </c>
       <c r="EQ3" s="1">
         <v>0</v>
@@ -966,13 +960,10 @@
       <c r="BN4" s="1">
         <v>0</v>
       </c>
-      <c r="DC4" s="1">
+      <c r="CY4" s="1">
         <v>0</v>
       </c>
       <c r="DO4" s="1">
-        <v>0</v>
-      </c>
-      <c r="DS4" s="1">
         <v>0</v>
       </c>
       <c r="ER4" s="1">
@@ -989,13 +980,10 @@
       <c r="BN5" s="1">
         <v>0</v>
       </c>
-      <c r="DC5" s="1">
+      <c r="CY5" s="1">
         <v>0</v>
       </c>
       <c r="DO5" s="1">
-        <v>0</v>
-      </c>
-      <c r="DS5" s="1">
         <v>0</v>
       </c>
       <c r="ES5" s="1">
@@ -1012,14 +1000,11 @@
       <c r="BN6" s="1">
         <v>4</v>
       </c>
-      <c r="DC6" s="1">
-        <v>3</v>
+      <c r="CY6" s="1">
+        <v>4</v>
       </c>
       <c r="DO6" s="1">
         <v>4</v>
-      </c>
-      <c r="DS6" s="1">
-        <v>3</v>
       </c>
       <c r="ET6" s="1">
         <v>0</v>
@@ -1035,13 +1020,10 @@
       <c r="BN7" s="1">
         <v>0</v>
       </c>
-      <c r="DC7" s="1">
+      <c r="CY7" s="1">
         <v>0</v>
       </c>
       <c r="DO7" s="1">
-        <v>0</v>
-      </c>
-      <c r="DS7" s="1">
         <v>0</v>
       </c>
       <c r="DZ7" s="4">
@@ -1073,10 +1055,13 @@
       <c r="BN8" s="1">
         <v>0</v>
       </c>
-      <c r="DC8" s="1">
+      <c r="CY8" s="1">
         <v>0</v>
       </c>
       <c r="DO8" s="1">
+        <v>0</v>
+      </c>
+      <c r="DT8" s="1">
         <v>0</v>
       </c>
       <c r="DZ8" s="4">
@@ -1108,10 +1093,13 @@
       <c r="BN9" s="1">
         <v>4</v>
       </c>
-      <c r="DC9" s="1">
-        <v>3</v>
+      <c r="CY9" s="1">
+        <v>4</v>
       </c>
       <c r="DO9" s="1">
+        <v>4</v>
+      </c>
+      <c r="DT9" s="1">
         <v>4</v>
       </c>
       <c r="DZ9" s="4">
@@ -1143,10 +1131,13 @@
       <c r="BN10" s="1">
         <v>0</v>
       </c>
-      <c r="DC10" s="1">
+      <c r="CY10" s="1">
         <v>0</v>
       </c>
       <c r="DO10" s="1">
+        <v>0</v>
+      </c>
+      <c r="DT10" s="1">
         <v>0</v>
       </c>
       <c r="DZ10" s="4">
@@ -1178,13 +1169,13 @@
       <c r="BN11" s="1">
         <v>0</v>
       </c>
-      <c r="DC11" s="1">
+      <c r="CY11" s="1">
         <v>0</v>
       </c>
       <c r="DO11" s="1">
         <v>0</v>
       </c>
-      <c r="DS11" s="1">
+      <c r="DT11" s="1">
         <v>0</v>
       </c>
       <c r="DZ11" s="4">
@@ -1276,14 +1267,14 @@
       <c r="BN12" s="1">
         <v>4</v>
       </c>
-      <c r="DC12" s="1">
-        <v>3</v>
+      <c r="CY12" s="1">
+        <v>4</v>
       </c>
       <c r="DO12" s="1">
         <v>4</v>
       </c>
-      <c r="DS12" s="1">
-        <v>3</v>
+      <c r="DT12" s="1">
+        <v>4</v>
       </c>
       <c r="ET12" s="1">
         <v>0</v>
@@ -1293,21 +1284,6 @@
       <c r="A13" s="1">
         <v>0</v>
       </c>
-      <c r="Y13" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="4">
-        <v>0</v>
-      </c>
       <c r="AI13" s="1">
         <v>0</v>
       </c>
@@ -1374,13 +1350,13 @@
       <c r="BN13" s="1">
         <v>0</v>
       </c>
-      <c r="DC13" s="1">
+      <c r="CY13" s="1">
         <v>0</v>
       </c>
       <c r="DO13" s="1">
         <v>0</v>
       </c>
-      <c r="DS13" s="1">
+      <c r="DT13" s="1">
         <v>0</v>
       </c>
       <c r="ET13" s="1">
@@ -1391,21 +1367,6 @@
       <c r="A14" s="1">
         <v>0</v>
       </c>
-      <c r="Y14" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="4">
-        <v>0</v>
-      </c>
       <c r="AI14" s="1">
         <v>4</v>
       </c>
@@ -1535,7 +1496,7 @@
       <c r="DO14" s="1">
         <v>0</v>
       </c>
-      <c r="DS14" s="1">
+      <c r="DT14" s="1">
         <v>0</v>
       </c>
       <c r="ET14" s="1">
@@ -1546,6 +1507,12 @@
       <c r="A15" s="1">
         <v>0</v>
       </c>
+      <c r="W15" s="4">
+        <v>0</v>
+      </c>
+      <c r="X15" s="4">
+        <v>0</v>
+      </c>
       <c r="Y15" s="4">
         <v>0</v>
       </c>
@@ -1553,12 +1520,6 @@
         <v>0</v>
       </c>
       <c r="AA15" s="4">
-        <v>11</v>
-      </c>
-      <c r="AB15" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="4">
         <v>0</v>
       </c>
       <c r="AI15" s="1">
@@ -1690,8 +1651,8 @@
       <c r="DO15" s="1">
         <v>4</v>
       </c>
-      <c r="DS15" s="1">
-        <v>3</v>
+      <c r="DT15" s="1">
+        <v>4</v>
       </c>
       <c r="ET15" s="1">
         <v>0</v>
@@ -1701,22 +1662,10 @@
       <c r="A16" s="1">
         <v>0</v>
       </c>
-      <c r="Q16" s="4">
-        <v>0</v>
-      </c>
-      <c r="R16" s="4">
-        <v>0</v>
-      </c>
-      <c r="S16" s="4">
-        <v>0</v>
-      </c>
-      <c r="T16" s="4">
-        <v>0</v>
-      </c>
-      <c r="U16" s="4">
-        <v>0</v>
-      </c>
-      <c r="X16" s="1">
+      <c r="W16" s="4">
+        <v>0</v>
+      </c>
+      <c r="X16" s="4">
         <v>0</v>
       </c>
       <c r="Y16" s="4">
@@ -1728,12 +1677,6 @@
       <c r="AA16" s="4">
         <v>0</v>
       </c>
-      <c r="AB16" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="4">
-        <v>0</v>
-      </c>
       <c r="AI16" s="1">
         <v>0</v>
       </c>
@@ -1863,7 +1806,7 @@
       <c r="DO16" s="1">
         <v>0</v>
       </c>
-      <c r="DS16" s="1">
+      <c r="DT16" s="1">
         <v>0</v>
       </c>
       <c r="ET16" s="1">
@@ -1874,26 +1817,14 @@
       <c r="A17" s="1">
         <v>0</v>
       </c>
-      <c r="Q17" s="4">
-        <v>0</v>
-      </c>
-      <c r="R17" s="4">
-        <v>0</v>
-      </c>
-      <c r="S17" s="4">
-        <v>0</v>
-      </c>
-      <c r="T17" s="4">
-        <v>0</v>
-      </c>
-      <c r="U17" s="4">
-        <v>0</v>
-      </c>
-      <c r="W17" s="1">
-        <v>5</v>
+      <c r="W17" s="4">
+        <v>0</v>
+      </c>
+      <c r="X17" s="4">
+        <v>0</v>
       </c>
       <c r="Y17" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z17" s="4">
         <v>0</v>
@@ -1901,12 +1832,6 @@
       <c r="AA17" s="4">
         <v>0</v>
       </c>
-      <c r="AB17" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="4">
-        <v>0</v>
-      </c>
       <c r="AI17" s="1">
         <v>4</v>
       </c>
@@ -1970,12 +1895,6 @@
       <c r="BI17" s="3">
         <v>0</v>
       </c>
-      <c r="BR17" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS17" s="4">
-        <v>0</v>
-      </c>
       <c r="BT17" s="4">
         <v>0</v>
       </c>
@@ -1985,6 +1904,12 @@
       <c r="BV17" s="4">
         <v>0</v>
       </c>
+      <c r="BW17" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX17" s="4">
+        <v>0</v>
+      </c>
       <c r="CO17" s="3">
         <v>0</v>
       </c>
@@ -2048,7 +1973,7 @@
       <c r="DO17" s="1">
         <v>0</v>
       </c>
-      <c r="DS17" s="1">
+      <c r="DT17" s="1">
         <v>0</v>
       </c>
       <c r="ET17" s="1">
@@ -2059,25 +1984,46 @@
       <c r="A18" s="1">
         <v>0</v>
       </c>
-      <c r="Q18" s="4">
-        <v>0</v>
-      </c>
-      <c r="R18" s="4">
-        <v>0</v>
-      </c>
-      <c r="S18" s="4">
-        <v>11</v>
-      </c>
-      <c r="T18" s="4">
-        <v>0</v>
-      </c>
-      <c r="U18" s="4">
-        <v>0</v>
+      <c r="I18" s="4">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4">
+        <v>0</v>
+      </c>
+      <c r="M18" s="4">
+        <v>0</v>
+      </c>
+      <c r="S18" s="1">
+        <v>0</v>
+      </c>
+      <c r="T18" s="1">
+        <v>0</v>
+      </c>
+      <c r="U18" s="1">
+        <v>3</v>
       </c>
       <c r="V18" s="1">
         <v>0</v>
       </c>
-      <c r="AC18" s="1">
+      <c r="W18" s="4">
+        <v>0</v>
+      </c>
+      <c r="X18" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="4">
         <v>0</v>
       </c>
       <c r="AI18" s="1">
@@ -2143,12 +2089,6 @@
       <c r="BI18" s="3">
         <v>0</v>
       </c>
-      <c r="BR18" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS18" s="4">
-        <v>0</v>
-      </c>
       <c r="BT18" s="4">
         <v>0</v>
       </c>
@@ -2158,6 +2098,12 @@
       <c r="BV18" s="4">
         <v>0</v>
       </c>
+      <c r="BW18" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX18" s="4">
+        <v>0</v>
+      </c>
       <c r="CO18" s="3">
         <v>0</v>
       </c>
@@ -2221,8 +2167,8 @@
       <c r="DO18" s="1">
         <v>4</v>
       </c>
-      <c r="DS18" s="1">
-        <v>3</v>
+      <c r="DT18" s="1">
+        <v>4</v>
       </c>
       <c r="DX18" s="4">
         <v>0</v>
@@ -2247,23 +2193,38 @@
       <c r="A19" s="1">
         <v>0</v>
       </c>
-      <c r="Q19" s="4">
-        <v>0</v>
-      </c>
-      <c r="R19" s="4">
-        <v>0</v>
-      </c>
-      <c r="S19" s="4">
-        <v>0</v>
-      </c>
-      <c r="T19" s="4">
-        <v>0</v>
-      </c>
-      <c r="U19" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="1">
-        <v>4</v>
+      <c r="I19" s="4">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4">
+        <v>0</v>
+      </c>
+      <c r="M19" s="4">
+        <v>0</v>
+      </c>
+      <c r="R19" s="1">
+        <v>5</v>
+      </c>
+      <c r="W19" s="4">
+        <v>0</v>
+      </c>
+      <c r="X19" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="4">
+        <v>0</v>
       </c>
       <c r="AI19" s="1">
         <v>0</v>
@@ -2328,19 +2289,19 @@
       <c r="BI19" s="3">
         <v>0</v>
       </c>
-      <c r="BR19" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS19" s="4">
-        <v>0</v>
-      </c>
       <c r="BT19" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU19" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV19" s="4">
         <v>11</v>
       </c>
-      <c r="BU19" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV19" s="4">
+      <c r="BW19" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX19" s="4">
         <v>0</v>
       </c>
       <c r="CO19" s="3">
@@ -2406,7 +2367,7 @@
       <c r="DO19" s="1">
         <v>0</v>
       </c>
-      <c r="DS19" s="1">
+      <c r="DT19" s="1">
         <v>0</v>
       </c>
       <c r="DX19" s="4">
@@ -2432,22 +2393,34 @@
       <c r="A20" s="1">
         <v>0</v>
       </c>
-      <c r="Q20" s="4">
-        <v>0</v>
-      </c>
-      <c r="R20" s="4">
-        <v>0</v>
-      </c>
-      <c r="S20" s="4">
-        <v>0</v>
-      </c>
-      <c r="T20" s="4">
-        <v>0</v>
-      </c>
-      <c r="U20" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="1">
+      <c r="I20" s="4">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4">
+        <v>11</v>
+      </c>
+      <c r="L20" s="4">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1">
+        <v>3</v>
+      </c>
+      <c r="P20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="1">
         <v>0</v>
       </c>
       <c r="AI20" s="1">
@@ -2513,12 +2486,6 @@
       <c r="BI20" s="3">
         <v>0</v>
       </c>
-      <c r="BR20" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS20" s="4">
-        <v>0</v>
-      </c>
       <c r="BT20" s="4">
         <v>0</v>
       </c>
@@ -2528,6 +2495,12 @@
       <c r="BV20" s="4">
         <v>0</v>
       </c>
+      <c r="BW20" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX20" s="4">
+        <v>0</v>
+      </c>
       <c r="CO20" s="3">
         <v>0</v>
       </c>
@@ -2591,7 +2564,7 @@
       <c r="DO20" s="1">
         <v>0</v>
       </c>
-      <c r="DS20" s="1">
+      <c r="DT20" s="1">
         <v>0</v>
       </c>
       <c r="DX20" s="4">
@@ -2617,8 +2590,23 @@
       <c r="A21" s="1">
         <v>0</v>
       </c>
-      <c r="AC21" s="1">
-        <v>0</v>
+      <c r="I21" s="4">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4">
+        <v>0</v>
+      </c>
+      <c r="M21" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>4</v>
       </c>
       <c r="AI21" s="1">
         <v>0</v>
@@ -2683,12 +2671,6 @@
       <c r="BI21" s="3">
         <v>0</v>
       </c>
-      <c r="BR21" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS21" s="4">
-        <v>0</v>
-      </c>
       <c r="BT21" s="4">
         <v>0</v>
       </c>
@@ -2698,6 +2680,12 @@
       <c r="BV21" s="4">
         <v>0</v>
       </c>
+      <c r="BW21" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX21" s="4">
+        <v>0</v>
+      </c>
       <c r="CO21" s="3">
         <v>0</v>
       </c>
@@ -2761,8 +2749,8 @@
       <c r="DO21" s="1">
         <v>4</v>
       </c>
-      <c r="DS21" s="1">
-        <v>3</v>
+      <c r="DT21" s="1">
+        <v>4</v>
       </c>
       <c r="DX21" s="4">
         <v>0</v>
@@ -2802,8 +2790,23 @@
       <c r="A22" s="1">
         <v>0</v>
       </c>
-      <c r="AC22" s="1">
-        <v>4</v>
+      <c r="I22" s="4">
+        <v>0</v>
+      </c>
+      <c r="J22" s="4">
+        <v>0</v>
+      </c>
+      <c r="K22" s="4">
+        <v>0</v>
+      </c>
+      <c r="L22" s="4">
+        <v>0</v>
+      </c>
+      <c r="M22" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="1">
+        <v>0</v>
       </c>
       <c r="AI22" s="1">
         <v>0</v>
@@ -2931,7 +2934,7 @@
       <c r="DO22" s="1">
         <v>0</v>
       </c>
-      <c r="DS22" s="1">
+      <c r="DT22" s="1">
         <v>0</v>
       </c>
       <c r="DX22" s="4">
@@ -2972,7 +2975,7 @@
       <c r="A23" s="1">
         <v>0</v>
       </c>
-      <c r="AC23" s="1">
+      <c r="Y23" s="1">
         <v>0</v>
       </c>
       <c r="AI23" s="1">
@@ -3098,7 +3101,7 @@
       <c r="DH23" s="3">
         <v>0</v>
       </c>
-      <c r="DS23" s="1">
+      <c r="DT23" s="1">
         <v>0</v>
       </c>
       <c r="EG23" s="4">
@@ -3124,23 +3127,8 @@
       <c r="A24" s="1">
         <v>0</v>
       </c>
-      <c r="R24" s="4">
-        <v>0</v>
-      </c>
-      <c r="S24" s="4">
-        <v>0</v>
-      </c>
-      <c r="T24" s="4">
-        <v>0</v>
-      </c>
-      <c r="U24" s="4">
-        <v>0</v>
-      </c>
-      <c r="V24" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="1">
-        <v>0</v>
+      <c r="Y24" s="1">
+        <v>4</v>
       </c>
       <c r="AI24" s="1">
         <v>0</v>
@@ -3205,6 +3193,15 @@
       <c r="BI24" s="3">
         <v>0</v>
       </c>
+      <c r="CF24" s="1">
+        <v>0</v>
+      </c>
+      <c r="CG24" s="1">
+        <v>3</v>
+      </c>
+      <c r="CH24" s="1">
+        <v>0</v>
+      </c>
       <c r="CI24" s="1">
         <v>0</v>
       </c>
@@ -3283,8 +3280,8 @@
       <c r="DH24" s="3">
         <v>0</v>
       </c>
-      <c r="DS24" s="1">
-        <v>3</v>
+      <c r="DT24" s="1">
+        <v>4</v>
       </c>
       <c r="EG24" s="4">
         <v>0</v>
@@ -3309,23 +3306,8 @@
       <c r="A25" s="1">
         <v>0</v>
       </c>
-      <c r="R25" s="4">
-        <v>0</v>
-      </c>
-      <c r="S25" s="4">
-        <v>0</v>
-      </c>
-      <c r="T25" s="4">
-        <v>0</v>
-      </c>
-      <c r="U25" s="4">
-        <v>0</v>
-      </c>
-      <c r="V25" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="1">
-        <v>4</v>
+      <c r="Y25" s="1">
+        <v>0</v>
       </c>
       <c r="AI25" s="1">
         <v>0</v>
@@ -3450,7 +3432,7 @@
       <c r="DH25" s="3">
         <v>0</v>
       </c>
-      <c r="DS25" s="1">
+      <c r="DT25" s="1">
         <v>0</v>
       </c>
       <c r="EG25" s="4">
@@ -3476,22 +3458,34 @@
       <c r="A26" s="1">
         <v>0</v>
       </c>
-      <c r="R26" s="4">
-        <v>0</v>
-      </c>
-      <c r="S26" s="4">
-        <v>0</v>
-      </c>
-      <c r="T26" s="4">
-        <v>11</v>
-      </c>
-      <c r="U26" s="4">
-        <v>0</v>
-      </c>
-      <c r="V26" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="1">
+      <c r="I26" s="4">
+        <v>0</v>
+      </c>
+      <c r="J26" s="4">
+        <v>0</v>
+      </c>
+      <c r="K26" s="4">
+        <v>0</v>
+      </c>
+      <c r="L26" s="4">
+        <v>0</v>
+      </c>
+      <c r="M26" s="4">
+        <v>0</v>
+      </c>
+      <c r="W26" s="4">
+        <v>0</v>
+      </c>
+      <c r="X26" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="4">
         <v>0</v>
       </c>
       <c r="AI26" s="1">
@@ -3620,7 +3614,7 @@
       <c r="DH26" s="3">
         <v>0</v>
       </c>
-      <c r="DS26" s="1">
+      <c r="DT26" s="1">
         <v>0</v>
       </c>
       <c r="ET26" s="1">
@@ -3631,22 +3625,40 @@
       <c r="A27" s="1">
         <v>0</v>
       </c>
-      <c r="R27" s="4">
-        <v>0</v>
-      </c>
-      <c r="S27" s="4">
-        <v>0</v>
-      </c>
-      <c r="T27" s="4">
-        <v>0</v>
-      </c>
-      <c r="U27" s="4">
-        <v>0</v>
-      </c>
-      <c r="V27" s="4">
-        <v>0</v>
-      </c>
-      <c r="W27" s="1">
+      <c r="I27" s="4">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4">
+        <v>0</v>
+      </c>
+      <c r="K27" s="4">
+        <v>0</v>
+      </c>
+      <c r="L27" s="4">
+        <v>0</v>
+      </c>
+      <c r="M27" s="4">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1">
+        <v>3</v>
+      </c>
+      <c r="P27" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>0</v>
+      </c>
+      <c r="W27" s="4">
+        <v>0</v>
+      </c>
+      <c r="X27" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="4">
         <v>0</v>
       </c>
       <c r="Z27" s="4">
@@ -3655,15 +3667,6 @@
       <c r="AA27" s="4">
         <v>0</v>
       </c>
-      <c r="AB27" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="4">
-        <v>0</v>
-      </c>
       <c r="AI27" s="1">
         <v>0</v>
       </c>
@@ -3790,8 +3793,8 @@
       <c r="DH27" s="3">
         <v>0</v>
       </c>
-      <c r="DS27" s="1">
-        <v>3</v>
+      <c r="DT27" s="1">
+        <v>4</v>
       </c>
       <c r="ET27" s="1">
         <v>0</v>
@@ -3801,39 +3804,39 @@
       <c r="A28" s="1">
         <v>0</v>
       </c>
-      <c r="R28" s="4">
-        <v>0</v>
-      </c>
-      <c r="S28" s="4">
-        <v>0</v>
-      </c>
-      <c r="T28" s="4">
-        <v>0</v>
-      </c>
-      <c r="U28" s="4">
-        <v>0</v>
-      </c>
-      <c r="V28" s="4">
-        <v>0</v>
-      </c>
-      <c r="X28" s="1">
+      <c r="I28" s="4">
+        <v>0</v>
+      </c>
+      <c r="J28" s="4">
+        <v>0</v>
+      </c>
+      <c r="K28" s="4">
+        <v>11</v>
+      </c>
+      <c r="L28" s="4">
+        <v>0</v>
+      </c>
+      <c r="M28" s="4">
+        <v>0</v>
+      </c>
+      <c r="R28" s="1">
         <v>6</v>
       </c>
+      <c r="W28" s="4">
+        <v>0</v>
+      </c>
+      <c r="X28" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="4">
+        <v>11</v>
+      </c>
       <c r="Z28" s="4">
         <v>0</v>
       </c>
       <c r="AA28" s="4">
         <v>0</v>
       </c>
-      <c r="AB28" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC28" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD28" s="4">
-        <v>0</v>
-      </c>
       <c r="AI28" s="1">
         <v>0</v>
       </c>
@@ -3960,7 +3963,7 @@
       <c r="DH28" s="3">
         <v>0</v>
       </c>
-      <c r="DS28" s="1">
+      <c r="DT28" s="1">
         <v>0</v>
       </c>
       <c r="ET28" s="1">
@@ -3971,7 +3974,40 @@
       <c r="A29" s="1">
         <v>0</v>
       </c>
-      <c r="Y29" s="1">
+      <c r="I29" s="4">
+        <v>0</v>
+      </c>
+      <c r="J29" s="4">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4">
+        <v>0</v>
+      </c>
+      <c r="L29" s="4">
+        <v>0</v>
+      </c>
+      <c r="M29" s="4">
+        <v>0</v>
+      </c>
+      <c r="S29" s="1">
+        <v>0</v>
+      </c>
+      <c r="T29" s="1">
+        <v>0</v>
+      </c>
+      <c r="U29" s="1">
+        <v>3</v>
+      </c>
+      <c r="V29" s="1">
+        <v>0</v>
+      </c>
+      <c r="W29" s="4">
+        <v>0</v>
+      </c>
+      <c r="X29" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="4">
         <v>0</v>
       </c>
       <c r="Z29" s="4">
@@ -3980,15 +4016,6 @@
       <c r="AA29" s="4">
         <v>0</v>
       </c>
-      <c r="AB29" s="4">
-        <v>11</v>
-      </c>
-      <c r="AC29" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="4">
-        <v>0</v>
-      </c>
       <c r="AI29" s="1">
         <v>4</v>
       </c>
@@ -4118,7 +4145,7 @@
       <c r="DO29" s="1">
         <v>0</v>
       </c>
-      <c r="DS29" s="1">
+      <c r="DT29" s="1">
         <v>0</v>
       </c>
       <c r="ET29" s="1">
@@ -4129,21 +4156,36 @@
       <c r="A30" s="1">
         <v>0</v>
       </c>
+      <c r="I30" s="4">
+        <v>0</v>
+      </c>
+      <c r="J30" s="4">
+        <v>0</v>
+      </c>
+      <c r="K30" s="4">
+        <v>0</v>
+      </c>
+      <c r="L30" s="4">
+        <v>0</v>
+      </c>
+      <c r="M30" s="4">
+        <v>0</v>
+      </c>
+      <c r="W30" s="4">
+        <v>0</v>
+      </c>
+      <c r="X30" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="4">
+        <v>0</v>
+      </c>
       <c r="Z30" s="4">
         <v>0</v>
       </c>
       <c r="AA30" s="4">
         <v>0</v>
       </c>
-      <c r="AB30" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC30" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD30" s="4">
-        <v>0</v>
-      </c>
       <c r="AI30" s="1">
         <v>0</v>
       </c>
@@ -4219,6 +4261,12 @@
       <c r="BN30" s="1">
         <v>4</v>
       </c>
+      <c r="CD30" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE30" s="4">
+        <v>0</v>
+      </c>
       <c r="CF30" s="4">
         <v>0</v>
       </c>
@@ -4228,12 +4276,6 @@
       <c r="CH30" s="4">
         <v>0</v>
       </c>
-      <c r="CI30" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ30" s="4">
-        <v>0</v>
-      </c>
       <c r="CO30" s="3">
         <v>0</v>
       </c>
@@ -4297,8 +4339,8 @@
       <c r="DO30" s="1">
         <v>4</v>
       </c>
-      <c r="DS30" s="1">
-        <v>3</v>
+      <c r="DT30" s="1">
+        <v>4</v>
       </c>
       <c r="ET30" s="1">
         <v>0</v>
@@ -4308,21 +4350,6 @@
       <c r="A31" s="1">
         <v>0</v>
       </c>
-      <c r="Z31" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB31" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC31" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="4">
-        <v>0</v>
-      </c>
       <c r="AP31" s="3">
         <v>0</v>
       </c>
@@ -4386,6 +4413,12 @@
       <c r="BN31" s="1">
         <v>0</v>
       </c>
+      <c r="CD31" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE31" s="4">
+        <v>0</v>
+      </c>
       <c r="CF31" s="4">
         <v>0</v>
       </c>
@@ -4395,12 +4428,6 @@
       <c r="CH31" s="4">
         <v>0</v>
       </c>
-      <c r="CI31" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ31" s="4">
-        <v>0</v>
-      </c>
       <c r="CO31" s="3">
         <v>0</v>
       </c>
@@ -4464,7 +4491,7 @@
       <c r="DO31" s="1">
         <v>0</v>
       </c>
-      <c r="DS31" s="1">
+      <c r="DT31" s="1">
         <v>0</v>
       </c>
       <c r="ET31" s="1">
@@ -4481,19 +4508,19 @@
       <c r="BN32" s="1">
         <v>0</v>
       </c>
+      <c r="CD32" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE32" s="4">
+        <v>0</v>
+      </c>
       <c r="CF32" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CG32" s="4">
         <v>0</v>
       </c>
       <c r="CH32" s="4">
-        <v>11</v>
-      </c>
-      <c r="CI32" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ32" s="4">
         <v>0</v>
       </c>
       <c r="CO32" s="3">
@@ -4559,7 +4586,7 @@
       <c r="DO32" s="1">
         <v>0</v>
       </c>
-      <c r="DS32" s="1">
+      <c r="DT32" s="1">
         <v>0</v>
       </c>
       <c r="ET32" s="1">
@@ -4576,6 +4603,12 @@
       <c r="BN33" s="1">
         <v>4</v>
       </c>
+      <c r="CD33" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE33" s="4">
+        <v>0</v>
+      </c>
       <c r="CF33" s="4">
         <v>0</v>
       </c>
@@ -4585,12 +4618,6 @@
       <c r="CH33" s="4">
         <v>0</v>
       </c>
-      <c r="CI33" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ33" s="4">
-        <v>0</v>
-      </c>
       <c r="CO33" s="3">
         <v>0</v>
       </c>
@@ -4654,8 +4681,8 @@
       <c r="DO33" s="1">
         <v>4</v>
       </c>
-      <c r="DS33" s="1">
-        <v>3</v>
+      <c r="DT33" s="1">
+        <v>4</v>
       </c>
       <c r="DY33" s="4">
         <v>0</v>
@@ -4701,6 +4728,12 @@
       <c r="BN34" s="1">
         <v>0</v>
       </c>
+      <c r="CD34" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE34" s="4">
+        <v>0</v>
+      </c>
       <c r="CF34" s="4">
         <v>0</v>
       </c>
@@ -4710,16 +4743,10 @@
       <c r="CH34" s="4">
         <v>0</v>
       </c>
-      <c r="CI34" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ34" s="4">
-        <v>0</v>
-      </c>
       <c r="DO34" s="1">
         <v>0</v>
       </c>
-      <c r="DS34" s="1">
+      <c r="DT34" s="1">
         <v>0</v>
       </c>
       <c r="DY34" s="4">
@@ -4766,13 +4793,13 @@
       <c r="BN35" s="1">
         <v>0</v>
       </c>
-      <c r="CH35" s="1">
+      <c r="CF35" s="1">
         <v>0</v>
       </c>
       <c r="DO35" s="1">
         <v>0</v>
       </c>
-      <c r="DS35" s="1">
+      <c r="DT35" s="1">
         <v>0</v>
       </c>
       <c r="DY35" s="4">
@@ -4819,14 +4846,14 @@
       <c r="BN36" s="1">
         <v>4</v>
       </c>
-      <c r="CG36" s="1">
-        <v>5</v>
+      <c r="CF36" s="1">
+        <v>4</v>
       </c>
       <c r="DO36" s="1">
         <v>4</v>
       </c>
-      <c r="DS36" s="1">
-        <v>3</v>
+      <c r="DT36" s="1">
+        <v>4</v>
       </c>
       <c r="DY36" s="4">
         <v>0</v>
@@ -4878,7 +4905,7 @@
       <c r="DO37" s="1">
         <v>0</v>
       </c>
-      <c r="DS37" s="1">
+      <c r="DT37" s="1">
         <v>0</v>
       </c>
       <c r="DY37" s="4">
@@ -4931,7 +4958,7 @@
       <c r="DO38" s="1">
         <v>0</v>
       </c>
-      <c r="DS38" s="1">
+      <c r="DT38" s="1">
         <v>0</v>
       </c>
       <c r="ET38" s="1">
@@ -4954,8 +4981,8 @@
       <c r="DO39" s="1">
         <v>4</v>
       </c>
-      <c r="DS39" s="1">
-        <v>3</v>
+      <c r="DT39" s="1">
+        <v>4</v>
       </c>
       <c r="ET39" s="1">
         <v>0</v>
@@ -4977,7 +5004,7 @@
       <c r="DO40" s="1">
         <v>0</v>
       </c>
-      <c r="DS40" s="1">
+      <c r="DT40" s="1">
         <v>0</v>
       </c>
       <c r="ET40" s="1">
@@ -5000,7 +5027,7 @@
       <c r="DO41" s="1">
         <v>0</v>
       </c>
-      <c r="DS41" s="1">
+      <c r="DT41" s="1">
         <v>0</v>
       </c>
       <c r="ET41" s="1">
@@ -5023,8 +5050,8 @@
       <c r="DO42" s="1">
         <v>4</v>
       </c>
-      <c r="DS42" s="1">
-        <v>3</v>
+      <c r="DT42" s="1">
+        <v>4</v>
       </c>
       <c r="ET42" s="1">
         <v>0</v>
@@ -5046,7 +5073,7 @@
       <c r="DO43" s="1">
         <v>0</v>
       </c>
-      <c r="DS43" s="1">
+      <c r="DT43" s="1">
         <v>0</v>
       </c>
       <c r="ET43" s="1">
@@ -5300,22 +5327,22 @@
       <c r="DO44" s="1">
         <v>0</v>
       </c>
-      <c r="DS44" s="1">
-        <v>0</v>
-      </c>
       <c r="DT44" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DU44" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DV44" s="1">
         <v>0</v>
       </c>
       <c r="DW44" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DX44" s="1">
+        <v>3</v>
+      </c>
+      <c r="DY44" s="1">
         <v>0</v>
       </c>
       <c r="ET44" s="1">
@@ -6817,7 +6844,7 @@
       <c r="AR60" s="4">
         <v>0</v>
       </c>
-      <c r="BK60" s="1">
+      <c r="BJ60" s="1">
         <v>0</v>
       </c>
       <c r="DM60" s="1">
@@ -6915,7 +6942,7 @@
       <c r="AR61" s="4">
         <v>0</v>
       </c>
-      <c r="BK61" s="1">
+      <c r="BJ61" s="1">
         <v>4</v>
       </c>
       <c r="DM61" s="1">
@@ -6998,7 +7025,7 @@
       <c r="AG62" s="1">
         <v>0</v>
       </c>
-      <c r="BK62" s="1">
+      <c r="BJ62" s="1">
         <v>0</v>
       </c>
       <c r="DM62" s="1">
@@ -7081,7 +7108,7 @@
       <c r="AG63" s="1">
         <v>0</v>
       </c>
-      <c r="BK63" s="1">
+      <c r="BJ63" s="1">
         <v>0</v>
       </c>
       <c r="DM63" s="1">
@@ -7164,7 +7191,7 @@
       <c r="AG64" s="1">
         <v>4</v>
       </c>
-      <c r="BK64" s="1">
+      <c r="BJ64" s="1">
         <v>4</v>
       </c>
       <c r="DM64" s="1">
@@ -7247,7 +7274,7 @@
       <c r="AG65" s="1">
         <v>0</v>
       </c>
-      <c r="BK65" s="1">
+      <c r="BJ65" s="1">
         <v>0</v>
       </c>
       <c r="DM65" s="1">
@@ -7330,7 +7357,7 @@
       <c r="AG66" s="1">
         <v>0</v>
       </c>
-      <c r="BK66" s="1">
+      <c r="BJ66" s="1">
         <v>0</v>
       </c>
       <c r="BP66" s="3">
@@ -7416,7 +7443,7 @@
       <c r="AG67" s="1">
         <v>4</v>
       </c>
-      <c r="BK67" s="1">
+      <c r="BJ67" s="1">
         <v>4</v>
       </c>
       <c r="BP67" s="3">
@@ -7502,7 +7529,7 @@
       <c r="AG68" s="1">
         <v>0</v>
       </c>
-      <c r="BK68" s="1">
+      <c r="BJ68" s="1">
         <v>0</v>
       </c>
       <c r="BP68" s="3">
@@ -7603,7 +7630,7 @@
       <c r="AG69" s="1">
         <v>0</v>
       </c>
-      <c r="BK69" s="1">
+      <c r="BJ69" s="1">
         <v>0</v>
       </c>
       <c r="BP69" s="3">
@@ -7704,7 +7731,7 @@
       <c r="AG70" s="1">
         <v>4</v>
       </c>
-      <c r="BK70" s="1">
+      <c r="BJ70" s="1">
         <v>4</v>
       </c>
       <c r="BP70" s="3">
@@ -7805,7 +7832,7 @@
       <c r="AG71" s="1">
         <v>0</v>
       </c>
-      <c r="BK71" s="1">
+      <c r="BJ71" s="1">
         <v>0</v>
       </c>
       <c r="BP71" s="3">
@@ -9037,7 +9064,7 @@
       <c r="AG81" s="1">
         <v>0</v>
       </c>
-      <c r="BK81" s="1">
+      <c r="BJ81" s="1">
         <v>0</v>
       </c>
       <c r="BP81" s="3">
@@ -9098,6 +9125,9 @@
         <v>0</v>
       </c>
       <c r="CI81" s="3">
+        <v>0</v>
+      </c>
+      <c r="CJ81" s="1">
         <v>0</v>
       </c>
       <c r="DM81" s="1">
@@ -9120,7 +9150,7 @@
       <c r="AG82" s="1">
         <v>4</v>
       </c>
-      <c r="BK82" s="1">
+      <c r="BJ82" s="1">
         <v>4</v>
       </c>
       <c r="BP82" s="3">
@@ -9182,6 +9212,9 @@
       </c>
       <c r="CI82" s="3">
         <v>0</v>
+      </c>
+      <c r="CJ82" s="1">
+        <v>4</v>
       </c>
       <c r="DM82" s="1">
         <v>4</v>
@@ -9203,7 +9236,7 @@
       <c r="AG83" s="1">
         <v>0</v>
       </c>
-      <c r="BK83" s="1">
+      <c r="BJ83" s="1">
         <v>0</v>
       </c>
       <c r="BP83" s="3">
@@ -9264,6 +9297,9 @@
         <v>0</v>
       </c>
       <c r="CI83" s="3">
+        <v>0</v>
+      </c>
+      <c r="CJ83" s="1">
         <v>0</v>
       </c>
       <c r="DM83" s="1">
@@ -9286,7 +9322,7 @@
       <c r="AG84" s="1">
         <v>0</v>
       </c>
-      <c r="BK84" s="1">
+      <c r="BJ84" s="1">
         <v>0</v>
       </c>
       <c r="BP84" s="3">
@@ -9372,7 +9408,7 @@
       <c r="AG85" s="1">
         <v>4</v>
       </c>
-      <c r="BK85" s="1">
+      <c r="BJ85" s="1">
         <v>4</v>
       </c>
       <c r="BP85" s="3">
@@ -9436,7 +9472,7 @@
         <v>0</v>
       </c>
       <c r="CJ85" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DM85" s="1">
         <v>4</v>
@@ -9458,7 +9494,7 @@
       <c r="AG86" s="1">
         <v>0</v>
       </c>
-      <c r="BK86" s="1">
+      <c r="BJ86" s="1">
         <v>0</v>
       </c>
       <c r="CJ86" s="1">
@@ -9511,7 +9547,7 @@
         <v>4</v>
       </c>
       <c r="CJ88" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DM88" s="1">
         <v>4</v>
@@ -9580,7 +9616,7 @@
         <v>4</v>
       </c>
       <c r="CJ91" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DM91" s="1">
         <v>4</v>
@@ -9602,9 +9638,6 @@
       <c r="AG92" s="1">
         <v>0</v>
       </c>
-      <c r="BK92" s="1">
-        <v>0</v>
-      </c>
       <c r="CJ92" s="1">
         <v>0</v>
       </c>
@@ -9628,25 +9661,31 @@
       <c r="AG93" s="1">
         <v>0</v>
       </c>
+      <c r="BJ93" s="1">
+        <v>0</v>
+      </c>
       <c r="BK93" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL93" s="1">
         <v>0</v>
       </c>
       <c r="BM93" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BN93" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BO93" s="1">
         <v>0</v>
       </c>
       <c r="BP93" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BQ93" s="1">
+        <v>3</v>
+      </c>
+      <c r="BR93" s="1">
         <v>0</v>
       </c>
       <c r="CH93" s="1">
@@ -9765,7 +9804,7 @@
       <c r="AG94" s="1">
         <v>4</v>
       </c>
-      <c r="BK94" s="1">
+      <c r="BJ94" s="1">
         <v>0</v>
       </c>
       <c r="BR94" s="1">
@@ -9791,14 +9830,14 @@
       <c r="AG95" s="1">
         <v>0</v>
       </c>
-      <c r="BK95" s="1">
-        <v>0</v>
+      <c r="BJ95" s="1">
+        <v>4</v>
       </c>
       <c r="BR95" s="1">
         <v>4</v>
       </c>
       <c r="CH95" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DJ95" t="s">
         <v>0</v>
@@ -9820,8 +9859,8 @@
       <c r="AG96" s="1">
         <v>0</v>
       </c>
-      <c r="BK96" s="1">
-        <v>4</v>
+      <c r="BJ96" s="1">
+        <v>0</v>
       </c>
       <c r="BR96" s="1">
         <v>0</v>
@@ -9846,7 +9885,7 @@
       <c r="AG97" s="1">
         <v>4</v>
       </c>
-      <c r="BK97" s="1">
+      <c r="BJ97" s="1">
         <v>0</v>
       </c>
       <c r="BP97" s="4">
@@ -9911,8 +9950,8 @@
       <c r="AG98" s="1">
         <v>0</v>
       </c>
-      <c r="BK98" s="1">
-        <v>0</v>
+      <c r="BJ98" s="1">
+        <v>4</v>
       </c>
       <c r="BP98" s="4">
         <v>0</v>
@@ -9976,8 +10015,8 @@
       <c r="AG99" s="1">
         <v>0</v>
       </c>
-      <c r="BK99" s="1">
-        <v>4</v>
+      <c r="BJ99" s="1">
+        <v>0</v>
       </c>
       <c r="BP99" s="4">
         <v>0</v>
@@ -10041,9 +10080,6 @@
       <c r="AG100" s="1">
         <v>4</v>
       </c>
-      <c r="BK100" s="1">
-        <v>0</v>
-      </c>
       <c r="BP100" s="4">
         <v>0</v>
       </c>
@@ -10195,7 +10231,7 @@
         <v>4</v>
       </c>
       <c r="CH103" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DS103" s="1">
         <v>0</v>
@@ -10949,7 +10985,7 @@
       <c r="N116" s="4">
         <v>0</v>
       </c>
-      <c r="S116" s="1">
+      <c r="Q116" s="1">
         <v>0</v>
       </c>
       <c r="AX116" s="1">
@@ -11050,7 +11086,7 @@
       <c r="N117" s="4">
         <v>0</v>
       </c>
-      <c r="S117" s="1">
+      <c r="Q117" s="1">
         <v>4</v>
       </c>
       <c r="AX117" s="1">
@@ -11151,7 +11187,7 @@
       <c r="N118" s="4">
         <v>0</v>
       </c>
-      <c r="S118" s="1">
+      <c r="Q118" s="1">
         <v>0</v>
       </c>
       <c r="AX118" s="1">
@@ -11252,7 +11288,7 @@
       <c r="J119" s="4">
         <v>0</v>
       </c>
-      <c r="S119" s="5">
+      <c r="Q119" s="1">
         <v>0</v>
       </c>
       <c r="Y119" s="3">
@@ -11416,8 +11452,8 @@
       <c r="J120" s="4">
         <v>0</v>
       </c>
-      <c r="S120" s="5">
-        <v>7</v>
+      <c r="Q120" s="1">
+        <v>4</v>
       </c>
       <c r="Y120" s="3">
         <v>0</v>
@@ -11561,21 +11597,6 @@
         <v>4</v>
       </c>
       <c r="DY120" s="1">
-        <v>0</v>
-      </c>
-      <c r="ED120" s="4">
-        <v>0</v>
-      </c>
-      <c r="EE120" s="4">
-        <v>0</v>
-      </c>
-      <c r="EF120" s="4">
-        <v>0</v>
-      </c>
-      <c r="EG120" s="4">
-        <v>0</v>
-      </c>
-      <c r="EH120" s="4">
         <v>0</v>
       </c>
       <c r="ET120" s="1">
@@ -11601,7 +11622,7 @@
       <c r="J121" s="4">
         <v>0</v>
       </c>
-      <c r="S121" s="5">
+      <c r="Q121" s="1">
         <v>0</v>
       </c>
       <c r="Y121" s="3">
@@ -11744,21 +11765,6 @@
       </c>
       <c r="DY121" s="1">
         <v>4</v>
-      </c>
-      <c r="ED121" s="4">
-        <v>0</v>
-      </c>
-      <c r="EE121" s="4">
-        <v>0</v>
-      </c>
-      <c r="EF121" s="4">
-        <v>0</v>
-      </c>
-      <c r="EG121" s="4">
-        <v>0</v>
-      </c>
-      <c r="EH121" s="4">
-        <v>0</v>
       </c>
       <c r="ET121" s="1">
         <v>0</v>
@@ -11783,7 +11789,7 @@
       <c r="J122" s="4">
         <v>0</v>
       </c>
-      <c r="S122" s="5">
+      <c r="Q122" s="5">
         <v>0</v>
       </c>
       <c r="Y122" s="3">
@@ -11934,7 +11940,7 @@
         <v>0</v>
       </c>
       <c r="EF122" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="EG122" s="4">
         <v>0</v>
@@ -11965,7 +11971,7 @@
       <c r="J123" s="4">
         <v>0</v>
       </c>
-      <c r="S123" s="5">
+      <c r="Q123" s="5">
         <v>7</v>
       </c>
       <c r="Y123" s="3">
@@ -12132,10 +12138,10 @@
       <c r="A124" s="1">
         <v>0</v>
       </c>
-      <c r="I124" s="1">
-        <v>0</v>
-      </c>
-      <c r="S124" s="5">
+      <c r="H124" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q124" s="5">
         <v>0</v>
       </c>
       <c r="Y124" s="3">
@@ -12313,7 +12319,7 @@
         <v>0</v>
       </c>
       <c r="EF124" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="EG124" s="4">
         <v>0</v>
@@ -12329,10 +12335,10 @@
       <c r="A125" s="1">
         <v>0</v>
       </c>
-      <c r="J125" s="1">
-        <v>6</v>
-      </c>
-      <c r="S125" s="1">
+      <c r="H125" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q125" s="5">
         <v>0</v>
       </c>
       <c r="Y125" s="3">
@@ -12471,6 +12477,21 @@
         <v>0</v>
       </c>
       <c r="DY125" s="1">
+        <v>0</v>
+      </c>
+      <c r="ED125" s="4">
+        <v>0</v>
+      </c>
+      <c r="EE125" s="4">
+        <v>0</v>
+      </c>
+      <c r="EF125" s="4">
+        <v>0</v>
+      </c>
+      <c r="EG125" s="4">
+        <v>0</v>
+      </c>
+      <c r="EH125" s="4">
         <v>0</v>
       </c>
       <c r="ET125" s="1">
@@ -12481,11 +12502,11 @@
       <c r="A126" s="1">
         <v>0</v>
       </c>
-      <c r="K126" s="1">
-        <v>0</v>
-      </c>
-      <c r="S126" s="1">
-        <v>4</v>
+      <c r="H126" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q126" s="5">
+        <v>7</v>
       </c>
       <c r="Y126" s="3">
         <v>0</v>
@@ -12641,6 +12662,21 @@
         <v>4</v>
       </c>
       <c r="DY126" s="1">
+        <v>0</v>
+      </c>
+      <c r="ED126" s="4">
+        <v>0</v>
+      </c>
+      <c r="EE126" s="4">
+        <v>0</v>
+      </c>
+      <c r="EF126" s="4">
+        <v>0</v>
+      </c>
+      <c r="EG126" s="4">
+        <v>0</v>
+      </c>
+      <c r="EH126" s="4">
         <v>0</v>
       </c>
       <c r="ET126" s="1">
@@ -12651,10 +12687,10 @@
       <c r="A127" s="1">
         <v>0</v>
       </c>
-      <c r="L127" s="1">
-        <v>0</v>
-      </c>
-      <c r="S127" s="1">
+      <c r="H127" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q127" s="5">
         <v>0</v>
       </c>
       <c r="Y127" s="3">
@@ -12809,22 +12845,10 @@
       <c r="A128" s="1">
         <v>0</v>
       </c>
-      <c r="M128" s="1">
-        <v>6</v>
-      </c>
-      <c r="O128" s="4">
-        <v>0</v>
-      </c>
-      <c r="P128" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q128" s="4">
-        <v>0</v>
-      </c>
-      <c r="R128" s="4">
-        <v>0</v>
-      </c>
-      <c r="S128" s="4">
+      <c r="H128" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q128" s="1">
         <v>0</v>
       </c>
       <c r="Y128" s="3">
@@ -12979,23 +13003,11 @@
       <c r="A129" s="1">
         <v>0</v>
       </c>
-      <c r="N129" s="1">
-        <v>0</v>
-      </c>
-      <c r="O129" s="4">
-        <v>0</v>
-      </c>
-      <c r="P129" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q129" s="4">
-        <v>0</v>
-      </c>
-      <c r="R129" s="4">
-        <v>0</v>
-      </c>
-      <c r="S129" s="4">
-        <v>0</v>
+      <c r="H129" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q129" s="1">
+        <v>4</v>
       </c>
       <c r="Y129" s="3">
         <v>0</v>
@@ -13149,19 +13161,10 @@
       <c r="A130" s="1">
         <v>0</v>
       </c>
-      <c r="O130" s="4">
-        <v>0</v>
-      </c>
-      <c r="P130" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q130" s="4">
-        <v>11</v>
-      </c>
-      <c r="R130" s="4">
-        <v>0</v>
-      </c>
-      <c r="S130" s="4">
+      <c r="H130" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q130" s="1">
         <v>0</v>
       </c>
       <c r="Y130" s="3">
@@ -13316,6 +13319,9 @@
       <c r="A131" s="1">
         <v>0</v>
       </c>
+      <c r="H131" s="1">
+        <v>4</v>
+      </c>
       <c r="O131" s="4">
         <v>0</v>
       </c>
@@ -13483,6 +13489,9 @@
       <c r="A132" s="1">
         <v>0</v>
       </c>
+      <c r="H132" s="1">
+        <v>0</v>
+      </c>
       <c r="O132" s="4">
         <v>0</v>
       </c>
@@ -13638,6 +13647,39 @@
       <c r="A133" s="1">
         <v>0</v>
       </c>
+      <c r="I133" s="1">
+        <v>0</v>
+      </c>
+      <c r="J133" s="1">
+        <v>3</v>
+      </c>
+      <c r="K133" s="1">
+        <v>0</v>
+      </c>
+      <c r="L133" s="1">
+        <v>0</v>
+      </c>
+      <c r="M133" s="1">
+        <v>3</v>
+      </c>
+      <c r="N133" s="1">
+        <v>0</v>
+      </c>
+      <c r="O133" s="4">
+        <v>0</v>
+      </c>
+      <c r="P133" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q133" s="4">
+        <v>11</v>
+      </c>
+      <c r="R133" s="4">
+        <v>0</v>
+      </c>
+      <c r="S133" s="4">
+        <v>0</v>
+      </c>
       <c r="Y133" s="3">
         <v>0</v>
       </c>
@@ -13802,6 +13844,21 @@
       <c r="A134" s="1">
         <v>0</v>
       </c>
+      <c r="O134" s="4">
+        <v>0</v>
+      </c>
+      <c r="P134" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q134" s="4">
+        <v>0</v>
+      </c>
+      <c r="R134" s="4">
+        <v>0</v>
+      </c>
+      <c r="S134" s="4">
+        <v>0</v>
+      </c>
       <c r="Y134" s="3">
         <v>0</v>
       </c>
@@ -13951,6 +14008,21 @@
       <c r="A135" s="1">
         <v>0</v>
       </c>
+      <c r="O135" s="4">
+        <v>0</v>
+      </c>
+      <c r="P135" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q135" s="4">
+        <v>0</v>
+      </c>
+      <c r="R135" s="4">
+        <v>0</v>
+      </c>
+      <c r="S135" s="4">
+        <v>0</v>
+      </c>
       <c r="Y135" s="3">
         <v>0</v>
       </c>
@@ -14354,40 +14426,40 @@
       <c r="AX140" s="1">
         <v>0</v>
       </c>
-      <c r="BN140" s="1">
-        <v>0</v>
-      </c>
       <c r="BO140" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BP140" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BQ140" s="1">
         <v>0</v>
       </c>
       <c r="BR140" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS140" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT140" s="1">
         <v>0</v>
       </c>
       <c r="BU140" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BV140" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BW140" s="1">
         <v>0</v>
       </c>
       <c r="BX140" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BY140" s="1">
+        <v>3</v>
+      </c>
+      <c r="BZ140" s="1">
         <v>0</v>
       </c>
       <c r="CM140" s="1">

--- a/media/Levels/Level_5.xlsx
+++ b/media/Levels/Level_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7EB12EC-BA92-4CCF-8AD8-D2257AEE576D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194210FC-CCB8-4C34-ACAC-F27038DCC71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3672" yWindow="84" windowWidth="13836" windowHeight="12156" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -1006,6 +1006,21 @@
       <c r="DO6" s="1">
         <v>4</v>
       </c>
+      <c r="DY6" s="4">
+        <v>0</v>
+      </c>
+      <c r="DZ6" s="4">
+        <v>0</v>
+      </c>
+      <c r="EA6" s="4">
+        <v>0</v>
+      </c>
+      <c r="EB6" s="4">
+        <v>0</v>
+      </c>
+      <c r="EC6" s="4">
+        <v>0</v>
+      </c>
       <c r="ET6" s="1">
         <v>0</v>
       </c>
@@ -1026,6 +1041,9 @@
       <c r="DO7" s="1">
         <v>0</v>
       </c>
+      <c r="DY7" s="4">
+        <v>0</v>
+      </c>
       <c r="DZ7" s="4">
         <v>0</v>
       </c>
@@ -1036,9 +1054,6 @@
         <v>0</v>
       </c>
       <c r="EC7" s="4">
-        <v>0</v>
-      </c>
-      <c r="ED7" s="4">
         <v>0</v>
       </c>
       <c r="ET7" s="1">
@@ -1064,19 +1079,19 @@
       <c r="DT8" s="1">
         <v>0</v>
       </c>
+      <c r="DY8" s="4">
+        <v>0</v>
+      </c>
       <c r="DZ8" s="4">
         <v>0</v>
       </c>
       <c r="EA8" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="EB8" s="4">
         <v>0</v>
       </c>
       <c r="EC8" s="4">
-        <v>0</v>
-      </c>
-      <c r="ED8" s="4">
         <v>0</v>
       </c>
       <c r="ET8" s="1">
@@ -1102,6 +1117,9 @@
       <c r="DT9" s="1">
         <v>4</v>
       </c>
+      <c r="DY9" s="4">
+        <v>0</v>
+      </c>
       <c r="DZ9" s="4">
         <v>0</v>
       </c>
@@ -1109,12 +1127,9 @@
         <v>0</v>
       </c>
       <c r="EB9" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="EC9" s="4">
-        <v>0</v>
-      </c>
-      <c r="ED9" s="4">
         <v>0</v>
       </c>
       <c r="ET9" s="1">
@@ -1140,6 +1155,9 @@
       <c r="DT10" s="1">
         <v>0</v>
       </c>
+      <c r="DY10" s="4">
+        <v>0</v>
+      </c>
       <c r="DZ10" s="4">
         <v>0</v>
       </c>
@@ -1150,9 +1168,6 @@
         <v>0</v>
       </c>
       <c r="EC10" s="4">
-        <v>0</v>
-      </c>
-      <c r="ED10" s="4">
         <v>0</v>
       </c>
       <c r="ET10" s="1">
@@ -1178,21 +1193,6 @@
       <c r="DT11" s="1">
         <v>0</v>
       </c>
-      <c r="DZ11" s="4">
-        <v>0</v>
-      </c>
-      <c r="EA11" s="4">
-        <v>0</v>
-      </c>
-      <c r="EB11" s="4">
-        <v>0</v>
-      </c>
-      <c r="EC11" s="4">
-        <v>0</v>
-      </c>
-      <c r="ED11" s="4">
-        <v>0</v>
-      </c>
       <c r="ET11" s="1">
         <v>0</v>
       </c>
@@ -2767,12 +2767,6 @@
       <c r="EB21" s="4">
         <v>0</v>
       </c>
-      <c r="EG21" s="4">
-        <v>0</v>
-      </c>
-      <c r="EH21" s="4">
-        <v>0</v>
-      </c>
       <c r="EI21" s="4">
         <v>0</v>
       </c>
@@ -2780,6 +2774,12 @@
         <v>0</v>
       </c>
       <c r="EK21" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL21" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM21" s="4">
         <v>0</v>
       </c>
       <c r="ET21" s="1">
@@ -2952,12 +2952,6 @@
       <c r="EB22" s="4">
         <v>0</v>
       </c>
-      <c r="EG22" s="4">
-        <v>0</v>
-      </c>
-      <c r="EH22" s="4">
-        <v>0</v>
-      </c>
       <c r="EI22" s="4">
         <v>0</v>
       </c>
@@ -2965,6 +2959,12 @@
         <v>0</v>
       </c>
       <c r="EK22" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL22" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM22" s="4">
         <v>0</v>
       </c>
       <c r="ET22" s="1">
@@ -3101,22 +3101,25 @@
       <c r="DH23" s="3">
         <v>0</v>
       </c>
+      <c r="DO23" s="1">
+        <v>0</v>
+      </c>
       <c r="DT23" s="1">
         <v>0</v>
       </c>
-      <c r="EG23" s="4">
-        <v>0</v>
-      </c>
-      <c r="EH23" s="4">
-        <v>0</v>
-      </c>
       <c r="EI23" s="4">
+        <v>0</v>
+      </c>
+      <c r="EJ23" s="4">
+        <v>0</v>
+      </c>
+      <c r="EK23" s="4">
         <v>11</v>
       </c>
-      <c r="EJ23" s="4">
-        <v>0</v>
-      </c>
-      <c r="EK23" s="4">
+      <c r="EL23" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM23" s="4">
         <v>0</v>
       </c>
       <c r="ET23" s="1">
@@ -3280,15 +3283,12 @@
       <c r="DH24" s="3">
         <v>0</v>
       </c>
+      <c r="DO24" s="1">
+        <v>4</v>
+      </c>
       <c r="DT24" s="1">
         <v>4</v>
       </c>
-      <c r="EG24" s="4">
-        <v>0</v>
-      </c>
-      <c r="EH24" s="4">
-        <v>0</v>
-      </c>
       <c r="EI24" s="4">
         <v>0</v>
       </c>
@@ -3296,6 +3296,12 @@
         <v>0</v>
       </c>
       <c r="EK24" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL24" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM24" s="4">
         <v>0</v>
       </c>
       <c r="ET24" s="1">
@@ -3432,15 +3438,12 @@
       <c r="DH25" s="3">
         <v>0</v>
       </c>
+      <c r="DO25" s="1">
+        <v>0</v>
+      </c>
       <c r="DT25" s="1">
         <v>0</v>
       </c>
-      <c r="EG25" s="4">
-        <v>0</v>
-      </c>
-      <c r="EH25" s="4">
-        <v>0</v>
-      </c>
       <c r="EI25" s="4">
         <v>0</v>
       </c>
@@ -3448,6 +3451,12 @@
         <v>0</v>
       </c>
       <c r="EK25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM25" s="4">
         <v>0</v>
       </c>
       <c r="ET25" s="1">
@@ -4142,9 +4151,6 @@
       <c r="DH29" s="3">
         <v>0</v>
       </c>
-      <c r="DO29" s="1">
-        <v>0</v>
-      </c>
       <c r="DT29" s="1">
         <v>0</v>
       </c>
@@ -4336,9 +4342,6 @@
       <c r="DH30" s="3">
         <v>0</v>
       </c>
-      <c r="DO30" s="1">
-        <v>4</v>
-      </c>
       <c r="DT30" s="1">
         <v>4</v>
       </c>
@@ -4488,9 +4491,6 @@
       <c r="DH31" s="3">
         <v>0</v>
       </c>
-      <c r="DO31" s="1">
-        <v>0</v>
-      </c>
       <c r="DT31" s="1">
         <v>0</v>
       </c>
@@ -4699,21 +4699,6 @@
       <c r="EC33" s="4">
         <v>0</v>
       </c>
-      <c r="EJ33" s="4">
-        <v>0</v>
-      </c>
-      <c r="EK33" s="4">
-        <v>0</v>
-      </c>
-      <c r="EL33" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM33" s="4">
-        <v>0</v>
-      </c>
-      <c r="EN33" s="4">
-        <v>0</v>
-      </c>
       <c r="ET33" s="1">
         <v>0</v>
       </c>
@@ -4764,21 +4749,6 @@
       <c r="EC34" s="4">
         <v>0</v>
       </c>
-      <c r="EJ34" s="4">
-        <v>0</v>
-      </c>
-      <c r="EK34" s="4">
-        <v>0</v>
-      </c>
-      <c r="EL34" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM34" s="4">
-        <v>0</v>
-      </c>
-      <c r="EN34" s="4">
-        <v>0</v>
-      </c>
       <c r="ET34" s="1">
         <v>0</v>
       </c>
@@ -4817,21 +4787,6 @@
       <c r="EC35" s="4">
         <v>0</v>
       </c>
-      <c r="EJ35" s="4">
-        <v>0</v>
-      </c>
-      <c r="EK35" s="4">
-        <v>0</v>
-      </c>
-      <c r="EL35" s="4">
-        <v>11</v>
-      </c>
-      <c r="EM35" s="4">
-        <v>0</v>
-      </c>
-      <c r="EN35" s="4">
-        <v>0</v>
-      </c>
       <c r="ET35" s="1">
         <v>0</v>
       </c>
@@ -4870,21 +4825,6 @@
       <c r="EC36" s="4">
         <v>0</v>
       </c>
-      <c r="EJ36" s="4">
-        <v>0</v>
-      </c>
-      <c r="EK36" s="4">
-        <v>0</v>
-      </c>
-      <c r="EL36" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM36" s="4">
-        <v>0</v>
-      </c>
-      <c r="EN36" s="4">
-        <v>0</v>
-      </c>
       <c r="ET36" s="1">
         <v>0</v>
       </c>
@@ -4923,21 +4863,6 @@
       <c r="EC37" s="4">
         <v>0</v>
       </c>
-      <c r="EJ37" s="4">
-        <v>0</v>
-      </c>
-      <c r="EK37" s="4">
-        <v>0</v>
-      </c>
-      <c r="EL37" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM37" s="4">
-        <v>0</v>
-      </c>
-      <c r="EN37" s="4">
-        <v>0</v>
-      </c>
       <c r="ET37" s="1">
         <v>0</v>
       </c>
@@ -4961,6 +4886,21 @@
       <c r="DT38" s="1">
         <v>0</v>
       </c>
+      <c r="EK38" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL38" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM38" s="4">
+        <v>0</v>
+      </c>
+      <c r="EN38" s="4">
+        <v>0</v>
+      </c>
+      <c r="EO38" s="4">
+        <v>0</v>
+      </c>
       <c r="ET38" s="1">
         <v>0</v>
       </c>
@@ -4984,6 +4924,21 @@
       <c r="DT39" s="1">
         <v>4</v>
       </c>
+      <c r="EK39" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL39" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM39" s="4">
+        <v>0</v>
+      </c>
+      <c r="EN39" s="4">
+        <v>0</v>
+      </c>
+      <c r="EO39" s="4">
+        <v>0</v>
+      </c>
       <c r="ET39" s="1">
         <v>0</v>
       </c>
@@ -5007,6 +4962,21 @@
       <c r="DT40" s="1">
         <v>0</v>
       </c>
+      <c r="EK40" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL40" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM40" s="4">
+        <v>11</v>
+      </c>
+      <c r="EN40" s="4">
+        <v>0</v>
+      </c>
+      <c r="EO40" s="4">
+        <v>0</v>
+      </c>
       <c r="ET40" s="1">
         <v>0</v>
       </c>
@@ -5030,6 +5000,21 @@
       <c r="DT41" s="1">
         <v>0</v>
       </c>
+      <c r="EK41" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL41" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM41" s="4">
+        <v>0</v>
+      </c>
+      <c r="EN41" s="4">
+        <v>0</v>
+      </c>
+      <c r="EO41" s="4">
+        <v>0</v>
+      </c>
       <c r="ET41" s="1">
         <v>0</v>
       </c>
@@ -5052,6 +5037,21 @@
       </c>
       <c r="DT42" s="1">
         <v>4</v>
+      </c>
+      <c r="EK42" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL42" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM42" s="4">
+        <v>0</v>
+      </c>
+      <c r="EN42" s="4">
+        <v>0</v>
+      </c>
+      <c r="EO42" s="4">
+        <v>0</v>
       </c>
       <c r="ET42" s="1">
         <v>0</v>
@@ -9566,6 +9566,21 @@
       <c r="A89" s="1">
         <v>0</v>
       </c>
+      <c r="H89" s="4">
+        <v>0</v>
+      </c>
+      <c r="I89" s="4">
+        <v>0</v>
+      </c>
+      <c r="J89" s="4">
+        <v>0</v>
+      </c>
+      <c r="K89" s="4">
+        <v>0</v>
+      </c>
+      <c r="L89" s="4">
+        <v>0</v>
+      </c>
       <c r="AG89" s="1">
         <v>0</v>
       </c>
@@ -9589,6 +9604,21 @@
       <c r="A90" s="1">
         <v>0</v>
       </c>
+      <c r="H90" s="4">
+        <v>0</v>
+      </c>
+      <c r="I90" s="4">
+        <v>0</v>
+      </c>
+      <c r="J90" s="4">
+        <v>0</v>
+      </c>
+      <c r="K90" s="4">
+        <v>0</v>
+      </c>
+      <c r="L90" s="4">
+        <v>0</v>
+      </c>
       <c r="AG90" s="1">
         <v>0</v>
       </c>
@@ -9612,6 +9642,21 @@
       <c r="A91" s="1">
         <v>0</v>
       </c>
+      <c r="H91" s="4">
+        <v>0</v>
+      </c>
+      <c r="I91" s="4">
+        <v>0</v>
+      </c>
+      <c r="J91" s="4">
+        <v>11</v>
+      </c>
+      <c r="K91" s="4">
+        <v>0</v>
+      </c>
+      <c r="L91" s="4">
+        <v>0</v>
+      </c>
       <c r="AG91" s="1">
         <v>4</v>
       </c>
@@ -9635,6 +9680,21 @@
       <c r="A92" s="1">
         <v>0</v>
       </c>
+      <c r="H92" s="4">
+        <v>0</v>
+      </c>
+      <c r="I92" s="4">
+        <v>0</v>
+      </c>
+      <c r="J92" s="4">
+        <v>0</v>
+      </c>
+      <c r="K92" s="4">
+        <v>0</v>
+      </c>
+      <c r="L92" s="4">
+        <v>0</v>
+      </c>
       <c r="AG92" s="1">
         <v>0</v>
       </c>
@@ -9658,6 +9718,21 @@
       <c r="A93" s="1">
         <v>0</v>
       </c>
+      <c r="H93" s="4">
+        <v>0</v>
+      </c>
+      <c r="I93" s="4">
+        <v>0</v>
+      </c>
+      <c r="J93" s="4">
+        <v>0</v>
+      </c>
+      <c r="K93" s="4">
+        <v>0</v>
+      </c>
+      <c r="L93" s="4">
+        <v>0</v>
+      </c>
       <c r="AG93" s="1">
         <v>0</v>
       </c>
@@ -10270,6 +10345,18 @@
       <c r="A105" s="1">
         <v>0</v>
       </c>
+      <c r="Q105" s="1">
+        <v>0</v>
+      </c>
+      <c r="R105" s="1">
+        <v>0</v>
+      </c>
+      <c r="S105" s="1">
+        <v>3</v>
+      </c>
+      <c r="T105" s="1">
+        <v>0</v>
+      </c>
       <c r="U105" s="1">
         <v>0</v>
       </c>
@@ -10486,13 +10573,13 @@
       <c r="CT105" s="5">
         <v>0</v>
       </c>
-      <c r="CU105" s="1">
-        <v>0</v>
-      </c>
-      <c r="CV105" s="1">
-        <v>3</v>
-      </c>
-      <c r="CW105" s="1">
+      <c r="CU105" s="5">
+        <v>0</v>
+      </c>
+      <c r="CV105" s="5">
+        <v>7</v>
+      </c>
+      <c r="CW105" s="5">
         <v>0</v>
       </c>
       <c r="CX105" s="1">
@@ -10572,8 +10659,8 @@
       <c r="A106" s="1">
         <v>0</v>
       </c>
-      <c r="T106" s="1">
-        <v>0</v>
+      <c r="Q106" s="1">
+        <v>4</v>
       </c>
       <c r="AX106" s="1">
         <v>0</v>
@@ -10598,8 +10685,8 @@
       <c r="A107" s="1">
         <v>0</v>
       </c>
-      <c r="S107" s="1">
-        <v>5</v>
+      <c r="Q107" s="1">
+        <v>0</v>
       </c>
       <c r="AX107" s="1">
         <v>4</v>
@@ -10624,7 +10711,7 @@
       <c r="A108" s="1">
         <v>0</v>
       </c>
-      <c r="R108" s="1">
+      <c r="Q108" s="1">
         <v>0</v>
       </c>
       <c r="AX108" s="1">
@@ -10651,7 +10738,7 @@
         <v>0</v>
       </c>
       <c r="Q109" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX109" s="1">
         <v>0</v>
@@ -10673,11 +10760,8 @@
       <c r="A110" s="1">
         <v>0</v>
       </c>
-      <c r="O110" s="1">
-        <v>0</v>
-      </c>
-      <c r="P110" s="1">
-        <v>5</v>
+      <c r="Q110" s="1">
+        <v>0</v>
       </c>
       <c r="AX110" s="1">
         <v>4</v>
@@ -10699,6 +10783,21 @@
       <c r="A111" s="1">
         <v>0</v>
       </c>
+      <c r="G111" s="4">
+        <v>0</v>
+      </c>
+      <c r="H111" s="4">
+        <v>0</v>
+      </c>
+      <c r="I111" s="4">
+        <v>0</v>
+      </c>
+      <c r="J111" s="4">
+        <v>0</v>
+      </c>
+      <c r="K111" s="4">
+        <v>0</v>
+      </c>
       <c r="O111" s="4">
         <v>0</v>
       </c>
@@ -10734,6 +10833,21 @@
       <c r="A112" s="1">
         <v>0</v>
       </c>
+      <c r="G112" s="4">
+        <v>0</v>
+      </c>
+      <c r="H112" s="4">
+        <v>0</v>
+      </c>
+      <c r="I112" s="4">
+        <v>0</v>
+      </c>
+      <c r="J112" s="4">
+        <v>0</v>
+      </c>
+      <c r="K112" s="4">
+        <v>0</v>
+      </c>
       <c r="O112" s="4">
         <v>0</v>
       </c>
@@ -10769,6 +10883,30 @@
       <c r="A113" s="1">
         <v>0</v>
       </c>
+      <c r="G113" s="4">
+        <v>0</v>
+      </c>
+      <c r="H113" s="4">
+        <v>0</v>
+      </c>
+      <c r="I113" s="4">
+        <v>11</v>
+      </c>
+      <c r="J113" s="4">
+        <v>0</v>
+      </c>
+      <c r="K113" s="4">
+        <v>0</v>
+      </c>
+      <c r="L113" s="1">
+        <v>0</v>
+      </c>
+      <c r="M113" s="1">
+        <v>3</v>
+      </c>
+      <c r="N113" s="1">
+        <v>0</v>
+      </c>
       <c r="O113" s="4">
         <v>0</v>
       </c>
@@ -10804,19 +10942,19 @@
       <c r="A114" s="1">
         <v>0</v>
       </c>
+      <c r="G114" s="4">
+        <v>0</v>
+      </c>
+      <c r="H114" s="4">
+        <v>0</v>
+      </c>
+      <c r="I114" s="4">
+        <v>0</v>
+      </c>
       <c r="J114" s="4">
         <v>0</v>
       </c>
       <c r="K114" s="4">
-        <v>0</v>
-      </c>
-      <c r="L114" s="4">
-        <v>0</v>
-      </c>
-      <c r="M114" s="4">
-        <v>0</v>
-      </c>
-      <c r="N114" s="4">
         <v>0</v>
       </c>
       <c r="O114" s="4">
@@ -10857,19 +10995,19 @@
       <c r="A115" s="1">
         <v>0</v>
       </c>
+      <c r="G115" s="4">
+        <v>0</v>
+      </c>
+      <c r="H115" s="4">
+        <v>0</v>
+      </c>
+      <c r="I115" s="4">
+        <v>0</v>
+      </c>
       <c r="J115" s="4">
         <v>0</v>
       </c>
       <c r="K115" s="4">
-        <v>0</v>
-      </c>
-      <c r="L115" s="4">
-        <v>0</v>
-      </c>
-      <c r="M115" s="4">
-        <v>0</v>
-      </c>
-      <c r="N115" s="4">
         <v>0</v>
       </c>
       <c r="O115" s="4">
@@ -10970,19 +11108,7 @@
       <c r="A116" s="1">
         <v>0</v>
       </c>
-      <c r="J116" s="4">
-        <v>0</v>
-      </c>
-      <c r="K116" s="4">
-        <v>0</v>
-      </c>
-      <c r="L116" s="4">
-        <v>11</v>
-      </c>
-      <c r="M116" s="4">
-        <v>0</v>
-      </c>
-      <c r="N116" s="4">
+      <c r="I116" s="1">
         <v>0</v>
       </c>
       <c r="Q116" s="1">
@@ -11071,20 +11197,8 @@
       <c r="A117" s="1">
         <v>0</v>
       </c>
-      <c r="J117" s="4">
-        <v>0</v>
-      </c>
-      <c r="K117" s="4">
-        <v>0</v>
-      </c>
-      <c r="L117" s="4">
-        <v>0</v>
-      </c>
-      <c r="M117" s="4">
-        <v>0</v>
-      </c>
-      <c r="N117" s="4">
-        <v>0</v>
+      <c r="I117" s="1">
+        <v>4</v>
       </c>
       <c r="Q117" s="1">
         <v>4</v>
@@ -11172,19 +11286,7 @@
       <c r="A118" s="1">
         <v>0</v>
       </c>
-      <c r="J118" s="4">
-        <v>0</v>
-      </c>
-      <c r="K118" s="4">
-        <v>0</v>
-      </c>
-      <c r="L118" s="4">
-        <v>0</v>
-      </c>
-      <c r="M118" s="4">
-        <v>0</v>
-      </c>
-      <c r="N118" s="4">
+      <c r="I118" s="1">
         <v>0</v>
       </c>
       <c r="Q118" s="1">
@@ -11273,24 +11375,15 @@
       <c r="A119" s="1">
         <v>0</v>
       </c>
-      <c r="F119" s="4">
-        <v>0</v>
-      </c>
-      <c r="G119" s="4">
-        <v>0</v>
-      </c>
-      <c r="H119" s="4">
-        <v>0</v>
-      </c>
-      <c r="I119" s="4">
-        <v>0</v>
-      </c>
-      <c r="J119" s="4">
+      <c r="I119" s="1">
         <v>0</v>
       </c>
       <c r="Q119" s="1">
         <v>0</v>
       </c>
+      <c r="X119" s="3">
+        <v>0</v>
+      </c>
       <c r="Y119" s="3">
         <v>0</v>
       </c>
@@ -11348,9 +11441,6 @@
       <c r="AQ119" s="3">
         <v>0</v>
       </c>
-      <c r="AR119" s="3">
-        <v>0</v>
-      </c>
       <c r="AX119" s="1">
         <v>4</v>
       </c>
@@ -11359,9 +11449,6 @@
       </c>
       <c r="BZ119" s="1">
         <v>4</v>
-      </c>
-      <c r="CJ119" s="1">
-        <v>0</v>
       </c>
       <c r="CK119" s="3">
         <v>0</v>
@@ -11437,24 +11524,15 @@
       <c r="A120" s="1">
         <v>0</v>
       </c>
-      <c r="F120" s="4">
-        <v>0</v>
-      </c>
-      <c r="G120" s="4">
-        <v>0</v>
-      </c>
-      <c r="H120" s="4">
-        <v>0</v>
-      </c>
-      <c r="I120" s="4">
-        <v>0</v>
-      </c>
-      <c r="J120" s="4">
-        <v>0</v>
+      <c r="I120" s="1">
+        <v>4</v>
       </c>
       <c r="Q120" s="1">
         <v>4</v>
       </c>
+      <c r="X120" s="3">
+        <v>0</v>
+      </c>
       <c r="Y120" s="3">
         <v>0</v>
       </c>
@@ -11512,9 +11590,6 @@
       <c r="AQ120" s="3">
         <v>0</v>
       </c>
-      <c r="AR120" s="3">
-        <v>0</v>
-      </c>
       <c r="AX120" s="1">
         <v>0</v>
       </c>
@@ -11530,8 +11605,8 @@
       <c r="BZ120" s="1">
         <v>0</v>
       </c>
-      <c r="CI120" s="1">
-        <v>5</v>
+      <c r="CJ120" s="1">
+        <v>0</v>
       </c>
       <c r="CK120" s="3">
         <v>0</v>
@@ -11607,24 +11682,15 @@
       <c r="A121" s="1">
         <v>0</v>
       </c>
-      <c r="F121" s="4">
-        <v>0</v>
-      </c>
-      <c r="G121" s="4">
-        <v>0</v>
-      </c>
-      <c r="H121" s="4">
-        <v>11</v>
-      </c>
-      <c r="I121" s="4">
-        <v>0</v>
-      </c>
-      <c r="J121" s="4">
+      <c r="I121" s="1">
         <v>0</v>
       </c>
       <c r="Q121" s="1">
         <v>0</v>
       </c>
+      <c r="X121" s="3">
+        <v>0</v>
+      </c>
       <c r="Y121" s="3">
         <v>0</v>
       </c>
@@ -11682,9 +11748,6 @@
       <c r="AQ121" s="3">
         <v>0</v>
       </c>
-      <c r="AR121" s="3">
-        <v>0</v>
-      </c>
       <c r="AX121" s="1">
         <v>0</v>
       </c>
@@ -11697,8 +11760,8 @@
       <c r="BZ121" s="1">
         <v>0</v>
       </c>
-      <c r="CH121" s="1">
-        <v>0</v>
+      <c r="CI121" s="1">
+        <v>5</v>
       </c>
       <c r="CK121" s="3">
         <v>0</v>
@@ -11774,24 +11837,15 @@
       <c r="A122" s="1">
         <v>0</v>
       </c>
-      <c r="F122" s="4">
-        <v>0</v>
-      </c>
-      <c r="G122" s="4">
-        <v>0</v>
-      </c>
-      <c r="H122" s="4">
-        <v>0</v>
-      </c>
-      <c r="I122" s="4">
-        <v>0</v>
-      </c>
-      <c r="J122" s="4">
+      <c r="I122" s="1">
         <v>0</v>
       </c>
       <c r="Q122" s="5">
         <v>0</v>
       </c>
+      <c r="X122" s="3">
+        <v>0</v>
+      </c>
       <c r="Y122" s="3">
         <v>0</v>
       </c>
@@ -11847,9 +11901,6 @@
         <v>0</v>
       </c>
       <c r="AQ122" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR122" s="3">
         <v>0</v>
       </c>
       <c r="AX122" s="1">
@@ -11864,7 +11915,7 @@
       <c r="BZ122" s="1">
         <v>4</v>
       </c>
-      <c r="CG122" s="1">
+      <c r="CH122" s="1">
         <v>0</v>
       </c>
       <c r="CK122" s="3">
@@ -11956,23 +12007,14 @@
       <c r="A123" s="1">
         <v>0</v>
       </c>
-      <c r="F123" s="4">
-        <v>0</v>
-      </c>
-      <c r="G123" s="4">
-        <v>0</v>
-      </c>
-      <c r="H123" s="4">
-        <v>0</v>
-      </c>
-      <c r="I123" s="4">
-        <v>0</v>
-      </c>
-      <c r="J123" s="4">
-        <v>0</v>
+      <c r="I123" s="1">
+        <v>4</v>
       </c>
       <c r="Q123" s="5">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="X123" s="3">
+        <v>0</v>
       </c>
       <c r="Y123" s="3">
         <v>0</v>
@@ -12031,9 +12073,6 @@
       <c r="AQ123" s="3">
         <v>0</v>
       </c>
-      <c r="AR123" s="3">
-        <v>0</v>
-      </c>
       <c r="AX123" s="1">
         <v>0</v>
       </c>
@@ -12046,8 +12085,8 @@
       <c r="BZ123" s="1">
         <v>0</v>
       </c>
-      <c r="CF123" s="1">
-        <v>5</v>
+      <c r="CG123" s="1">
+        <v>0</v>
       </c>
       <c r="CK123" s="3">
         <v>0</v>
@@ -12138,12 +12177,15 @@
       <c r="A124" s="1">
         <v>0</v>
       </c>
-      <c r="H124" s="1">
+      <c r="I124" s="1">
         <v>0</v>
       </c>
       <c r="Q124" s="5">
         <v>0</v>
       </c>
+      <c r="X124" s="3">
+        <v>0</v>
+      </c>
       <c r="Y124" s="3">
         <v>0</v>
       </c>
@@ -12201,9 +12243,6 @@
       <c r="AQ124" s="3">
         <v>0</v>
       </c>
-      <c r="AR124" s="3">
-        <v>0</v>
-      </c>
       <c r="AX124" s="1">
         <v>0</v>
       </c>
@@ -12216,8 +12255,8 @@
       <c r="BZ124" s="1">
         <v>0</v>
       </c>
-      <c r="CE124" s="1">
-        <v>0</v>
+      <c r="CF124" s="1">
+        <v>5</v>
       </c>
       <c r="CK124" s="3">
         <v>0</v>
@@ -12335,12 +12374,15 @@
       <c r="A125" s="1">
         <v>0</v>
       </c>
-      <c r="H125" s="1">
-        <v>4</v>
+      <c r="I125" s="1">
+        <v>0</v>
       </c>
       <c r="Q125" s="5">
         <v>0</v>
       </c>
+      <c r="X125" s="3">
+        <v>0</v>
+      </c>
       <c r="Y125" s="3">
         <v>0</v>
       </c>
@@ -12396,9 +12438,6 @@
         <v>0</v>
       </c>
       <c r="AQ125" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR125" s="3">
         <v>0</v>
       </c>
       <c r="AX125" s="1">
@@ -12412,6 +12451,9 @@
       </c>
       <c r="BZ125" s="1">
         <v>4</v>
+      </c>
+      <c r="CE125" s="1">
+        <v>0</v>
       </c>
       <c r="CK125" s="3">
         <v>0</v>
@@ -12502,11 +12544,14 @@
       <c r="A126" s="1">
         <v>0</v>
       </c>
-      <c r="H126" s="1">
-        <v>0</v>
+      <c r="I126" s="1">
+        <v>4</v>
       </c>
       <c r="Q126" s="5">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="X126" s="3">
+        <v>0</v>
       </c>
       <c r="Y126" s="3">
         <v>0</v>
@@ -12563,9 +12608,6 @@
         <v>0</v>
       </c>
       <c r="AQ126" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR126" s="3">
         <v>0</v>
       </c>
       <c r="AX126" s="1">
@@ -12687,12 +12729,15 @@
       <c r="A127" s="1">
         <v>0</v>
       </c>
-      <c r="H127" s="1">
+      <c r="I127" s="1">
         <v>0</v>
       </c>
       <c r="Q127" s="5">
         <v>0</v>
       </c>
+      <c r="X127" s="3">
+        <v>0</v>
+      </c>
       <c r="Y127" s="3">
         <v>0</v>
       </c>
@@ -12748,24 +12793,6 @@
         <v>0</v>
       </c>
       <c r="AQ127" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR127" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD127" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE127" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF127" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG127" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH127" s="4">
         <v>0</v>
       </c>
       <c r="BZ127" s="1">
@@ -12845,12 +12872,15 @@
       <c r="A128" s="1">
         <v>0</v>
       </c>
-      <c r="H128" s="1">
-        <v>4</v>
+      <c r="I128" s="1">
+        <v>0</v>
       </c>
       <c r="Q128" s="1">
         <v>0</v>
       </c>
+      <c r="X128" s="3">
+        <v>0</v>
+      </c>
       <c r="Y128" s="3">
         <v>0</v>
       </c>
@@ -12879,10 +12909,10 @@
         <v>0</v>
       </c>
       <c r="AH128" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AI128" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AJ128" s="3">
         <v>0</v>
@@ -12906,9 +12936,6 @@
         <v>0</v>
       </c>
       <c r="AQ128" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR128" s="3">
         <v>0</v>
       </c>
       <c r="BD128" s="4">
@@ -13003,12 +13030,15 @@
       <c r="A129" s="1">
         <v>0</v>
       </c>
-      <c r="H129" s="1">
-        <v>0</v>
+      <c r="I129" s="1">
+        <v>4</v>
       </c>
       <c r="Q129" s="1">
         <v>4</v>
       </c>
+      <c r="X129" s="3">
+        <v>0</v>
+      </c>
       <c r="Y129" s="3">
         <v>0</v>
       </c>
@@ -13066,9 +13096,6 @@
       <c r="AQ129" s="3">
         <v>0</v>
       </c>
-      <c r="AR129" s="3">
-        <v>0</v>
-      </c>
       <c r="BD129" s="4">
         <v>0</v>
       </c>
@@ -13076,7 +13103,7 @@
         <v>0</v>
       </c>
       <c r="BF129" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BG129" s="4">
         <v>0</v>
@@ -13161,12 +13188,15 @@
       <c r="A130" s="1">
         <v>0</v>
       </c>
-      <c r="H130" s="1">
+      <c r="I130" s="1">
         <v>0</v>
       </c>
       <c r="Q130" s="1">
         <v>0</v>
       </c>
+      <c r="X130" s="3">
+        <v>0</v>
+      </c>
       <c r="Y130" s="3">
         <v>0</v>
       </c>
@@ -13224,9 +13254,6 @@
       <c r="AQ130" s="3">
         <v>0</v>
       </c>
-      <c r="AR130" s="3">
-        <v>0</v>
-      </c>
       <c r="BD130" s="4">
         <v>0</v>
       </c>
@@ -13234,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="BF130" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG130" s="4">
         <v>0</v>
@@ -13319,8 +13346,20 @@
       <c r="A131" s="1">
         <v>0</v>
       </c>
-      <c r="H131" s="1">
-        <v>4</v>
+      <c r="G131" s="4">
+        <v>0</v>
+      </c>
+      <c r="H131" s="4">
+        <v>0</v>
+      </c>
+      <c r="I131" s="4">
+        <v>0</v>
+      </c>
+      <c r="J131" s="4">
+        <v>0</v>
+      </c>
+      <c r="K131" s="4">
+        <v>0</v>
       </c>
       <c r="O131" s="4">
         <v>0</v>
@@ -13337,6 +13376,9 @@
       <c r="S131" s="4">
         <v>0</v>
       </c>
+      <c r="X131" s="3">
+        <v>0</v>
+      </c>
       <c r="Y131" s="3">
         <v>0</v>
       </c>
@@ -13392,9 +13434,6 @@
         <v>0</v>
       </c>
       <c r="AQ131" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR131" s="3">
         <v>0</v>
       </c>
       <c r="BD131" s="4">
@@ -13489,7 +13528,19 @@
       <c r="A132" s="1">
         <v>0</v>
       </c>
-      <c r="H132" s="1">
+      <c r="G132" s="4">
+        <v>0</v>
+      </c>
+      <c r="H132" s="4">
+        <v>0</v>
+      </c>
+      <c r="I132" s="4">
+        <v>0</v>
+      </c>
+      <c r="J132" s="4">
+        <v>0</v>
+      </c>
+      <c r="K132" s="4">
         <v>0</v>
       </c>
       <c r="O132" s="4">
@@ -13507,6 +13558,9 @@
       <c r="S132" s="4">
         <v>0</v>
       </c>
+      <c r="X132" s="3">
+        <v>0</v>
+      </c>
       <c r="Y132" s="3">
         <v>0</v>
       </c>
@@ -13564,10 +13618,19 @@
       <c r="AQ132" s="3">
         <v>0</v>
       </c>
-      <c r="AR132" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX132" s="1">
+      <c r="BD132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH132" s="4">
         <v>0</v>
       </c>
       <c r="BZ132" s="1">
@@ -13647,13 +13710,19 @@
       <c r="A133" s="1">
         <v>0</v>
       </c>
-      <c r="I133" s="1">
-        <v>0</v>
-      </c>
-      <c r="J133" s="1">
-        <v>3</v>
-      </c>
-      <c r="K133" s="1">
+      <c r="G133" s="4">
+        <v>0</v>
+      </c>
+      <c r="H133" s="4">
+        <v>0</v>
+      </c>
+      <c r="I133" s="4">
+        <v>11</v>
+      </c>
+      <c r="J133" s="4">
+        <v>0</v>
+      </c>
+      <c r="K133" s="4">
         <v>0</v>
       </c>
       <c r="L133" s="1">
@@ -13680,6 +13749,9 @@
       <c r="S133" s="4">
         <v>0</v>
       </c>
+      <c r="X133" s="3">
+        <v>0</v>
+      </c>
       <c r="Y133" s="3">
         <v>0</v>
       </c>
@@ -13735,36 +13807,6 @@
         <v>0</v>
       </c>
       <c r="AQ133" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR133" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX133" s="1">
-        <v>4</v>
-      </c>
-      <c r="AY133" s="1">
-        <v>0</v>
-      </c>
-      <c r="BM133" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN133" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO133" s="1">
-        <v>3</v>
-      </c>
-      <c r="BP133" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ133" s="1">
-        <v>0</v>
-      </c>
-      <c r="BR133" s="1">
-        <v>3</v>
-      </c>
-      <c r="BS133" s="1">
         <v>0</v>
       </c>
       <c r="BZ133" s="1">
@@ -13844,6 +13886,21 @@
       <c r="A134" s="1">
         <v>0</v>
       </c>
+      <c r="G134" s="4">
+        <v>0</v>
+      </c>
+      <c r="H134" s="4">
+        <v>0</v>
+      </c>
+      <c r="I134" s="4">
+        <v>0</v>
+      </c>
+      <c r="J134" s="4">
+        <v>0</v>
+      </c>
+      <c r="K134" s="4">
+        <v>0</v>
+      </c>
       <c r="O134" s="4">
         <v>0</v>
       </c>
@@ -13859,6 +13916,9 @@
       <c r="S134" s="4">
         <v>0</v>
       </c>
+      <c r="X134" s="3">
+        <v>0</v>
+      </c>
       <c r="Y134" s="3">
         <v>0</v>
       </c>
@@ -13916,22 +13976,10 @@
       <c r="AQ134" s="3">
         <v>0</v>
       </c>
-      <c r="AR134" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX134" s="1">
-        <v>0</v>
-      </c>
-      <c r="AZ134" s="1">
-        <v>6</v>
-      </c>
-      <c r="BL134" s="1">
-        <v>5</v>
-      </c>
       <c r="BZ134" s="1">
         <v>4</v>
       </c>
-      <c r="CE134" s="1">
+      <c r="CF134" s="1">
         <v>0</v>
       </c>
       <c r="CK134" s="3">
@@ -14008,6 +14056,21 @@
       <c r="A135" s="1">
         <v>0</v>
       </c>
+      <c r="G135" s="4">
+        <v>0</v>
+      </c>
+      <c r="H135" s="4">
+        <v>0</v>
+      </c>
+      <c r="I135" s="4">
+        <v>0</v>
+      </c>
+      <c r="J135" s="4">
+        <v>0</v>
+      </c>
+      <c r="K135" s="4">
+        <v>0</v>
+      </c>
       <c r="O135" s="4">
         <v>0</v>
       </c>
@@ -14023,6 +14086,9 @@
       <c r="S135" s="4">
         <v>0</v>
       </c>
+      <c r="X135" s="3">
+        <v>0</v>
+      </c>
       <c r="Y135" s="3">
         <v>0</v>
       </c>
@@ -14080,25 +14146,40 @@
       <c r="AQ135" s="3">
         <v>0</v>
       </c>
-      <c r="AR135" s="3">
-        <v>0</v>
-      </c>
       <c r="AX135" s="1">
         <v>0</v>
       </c>
-      <c r="BA135" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK135" s="1">
+      <c r="AY135" s="1">
+        <v>0</v>
+      </c>
+      <c r="BM135" s="1">
+        <v>0</v>
+      </c>
+      <c r="BN135" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO135" s="1">
+        <v>3</v>
+      </c>
+      <c r="BP135" s="1">
+        <v>0</v>
+      </c>
+      <c r="BQ135" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR135" s="1">
+        <v>3</v>
+      </c>
+      <c r="BS135" s="1">
         <v>0</v>
       </c>
       <c r="BZ135" s="1">
         <v>0</v>
       </c>
-      <c r="CD135" s="1">
+      <c r="CE135" s="1">
         <v>5</v>
       </c>
-      <c r="CR135" s="1">
+      <c r="CS135" s="1">
         <v>0</v>
       </c>
       <c r="DS135" s="1">
@@ -14115,6 +14196,9 @@
       <c r="A136" s="1">
         <v>0</v>
       </c>
+      <c r="X136" s="3">
+        <v>0</v>
+      </c>
       <c r="Y136" s="3">
         <v>0</v>
       </c>
@@ -14172,25 +14256,22 @@
       <c r="AQ136" s="3">
         <v>0</v>
       </c>
-      <c r="AR136" s="3">
-        <v>0</v>
-      </c>
       <c r="AX136" s="1">
         <v>4</v>
       </c>
-      <c r="BB136" s="1">
-        <v>0</v>
-      </c>
-      <c r="BJ136" s="1">
-        <v>0</v>
+      <c r="AZ136" s="1">
+        <v>6</v>
+      </c>
+      <c r="BL136" s="1">
+        <v>5</v>
       </c>
       <c r="BZ136" s="1">
         <v>0</v>
       </c>
-      <c r="CC136" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ136" s="1">
+      <c r="CD136" s="1">
+        <v>0</v>
+      </c>
+      <c r="CR136" s="1">
         <v>5</v>
       </c>
       <c r="DS136" s="1">
@@ -14207,6 +14288,9 @@
       <c r="A137" s="1">
         <v>0</v>
       </c>
+      <c r="X137" s="3">
+        <v>0</v>
+      </c>
       <c r="Y137" s="3">
         <v>0</v>
       </c>
@@ -14264,25 +14348,22 @@
       <c r="AQ137" s="3">
         <v>0</v>
       </c>
-      <c r="AR137" s="3">
-        <v>0</v>
-      </c>
       <c r="AX137" s="1">
         <v>0</v>
       </c>
-      <c r="BC137" s="1">
-        <v>6</v>
-      </c>
-      <c r="BI137" s="1">
-        <v>5</v>
+      <c r="BA137" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK137" s="1">
+        <v>0</v>
       </c>
       <c r="BZ137" s="1">
         <v>4</v>
       </c>
-      <c r="CB137" s="1">
-        <v>0</v>
-      </c>
-      <c r="CP137" s="1">
+      <c r="CC137" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ137" s="1">
         <v>0</v>
       </c>
       <c r="DS137" s="1">
@@ -14299,6 +14380,9 @@
       <c r="A138" s="1">
         <v>0</v>
       </c>
+      <c r="X138" s="3">
+        <v>0</v>
+      </c>
       <c r="Y138" s="3">
         <v>0</v>
       </c>
@@ -14356,25 +14440,22 @@
       <c r="AQ138" s="3">
         <v>0</v>
       </c>
-      <c r="AR138" s="3">
-        <v>0</v>
-      </c>
       <c r="AX138" s="1">
         <v>0</v>
       </c>
-      <c r="BD138" s="1">
-        <v>0</v>
-      </c>
-      <c r="BH138" s="1">
+      <c r="BB138" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ138" s="1">
         <v>0</v>
       </c>
       <c r="BZ138" s="1">
         <v>0</v>
       </c>
-      <c r="CA138" s="1">
+      <c r="CB138" s="1">
         <v>5</v>
       </c>
-      <c r="CO138" s="1">
+      <c r="CP138" s="1">
         <v>0</v>
       </c>
       <c r="DS138" s="1">
@@ -14394,19 +14475,19 @@
       <c r="AX139" s="1">
         <v>4</v>
       </c>
-      <c r="BE139" s="1">
-        <v>0</v>
-      </c>
-      <c r="BF139" s="1">
-        <v>3</v>
-      </c>
-      <c r="BG139" s="1">
-        <v>0</v>
+      <c r="BC139" s="1">
+        <v>6</v>
+      </c>
+      <c r="BI139" s="1">
+        <v>5</v>
       </c>
       <c r="BZ139" s="1">
         <v>0</v>
       </c>
-      <c r="CN139" s="1">
+      <c r="CA139" s="1">
+        <v>0</v>
+      </c>
+      <c r="CO139" s="1">
         <v>5</v>
       </c>
       <c r="DS139" s="1">
@@ -14426,58 +14507,31 @@
       <c r="AX140" s="1">
         <v>0</v>
       </c>
-      <c r="BO140" s="1">
-        <v>0</v>
-      </c>
-      <c r="BP140" s="1">
-        <v>3</v>
-      </c>
-      <c r="BQ140" s="1">
-        <v>0</v>
-      </c>
-      <c r="BR140" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS140" s="1">
-        <v>3</v>
-      </c>
-      <c r="BT140" s="1">
-        <v>0</v>
-      </c>
-      <c r="BU140" s="1">
-        <v>0</v>
-      </c>
-      <c r="BV140" s="1">
-        <v>3</v>
-      </c>
-      <c r="BW140" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX140" s="1">
-        <v>0</v>
-      </c>
-      <c r="BY140" s="1">
-        <v>3</v>
+      <c r="BD140" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH140" s="1">
+        <v>0</v>
       </c>
       <c r="BZ140" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM140" s="1">
-        <v>0</v>
-      </c>
-      <c r="CV140" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW140" s="4">
-        <v>0</v>
-      </c>
-      <c r="CX140" s="4">
+        <v>4</v>
+      </c>
+      <c r="CN140" s="1">
         <v>0</v>
       </c>
       <c r="CY140" s="4">
         <v>0</v>
       </c>
       <c r="CZ140" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA140" s="4">
+        <v>0</v>
+      </c>
+      <c r="DB140" s="4">
+        <v>0</v>
+      </c>
+      <c r="DC140" s="4">
         <v>0</v>
       </c>
       <c r="DS140" s="1">
@@ -14497,22 +14551,34 @@
       <c r="AX141" s="1">
         <v>0</v>
       </c>
-      <c r="CL141" s="1">
-        <v>0</v>
-      </c>
-      <c r="CV141" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW141" s="4">
-        <v>0</v>
-      </c>
-      <c r="CX141" s="4">
+      <c r="BE141" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF141" s="1">
+        <v>3</v>
+      </c>
+      <c r="BG141" s="1">
+        <v>0</v>
+      </c>
+      <c r="BZ141" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM141" s="1">
         <v>0</v>
       </c>
       <c r="CY141" s="4">
         <v>0</v>
       </c>
       <c r="CZ141" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA141" s="4">
+        <v>0</v>
+      </c>
+      <c r="DB141" s="4">
+        <v>0</v>
+      </c>
+      <c r="DC141" s="4">
         <v>0</v>
       </c>
       <c r="DS141" s="1">
@@ -14532,31 +14598,58 @@
       <c r="AX142" s="1">
         <v>4</v>
       </c>
-      <c r="CK142" s="1">
+      <c r="BO142" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP142" s="1">
+        <v>3</v>
+      </c>
+      <c r="BQ142" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR142" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS142" s="1">
+        <v>3</v>
+      </c>
+      <c r="BT142" s="1">
+        <v>0</v>
+      </c>
+      <c r="BU142" s="1">
+        <v>0</v>
+      </c>
+      <c r="BV142" s="1">
+        <v>3</v>
+      </c>
+      <c r="BW142" s="1">
+        <v>0</v>
+      </c>
+      <c r="BX142" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY142" s="1">
+        <v>3</v>
+      </c>
+      <c r="BZ142" s="1">
+        <v>0</v>
+      </c>
+      <c r="CL142" s="1">
         <v>5</v>
       </c>
-      <c r="CV142" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW142" s="4">
-        <v>0</v>
-      </c>
-      <c r="CX142" s="4">
+      <c r="CY142" s="4">
+        <v>0</v>
+      </c>
+      <c r="CZ142" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA142" s="4">
         <v>11</v>
       </c>
-      <c r="CY142" s="4">
-        <v>0</v>
-      </c>
-      <c r="CZ142" s="4">
-        <v>0</v>
-      </c>
-      <c r="DA142" s="1">
-        <v>0</v>
-      </c>
-      <c r="DB142" s="1">
-        <v>3</v>
-      </c>
-      <c r="DC142" s="1">
+      <c r="DB142" s="4">
+        <v>0</v>
+      </c>
+      <c r="DC142" s="4">
         <v>0</v>
       </c>
       <c r="DD142" s="1">
@@ -14621,22 +14714,22 @@
       <c r="AX143" s="1">
         <v>0</v>
       </c>
-      <c r="CJ143" s="1">
-        <v>0</v>
-      </c>
-      <c r="CV143" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW143" s="4">
-        <v>0</v>
-      </c>
-      <c r="CX143" s="4">
+      <c r="CK143" s="1">
         <v>0</v>
       </c>
       <c r="CY143" s="4">
         <v>0</v>
       </c>
       <c r="CZ143" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA143" s="4">
+        <v>0</v>
+      </c>
+      <c r="DB143" s="4">
+        <v>0</v>
+      </c>
+      <c r="DC143" s="4">
         <v>0</v>
       </c>
       <c r="DY143" s="1">
@@ -14653,22 +14746,22 @@
       <c r="AX144" s="1">
         <v>0</v>
       </c>
-      <c r="CI144" s="1">
-        <v>0</v>
-      </c>
-      <c r="CV144" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW144" s="4">
-        <v>0</v>
-      </c>
-      <c r="CX144" s="4">
+      <c r="CJ144" s="1">
         <v>0</v>
       </c>
       <c r="CY144" s="4">
         <v>0</v>
       </c>
       <c r="CZ144" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA144" s="4">
+        <v>0</v>
+      </c>
+      <c r="DB144" s="4">
+        <v>0</v>
+      </c>
+      <c r="DC144" s="4">
         <v>0</v>
       </c>
       <c r="DY144" s="1">
@@ -14685,7 +14778,7 @@
       <c r="AX145" s="1">
         <v>4</v>
       </c>
-      <c r="CH145" s="1">
+      <c r="CI145" s="1">
         <v>5</v>
       </c>
       <c r="DY145" s="1">
@@ -14702,7 +14795,7 @@
       <c r="AX146" s="1">
         <v>0</v>
       </c>
-      <c r="CG146" s="1">
+      <c r="CH146" s="1">
         <v>0</v>
       </c>
       <c r="DY146" s="1">
@@ -14719,7 +14812,7 @@
       <c r="AX147" s="1">
         <v>0</v>
       </c>
-      <c r="CF147" s="1">
+      <c r="CG147" s="1">
         <v>0</v>
       </c>
       <c r="DY147" s="1">
@@ -14736,7 +14829,7 @@
       <c r="AX148" s="1">
         <v>4</v>
       </c>
-      <c r="CE148" s="1">
+      <c r="CF148" s="1">
         <v>5</v>
       </c>
       <c r="DY148" s="1">
@@ -14753,7 +14846,7 @@
       <c r="AX149" s="1">
         <v>0</v>
       </c>
-      <c r="CD149" s="1">
+      <c r="CE149" s="1">
         <v>0</v>
       </c>
       <c r="DY149" s="1">

--- a/media/Levels/Level_5.xlsx
+++ b/media/Levels/Level_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194210FC-CCB8-4C34-ACAC-F27038DCC71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839E50B8-4C55-4AB0-A2D9-CCA828533DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3672" yWindow="84" windowWidth="13836" windowHeight="12156" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -914,7 +914,7 @@
       <c r="E2" s="1">
         <v>5</v>
       </c>
-      <c r="AB2" s="1">
+      <c r="AI2" s="1">
         <v>0</v>
       </c>
       <c r="BN2" s="1">
@@ -934,8 +934,8 @@
       <c r="D3" s="1">
         <v>0</v>
       </c>
-      <c r="AC3" s="1">
-        <v>6</v>
+      <c r="AI3" s="1">
+        <v>4</v>
       </c>
       <c r="BN3" s="1">
         <v>4</v>
@@ -954,7 +954,7 @@
       <c r="C4" s="1">
         <v>0</v>
       </c>
-      <c r="AD4" s="1">
+      <c r="AI4" s="1">
         <v>0</v>
       </c>
       <c r="BN4" s="1">
@@ -974,8 +974,8 @@
       <c r="B5" s="1">
         <v>5</v>
       </c>
-      <c r="AE5" s="1">
-        <v>6</v>
+      <c r="AI5" s="1">
+        <v>0</v>
       </c>
       <c r="BN5" s="1">
         <v>0</v>
@@ -994,8 +994,8 @@
       <c r="A6" s="1">
         <v>0</v>
       </c>
-      <c r="AF6" s="1">
-        <v>0</v>
+      <c r="AI6" s="1">
+        <v>4</v>
       </c>
       <c r="BN6" s="1">
         <v>4</v>
@@ -1029,7 +1029,7 @@
       <c r="A7" s="1">
         <v>0</v>
       </c>
-      <c r="AG7" s="1">
+      <c r="AI7" s="1">
         <v>0</v>
       </c>
       <c r="BN7" s="1">
@@ -1064,8 +1064,8 @@
       <c r="A8" s="1">
         <v>0</v>
       </c>
-      <c r="AH8" s="1">
-        <v>6</v>
+      <c r="AI8" s="1">
+        <v>0</v>
       </c>
       <c r="BN8" s="1">
         <v>0</v>
@@ -1103,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BN9" s="1">
         <v>4</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BN11" s="1">
         <v>0</v>
@@ -1202,7 +1202,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AP12" s="3">
         <v>0</v>
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AP14" s="3">
         <v>0</v>
@@ -1523,7 +1523,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AP15" s="3">
         <v>0</v>
@@ -1833,7 +1833,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AP17" s="3">
         <v>0</v>
@@ -1893,6 +1893,9 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3">
+        <v>0</v>
+      </c>
+      <c r="BN17" s="1">
         <v>0</v>
       </c>
       <c r="BT17" s="4">
@@ -2027,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AP18" s="3">
         <v>0</v>
@@ -2088,6 +2091,9 @@
       </c>
       <c r="BI18" s="3">
         <v>0</v>
+      </c>
+      <c r="BN18" s="1">
+        <v>4</v>
       </c>
       <c r="BT18" s="4">
         <v>0</v>
@@ -2289,6 +2295,9 @@
       <c r="BI19" s="3">
         <v>0</v>
       </c>
+      <c r="BN19" s="1">
+        <v>0</v>
+      </c>
       <c r="BT19" s="4">
         <v>0</v>
       </c>
@@ -2424,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AP20" s="3">
         <v>0</v>
@@ -2609,7 +2618,7 @@
         <v>4</v>
       </c>
       <c r="AI21" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AP21" s="3">
         <v>0</v>
@@ -2811,6 +2820,15 @@
       <c r="AI22" s="1">
         <v>0</v>
       </c>
+      <c r="AM22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="1">
+        <v>3</v>
+      </c>
+      <c r="AO22" s="1">
+        <v>0</v>
+      </c>
       <c r="AP22" s="3">
         <v>0</v>
       </c>
@@ -2978,9 +2996,6 @@
       <c r="Y23" s="1">
         <v>0</v>
       </c>
-      <c r="AI23" s="1">
-        <v>4</v>
-      </c>
       <c r="AP23" s="3">
         <v>0</v>
       </c>
@@ -3133,9 +3148,6 @@
       <c r="Y24" s="1">
         <v>4</v>
       </c>
-      <c r="AI24" s="1">
-        <v>0</v>
-      </c>
       <c r="AP24" s="3">
         <v>0</v>
       </c>
@@ -3315,9 +3327,6 @@
       <c r="Y25" s="1">
         <v>0</v>
       </c>
-      <c r="AI25" s="1">
-        <v>0</v>
-      </c>
       <c r="AP25" s="3">
         <v>0</v>
       </c>
@@ -3497,9 +3506,6 @@
       <c r="AA26" s="4">
         <v>0</v>
       </c>
-      <c r="AI26" s="1">
-        <v>4</v>
-      </c>
       <c r="AP26" s="3">
         <v>0</v>
       </c>
@@ -3676,9 +3682,6 @@
       <c r="AA27" s="4">
         <v>0</v>
       </c>
-      <c r="AI27" s="1">
-        <v>0</v>
-      </c>
       <c r="AP27" s="3">
         <v>0</v>
       </c>
@@ -3846,9 +3849,6 @@
       <c r="AA28" s="4">
         <v>0</v>
       </c>
-      <c r="AI28" s="1">
-        <v>0</v>
-      </c>
       <c r="AP28" s="3">
         <v>0</v>
       </c>
@@ -4025,9 +4025,6 @@
       <c r="AA29" s="4">
         <v>0</v>
       </c>
-      <c r="AI29" s="1">
-        <v>4</v>
-      </c>
       <c r="AP29" s="3">
         <v>0</v>
       </c>
@@ -4192,18 +4189,6 @@
       <c r="AA30" s="4">
         <v>0</v>
       </c>
-      <c r="AI30" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM30" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN30" s="1">
-        <v>3</v>
-      </c>
-      <c r="AO30" s="1">
-        <v>0</v>
-      </c>
       <c r="AP30" s="3">
         <v>0</v>
       </c>
@@ -4502,7 +4487,7 @@
       <c r="A32" s="1">
         <v>0</v>
       </c>
-      <c r="BF32" s="1">
+      <c r="BC32" s="1">
         <v>0</v>
       </c>
       <c r="BN32" s="1">
@@ -4597,7 +4582,7 @@
       <c r="A33" s="1">
         <v>0</v>
       </c>
-      <c r="BF33" s="1">
+      <c r="BC33" s="1">
         <v>4</v>
       </c>
       <c r="BN33" s="1">
@@ -4707,7 +4692,7 @@
       <c r="A34" s="1">
         <v>0</v>
       </c>
-      <c r="BF34" s="1">
+      <c r="BC34" s="1">
         <v>0</v>
       </c>
       <c r="BN34" s="1">
@@ -4757,7 +4742,7 @@
       <c r="A35" s="1">
         <v>0</v>
       </c>
-      <c r="BF35" s="1">
+      <c r="BC35" s="1">
         <v>0</v>
       </c>
       <c r="BN35" s="1">
@@ -4795,7 +4780,7 @@
       <c r="A36" s="1">
         <v>0</v>
       </c>
-      <c r="BF36" s="1">
+      <c r="BC36" s="1">
         <v>4</v>
       </c>
       <c r="BN36" s="1">
@@ -4833,7 +4818,7 @@
       <c r="A37" s="1">
         <v>0</v>
       </c>
-      <c r="BF37" s="1">
+      <c r="BC37" s="1">
         <v>0</v>
       </c>
       <c r="BN37" s="1">
@@ -4871,7 +4856,7 @@
       <c r="A38" s="1">
         <v>0</v>
       </c>
-      <c r="BF38" s="1">
+      <c r="BC38" s="1">
         <v>0</v>
       </c>
       <c r="BN38" s="1">
@@ -4909,7 +4894,7 @@
       <c r="A39" s="1">
         <v>0</v>
       </c>
-      <c r="BF39" s="1">
+      <c r="BC39" s="1">
         <v>4</v>
       </c>
       <c r="BN39" s="1">
@@ -4947,7 +4932,7 @@
       <c r="A40" s="1">
         <v>0</v>
       </c>
-      <c r="BF40" s="1">
+      <c r="BC40" s="1">
         <v>0</v>
       </c>
       <c r="BN40" s="1">
@@ -4985,7 +4970,7 @@
       <c r="A41" s="1">
         <v>0</v>
       </c>
-      <c r="BF41" s="1">
+      <c r="BC41" s="1">
         <v>0</v>
       </c>
       <c r="BN41" s="1">
@@ -5023,7 +5008,7 @@
       <c r="A42" s="1">
         <v>0</v>
       </c>
-      <c r="BF42" s="1">
+      <c r="BC42" s="1">
         <v>4</v>
       </c>
       <c r="BN42" s="1">
@@ -5061,7 +5046,7 @@
       <c r="A43" s="1">
         <v>0</v>
       </c>
-      <c r="BF43" s="1">
+      <c r="BC43" s="1">
         <v>0</v>
       </c>
       <c r="BN43" s="1">
@@ -5138,13 +5123,13 @@
       <c r="AX44" s="1">
         <v>0</v>
       </c>
-      <c r="AY44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AZ44" s="1">
-        <v>3</v>
-      </c>
-      <c r="BA44" s="1">
+      <c r="BB44" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC44" s="1">
+        <v>3</v>
+      </c>
+      <c r="BD44" s="1">
         <v>0</v>
       </c>
       <c r="BE44" s="1">
@@ -5199,6 +5184,15 @@
         <v>3</v>
       </c>
       <c r="BV44" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW44" s="5">
+        <v>0</v>
+      </c>
+      <c r="BX44" s="5">
+        <v>7</v>
+      </c>
+      <c r="BY44" s="5">
         <v>0</v>
       </c>
       <c r="BZ44" s="1">

--- a/media/Levels/Level_5.xlsx
+++ b/media/Levels/Level_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839E50B8-4C55-4AB0-A2D9-CCA828533DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A99F0A-9021-4174-815E-BB3667F9CBC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3672" yWindow="84" windowWidth="13836" windowHeight="12156" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -917,7 +917,7 @@
       <c r="AI2" s="1">
         <v>0</v>
       </c>
-      <c r="BN2" s="1">
+      <c r="BQ2" s="1">
         <v>0</v>
       </c>
       <c r="CY2" s="1">
@@ -937,7 +937,7 @@
       <c r="AI3" s="1">
         <v>4</v>
       </c>
-      <c r="BN3" s="1">
+      <c r="BQ3" s="1">
         <v>4</v>
       </c>
       <c r="CY3" s="1">
@@ -957,7 +957,7 @@
       <c r="AI4" s="1">
         <v>0</v>
       </c>
-      <c r="BN4" s="1">
+      <c r="BQ4" s="1">
         <v>0</v>
       </c>
       <c r="CY4" s="1">
@@ -977,7 +977,7 @@
       <c r="AI5" s="1">
         <v>0</v>
       </c>
-      <c r="BN5" s="1">
+      <c r="BQ5" s="1">
         <v>0</v>
       </c>
       <c r="CY5" s="1">
@@ -997,7 +997,7 @@
       <c r="AI6" s="1">
         <v>4</v>
       </c>
-      <c r="BN6" s="1">
+      <c r="BQ6" s="1">
         <v>4</v>
       </c>
       <c r="CY6" s="1">
@@ -1032,7 +1032,7 @@
       <c r="AI7" s="1">
         <v>0</v>
       </c>
-      <c r="BN7" s="1">
+      <c r="BQ7" s="1">
         <v>0</v>
       </c>
       <c r="CY7" s="1">
@@ -1067,7 +1067,7 @@
       <c r="AI8" s="1">
         <v>0</v>
       </c>
-      <c r="BN8" s="1">
+      <c r="BQ8" s="1">
         <v>0</v>
       </c>
       <c r="CY8" s="1">
@@ -1105,7 +1105,7 @@
       <c r="AI9" s="1">
         <v>4</v>
       </c>
-      <c r="BN9" s="1">
+      <c r="BQ9" s="1">
         <v>4</v>
       </c>
       <c r="CY9" s="1">
@@ -1143,7 +1143,7 @@
       <c r="AI10" s="1">
         <v>0</v>
       </c>
-      <c r="BN10" s="1">
+      <c r="BQ10" s="1">
         <v>0</v>
       </c>
       <c r="CY10" s="1">
@@ -1181,7 +1181,7 @@
       <c r="AI11" s="1">
         <v>0</v>
       </c>
-      <c r="BN11" s="1">
+      <c r="BQ11" s="1">
         <v>0</v>
       </c>
       <c r="CY11" s="1">
@@ -1264,7 +1264,7 @@
       <c r="BI12" s="3">
         <v>0</v>
       </c>
-      <c r="BN12" s="1">
+      <c r="BQ12" s="1">
         <v>4</v>
       </c>
       <c r="CY12" s="1">
@@ -1347,7 +1347,7 @@
       <c r="BI13" s="3">
         <v>0</v>
       </c>
-      <c r="BN13" s="1">
+      <c r="BQ13" s="1">
         <v>0</v>
       </c>
       <c r="CY13" s="1">
@@ -1430,7 +1430,7 @@
       <c r="BI14" s="3">
         <v>0</v>
       </c>
-      <c r="BN14" s="1">
+      <c r="BQ14" s="1">
         <v>0</v>
       </c>
       <c r="CO14" s="3">
@@ -1585,7 +1585,7 @@
       <c r="BI15" s="3">
         <v>0</v>
       </c>
-      <c r="BN15" s="1">
+      <c r="BQ15" s="1">
         <v>4</v>
       </c>
       <c r="CO15" s="3">
@@ -1740,7 +1740,7 @@
       <c r="BI16" s="3">
         <v>0</v>
       </c>
-      <c r="BN16" s="1">
+      <c r="BQ16" s="1">
         <v>0</v>
       </c>
       <c r="CO16" s="3">
@@ -1895,22 +1895,7 @@
       <c r="BI17" s="3">
         <v>0</v>
       </c>
-      <c r="BN17" s="1">
-        <v>0</v>
-      </c>
-      <c r="BT17" s="4">
-        <v>0</v>
-      </c>
-      <c r="BU17" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV17" s="4">
-        <v>0</v>
-      </c>
-      <c r="BW17" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX17" s="4">
+      <c r="BQ17" s="1">
         <v>0</v>
       </c>
       <c r="CO17" s="3">
@@ -2092,11 +2077,8 @@
       <c r="BI18" s="3">
         <v>0</v>
       </c>
-      <c r="BN18" s="1">
-        <v>4</v>
-      </c>
-      <c r="BT18" s="4">
-        <v>0</v>
+      <c r="BQ18" s="1">
+        <v>4</v>
       </c>
       <c r="BU18" s="4">
         <v>0</v>
@@ -2108,6 +2090,9 @@
         <v>0</v>
       </c>
       <c r="BX18" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY18" s="4">
         <v>0</v>
       </c>
       <c r="CO18" s="3">
@@ -2295,22 +2280,22 @@
       <c r="BI19" s="3">
         <v>0</v>
       </c>
-      <c r="BN19" s="1">
-        <v>0</v>
-      </c>
-      <c r="BT19" s="4">
+      <c r="BQ19" s="1">
         <v>0</v>
       </c>
       <c r="BU19" s="4">
         <v>0</v>
       </c>
       <c r="BV19" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BW19" s="4">
         <v>0</v>
       </c>
       <c r="BX19" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY19" s="4">
         <v>0</v>
       </c>
       <c r="CO19" s="3">
@@ -2495,9 +2480,6 @@
       <c r="BI20" s="3">
         <v>0</v>
       </c>
-      <c r="BT20" s="4">
-        <v>0</v>
-      </c>
       <c r="BU20" s="4">
         <v>0</v>
       </c>
@@ -2505,9 +2487,12 @@
         <v>0</v>
       </c>
       <c r="BW20" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BX20" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY20" s="4">
         <v>0</v>
       </c>
       <c r="CO20" s="3">
@@ -2680,9 +2665,6 @@
       <c r="BI21" s="3">
         <v>0</v>
       </c>
-      <c r="BT21" s="4">
-        <v>0</v>
-      </c>
       <c r="BU21" s="4">
         <v>0</v>
       </c>
@@ -2693,6 +2675,9 @@
         <v>0</v>
       </c>
       <c r="BX21" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY21" s="4">
         <v>0</v>
       </c>
       <c r="CO21" s="3">
@@ -2889,6 +2874,21 @@
       <c r="BI22" s="3">
         <v>0</v>
       </c>
+      <c r="BU22" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV22" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW22" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX22" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY22" s="4">
+        <v>0</v>
+      </c>
       <c r="CO22" s="3">
         <v>0</v>
       </c>
@@ -3566,7 +3566,7 @@
       <c r="BI26" s="3">
         <v>0</v>
       </c>
-      <c r="BN26" s="1">
+      <c r="BQ26" s="1">
         <v>0</v>
       </c>
       <c r="CO26" s="3">
@@ -3742,7 +3742,7 @@
       <c r="BI27" s="3">
         <v>0</v>
       </c>
-      <c r="BN27" s="1">
+      <c r="BQ27" s="1">
         <v>4</v>
       </c>
       <c r="CO27" s="3">
@@ -3909,7 +3909,7 @@
       <c r="BI28" s="3">
         <v>0</v>
       </c>
-      <c r="BN28" s="1">
+      <c r="BQ28" s="1">
         <v>0</v>
       </c>
       <c r="CO28" s="3">
@@ -4085,7 +4085,7 @@
       <c r="BI29" s="3">
         <v>0</v>
       </c>
-      <c r="BN29" s="1">
+      <c r="BQ29" s="1">
         <v>0</v>
       </c>
       <c r="CO29" s="3">
@@ -4249,7 +4249,7 @@
       <c r="BI30" s="3">
         <v>0</v>
       </c>
-      <c r="BN30" s="1">
+      <c r="BQ30" s="1">
         <v>4</v>
       </c>
       <c r="CD30" s="4">
@@ -4398,7 +4398,7 @@
       <c r="BI31" s="3">
         <v>0</v>
       </c>
-      <c r="BN31" s="1">
+      <c r="BQ31" s="1">
         <v>0</v>
       </c>
       <c r="CD31" s="4">
@@ -4490,7 +4490,7 @@
       <c r="BC32" s="1">
         <v>0</v>
       </c>
-      <c r="BN32" s="1">
+      <c r="BQ32" s="1">
         <v>0</v>
       </c>
       <c r="CD32" s="4">
@@ -4585,7 +4585,7 @@
       <c r="BC33" s="1">
         <v>4</v>
       </c>
-      <c r="BN33" s="1">
+      <c r="BQ33" s="1">
         <v>4</v>
       </c>
       <c r="CD33" s="4">
@@ -4695,7 +4695,7 @@
       <c r="BC34" s="1">
         <v>0</v>
       </c>
-      <c r="BN34" s="1">
+      <c r="BQ34" s="1">
         <v>0</v>
       </c>
       <c r="CD34" s="4">
@@ -4745,7 +4745,7 @@
       <c r="BC35" s="1">
         <v>0</v>
       </c>
-      <c r="BN35" s="1">
+      <c r="BQ35" s="1">
         <v>0</v>
       </c>
       <c r="CF35" s="1">
@@ -4783,7 +4783,7 @@
       <c r="BC36" s="1">
         <v>4</v>
       </c>
-      <c r="BN36" s="1">
+      <c r="BQ36" s="1">
         <v>4</v>
       </c>
       <c r="CF36" s="1">
@@ -4821,7 +4821,7 @@
       <c r="BC37" s="1">
         <v>0</v>
       </c>
-      <c r="BN37" s="1">
+      <c r="BQ37" s="1">
         <v>0</v>
       </c>
       <c r="CF37" s="1">
@@ -4859,7 +4859,7 @@
       <c r="BC38" s="1">
         <v>0</v>
       </c>
-      <c r="BN38" s="1">
+      <c r="BQ38" s="1">
         <v>0</v>
       </c>
       <c r="CE38" s="1">
@@ -4897,7 +4897,7 @@
       <c r="BC39" s="1">
         <v>4</v>
       </c>
-      <c r="BN39" s="1">
+      <c r="BQ39" s="1">
         <v>4</v>
       </c>
       <c r="CD39" s="1">
@@ -4935,7 +4935,7 @@
       <c r="BC40" s="1">
         <v>0</v>
       </c>
-      <c r="BN40" s="1">
+      <c r="BQ40" s="1">
         <v>0</v>
       </c>
       <c r="CC40" s="1">
@@ -4973,7 +4973,7 @@
       <c r="BC41" s="1">
         <v>0</v>
       </c>
-      <c r="BN41" s="1">
+      <c r="BQ41" s="1">
         <v>0</v>
       </c>
       <c r="CB41" s="1">
@@ -5011,7 +5011,7 @@
       <c r="BC42" s="1">
         <v>4</v>
       </c>
-      <c r="BN42" s="1">
+      <c r="BQ42" s="1">
         <v>4</v>
       </c>
       <c r="CA42" s="1">
@@ -5049,7 +5049,7 @@
       <c r="BC43" s="1">
         <v>0</v>
       </c>
-      <c r="BN43" s="1">
+      <c r="BQ43" s="1">
         <v>0</v>
       </c>
       <c r="BZ43" s="1">
@@ -5150,13 +5150,13 @@
       <c r="BJ44" s="1">
         <v>0</v>
       </c>
-      <c r="BK44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BL44" s="1">
-        <v>3</v>
-      </c>
-      <c r="BM44" s="1">
+      <c r="BK44" s="5">
+        <v>0</v>
+      </c>
+      <c r="BL44" s="5">
+        <v>7</v>
+      </c>
+      <c r="BM44" s="5">
         <v>0</v>
       </c>
       <c r="BN44" s="1">
@@ -5350,7 +5350,7 @@
       <c r="AG45" s="1">
         <v>0</v>
       </c>
-      <c r="BK45" s="1">
+      <c r="BN45" s="1">
         <v>0</v>
       </c>
       <c r="DY45" s="1">
@@ -5367,7 +5367,7 @@
       <c r="AG46" s="1">
         <v>4</v>
       </c>
-      <c r="BK46" s="1">
+      <c r="BN46" s="1">
         <v>4</v>
       </c>
       <c r="DY46" s="1">
@@ -5444,7 +5444,7 @@
       <c r="AG47" s="1">
         <v>0</v>
       </c>
-      <c r="BK47" s="1">
+      <c r="BN47" s="1">
         <v>0</v>
       </c>
       <c r="DY47" s="1">
@@ -5521,7 +5521,7 @@
       <c r="AG48" s="1">
         <v>0</v>
       </c>
-      <c r="BK48" s="1">
+      <c r="BN48" s="1">
         <v>0</v>
       </c>
       <c r="DY48" s="1">
@@ -5598,7 +5598,7 @@
       <c r="AG49" s="1">
         <v>4</v>
       </c>
-      <c r="BK49" s="1">
+      <c r="BN49" s="1">
         <v>4</v>
       </c>
       <c r="DY49" s="1">
@@ -5675,7 +5675,7 @@
       <c r="AG50" s="1">
         <v>0</v>
       </c>
-      <c r="BK50" s="1">
+      <c r="BN50" s="1">
         <v>0</v>
       </c>
       <c r="DY50" s="1">
@@ -5752,7 +5752,7 @@
       <c r="AG51" s="1">
         <v>0</v>
       </c>
-      <c r="BK51" s="1">
+      <c r="BN51" s="1">
         <v>0</v>
       </c>
       <c r="DY51" s="1">
@@ -5829,26 +5829,11 @@
       <c r="AG52" s="1">
         <v>4</v>
       </c>
-      <c r="BK52" s="1">
+      <c r="BN52" s="1">
         <v>4</v>
       </c>
       <c r="DY52" s="1">
         <v>4</v>
-      </c>
-      <c r="EF52" s="4">
-        <v>0</v>
-      </c>
-      <c r="EG52" s="4">
-        <v>0</v>
-      </c>
-      <c r="EH52" s="4">
-        <v>0</v>
-      </c>
-      <c r="EI52" s="4">
-        <v>0</v>
-      </c>
-      <c r="EJ52" s="4">
-        <v>0</v>
       </c>
       <c r="ET52" s="1">
         <v>0</v>
@@ -5921,25 +5906,10 @@
       <c r="AG53" s="1">
         <v>0</v>
       </c>
-      <c r="BK53" s="1">
+      <c r="BN53" s="1">
         <v>0</v>
       </c>
       <c r="DY53" s="1">
-        <v>0</v>
-      </c>
-      <c r="EF53" s="4">
-        <v>0</v>
-      </c>
-      <c r="EG53" s="4">
-        <v>0</v>
-      </c>
-      <c r="EH53" s="4">
-        <v>0</v>
-      </c>
-      <c r="EI53" s="4">
-        <v>0</v>
-      </c>
-      <c r="EJ53" s="4">
         <v>0</v>
       </c>
       <c r="ET53" s="1">
@@ -6013,25 +5983,10 @@
       <c r="AG54" s="1">
         <v>0</v>
       </c>
-      <c r="BK54" s="1">
+      <c r="BN54" s="1">
         <v>0</v>
       </c>
       <c r="DY54" s="1">
-        <v>0</v>
-      </c>
-      <c r="EF54" s="4">
-        <v>0</v>
-      </c>
-      <c r="EG54" s="4">
-        <v>0</v>
-      </c>
-      <c r="EH54" s="4">
-        <v>11</v>
-      </c>
-      <c r="EI54" s="4">
-        <v>0</v>
-      </c>
-      <c r="EJ54" s="4">
         <v>0</v>
       </c>
       <c r="ET54" s="1">
@@ -6105,26 +6060,11 @@
       <c r="AG55" s="1">
         <v>4</v>
       </c>
-      <c r="BK55" s="1">
+      <c r="BN55" s="1">
         <v>4</v>
       </c>
       <c r="DY55" s="1">
         <v>4</v>
-      </c>
-      <c r="EF55" s="4">
-        <v>0</v>
-      </c>
-      <c r="EG55" s="4">
-        <v>0</v>
-      </c>
-      <c r="EH55" s="4">
-        <v>0</v>
-      </c>
-      <c r="EI55" s="4">
-        <v>0</v>
-      </c>
-      <c r="EJ55" s="4">
-        <v>0</v>
       </c>
       <c r="ET55" s="1">
         <v>0</v>
@@ -6197,25 +6137,10 @@
       <c r="AG56" s="1">
         <v>0</v>
       </c>
-      <c r="BK56" s="1">
+      <c r="BN56" s="1">
         <v>0</v>
       </c>
       <c r="DY56" s="1">
-        <v>0</v>
-      </c>
-      <c r="EF56" s="4">
-        <v>0</v>
-      </c>
-      <c r="EG56" s="4">
-        <v>0</v>
-      </c>
-      <c r="EH56" s="4">
-        <v>0</v>
-      </c>
-      <c r="EI56" s="4">
-        <v>0</v>
-      </c>
-      <c r="EJ56" s="4">
         <v>0</v>
       </c>
       <c r="ET56" s="1">
@@ -6322,10 +6247,25 @@
       <c r="AR57" s="4">
         <v>0</v>
       </c>
-      <c r="BK57" s="1">
+      <c r="BN57" s="1">
         <v>0</v>
       </c>
       <c r="DY57" s="1">
+        <v>0</v>
+      </c>
+      <c r="EJ57" s="4">
+        <v>0</v>
+      </c>
+      <c r="EK57" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL57" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM57" s="4">
+        <v>0</v>
+      </c>
+      <c r="EN57" s="4">
         <v>0</v>
       </c>
       <c r="ET57" s="1">
@@ -6414,17 +6354,8 @@
       <c r="AR58" s="4">
         <v>0</v>
       </c>
-      <c r="BK58" s="1">
-        <v>4</v>
-      </c>
-      <c r="BL58" s="1">
-        <v>0</v>
-      </c>
-      <c r="BM58" s="1">
-        <v>3</v>
-      </c>
       <c r="BN58" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BO58" s="1">
         <v>0</v>
@@ -6599,6 +6530,21 @@
       </c>
       <c r="DY58" s="1">
         <v>4</v>
+      </c>
+      <c r="EJ58" s="4">
+        <v>0</v>
+      </c>
+      <c r="EK58" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL58" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM58" s="4">
+        <v>0</v>
+      </c>
+      <c r="EN58" s="4">
+        <v>0</v>
       </c>
       <c r="ET58" s="1">
         <v>0</v>
@@ -6743,6 +6689,15 @@
       <c r="BK59" s="1">
         <v>0</v>
       </c>
+      <c r="BL59" s="1">
+        <v>3</v>
+      </c>
+      <c r="BM59" s="1">
+        <v>0</v>
+      </c>
+      <c r="BN59" s="1">
+        <v>0</v>
+      </c>
       <c r="DM59" s="1">
         <v>0</v>
       </c>
@@ -6750,6 +6705,21 @@
         <v>0</v>
       </c>
       <c r="DY59" s="1">
+        <v>0</v>
+      </c>
+      <c r="EJ59" s="4">
+        <v>0</v>
+      </c>
+      <c r="EK59" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL59" s="4">
+        <v>11</v>
+      </c>
+      <c r="EM59" s="4">
+        <v>0</v>
+      </c>
+      <c r="EN59" s="4">
         <v>0</v>
       </c>
       <c r="ET59" s="1">
@@ -6838,7 +6808,7 @@
       <c r="AR60" s="4">
         <v>0</v>
       </c>
-      <c r="BJ60" s="1">
+      <c r="BI60" s="1">
         <v>0</v>
       </c>
       <c r="DM60" s="1">
@@ -6848,6 +6818,21 @@
         <v>4</v>
       </c>
       <c r="DY60" s="1">
+        <v>0</v>
+      </c>
+      <c r="EJ60" s="4">
+        <v>0</v>
+      </c>
+      <c r="EK60" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL60" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM60" s="4">
+        <v>0</v>
+      </c>
+      <c r="EN60" s="4">
         <v>0</v>
       </c>
       <c r="ET60" s="1">
@@ -6936,7 +6921,7 @@
       <c r="AR61" s="4">
         <v>0</v>
       </c>
-      <c r="BJ61" s="1">
+      <c r="BI61" s="1">
         <v>4</v>
       </c>
       <c r="DM61" s="1">
@@ -6947,6 +6932,21 @@
       </c>
       <c r="DY61" s="1">
         <v>4</v>
+      </c>
+      <c r="EJ61" s="4">
+        <v>0</v>
+      </c>
+      <c r="EK61" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL61" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM61" s="4">
+        <v>0</v>
+      </c>
+      <c r="EN61" s="4">
+        <v>0</v>
       </c>
       <c r="ET61" s="1">
         <v>0</v>
@@ -7019,7 +7019,7 @@
       <c r="AG62" s="1">
         <v>0</v>
       </c>
-      <c r="BJ62" s="1">
+      <c r="BI62" s="1">
         <v>0</v>
       </c>
       <c r="DM62" s="1">
@@ -7102,7 +7102,7 @@
       <c r="AG63" s="1">
         <v>0</v>
       </c>
-      <c r="BJ63" s="1">
+      <c r="BI63" s="1">
         <v>0</v>
       </c>
       <c r="DM63" s="1">
@@ -7185,7 +7185,7 @@
       <c r="AG64" s="1">
         <v>4</v>
       </c>
-      <c r="BJ64" s="1">
+      <c r="BI64" s="1">
         <v>4</v>
       </c>
       <c r="DM64" s="1">
@@ -7268,7 +7268,7 @@
       <c r="AG65" s="1">
         <v>0</v>
       </c>
-      <c r="BJ65" s="1">
+      <c r="BI65" s="1">
         <v>0</v>
       </c>
       <c r="DM65" s="1">
@@ -7351,7 +7351,7 @@
       <c r="AG66" s="1">
         <v>0</v>
       </c>
-      <c r="BJ66" s="1">
+      <c r="BI66" s="1">
         <v>0</v>
       </c>
       <c r="BP66" s="3">
@@ -7437,7 +7437,7 @@
       <c r="AG67" s="1">
         <v>4</v>
       </c>
-      <c r="BJ67" s="1">
+      <c r="BI67" s="1">
         <v>4</v>
       </c>
       <c r="BP67" s="3">
@@ -7523,7 +7523,7 @@
       <c r="AG68" s="1">
         <v>0</v>
       </c>
-      <c r="BJ68" s="1">
+      <c r="BI68" s="1">
         <v>0</v>
       </c>
       <c r="BP68" s="3">
@@ -7593,21 +7593,6 @@
         <v>0</v>
       </c>
       <c r="DY68" s="1">
-        <v>0</v>
-      </c>
-      <c r="EB68" s="4">
-        <v>0</v>
-      </c>
-      <c r="EC68" s="4">
-        <v>0</v>
-      </c>
-      <c r="ED68" s="4">
-        <v>0</v>
-      </c>
-      <c r="EE68" s="4">
-        <v>0</v>
-      </c>
-      <c r="EF68" s="4">
         <v>0</v>
       </c>
       <c r="ET68" s="1">
@@ -7624,7 +7609,7 @@
       <c r="AG69" s="1">
         <v>0</v>
       </c>
-      <c r="BJ69" s="1">
+      <c r="BI69" s="1">
         <v>0</v>
       </c>
       <c r="BP69" s="3">
@@ -7694,21 +7679,6 @@
         <v>4</v>
       </c>
       <c r="DY69" s="1">
-        <v>0</v>
-      </c>
-      <c r="EB69" s="4">
-        <v>0</v>
-      </c>
-      <c r="EC69" s="4">
-        <v>0</v>
-      </c>
-      <c r="ED69" s="4">
-        <v>0</v>
-      </c>
-      <c r="EE69" s="4">
-        <v>0</v>
-      </c>
-      <c r="EF69" s="4">
         <v>0</v>
       </c>
       <c r="ET69" s="1">
@@ -7725,7 +7695,7 @@
       <c r="AG70" s="1">
         <v>4</v>
       </c>
-      <c r="BJ70" s="1">
+      <c r="BI70" s="1">
         <v>4</v>
       </c>
       <c r="BP70" s="3">
@@ -7796,21 +7766,6 @@
       </c>
       <c r="DY70" s="1">
         <v>4</v>
-      </c>
-      <c r="EB70" s="4">
-        <v>0</v>
-      </c>
-      <c r="EC70" s="4">
-        <v>0</v>
-      </c>
-      <c r="ED70" s="4">
-        <v>11</v>
-      </c>
-      <c r="EE70" s="4">
-        <v>0</v>
-      </c>
-      <c r="EF70" s="4">
-        <v>0</v>
       </c>
       <c r="ET70" s="1">
         <v>0</v>
@@ -7826,7 +7781,7 @@
       <c r="AG71" s="1">
         <v>0</v>
       </c>
-      <c r="BJ71" s="1">
+      <c r="BI71" s="1">
         <v>0</v>
       </c>
       <c r="BP71" s="3">
@@ -7889,15 +7844,6 @@
       <c r="CI71" s="3">
         <v>0</v>
       </c>
-      <c r="CP71" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ71" s="1">
-        <v>3</v>
-      </c>
-      <c r="CR71" s="1">
-        <v>0</v>
-      </c>
       <c r="CS71" s="1">
         <v>0</v>
       </c>
@@ -7965,21 +7911,6 @@
         <v>0</v>
       </c>
       <c r="DY71" s="1">
-        <v>0</v>
-      </c>
-      <c r="EB71" s="4">
-        <v>0</v>
-      </c>
-      <c r="EC71" s="4">
-        <v>0</v>
-      </c>
-      <c r="ED71" s="4">
-        <v>0</v>
-      </c>
-      <c r="EE71" s="4">
-        <v>0</v>
-      </c>
-      <c r="EF71" s="4">
         <v>0</v>
       </c>
       <c r="ET71" s="1">
@@ -8147,21 +8078,6 @@
         <v>4</v>
       </c>
       <c r="DY72" s="1">
-        <v>0</v>
-      </c>
-      <c r="EB72" s="4">
-        <v>0</v>
-      </c>
-      <c r="EC72" s="4">
-        <v>0</v>
-      </c>
-      <c r="ED72" s="4">
-        <v>0</v>
-      </c>
-      <c r="EE72" s="4">
-        <v>0</v>
-      </c>
-      <c r="EF72" s="4">
         <v>0</v>
       </c>
       <c r="ET72" s="1">
@@ -8692,6 +8608,21 @@
       <c r="DY78" s="1">
         <v>0</v>
       </c>
+      <c r="EB78" s="4">
+        <v>0</v>
+      </c>
+      <c r="EC78" s="4">
+        <v>0</v>
+      </c>
+      <c r="ED78" s="4">
+        <v>0</v>
+      </c>
+      <c r="EE78" s="4">
+        <v>0</v>
+      </c>
+      <c r="EF78" s="4">
+        <v>0</v>
+      </c>
       <c r="ET78" s="1">
         <v>0</v>
       </c>
@@ -8781,6 +8712,21 @@
       <c r="DY79" s="1">
         <v>4</v>
       </c>
+      <c r="EB79" s="4">
+        <v>0</v>
+      </c>
+      <c r="EC79" s="4">
+        <v>0</v>
+      </c>
+      <c r="ED79" s="4">
+        <v>0</v>
+      </c>
+      <c r="EE79" s="4">
+        <v>0</v>
+      </c>
+      <c r="EF79" s="4">
+        <v>0</v>
+      </c>
       <c r="ET79" s="1">
         <v>0</v>
       </c>
@@ -8954,13 +8900,31 @@
       <c r="CI80" s="3">
         <v>0</v>
       </c>
-      <c r="CP80" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ80" s="1">
-        <v>3</v>
-      </c>
-      <c r="CR80" s="1">
+      <c r="CJ80" s="1">
+        <v>0</v>
+      </c>
+      <c r="CK80" s="1">
+        <v>3</v>
+      </c>
+      <c r="CL80" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM80" s="5">
+        <v>0</v>
+      </c>
+      <c r="CN80" s="5">
+        <v>7</v>
+      </c>
+      <c r="CO80" s="5">
+        <v>0</v>
+      </c>
+      <c r="CP80" s="5">
+        <v>0</v>
+      </c>
+      <c r="CQ80" s="5">
+        <v>7</v>
+      </c>
+      <c r="CR80" s="5">
         <v>0</v>
       </c>
       <c r="CS80" s="1">
@@ -9030,6 +8994,21 @@
         <v>0</v>
       </c>
       <c r="DY80" s="1">
+        <v>0</v>
+      </c>
+      <c r="EB80" s="4">
+        <v>0</v>
+      </c>
+      <c r="EC80" s="4">
+        <v>0</v>
+      </c>
+      <c r="ED80" s="4">
+        <v>11</v>
+      </c>
+      <c r="EE80" s="4">
+        <v>0</v>
+      </c>
+      <c r="EF80" s="4">
         <v>0</v>
       </c>
       <c r="ET80" s="1">
@@ -9058,7 +9037,7 @@
       <c r="AG81" s="1">
         <v>0</v>
       </c>
-      <c r="BJ81" s="1">
+      <c r="BI81" s="1">
         <v>0</v>
       </c>
       <c r="BP81" s="3">
@@ -9131,6 +9110,21 @@
         <v>4</v>
       </c>
       <c r="DY81" s="1">
+        <v>0</v>
+      </c>
+      <c r="EB81" s="4">
+        <v>0</v>
+      </c>
+      <c r="EC81" s="4">
+        <v>0</v>
+      </c>
+      <c r="ED81" s="4">
+        <v>0</v>
+      </c>
+      <c r="EE81" s="4">
+        <v>0</v>
+      </c>
+      <c r="EF81" s="4">
         <v>0</v>
       </c>
       <c r="ET81" s="1">
@@ -9144,7 +9138,7 @@
       <c r="AG82" s="1">
         <v>4</v>
       </c>
-      <c r="BJ82" s="1">
+      <c r="BI82" s="1">
         <v>4</v>
       </c>
       <c r="BP82" s="3">
@@ -9218,6 +9212,21 @@
       </c>
       <c r="DY82" s="1">
         <v>4</v>
+      </c>
+      <c r="EB82" s="4">
+        <v>0</v>
+      </c>
+      <c r="EC82" s="4">
+        <v>0</v>
+      </c>
+      <c r="ED82" s="4">
+        <v>0</v>
+      </c>
+      <c r="EE82" s="4">
+        <v>0</v>
+      </c>
+      <c r="EF82" s="4">
+        <v>0</v>
       </c>
       <c r="ET82" s="1">
         <v>0</v>
@@ -9230,7 +9239,7 @@
       <c r="AG83" s="1">
         <v>0</v>
       </c>
-      <c r="BJ83" s="1">
+      <c r="BI83" s="1">
         <v>0</v>
       </c>
       <c r="BP83" s="3">
@@ -9316,7 +9325,7 @@
       <c r="AG84" s="1">
         <v>0</v>
       </c>
-      <c r="BJ84" s="1">
+      <c r="BI84" s="1">
         <v>0</v>
       </c>
       <c r="BP84" s="3">
@@ -9402,7 +9411,7 @@
       <c r="AG85" s="1">
         <v>4</v>
       </c>
-      <c r="BJ85" s="1">
+      <c r="BI85" s="1">
         <v>4</v>
       </c>
       <c r="BP85" s="3">
@@ -9488,7 +9497,7 @@
       <c r="AG86" s="1">
         <v>0</v>
       </c>
-      <c r="BJ86" s="1">
+      <c r="BI86" s="1">
         <v>0</v>
       </c>
       <c r="CJ86" s="1">
@@ -9730,130 +9739,94 @@
       <c r="AG93" s="1">
         <v>0</v>
       </c>
-      <c r="BJ93" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK93" s="1">
-        <v>3</v>
-      </c>
-      <c r="BL93" s="1">
-        <v>0</v>
-      </c>
-      <c r="BM93" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN93" s="1">
-        <v>3</v>
-      </c>
-      <c r="BO93" s="1">
-        <v>0</v>
-      </c>
-      <c r="BP93" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ93" s="1">
-        <v>3</v>
-      </c>
-      <c r="BR93" s="1">
-        <v>0</v>
-      </c>
-      <c r="CH93" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI93" s="1">
-        <v>3</v>
-      </c>
       <c r="CJ93" s="1">
         <v>0</v>
       </c>
       <c r="CK93" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CL93" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CM93" s="1">
         <v>0</v>
       </c>
       <c r="CN93" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CO93" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CP93" s="1">
         <v>0</v>
       </c>
       <c r="CQ93" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CR93" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CS93" s="1">
         <v>0</v>
       </c>
       <c r="CT93" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CU93" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CV93" s="1">
         <v>0</v>
       </c>
       <c r="CW93" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CX93" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CY93" s="1">
         <v>0</v>
       </c>
       <c r="CZ93" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DA93" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DB93" s="1">
         <v>0</v>
       </c>
       <c r="DC93" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DD93" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DE93" s="1">
         <v>0</v>
       </c>
       <c r="DF93" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DG93" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH93" s="1">
         <v>0</v>
       </c>
       <c r="DI93" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DJ93" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DK93" s="1">
         <v>0</v>
       </c>
       <c r="DL93" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DM93" s="1">
-        <v>3</v>
-      </c>
-      <c r="DN93" s="1">
         <v>0</v>
       </c>
       <c r="DS93" s="1">
@@ -9873,13 +9846,10 @@
       <c r="AG94" s="1">
         <v>4</v>
       </c>
-      <c r="BJ94" s="1">
-        <v>0</v>
-      </c>
-      <c r="BR94" s="1">
-        <v>0</v>
-      </c>
-      <c r="CH94" s="1">
+      <c r="BI94" s="1">
+        <v>0</v>
+      </c>
+      <c r="CJ94" s="1">
         <v>0</v>
       </c>
       <c r="DS94" s="1">
@@ -9899,13 +9869,10 @@
       <c r="AG95" s="1">
         <v>0</v>
       </c>
-      <c r="BJ95" s="1">
-        <v>4</v>
-      </c>
-      <c r="BR95" s="1">
-        <v>4</v>
-      </c>
-      <c r="CH95" s="1">
+      <c r="BI95" s="1">
+        <v>4</v>
+      </c>
+      <c r="CJ95" s="1">
         <v>4</v>
       </c>
       <c r="DJ95" t="s">
@@ -9928,13 +9895,10 @@
       <c r="AG96" s="1">
         <v>0</v>
       </c>
-      <c r="BJ96" s="1">
-        <v>0</v>
-      </c>
-      <c r="BR96" s="1">
-        <v>0</v>
-      </c>
-      <c r="CH96" s="1">
+      <c r="BI96" s="1">
+        <v>0</v>
+      </c>
+      <c r="CJ96" s="1">
         <v>0</v>
       </c>
       <c r="DS96" s="1">
@@ -9954,7 +9918,16 @@
       <c r="AG97" s="1">
         <v>4</v>
       </c>
-      <c r="BJ97" s="1">
+      <c r="BI97" s="1">
+        <v>0</v>
+      </c>
+      <c r="BM97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO97" s="4">
         <v>0</v>
       </c>
       <c r="BP97" s="4">
@@ -9963,21 +9936,6 @@
       <c r="BQ97" s="4">
         <v>0</v>
       </c>
-      <c r="BR97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT97" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF97" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG97" s="4">
-        <v>0</v>
-      </c>
       <c r="CH97" s="4">
         <v>0</v>
       </c>
@@ -9987,26 +9945,17 @@
       <c r="CJ97" s="4">
         <v>0</v>
       </c>
+      <c r="CK97" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL97" s="4">
+        <v>0</v>
+      </c>
       <c r="DS97" s="1">
         <v>0</v>
       </c>
       <c r="DY97" s="1">
         <v>4</v>
-      </c>
-      <c r="EK97" s="4">
-        <v>0</v>
-      </c>
-      <c r="EL97" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM97" s="4">
-        <v>0</v>
-      </c>
-      <c r="EN97" s="4">
-        <v>0</v>
-      </c>
-      <c r="EO97" s="4">
-        <v>0</v>
       </c>
       <c r="ET97" s="1">
         <v>0</v>
@@ -10019,8 +9968,17 @@
       <c r="AG98" s="1">
         <v>0</v>
       </c>
-      <c r="BJ98" s="1">
-        <v>4</v>
+      <c r="BI98" s="1">
+        <v>4</v>
+      </c>
+      <c r="BM98" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN98" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO98" s="4">
+        <v>0</v>
       </c>
       <c r="BP98" s="4">
         <v>0</v>
@@ -10028,21 +9986,6 @@
       <c r="BQ98" s="4">
         <v>0</v>
       </c>
-      <c r="BR98" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS98" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT98" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF98" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG98" s="4">
-        <v>0</v>
-      </c>
       <c r="CH98" s="4">
         <v>0</v>
       </c>
@@ -10052,25 +9995,16 @@
       <c r="CJ98" s="4">
         <v>0</v>
       </c>
+      <c r="CK98" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL98" s="4">
+        <v>0</v>
+      </c>
       <c r="DS98" s="1">
         <v>0</v>
       </c>
       <c r="DY98" s="1">
-        <v>0</v>
-      </c>
-      <c r="EK98" s="4">
-        <v>0</v>
-      </c>
-      <c r="EL98" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM98" s="4">
-        <v>0</v>
-      </c>
-      <c r="EN98" s="4">
-        <v>0</v>
-      </c>
-      <c r="EO98" s="4">
         <v>0</v>
       </c>
       <c r="ET98" s="1">
@@ -10084,37 +10018,46 @@
       <c r="AG99" s="1">
         <v>0</v>
       </c>
+      <c r="BI99" s="1">
+        <v>0</v>
+      </c>
       <c r="BJ99" s="1">
         <v>0</v>
       </c>
+      <c r="BK99" s="1">
+        <v>3</v>
+      </c>
+      <c r="BL99" s="1">
+        <v>0</v>
+      </c>
+      <c r="BM99" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN99" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO99" s="4">
+        <v>11</v>
+      </c>
       <c r="BP99" s="4">
         <v>0</v>
       </c>
       <c r="BQ99" s="4">
         <v>0</v>
       </c>
-      <c r="BR99" s="4">
+      <c r="CH99" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI99" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ99" s="4">
         <v>11</v>
       </c>
-      <c r="BS99" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT99" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF99" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG99" s="4">
-        <v>0</v>
-      </c>
-      <c r="CH99" s="4">
-        <v>11</v>
-      </c>
-      <c r="CI99" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ99" s="4">
+      <c r="CK99" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL99" s="4">
         <v>0</v>
       </c>
       <c r="DS99" s="1">
@@ -10130,7 +10073,7 @@
         <v>0</v>
       </c>
       <c r="EM99" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="EN99" s="4">
         <v>0</v>
@@ -10149,27 +10092,21 @@
       <c r="AG100" s="1">
         <v>4</v>
       </c>
+      <c r="BM100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO100" s="4">
+        <v>0</v>
+      </c>
       <c r="BP100" s="4">
         <v>0</v>
       </c>
       <c r="BQ100" s="4">
         <v>0</v>
       </c>
-      <c r="BR100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT100" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF100" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG100" s="4">
-        <v>0</v>
-      </c>
       <c r="CH100" s="4">
         <v>0</v>
       </c>
@@ -10177,6 +10114,12 @@
         <v>0</v>
       </c>
       <c r="CJ100" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK100" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL100" s="4">
         <v>0</v>
       </c>
       <c r="DS100" s="1">
@@ -10211,27 +10154,21 @@
       <c r="AG101" s="1">
         <v>0</v>
       </c>
+      <c r="BM101" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN101" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO101" s="4">
+        <v>0</v>
+      </c>
       <c r="BP101" s="4">
         <v>0</v>
       </c>
       <c r="BQ101" s="4">
         <v>0</v>
       </c>
-      <c r="BR101" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS101" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT101" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF101" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG101" s="4">
-        <v>0</v>
-      </c>
       <c r="CH101" s="4">
         <v>0</v>
       </c>
@@ -10241,6 +10178,12 @@
       <c r="CJ101" s="4">
         <v>0</v>
       </c>
+      <c r="CK101" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL101" s="4">
+        <v>0</v>
+      </c>
       <c r="DS101" s="1">
         <v>0</v>
       </c>
@@ -10254,7 +10197,7 @@
         <v>0</v>
       </c>
       <c r="EM101" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="EN101" s="4">
         <v>0</v>
@@ -10273,16 +10216,31 @@
       <c r="AG102" s="1">
         <v>0</v>
       </c>
-      <c r="BR102" s="1">
-        <v>0</v>
-      </c>
-      <c r="CH102" s="1">
+      <c r="BO102" s="1">
+        <v>0</v>
+      </c>
+      <c r="CJ102" s="1">
         <v>0</v>
       </c>
       <c r="DS102" s="1">
         <v>4</v>
       </c>
       <c r="DY102" s="1">
+        <v>0</v>
+      </c>
+      <c r="EK102" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL102" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM102" s="4">
+        <v>0</v>
+      </c>
+      <c r="EN102" s="4">
+        <v>0</v>
+      </c>
+      <c r="EO102" s="4">
         <v>0</v>
       </c>
       <c r="ET102" s="1">
@@ -10296,10 +10254,10 @@
       <c r="AG103" s="1">
         <v>4</v>
       </c>
-      <c r="BR103" s="1">
-        <v>4</v>
-      </c>
-      <c r="CH103" s="1">
+      <c r="BO103" s="1">
+        <v>4</v>
+      </c>
+      <c r="CJ103" s="1">
         <v>4</v>
       </c>
       <c r="DS103" s="1">
@@ -10307,6 +10265,21 @@
       </c>
       <c r="DY103" s="1">
         <v>4</v>
+      </c>
+      <c r="EK103" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL103" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM103" s="4">
+        <v>0</v>
+      </c>
+      <c r="EN103" s="4">
+        <v>0</v>
+      </c>
+      <c r="EO103" s="4">
+        <v>0</v>
       </c>
       <c r="ET103" s="1">
         <v>0</v>
@@ -10319,10 +10292,10 @@
       <c r="AG104" s="1">
         <v>0</v>
       </c>
-      <c r="BR104" s="1">
-        <v>0</v>
-      </c>
-      <c r="CH104" s="1">
+      <c r="BO104" s="1">
+        <v>0</v>
+      </c>
+      <c r="CJ104" s="1">
         <v>0</v>
       </c>
       <c r="DS104" s="1">
@@ -11375,64 +11348,34 @@
       <c r="Q119" s="1">
         <v>0</v>
       </c>
-      <c r="X119" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y119" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z119" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA119" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB119" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC119" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD119" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE119" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF119" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG119" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH119" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI119" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ119" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK119" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL119" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM119" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN119" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO119" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP119" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ119" s="3">
+      <c r="AB119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ119" s="4">
         <v>0</v>
       </c>
       <c r="AX119" s="1">
@@ -11524,64 +11467,34 @@
       <c r="Q120" s="1">
         <v>4</v>
       </c>
-      <c r="X120" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y120" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z120" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA120" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB120" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC120" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD120" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE120" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF120" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG120" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH120" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI120" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ120" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK120" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL120" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM120" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN120" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO120" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP120" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ120" s="3">
+      <c r="AB120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ120" s="4">
         <v>0</v>
       </c>
       <c r="AX120" s="1">
@@ -11682,64 +11595,70 @@
       <c r="Q121" s="1">
         <v>0</v>
       </c>
-      <c r="X121" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y121" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z121" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA121" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB121" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC121" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD121" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE121" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF121" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG121" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH121" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI121" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ121" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK121" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL121" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM121" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN121" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO121" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP121" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ121" s="3">
+      <c r="AB121" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC121" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD121" s="4">
+        <v>11</v>
+      </c>
+      <c r="AE121" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF121" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH121" s="1">
+        <v>3</v>
+      </c>
+      <c r="AI121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK121" s="1">
+        <v>3</v>
+      </c>
+      <c r="AL121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM121" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN121" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO121" s="4">
+        <v>11</v>
+      </c>
+      <c r="AP121" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ121" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS121" s="1">
+        <v>3</v>
+      </c>
+      <c r="AT121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV121" s="1">
+        <v>3</v>
+      </c>
+      <c r="AW121" s="1">
         <v>0</v>
       </c>
       <c r="AX121" s="1">
@@ -11837,64 +11756,34 @@
       <c r="Q122" s="5">
         <v>0</v>
       </c>
-      <c r="X122" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y122" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z122" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA122" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB122" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC122" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD122" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE122" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF122" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG122" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH122" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI122" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ122" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK122" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL122" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM122" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN122" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO122" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP122" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ122" s="3">
+      <c r="AB122" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC122" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD122" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE122" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF122" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM122" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN122" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO122" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP122" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ122" s="4">
         <v>0</v>
       </c>
       <c r="AX122" s="1">
@@ -11978,21 +11867,6 @@
       <c r="DY122" s="1">
         <v>0</v>
       </c>
-      <c r="ED122" s="4">
-        <v>0</v>
-      </c>
-      <c r="EE122" s="4">
-        <v>0</v>
-      </c>
-      <c r="EF122" s="4">
-        <v>0</v>
-      </c>
-      <c r="EG122" s="4">
-        <v>0</v>
-      </c>
-      <c r="EH122" s="4">
-        <v>0</v>
-      </c>
       <c r="ET122" s="1">
         <v>0</v>
       </c>
@@ -12007,64 +11881,34 @@
       <c r="Q123" s="5">
         <v>8</v>
       </c>
-      <c r="X123" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y123" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z123" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA123" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB123" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC123" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD123" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE123" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF123" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG123" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH123" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI123" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ123" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK123" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL123" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM123" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN123" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO123" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP123" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ123" s="3">
+      <c r="AB123" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC123" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD123" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE123" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF123" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM123" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN123" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO123" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP123" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ123" s="4">
         <v>0</v>
       </c>
       <c r="AX123" s="1">
@@ -12146,21 +11990,6 @@
         <v>4</v>
       </c>
       <c r="DY123" s="1">
-        <v>0</v>
-      </c>
-      <c r="ED123" s="4">
-        <v>0</v>
-      </c>
-      <c r="EE123" s="4">
-        <v>0</v>
-      </c>
-      <c r="EF123" s="4">
-        <v>0</v>
-      </c>
-      <c r="EG123" s="4">
-        <v>0</v>
-      </c>
-      <c r="EH123" s="4">
         <v>0</v>
       </c>
       <c r="ET123" s="1">
@@ -12177,64 +12006,7 @@
       <c r="Q124" s="5">
         <v>0</v>
       </c>
-      <c r="X124" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y124" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z124" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA124" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB124" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC124" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD124" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE124" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF124" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG124" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH124" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI124" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ124" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK124" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL124" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM124" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN124" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO124" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP124" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ124" s="3">
+      <c r="AD124" s="1">
         <v>0</v>
       </c>
       <c r="AX124" s="1">
@@ -12352,7 +12124,7 @@
         <v>0</v>
       </c>
       <c r="EF124" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="EG124" s="4">
         <v>0</v>
@@ -12374,65 +12146,8 @@
       <c r="Q125" s="5">
         <v>0</v>
       </c>
-      <c r="X125" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y125" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z125" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA125" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB125" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC125" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD125" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE125" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF125" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG125" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH125" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI125" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ125" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK125" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL125" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM125" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN125" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO125" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP125" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ125" s="3">
-        <v>0</v>
+      <c r="AD125" s="1">
+        <v>4</v>
       </c>
       <c r="AX125" s="1">
         <v>4</v>
@@ -12544,64 +12259,7 @@
       <c r="Q126" s="5">
         <v>8</v>
       </c>
-      <c r="X126" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y126" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z126" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA126" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB126" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC126" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD126" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE126" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF126" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG126" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH126" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI126" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ126" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK126" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL126" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM126" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN126" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO126" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP126" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ126" s="3">
+      <c r="AD126" s="1">
         <v>0</v>
       </c>
       <c r="AX126" s="1">
@@ -12707,7 +12365,7 @@
         <v>0</v>
       </c>
       <c r="EF126" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="EG126" s="4">
         <v>0</v>
@@ -12729,64 +12387,7 @@
       <c r="Q127" s="5">
         <v>0</v>
       </c>
-      <c r="X127" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y127" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z127" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA127" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB127" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC127" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD127" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE127" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF127" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG127" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH127" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI127" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ127" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK127" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL127" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM127" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN127" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO127" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP127" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ127" s="3">
+      <c r="AD127" s="1">
         <v>0</v>
       </c>
       <c r="BZ127" s="1">
@@ -12857,6 +12458,21 @@
       </c>
       <c r="DY127" s="1">
         <v>4</v>
+      </c>
+      <c r="ED127" s="4">
+        <v>0</v>
+      </c>
+      <c r="EE127" s="4">
+        <v>0</v>
+      </c>
+      <c r="EF127" s="4">
+        <v>0</v>
+      </c>
+      <c r="EG127" s="4">
+        <v>0</v>
+      </c>
+      <c r="EH127" s="4">
+        <v>0</v>
       </c>
       <c r="ET127" s="1">
         <v>0</v>
@@ -12872,65 +12488,8 @@
       <c r="Q128" s="1">
         <v>0</v>
       </c>
-      <c r="X128" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y128" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z128" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA128" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB128" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC128" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD128" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE128" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF128" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG128" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH128" s="3">
-        <v>13</v>
-      </c>
-      <c r="AI128" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ128" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK128" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL128" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM128" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN128" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO128" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP128" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ128" s="3">
-        <v>0</v>
+      <c r="AD128" s="1">
+        <v>4</v>
       </c>
       <c r="BD128" s="4">
         <v>0</v>
@@ -13014,6 +12573,21 @@
         <v>0</v>
       </c>
       <c r="DY128" s="1">
+        <v>0</v>
+      </c>
+      <c r="ED128" s="4">
+        <v>0</v>
+      </c>
+      <c r="EE128" s="4">
+        <v>0</v>
+      </c>
+      <c r="EF128" s="4">
+        <v>0</v>
+      </c>
+      <c r="EG128" s="4">
+        <v>0</v>
+      </c>
+      <c r="EH128" s="4">
         <v>0</v>
       </c>
       <c r="ET128" s="1">
@@ -13030,64 +12604,7 @@
       <c r="Q129" s="1">
         <v>4</v>
       </c>
-      <c r="X129" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y129" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z129" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA129" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB129" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC129" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD129" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE129" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF129" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG129" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH129" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI129" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ129" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK129" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL129" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM129" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN129" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO129" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP129" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ129" s="3">
+      <c r="AD129" s="1">
         <v>0</v>
       </c>
       <c r="BD129" s="4">
@@ -13188,64 +12705,7 @@
       <c r="Q130" s="1">
         <v>0</v>
       </c>
-      <c r="X130" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y130" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z130" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA130" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB130" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC130" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD130" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE130" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF130" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG130" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH130" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI130" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ130" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK130" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL130" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM130" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN130" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO130" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP130" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ130" s="3">
+      <c r="AD130" s="1">
         <v>0</v>
       </c>
       <c r="BD130" s="4">
@@ -13370,65 +12830,8 @@
       <c r="S131" s="4">
         <v>0</v>
       </c>
-      <c r="X131" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y131" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z131" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA131" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB131" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC131" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD131" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE131" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF131" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG131" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH131" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI131" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ131" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK131" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL131" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM131" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN131" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO131" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP131" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ131" s="3">
-        <v>0</v>
+      <c r="AD131" s="1">
+        <v>4</v>
       </c>
       <c r="BD131" s="4">
         <v>0</v>
@@ -13552,64 +12955,7 @@
       <c r="S132" s="4">
         <v>0</v>
       </c>
-      <c r="X132" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y132" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z132" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA132" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB132" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC132" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD132" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE132" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF132" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG132" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH132" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI132" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ132" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK132" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL132" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM132" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN132" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO132" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP132" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ132" s="3">
+      <c r="AD132" s="1">
         <v>0</v>
       </c>
       <c r="BD132" s="4">
@@ -13743,64 +13089,7 @@
       <c r="S133" s="4">
         <v>0</v>
       </c>
-      <c r="X133" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y133" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z133" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA133" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB133" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC133" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD133" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE133" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF133" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG133" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH133" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI133" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ133" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK133" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL133" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM133" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN133" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO133" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP133" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ133" s="3">
+      <c r="AD133" s="1">
         <v>0</v>
       </c>
       <c r="BZ133" s="1">
@@ -13910,65 +13199,8 @@
       <c r="S134" s="4">
         <v>0</v>
       </c>
-      <c r="X134" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y134" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z134" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA134" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB134" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC134" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD134" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE134" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF134" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG134" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH134" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI134" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ134" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK134" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL134" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM134" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN134" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO134" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP134" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ134" s="3">
-        <v>0</v>
+      <c r="AD134" s="1">
+        <v>4</v>
       </c>
       <c r="BZ134" s="1">
         <v>4</v>
@@ -14080,64 +13312,7 @@
       <c r="S135" s="4">
         <v>0</v>
       </c>
-      <c r="X135" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y135" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z135" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA135" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB135" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC135" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD135" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE135" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF135" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG135" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH135" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI135" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ135" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK135" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL135" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM135" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN135" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO135" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP135" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ135" s="3">
+      <c r="AD135" s="1">
         <v>0</v>
       </c>
       <c r="AX135" s="1">
@@ -14190,64 +13365,19 @@
       <c r="A136" s="1">
         <v>0</v>
       </c>
-      <c r="X136" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y136" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z136" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA136" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB136" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC136" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD136" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE136" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF136" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG136" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH136" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI136" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ136" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK136" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL136" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM136" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN136" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO136" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP136" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ136" s="3">
+      <c r="AB136" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC136" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD136" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE136" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF136" s="4">
         <v>0</v>
       </c>
       <c r="AX136" s="1">
@@ -14282,64 +13412,34 @@
       <c r="A137" s="1">
         <v>0</v>
       </c>
-      <c r="X137" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y137" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z137" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA137" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB137" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC137" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD137" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE137" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF137" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG137" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH137" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI137" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ137" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK137" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL137" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM137" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN137" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO137" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP137" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ137" s="3">
+      <c r="AB137" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC137" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD137" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE137" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF137" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM137" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN137" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO137" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP137" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ137" s="4">
         <v>0</v>
       </c>
       <c r="AX137" s="1">
@@ -14374,64 +13474,34 @@
       <c r="A138" s="1">
         <v>0</v>
       </c>
-      <c r="X138" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y138" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z138" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA138" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB138" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC138" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD138" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE138" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF138" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG138" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH138" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI138" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ138" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK138" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL138" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM138" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN138" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO138" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP138" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ138" s="3">
+      <c r="AB138" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC138" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD138" s="4">
+        <v>11</v>
+      </c>
+      <c r="AE138" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF138" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM138" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN138" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO138" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP138" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ138" s="4">
         <v>0</v>
       </c>
       <c r="AX138" s="1">
@@ -14466,6 +13536,36 @@
       <c r="A139" s="1">
         <v>0</v>
       </c>
+      <c r="AB139" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC139" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD139" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE139" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF139" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM139" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN139" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO139" s="4">
+        <v>11</v>
+      </c>
+      <c r="AP139" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ139" s="4">
+        <v>0</v>
+      </c>
       <c r="AX139" s="1">
         <v>4</v>
       </c>
@@ -14498,6 +13598,36 @@
       <c r="A140" s="1">
         <v>0</v>
       </c>
+      <c r="AB140" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC140" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD140" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE140" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF140" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM140" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN140" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO140" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP140" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ140" s="4">
+        <v>0</v>
+      </c>
       <c r="AX140" s="1">
         <v>0</v>
       </c>
@@ -14542,6 +13672,24 @@
       <c r="A141" s="1">
         <v>0</v>
       </c>
+      <c r="AD141" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM141" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN141" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO141" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP141" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ141" s="4">
+        <v>0</v>
+      </c>
       <c r="AX141" s="1">
         <v>0</v>
       </c>
@@ -14589,6 +13737,9 @@
       <c r="A142" s="1">
         <v>0</v>
       </c>
+      <c r="AD142" s="1">
+        <v>4</v>
+      </c>
       <c r="AX142" s="1">
         <v>4</v>
       </c>
@@ -14705,6 +13856,9 @@
       <c r="A143" s="1">
         <v>0</v>
       </c>
+      <c r="AD143" s="1">
+        <v>0</v>
+      </c>
       <c r="AX143" s="1">
         <v>0</v>
       </c>
@@ -14737,6 +13891,9 @@
       <c r="A144" s="1">
         <v>0</v>
       </c>
+      <c r="AD144" s="1">
+        <v>0</v>
+      </c>
       <c r="AX144" s="1">
         <v>0</v>
       </c>
@@ -14768,6 +13925,9 @@
     <row r="145" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A145" s="1">
         <v>0</v>
+      </c>
+      <c r="AD145" s="1">
+        <v>4</v>
       </c>
       <c r="AX145" s="1">
         <v>4</v>
@@ -14786,6 +13946,9 @@
       <c r="B146" s="1">
         <v>6</v>
       </c>
+      <c r="AD146" s="1">
+        <v>0</v>
+      </c>
       <c r="AX146" s="1">
         <v>0</v>
       </c>
@@ -14803,6 +13966,9 @@
       <c r="C147" s="1">
         <v>0</v>
       </c>
+      <c r="AD147" s="1">
+        <v>0</v>
+      </c>
       <c r="AX147" s="1">
         <v>0</v>
       </c>
@@ -14819,6 +13985,9 @@
     <row r="148" spans="1:150" x14ac:dyDescent="0.45">
       <c r="D148" s="1">
         <v>0</v>
+      </c>
+      <c r="AD148" s="1">
+        <v>4</v>
       </c>
       <c r="AX148" s="1">
         <v>4</v>
@@ -14836,6 +14005,9 @@
     <row r="149" spans="1:150" x14ac:dyDescent="0.45">
       <c r="E149" s="1">
         <v>6</v>
+      </c>
+      <c r="AD149" s="1">
+        <v>0</v>
       </c>
       <c r="AX149" s="1">
         <v>0</v>

--- a/media/Levels/Level_5.xlsx
+++ b/media/Levels/Level_5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A99F0A-9021-4174-815E-BB3667F9CBC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1440AB1B-9A39-44E7-BEAE-C43134BEA527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3672" yWindow="84" windowWidth="13836" windowHeight="12156" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
+    <workbookView xWindow="228" yWindow="72" windowWidth="13836" windowHeight="12168" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2636,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="AZ21" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA21" s="3">
         <v>0</v>
@@ -3087,7 +3087,7 @@
         <v>0</v>
       </c>
       <c r="CY23" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CZ23" s="3">
         <v>0</v>
@@ -12055,7 +12055,7 @@
         <v>0</v>
       </c>
       <c r="CU124" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CV124" s="3">
         <v>0</v>
@@ -13643,21 +13643,6 @@
       <c r="CN140" s="1">
         <v>0</v>
       </c>
-      <c r="CY140" s="4">
-        <v>0</v>
-      </c>
-      <c r="CZ140" s="4">
-        <v>0</v>
-      </c>
-      <c r="DA140" s="4">
-        <v>0</v>
-      </c>
-      <c r="DB140" s="4">
-        <v>0</v>
-      </c>
-      <c r="DC140" s="4">
-        <v>0</v>
-      </c>
       <c r="DS140" s="1">
         <v>0</v>
       </c>
@@ -13708,21 +13693,6 @@
       <c r="CM141" s="1">
         <v>0</v>
       </c>
-      <c r="CY141" s="4">
-        <v>0</v>
-      </c>
-      <c r="CZ141" s="4">
-        <v>0</v>
-      </c>
-      <c r="DA141" s="4">
-        <v>0</v>
-      </c>
-      <c r="DB141" s="4">
-        <v>0</v>
-      </c>
-      <c r="DC141" s="4">
-        <v>0</v>
-      </c>
       <c r="DS141" s="1">
         <v>4</v>
       </c>
@@ -13782,19 +13752,13 @@
       <c r="CL142" s="1">
         <v>5</v>
       </c>
-      <c r="CY142" s="4">
-        <v>0</v>
-      </c>
-      <c r="CZ142" s="4">
-        <v>0</v>
-      </c>
-      <c r="DA142" s="4">
-        <v>11</v>
-      </c>
-      <c r="DB142" s="4">
-        <v>0</v>
-      </c>
-      <c r="DC142" s="4">
+      <c r="DA142" s="1">
+        <v>0</v>
+      </c>
+      <c r="DB142" s="1">
+        <v>3</v>
+      </c>
+      <c r="DC142" s="1">
         <v>0</v>
       </c>
       <c r="DD142" s="1">
@@ -13865,21 +13829,6 @@
       <c r="CK143" s="1">
         <v>0</v>
       </c>
-      <c r="CY143" s="4">
-        <v>0</v>
-      </c>
-      <c r="CZ143" s="4">
-        <v>0</v>
-      </c>
-      <c r="DA143" s="4">
-        <v>0</v>
-      </c>
-      <c r="DB143" s="4">
-        <v>0</v>
-      </c>
-      <c r="DC143" s="4">
-        <v>0</v>
-      </c>
       <c r="DY143" s="1">
         <v>0</v>
       </c>
@@ -13898,21 +13847,6 @@
         <v>0</v>
       </c>
       <c r="CJ144" s="1">
-        <v>0</v>
-      </c>
-      <c r="CY144" s="4">
-        <v>0</v>
-      </c>
-      <c r="CZ144" s="4">
-        <v>0</v>
-      </c>
-      <c r="DA144" s="4">
-        <v>0</v>
-      </c>
-      <c r="DB144" s="4">
-        <v>0</v>
-      </c>
-      <c r="DC144" s="4">
         <v>0</v>
       </c>
       <c r="DY144" s="1">

--- a/media/Levels/Level_5.xlsx
+++ b/media/Levels/Level_5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1440AB1B-9A39-44E7-BEAE-C43134BEA527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A74B9E7-4006-4234-81D7-6D01879E53C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="228" yWindow="72" windowWidth="13836" windowHeight="12168" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
+    <workbookView xWindow="2340" yWindow="72" windowWidth="15660" windowHeight="12168" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,15 +33,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="1">
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1"/>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -917,7 +908,7 @@
       <c r="AI2" s="1">
         <v>0</v>
       </c>
-      <c r="BQ2" s="1">
+      <c r="BR2" s="1">
         <v>0</v>
       </c>
       <c r="CY2" s="1">
@@ -937,7 +928,7 @@
       <c r="AI3" s="1">
         <v>4</v>
       </c>
-      <c r="BQ3" s="1">
+      <c r="BR3" s="1">
         <v>4</v>
       </c>
       <c r="CY3" s="1">
@@ -957,7 +948,7 @@
       <c r="AI4" s="1">
         <v>0</v>
       </c>
-      <c r="BQ4" s="1">
+      <c r="BR4" s="1">
         <v>0</v>
       </c>
       <c r="CY4" s="1">
@@ -977,10 +968,22 @@
       <c r="AI5" s="1">
         <v>0</v>
       </c>
-      <c r="BQ5" s="1">
-        <v>0</v>
-      </c>
-      <c r="CY5" s="1">
+      <c r="BR5" s="1">
+        <v>0</v>
+      </c>
+      <c r="CW5" s="4">
+        <v>0</v>
+      </c>
+      <c r="CX5" s="4">
+        <v>0</v>
+      </c>
+      <c r="CY5" s="4">
+        <v>0</v>
+      </c>
+      <c r="CZ5" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA5" s="4">
         <v>0</v>
       </c>
       <c r="DO5" s="1">
@@ -997,11 +1000,23 @@
       <c r="AI6" s="1">
         <v>4</v>
       </c>
-      <c r="BQ6" s="1">
+      <c r="BR6" s="1">
         <v>4</v>
       </c>
-      <c r="CY6" s="1">
-        <v>4</v>
+      <c r="CW6" s="4">
+        <v>0</v>
+      </c>
+      <c r="CX6" s="4">
+        <v>0</v>
+      </c>
+      <c r="CY6" s="4">
+        <v>0</v>
+      </c>
+      <c r="CZ6" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA6" s="4">
+        <v>0</v>
       </c>
       <c r="DO6" s="1">
         <v>4</v>
@@ -1032,10 +1047,22 @@
       <c r="AI7" s="1">
         <v>0</v>
       </c>
-      <c r="BQ7" s="1">
-        <v>0</v>
-      </c>
-      <c r="CY7" s="1">
+      <c r="BR7" s="1">
+        <v>0</v>
+      </c>
+      <c r="CW7" s="4">
+        <v>0</v>
+      </c>
+      <c r="CX7" s="4">
+        <v>0</v>
+      </c>
+      <c r="CY7" s="4">
+        <v>11</v>
+      </c>
+      <c r="CZ7" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA7" s="4">
         <v>0</v>
       </c>
       <c r="DO7" s="1">
@@ -1067,10 +1094,49 @@
       <c r="AI8" s="1">
         <v>0</v>
       </c>
-      <c r="BQ8" s="1">
-        <v>0</v>
-      </c>
-      <c r="CY8" s="1">
+      <c r="BP8" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ8" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR8" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS8" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT8" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU8" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV8" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW8" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX8" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY8" s="4">
+        <v>0</v>
+      </c>
+      <c r="CW8" s="4">
+        <v>0</v>
+      </c>
+      <c r="CX8" s="4">
+        <v>0</v>
+      </c>
+      <c r="CY8" s="4">
+        <v>0</v>
+      </c>
+      <c r="CZ8" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA8" s="4">
         <v>0</v>
       </c>
       <c r="DO8" s="1">
@@ -1105,11 +1171,50 @@
       <c r="AI9" s="1">
         <v>4</v>
       </c>
-      <c r="BQ9" s="1">
-        <v>4</v>
-      </c>
-      <c r="CY9" s="1">
-        <v>4</v>
+      <c r="BP9" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ9" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR9" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS9" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT9" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU9" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV9" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW9" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX9" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY9" s="4">
+        <v>0</v>
+      </c>
+      <c r="CW9" s="4">
+        <v>0</v>
+      </c>
+      <c r="CX9" s="4">
+        <v>0</v>
+      </c>
+      <c r="CY9" s="4">
+        <v>0</v>
+      </c>
+      <c r="CZ9" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA9" s="4">
+        <v>0</v>
       </c>
       <c r="DO9" s="1">
         <v>4</v>
@@ -1143,7 +1248,94 @@
       <c r="AI10" s="1">
         <v>0</v>
       </c>
-      <c r="BQ10" s="1">
+      <c r="AP10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="3">
+        <v>0</v>
+      </c>
+      <c r="BA10" s="3">
+        <v>0</v>
+      </c>
+      <c r="BB10" s="3">
+        <v>0</v>
+      </c>
+      <c r="BC10" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD10" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE10" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF10" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG10" s="3">
+        <v>0</v>
+      </c>
+      <c r="BH10" s="3">
+        <v>0</v>
+      </c>
+      <c r="BI10" s="3">
+        <v>0</v>
+      </c>
+      <c r="BP10" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ10" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR10" s="4">
+        <v>11</v>
+      </c>
+      <c r="BS10" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT10" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU10" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV10" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW10" s="4">
+        <v>11</v>
+      </c>
+      <c r="BX10" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY10" s="4">
         <v>0</v>
       </c>
       <c r="CY10" s="1">
@@ -1181,11 +1373,98 @@
       <c r="AI11" s="1">
         <v>0</v>
       </c>
-      <c r="BQ11" s="1">
+      <c r="AP11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="3">
+        <v>0</v>
+      </c>
+      <c r="BA11" s="3">
+        <v>0</v>
+      </c>
+      <c r="BB11" s="3">
+        <v>0</v>
+      </c>
+      <c r="BC11" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD11" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE11" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF11" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG11" s="3">
+        <v>0</v>
+      </c>
+      <c r="BH11" s="3">
+        <v>0</v>
+      </c>
+      <c r="BI11" s="3">
+        <v>0</v>
+      </c>
+      <c r="BP11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY11" s="4">
         <v>0</v>
       </c>
       <c r="CY11" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DO11" s="1">
         <v>0</v>
@@ -1264,11 +1543,38 @@
       <c r="BI12" s="3">
         <v>0</v>
       </c>
-      <c r="BQ12" s="1">
-        <v>4</v>
+      <c r="BP12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY12" s="4">
+        <v>0</v>
       </c>
       <c r="CY12" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DO12" s="1">
         <v>4</v>
@@ -1347,10 +1653,79 @@
       <c r="BI13" s="3">
         <v>0</v>
       </c>
-      <c r="BQ13" s="1">
-        <v>0</v>
-      </c>
-      <c r="CY13" s="1">
+      <c r="BP13" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ13" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR13" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS13" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT13" s="4">
+        <v>0</v>
+      </c>
+      <c r="CO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="CP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="CQ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="CR13" s="3">
+        <v>0</v>
+      </c>
+      <c r="CS13" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT13" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU13" s="3">
+        <v>0</v>
+      </c>
+      <c r="CV13" s="3">
+        <v>0</v>
+      </c>
+      <c r="CW13" s="3">
+        <v>0</v>
+      </c>
+      <c r="CX13" s="3">
+        <v>0</v>
+      </c>
+      <c r="CY13" s="3">
+        <v>0</v>
+      </c>
+      <c r="CZ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="DA13" s="3">
+        <v>0</v>
+      </c>
+      <c r="DB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="DC13" s="3">
+        <v>0</v>
+      </c>
+      <c r="DD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="DE13" s="3">
+        <v>0</v>
+      </c>
+      <c r="DF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="DG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="DH13" s="3">
         <v>0</v>
       </c>
       <c r="DO13" s="1">
@@ -1430,7 +1805,19 @@
       <c r="BI14" s="3">
         <v>0</v>
       </c>
-      <c r="BQ14" s="1">
+      <c r="BP14" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ14" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR14" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS14" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT14" s="4">
         <v>0</v>
       </c>
       <c r="CO14" s="3">
@@ -1585,8 +1972,20 @@
       <c r="BI15" s="3">
         <v>0</v>
       </c>
-      <c r="BQ15" s="1">
-        <v>4</v>
+      <c r="BP15" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ15" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR15" s="4">
+        <v>11</v>
+      </c>
+      <c r="BS15" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT15" s="4">
+        <v>0</v>
       </c>
       <c r="CO15" s="3">
         <v>0</v>
@@ -1740,7 +2139,19 @@
       <c r="BI16" s="3">
         <v>0</v>
       </c>
-      <c r="BQ16" s="1">
+      <c r="BP16" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ16" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR16" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS16" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT16" s="4">
         <v>0</v>
       </c>
       <c r="CO16" s="3">
@@ -1895,7 +2306,19 @@
       <c r="BI17" s="3">
         <v>0</v>
       </c>
-      <c r="BQ17" s="1">
+      <c r="BP17" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ17" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR17" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS17" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT17" s="4">
         <v>0</v>
       </c>
       <c r="CO17" s="3">
@@ -2077,24 +2500,6 @@
       <c r="BI18" s="3">
         <v>0</v>
       </c>
-      <c r="BQ18" s="1">
-        <v>4</v>
-      </c>
-      <c r="BU18" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV18" s="4">
-        <v>0</v>
-      </c>
-      <c r="BW18" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX18" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY18" s="4">
-        <v>0</v>
-      </c>
       <c r="CO18" s="3">
         <v>0</v>
       </c>
@@ -2251,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="AZ19" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA19" s="3">
         <v>0</v>
@@ -2278,24 +2683,6 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3">
-        <v>0</v>
-      </c>
-      <c r="BQ19" s="1">
-        <v>0</v>
-      </c>
-      <c r="BU19" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV19" s="4">
-        <v>0</v>
-      </c>
-      <c r="BW19" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX19" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY19" s="4">
         <v>0</v>
       </c>
       <c r="CO19" s="3">
@@ -2420,6 +2807,15 @@
       <c r="AI20" s="1">
         <v>0</v>
       </c>
+      <c r="AM20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="1">
+        <v>3</v>
+      </c>
+      <c r="AO20" s="1">
+        <v>0</v>
+      </c>
       <c r="AP20" s="3">
         <v>0</v>
       </c>
@@ -2478,21 +2874,6 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3">
-        <v>0</v>
-      </c>
-      <c r="BU20" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV20" s="4">
-        <v>0</v>
-      </c>
-      <c r="BW20" s="4">
-        <v>11</v>
-      </c>
-      <c r="BX20" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY20" s="4">
         <v>0</v>
       </c>
       <c r="CO20" s="3">
@@ -2636,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="AZ21" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BA21" s="3">
         <v>0</v>
@@ -2663,21 +3044,6 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3">
-        <v>0</v>
-      </c>
-      <c r="BU21" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV21" s="4">
-        <v>0</v>
-      </c>
-      <c r="BW21" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX21" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY21" s="4">
         <v>0</v>
       </c>
       <c r="CO21" s="3">
@@ -2805,15 +3171,6 @@
       <c r="AI22" s="1">
         <v>0</v>
       </c>
-      <c r="AM22" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN22" s="1">
-        <v>3</v>
-      </c>
-      <c r="AO22" s="1">
-        <v>0</v>
-      </c>
       <c r="AP22" s="3">
         <v>0</v>
       </c>
@@ -2874,19 +3231,19 @@
       <c r="BI22" s="3">
         <v>0</v>
       </c>
-      <c r="BU22" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV22" s="4">
-        <v>0</v>
-      </c>
-      <c r="BW22" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX22" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY22" s="4">
+      <c r="CD22" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE22" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF22" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG22" s="4">
+        <v>0</v>
+      </c>
+      <c r="CH22" s="4">
         <v>0</v>
       </c>
       <c r="CO22" s="3">
@@ -2920,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="CY22" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CZ22" s="3">
         <v>0</v>
@@ -3056,6 +3413,36 @@
       <c r="BI23" s="3">
         <v>0</v>
       </c>
+      <c r="BP23" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ23" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR23" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS23" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CH23" s="4">
+        <v>0</v>
+      </c>
       <c r="CO23" s="3">
         <v>0</v>
       </c>
@@ -3087,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="CY23" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="CZ23" s="3">
         <v>0</v>
@@ -3208,22 +3595,34 @@
       <c r="BI24" s="3">
         <v>0</v>
       </c>
-      <c r="CF24" s="1">
-        <v>0</v>
-      </c>
-      <c r="CG24" s="1">
-        <v>3</v>
-      </c>
-      <c r="CH24" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI24" s="1">
-        <v>0</v>
-      </c>
-      <c r="CJ24" s="1">
-        <v>3</v>
-      </c>
-      <c r="CK24" s="1">
+      <c r="BP24" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ24" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR24" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS24" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF24" s="4">
+        <v>11</v>
+      </c>
+      <c r="CG24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CH24" s="4">
         <v>0</v>
       </c>
       <c r="CL24" s="1">
@@ -3387,6 +3786,36 @@
       <c r="BI25" s="3">
         <v>0</v>
       </c>
+      <c r="BP25" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ25" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR25" s="4">
+        <v>11</v>
+      </c>
+      <c r="BS25" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CH25" s="4">
+        <v>0</v>
+      </c>
       <c r="CO25" s="3">
         <v>0</v>
       </c>
@@ -3566,7 +3995,34 @@
       <c r="BI26" s="3">
         <v>0</v>
       </c>
-      <c r="BQ26" s="1">
+      <c r="BP26" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ26" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR26" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS26" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT26" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD26" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE26" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF26" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG26" s="4">
+        <v>0</v>
+      </c>
+      <c r="CH26" s="4">
         <v>0</v>
       </c>
       <c r="CO26" s="3">
@@ -3742,8 +4198,23 @@
       <c r="BI27" s="3">
         <v>0</v>
       </c>
-      <c r="BQ27" s="1">
-        <v>4</v>
+      <c r="BP27" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ27" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR27" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS27" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT27" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF27" s="1">
+        <v>0</v>
       </c>
       <c r="CO27" s="3">
         <v>0</v>
@@ -3909,8 +4380,23 @@
       <c r="BI28" s="3">
         <v>0</v>
       </c>
-      <c r="BQ28" s="1">
-        <v>0</v>
+      <c r="BP28" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ28" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR28" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS28" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT28" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF28" s="1">
+        <v>4</v>
       </c>
       <c r="CO28" s="3">
         <v>0</v>
@@ -4085,7 +4571,22 @@
       <c r="BI29" s="3">
         <v>0</v>
       </c>
-      <c r="BQ29" s="1">
+      <c r="BP29" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ29" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR29" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS29" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT29" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF29" s="1">
         <v>0</v>
       </c>
       <c r="CO29" s="3">
@@ -4189,82 +4690,25 @@
       <c r="AA30" s="4">
         <v>0</v>
       </c>
-      <c r="AP30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AV30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AW30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AY30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ30" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA30" s="3">
-        <v>0</v>
-      </c>
-      <c r="BB30" s="3">
-        <v>0</v>
-      </c>
-      <c r="BC30" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD30" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE30" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF30" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG30" s="3">
-        <v>0</v>
-      </c>
-      <c r="BH30" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI30" s="3">
-        <v>0</v>
-      </c>
-      <c r="BQ30" s="1">
-        <v>4</v>
-      </c>
-      <c r="CD30" s="4">
-        <v>0</v>
-      </c>
-      <c r="CE30" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF30" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG30" s="4">
-        <v>0</v>
-      </c>
-      <c r="CH30" s="4">
+      <c r="AZ30" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP30" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ30" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR30" s="4">
+        <v>11</v>
+      </c>
+      <c r="BS30" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT30" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF30" s="1">
         <v>0</v>
       </c>
       <c r="CO30" s="3">
@@ -4325,6 +4769,9 @@
         <v>0</v>
       </c>
       <c r="DH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="DO30" s="1">
         <v>0</v>
       </c>
       <c r="DT30" s="1">
@@ -4338,83 +4785,26 @@
       <c r="A31" s="1">
         <v>0</v>
       </c>
-      <c r="AP31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AV31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AW31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AY31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ31" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA31" s="3">
-        <v>0</v>
-      </c>
-      <c r="BB31" s="3">
-        <v>0</v>
-      </c>
-      <c r="BC31" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD31" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE31" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF31" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG31" s="3">
-        <v>0</v>
-      </c>
-      <c r="BH31" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI31" s="3">
-        <v>0</v>
-      </c>
-      <c r="BQ31" s="1">
-        <v>0</v>
-      </c>
-      <c r="CD31" s="4">
-        <v>0</v>
-      </c>
-      <c r="CE31" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF31" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG31" s="4">
-        <v>0</v>
-      </c>
-      <c r="CH31" s="4">
-        <v>0</v>
+      <c r="AZ31" s="1">
+        <v>4</v>
+      </c>
+      <c r="BP31" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ31" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR31" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS31" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT31" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF31" s="1">
+        <v>4</v>
       </c>
       <c r="CO31" s="3">
         <v>0</v>
@@ -4475,6 +4865,9 @@
       </c>
       <c r="DH31" s="3">
         <v>0</v>
+      </c>
+      <c r="DO31" s="1">
+        <v>4</v>
       </c>
       <c r="DT31" s="1">
         <v>0</v>
@@ -4487,25 +4880,25 @@
       <c r="A32" s="1">
         <v>0</v>
       </c>
-      <c r="BC32" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ32" s="1">
-        <v>0</v>
-      </c>
-      <c r="CD32" s="4">
-        <v>0</v>
-      </c>
-      <c r="CE32" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF32" s="4">
-        <v>11</v>
-      </c>
-      <c r="CG32" s="4">
-        <v>0</v>
-      </c>
-      <c r="CH32" s="4">
+      <c r="AZ32" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP32" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ32" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR32" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS32" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT32" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF32" s="1">
         <v>0</v>
       </c>
       <c r="CO32" s="3">
@@ -4582,89 +4975,17 @@
       <c r="A33" s="1">
         <v>0</v>
       </c>
-      <c r="BC33" s="1">
-        <v>4</v>
-      </c>
-      <c r="BQ33" s="1">
-        <v>4</v>
-      </c>
-      <c r="CD33" s="4">
-        <v>0</v>
-      </c>
-      <c r="CE33" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF33" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG33" s="4">
-        <v>0</v>
-      </c>
-      <c r="CH33" s="4">
-        <v>0</v>
-      </c>
-      <c r="CO33" s="3">
-        <v>0</v>
-      </c>
-      <c r="CP33" s="3">
-        <v>0</v>
-      </c>
-      <c r="CQ33" s="3">
-        <v>0</v>
-      </c>
-      <c r="CR33" s="3">
-        <v>0</v>
-      </c>
-      <c r="CS33" s="3">
-        <v>0</v>
-      </c>
-      <c r="CT33" s="3">
-        <v>0</v>
-      </c>
-      <c r="CU33" s="3">
-        <v>0</v>
-      </c>
-      <c r="CV33" s="3">
-        <v>0</v>
-      </c>
-      <c r="CW33" s="3">
-        <v>0</v>
-      </c>
-      <c r="CX33" s="3">
-        <v>0</v>
-      </c>
-      <c r="CY33" s="3">
-        <v>0</v>
-      </c>
-      <c r="CZ33" s="3">
-        <v>0</v>
-      </c>
-      <c r="DA33" s="3">
-        <v>0</v>
-      </c>
-      <c r="DB33" s="3">
-        <v>0</v>
-      </c>
-      <c r="DC33" s="3">
-        <v>0</v>
-      </c>
-      <c r="DD33" s="3">
-        <v>0</v>
-      </c>
-      <c r="DE33" s="3">
-        <v>0</v>
-      </c>
-      <c r="DF33" s="3">
-        <v>0</v>
-      </c>
-      <c r="DG33" s="3">
-        <v>0</v>
-      </c>
-      <c r="DH33" s="3">
+      <c r="AZ33" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR33" s="1">
+        <v>0</v>
+      </c>
+      <c r="CF33" s="1">
         <v>0</v>
       </c>
       <c r="DO33" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DT33" s="1">
         <v>4</v>
@@ -4692,29 +5013,17 @@
       <c r="A34" s="1">
         <v>0</v>
       </c>
-      <c r="BC34" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ34" s="1">
-        <v>0</v>
-      </c>
-      <c r="CD34" s="4">
-        <v>0</v>
-      </c>
-      <c r="CE34" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF34" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG34" s="4">
-        <v>0</v>
-      </c>
-      <c r="CH34" s="4">
-        <v>0</v>
+      <c r="AZ34" s="1">
+        <v>4</v>
+      </c>
+      <c r="BR34" s="1">
+        <v>4</v>
+      </c>
+      <c r="CF34" s="1">
+        <v>4</v>
       </c>
       <c r="DO34" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DT34" s="1">
         <v>0</v>
@@ -4742,10 +5051,10 @@
       <c r="A35" s="1">
         <v>0</v>
       </c>
-      <c r="BC35" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ35" s="1">
+      <c r="AZ35" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR35" s="1">
         <v>0</v>
       </c>
       <c r="CF35" s="1">
@@ -4780,17 +5089,17 @@
       <c r="A36" s="1">
         <v>0</v>
       </c>
-      <c r="BC36" s="1">
-        <v>4</v>
-      </c>
-      <c r="BQ36" s="1">
-        <v>4</v>
+      <c r="AZ36" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR36" s="1">
+        <v>0</v>
       </c>
       <c r="CF36" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DO36" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DT36" s="1">
         <v>4</v>
@@ -4818,17 +5127,17 @@
       <c r="A37" s="1">
         <v>0</v>
       </c>
-      <c r="BC37" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ37" s="1">
-        <v>0</v>
+      <c r="AZ37" s="1">
+        <v>4</v>
+      </c>
+      <c r="BR37" s="1">
+        <v>4</v>
       </c>
       <c r="CF37" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DO37" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DT37" s="1">
         <v>0</v>
@@ -4856,13 +5165,13 @@
       <c r="A38" s="1">
         <v>0</v>
       </c>
-      <c r="BC38" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ38" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE38" s="1">
+      <c r="AZ38" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR38" s="1">
+        <v>0</v>
+      </c>
+      <c r="CF38" s="1">
         <v>0</v>
       </c>
       <c r="DO38" s="1">
@@ -4894,17 +5203,17 @@
       <c r="A39" s="1">
         <v>0</v>
       </c>
-      <c r="BC39" s="1">
-        <v>4</v>
-      </c>
-      <c r="BQ39" s="1">
-        <v>4</v>
-      </c>
-      <c r="CD39" s="1">
-        <v>5</v>
+      <c r="AZ39" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR39" s="1">
+        <v>0</v>
+      </c>
+      <c r="CF39" s="1">
+        <v>0</v>
       </c>
       <c r="DO39" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DT39" s="1">
         <v>4</v>
@@ -4932,17 +5241,17 @@
       <c r="A40" s="1">
         <v>0</v>
       </c>
-      <c r="BC40" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ40" s="1">
-        <v>0</v>
-      </c>
-      <c r="CC40" s="1">
-        <v>0</v>
+      <c r="AZ40" s="1">
+        <v>4</v>
+      </c>
+      <c r="BR40" s="1">
+        <v>4</v>
+      </c>
+      <c r="CF40" s="1">
+        <v>4</v>
       </c>
       <c r="DO40" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DT40" s="1">
         <v>0</v>
@@ -4970,13 +5279,13 @@
       <c r="A41" s="1">
         <v>0</v>
       </c>
-      <c r="BC41" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ41" s="1">
-        <v>0</v>
-      </c>
-      <c r="CB41" s="1">
+      <c r="AZ41" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR41" s="1">
+        <v>0</v>
+      </c>
+      <c r="CF41" s="1">
         <v>0</v>
       </c>
       <c r="DO41" s="1">
@@ -5008,17 +5317,212 @@
       <c r="A42" s="1">
         <v>0</v>
       </c>
+      <c r="AY42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ42" s="1">
+        <v>3</v>
+      </c>
+      <c r="BA42" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB42" s="1">
+        <v>0</v>
+      </c>
       <c r="BC42" s="1">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="BD42" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE42" s="5">
+        <v>0</v>
+      </c>
+      <c r="BF42" s="5">
+        <v>7</v>
+      </c>
+      <c r="BG42" s="5">
+        <v>0</v>
+      </c>
+      <c r="BH42" s="5">
+        <v>0</v>
+      </c>
+      <c r="BI42" s="5">
+        <v>7</v>
+      </c>
+      <c r="BJ42" s="5">
+        <v>0</v>
+      </c>
+      <c r="BK42" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL42" s="1">
+        <v>3</v>
+      </c>
+      <c r="BM42" s="1">
+        <v>0</v>
+      </c>
+      <c r="BN42" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO42" s="1">
+        <v>3</v>
+      </c>
+      <c r="BP42" s="1">
+        <v>0</v>
       </c>
       <c r="BQ42" s="1">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="BR42" s="1">
+        <v>3</v>
+      </c>
+      <c r="BS42" s="1">
+        <v>0</v>
+      </c>
+      <c r="BT42" s="1">
+        <v>0</v>
+      </c>
+      <c r="BU42" s="1">
+        <v>3</v>
+      </c>
+      <c r="BV42" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW42" s="5">
+        <v>0</v>
+      </c>
+      <c r="BX42" s="5">
+        <v>7</v>
+      </c>
+      <c r="BY42" s="5">
+        <v>0</v>
+      </c>
+      <c r="BZ42" s="1">
+        <v>0</v>
       </c>
       <c r="CA42" s="1">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="CB42" s="1">
+        <v>0</v>
+      </c>
+      <c r="CC42" s="1">
+        <v>0</v>
+      </c>
+      <c r="CD42" s="1">
+        <v>3</v>
+      </c>
+      <c r="CE42" s="1">
+        <v>0</v>
+      </c>
+      <c r="CF42" s="1">
+        <v>0</v>
+      </c>
+      <c r="CG42" s="1">
+        <v>3</v>
+      </c>
+      <c r="CH42" s="1">
+        <v>0</v>
+      </c>
+      <c r="CI42" s="1">
+        <v>0</v>
+      </c>
+      <c r="CJ42" s="1">
+        <v>3</v>
+      </c>
+      <c r="CK42" s="1">
+        <v>0</v>
+      </c>
+      <c r="CL42" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM42" s="1">
+        <v>3</v>
+      </c>
+      <c r="CN42" s="1">
+        <v>0</v>
+      </c>
+      <c r="CO42" s="1">
+        <v>0</v>
+      </c>
+      <c r="CP42" s="1">
+        <v>3</v>
+      </c>
+      <c r="CQ42" s="1">
+        <v>0</v>
+      </c>
+      <c r="CR42" s="1">
+        <v>0</v>
+      </c>
+      <c r="CS42" s="1">
+        <v>3</v>
+      </c>
+      <c r="CT42" s="1">
+        <v>0</v>
+      </c>
+      <c r="CU42" s="1">
+        <v>0</v>
+      </c>
+      <c r="CV42" s="1">
+        <v>3</v>
+      </c>
+      <c r="CW42" s="1">
+        <v>0</v>
+      </c>
+      <c r="CX42" s="1">
+        <v>0</v>
+      </c>
+      <c r="CY42" s="1">
+        <v>3</v>
+      </c>
+      <c r="CZ42" s="1">
+        <v>0</v>
+      </c>
+      <c r="DA42" s="1">
+        <v>0</v>
+      </c>
+      <c r="DB42" s="1">
+        <v>3</v>
+      </c>
+      <c r="DC42" s="1">
+        <v>0</v>
+      </c>
+      <c r="DD42" s="1">
+        <v>0</v>
+      </c>
+      <c r="DE42" s="1">
+        <v>3</v>
+      </c>
+      <c r="DF42" s="1">
+        <v>0</v>
+      </c>
+      <c r="DG42" s="1">
+        <v>0</v>
+      </c>
+      <c r="DH42" s="1">
+        <v>3</v>
+      </c>
+      <c r="DI42" s="1">
+        <v>0</v>
+      </c>
+      <c r="DJ42" s="1">
+        <v>0</v>
+      </c>
+      <c r="DK42" s="1">
+        <v>3</v>
+      </c>
+      <c r="DL42" s="1">
+        <v>0</v>
+      </c>
+      <c r="DM42" s="1">
+        <v>0</v>
+      </c>
+      <c r="DN42" s="1">
+        <v>3</v>
       </c>
       <c r="DO42" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DT42" s="1">
         <v>4</v>
@@ -5046,16 +5550,7 @@
       <c r="A43" s="1">
         <v>0</v>
       </c>
-      <c r="BC43" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ43" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ43" s="1">
-        <v>0</v>
-      </c>
-      <c r="DO43" s="1">
+      <c r="BM43" s="1">
         <v>0</v>
       </c>
       <c r="DT43" s="1">
@@ -5114,212 +5609,8 @@
       <c r="AU44" s="1">
         <v>0</v>
       </c>
-      <c r="AV44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AW44" s="1">
-        <v>3</v>
-      </c>
-      <c r="AX44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC44" s="1">
-        <v>3</v>
-      </c>
-      <c r="BD44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BE44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BF44" s="1">
-        <v>3</v>
-      </c>
-      <c r="BG44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BH44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI44" s="1">
-        <v>3</v>
-      </c>
-      <c r="BJ44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK44" s="5">
-        <v>0</v>
-      </c>
-      <c r="BL44" s="5">
-        <v>7</v>
-      </c>
-      <c r="BM44" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO44" s="1">
-        <v>3</v>
-      </c>
-      <c r="BP44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BR44" s="1">
-        <v>3</v>
-      </c>
-      <c r="BS44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BT44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BU44" s="1">
-        <v>3</v>
-      </c>
-      <c r="BV44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW44" s="5">
-        <v>0</v>
-      </c>
-      <c r="BX44" s="5">
-        <v>7</v>
-      </c>
-      <c r="BY44" s="5">
-        <v>0</v>
-      </c>
-      <c r="BZ44" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA44" s="1">
-        <v>3</v>
-      </c>
-      <c r="CB44" s="1">
-        <v>0</v>
-      </c>
-      <c r="CC44" s="1">
-        <v>0</v>
-      </c>
-      <c r="CD44" s="1">
-        <v>3</v>
-      </c>
-      <c r="CE44" s="1">
-        <v>0</v>
-      </c>
-      <c r="CF44" s="1">
-        <v>0</v>
-      </c>
-      <c r="CG44" s="1">
-        <v>3</v>
-      </c>
-      <c r="CH44" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI44" s="1">
-        <v>0</v>
-      </c>
-      <c r="CJ44" s="1">
-        <v>3</v>
-      </c>
-      <c r="CK44" s="1">
-        <v>0</v>
-      </c>
-      <c r="CL44" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM44" s="1">
-        <v>3</v>
-      </c>
-      <c r="CN44" s="1">
-        <v>0</v>
-      </c>
-      <c r="CO44" s="1">
-        <v>0</v>
-      </c>
-      <c r="CP44" s="1">
-        <v>3</v>
-      </c>
-      <c r="CQ44" s="1">
-        <v>0</v>
-      </c>
-      <c r="CR44" s="1">
-        <v>0</v>
-      </c>
-      <c r="CS44" s="1">
-        <v>3</v>
-      </c>
-      <c r="CT44" s="1">
-        <v>0</v>
-      </c>
-      <c r="CU44" s="1">
-        <v>0</v>
-      </c>
-      <c r="CV44" s="1">
-        <v>3</v>
-      </c>
-      <c r="CW44" s="1">
-        <v>0</v>
-      </c>
-      <c r="CX44" s="1">
-        <v>0</v>
-      </c>
-      <c r="CY44" s="1">
-        <v>3</v>
-      </c>
-      <c r="CZ44" s="1">
-        <v>0</v>
-      </c>
-      <c r="DA44" s="1">
-        <v>0</v>
-      </c>
-      <c r="DB44" s="1">
-        <v>3</v>
-      </c>
-      <c r="DC44" s="1">
-        <v>0</v>
-      </c>
-      <c r="DD44" s="1">
-        <v>0</v>
-      </c>
-      <c r="DE44" s="1">
-        <v>3</v>
-      </c>
-      <c r="DF44" s="1">
-        <v>0</v>
-      </c>
-      <c r="DG44" s="1">
-        <v>0</v>
-      </c>
-      <c r="DH44" s="1">
-        <v>3</v>
-      </c>
-      <c r="DI44" s="1">
-        <v>0</v>
-      </c>
-      <c r="DJ44" s="1">
-        <v>0</v>
-      </c>
-      <c r="DK44" s="1">
-        <v>3</v>
-      </c>
-      <c r="DL44" s="1">
-        <v>0</v>
-      </c>
-      <c r="DM44" s="1">
-        <v>0</v>
-      </c>
-      <c r="DN44" s="1">
-        <v>3</v>
-      </c>
-      <c r="DO44" s="1">
-        <v>0</v>
+      <c r="BM44" s="1">
+        <v>4</v>
       </c>
       <c r="DT44" s="1">
         <v>0</v>
@@ -5350,7 +5641,7 @@
       <c r="AG45" s="1">
         <v>0</v>
       </c>
-      <c r="BN45" s="1">
+      <c r="BM45" s="1">
         <v>0</v>
       </c>
       <c r="DY45" s="1">
@@ -5367,8 +5658,20 @@
       <c r="AG46" s="1">
         <v>4</v>
       </c>
-      <c r="BN46" s="1">
-        <v>4</v>
+      <c r="BK46" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL46" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM46" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN46" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO46" s="4">
+        <v>0</v>
       </c>
       <c r="DY46" s="1">
         <v>4</v>
@@ -5444,7 +5747,19 @@
       <c r="AG47" s="1">
         <v>0</v>
       </c>
-      <c r="BN47" s="1">
+      <c r="BK47" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL47" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM47" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN47" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO47" s="4">
         <v>0</v>
       </c>
       <c r="DY47" s="1">
@@ -5521,7 +5836,19 @@
       <c r="AG48" s="1">
         <v>0</v>
       </c>
-      <c r="BN48" s="1">
+      <c r="BK48" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL48" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM48" s="4">
+        <v>11</v>
+      </c>
+      <c r="BN48" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO48" s="4">
         <v>0</v>
       </c>
       <c r="DY48" s="1">
@@ -5598,8 +5925,20 @@
       <c r="AG49" s="1">
         <v>4</v>
       </c>
-      <c r="BN49" s="1">
-        <v>4</v>
+      <c r="BK49" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL49" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM49" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN49" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO49" s="4">
+        <v>0</v>
       </c>
       <c r="DY49" s="1">
         <v>4</v>
@@ -5675,7 +6014,19 @@
       <c r="AG50" s="1">
         <v>0</v>
       </c>
-      <c r="BN50" s="1">
+      <c r="BK50" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL50" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM50" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN50" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO50" s="4">
         <v>0</v>
       </c>
       <c r="DY50" s="1">
@@ -5752,7 +6103,19 @@
       <c r="AG51" s="1">
         <v>0</v>
       </c>
-      <c r="BN51" s="1">
+      <c r="BK51" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL51" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM51" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN51" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO51" s="4">
         <v>0</v>
       </c>
       <c r="DY51" s="1">
@@ -5829,8 +6192,20 @@
       <c r="AG52" s="1">
         <v>4</v>
       </c>
-      <c r="BN52" s="1">
-        <v>4</v>
+      <c r="BK52" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL52" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM52" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN52" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO52" s="4">
+        <v>0</v>
       </c>
       <c r="DY52" s="1">
         <v>4</v>
@@ -5906,7 +6281,19 @@
       <c r="AG53" s="1">
         <v>0</v>
       </c>
-      <c r="BN53" s="1">
+      <c r="BK53" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL53" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM53" s="4">
+        <v>11</v>
+      </c>
+      <c r="BN53" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO53" s="4">
         <v>0</v>
       </c>
       <c r="DY53" s="1">
@@ -5983,7 +6370,34 @@
       <c r="AG54" s="1">
         <v>0</v>
       </c>
-      <c r="BN54" s="1">
+      <c r="BK54" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL54" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM54" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN54" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO54" s="4">
+        <v>0</v>
+      </c>
+      <c r="DF54" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG54" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH54" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI54" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ54" s="4">
         <v>0</v>
       </c>
       <c r="DY54" s="1">
@@ -6060,8 +6474,35 @@
       <c r="AG55" s="1">
         <v>4</v>
       </c>
-      <c r="BN55" s="1">
-        <v>4</v>
+      <c r="BK55" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL55" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM55" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN55" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO55" s="4">
+        <v>0</v>
+      </c>
+      <c r="DF55" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG55" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH55" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI55" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ55" s="4">
+        <v>0</v>
       </c>
       <c r="DY55" s="1">
         <v>4</v>
@@ -6137,7 +6578,151 @@
       <c r="AG56" s="1">
         <v>0</v>
       </c>
-      <c r="BN56" s="1">
+      <c r="BK56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY56" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC56" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD56" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE56" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF56" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG56" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK56" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL56" s="4">
+        <v>0</v>
+      </c>
+      <c r="CM56" s="4">
+        <v>0</v>
+      </c>
+      <c r="CN56" s="4">
+        <v>0</v>
+      </c>
+      <c r="CO56" s="4">
+        <v>0</v>
+      </c>
+      <c r="CS56" s="4">
+        <v>0</v>
+      </c>
+      <c r="CT56" s="4">
+        <v>0</v>
+      </c>
+      <c r="CU56" s="4">
+        <v>0</v>
+      </c>
+      <c r="CV56" s="4">
+        <v>0</v>
+      </c>
+      <c r="CW56" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA56" s="4">
+        <v>0</v>
+      </c>
+      <c r="DB56" s="4">
+        <v>0</v>
+      </c>
+      <c r="DC56" s="4">
+        <v>0</v>
+      </c>
+      <c r="DD56" s="4">
+        <v>0</v>
+      </c>
+      <c r="DE56" s="4">
+        <v>0</v>
+      </c>
+      <c r="DF56" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG56" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH56" s="4">
+        <v>11</v>
+      </c>
+      <c r="DI56" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ56" s="4">
+        <v>0</v>
+      </c>
+      <c r="DK56" s="1">
+        <v>0</v>
+      </c>
+      <c r="DL56" s="1">
+        <v>3</v>
+      </c>
+      <c r="DM56" s="1">
+        <v>0</v>
+      </c>
+      <c r="DN56" s="1">
+        <v>0</v>
+      </c>
+      <c r="DO56" s="1">
+        <v>3</v>
+      </c>
+      <c r="DP56" s="1">
+        <v>0</v>
+      </c>
+      <c r="DQ56" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR56" s="1">
+        <v>3</v>
+      </c>
+      <c r="DS56" s="1">
         <v>0</v>
       </c>
       <c r="DY56" s="1">
@@ -6247,7 +6832,127 @@
       <c r="AR57" s="4">
         <v>0</v>
       </c>
-      <c r="BN57" s="1">
+      <c r="BK57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY57" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC57" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD57" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE57" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF57" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG57" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK57" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL57" s="4">
+        <v>0</v>
+      </c>
+      <c r="CM57" s="4">
+        <v>0</v>
+      </c>
+      <c r="CN57" s="4">
+        <v>0</v>
+      </c>
+      <c r="CO57" s="4">
+        <v>0</v>
+      </c>
+      <c r="CS57" s="4">
+        <v>0</v>
+      </c>
+      <c r="CT57" s="4">
+        <v>0</v>
+      </c>
+      <c r="CU57" s="4">
+        <v>0</v>
+      </c>
+      <c r="CV57" s="4">
+        <v>0</v>
+      </c>
+      <c r="CW57" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA57" s="4">
+        <v>0</v>
+      </c>
+      <c r="DB57" s="4">
+        <v>0</v>
+      </c>
+      <c r="DC57" s="4">
+        <v>0</v>
+      </c>
+      <c r="DD57" s="4">
+        <v>0</v>
+      </c>
+      <c r="DE57" s="4">
+        <v>0</v>
+      </c>
+      <c r="DF57" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG57" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH57" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI57" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ57" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS57" s="1">
         <v>0</v>
       </c>
       <c r="DY57" s="1">
@@ -6354,88 +7059,97 @@
       <c r="AR58" s="4">
         <v>0</v>
       </c>
-      <c r="BN58" s="1">
-        <v>4</v>
-      </c>
-      <c r="BO58" s="1">
-        <v>0</v>
-      </c>
-      <c r="BP58" s="1">
+      <c r="BK58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM58" s="4">
+        <v>11</v>
+      </c>
+      <c r="BN58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR58" s="4">
+        <v>11</v>
+      </c>
+      <c r="BS58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW58" s="4">
+        <v>11</v>
+      </c>
+      <c r="BX58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ58" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA58" s="1">
         <v>3</v>
       </c>
-      <c r="BQ58" s="1">
-        <v>0</v>
-      </c>
-      <c r="BR58" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS58" s="1">
+      <c r="CB58" s="1">
+        <v>0</v>
+      </c>
+      <c r="CC58" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD58" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE58" s="4">
+        <v>11</v>
+      </c>
+      <c r="CF58" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG58" s="4">
+        <v>0</v>
+      </c>
+      <c r="CH58" s="1">
+        <v>0</v>
+      </c>
+      <c r="CI58" s="1">
         <v>3</v>
       </c>
-      <c r="BT58" s="1">
-        <v>0</v>
-      </c>
-      <c r="BU58" s="1">
-        <v>0</v>
-      </c>
-      <c r="BV58" s="1">
-        <v>3</v>
-      </c>
-      <c r="BW58" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX58" s="1">
-        <v>0</v>
-      </c>
-      <c r="BY58" s="1">
-        <v>3</v>
-      </c>
-      <c r="BZ58" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA58" s="1">
-        <v>0</v>
-      </c>
-      <c r="CB58" s="1">
-        <v>3</v>
-      </c>
-      <c r="CC58" s="1">
-        <v>0</v>
-      </c>
-      <c r="CD58" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE58" s="1">
-        <v>3</v>
-      </c>
-      <c r="CF58" s="1">
-        <v>0</v>
-      </c>
-      <c r="CG58" s="1">
-        <v>0</v>
-      </c>
-      <c r="CH58" s="1">
-        <v>3</v>
-      </c>
-      <c r="CI58" s="1">
-        <v>0</v>
-      </c>
       <c r="CJ58" s="1">
         <v>0</v>
       </c>
-      <c r="CK58" s="1">
-        <v>3</v>
-      </c>
-      <c r="CL58" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM58" s="1">
-        <v>0</v>
-      </c>
-      <c r="CN58" s="1">
-        <v>3</v>
-      </c>
-      <c r="CO58" s="1">
+      <c r="CK58" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL58" s="4">
+        <v>0</v>
+      </c>
+      <c r="CM58" s="4">
+        <v>11</v>
+      </c>
+      <c r="CN58" s="4">
+        <v>0</v>
+      </c>
+      <c r="CO58" s="4">
         <v>0</v>
       </c>
       <c r="CP58" s="1">
@@ -6447,86 +7161,62 @@
       <c r="CR58" s="1">
         <v>0</v>
       </c>
-      <c r="CS58" s="1">
-        <v>0</v>
-      </c>
-      <c r="CT58" s="1">
+      <c r="CS58" s="4">
+        <v>0</v>
+      </c>
+      <c r="CT58" s="4">
+        <v>0</v>
+      </c>
+      <c r="CU58" s="4">
+        <v>11</v>
+      </c>
+      <c r="CV58" s="4">
+        <v>0</v>
+      </c>
+      <c r="CW58" s="4">
+        <v>0</v>
+      </c>
+      <c r="CX58" s="1">
+        <v>0</v>
+      </c>
+      <c r="CY58" s="1">
         <v>3</v>
       </c>
-      <c r="CU58" s="1">
-        <v>0</v>
-      </c>
-      <c r="CV58" s="1">
-        <v>0</v>
-      </c>
-      <c r="CW58" s="1">
-        <v>3</v>
-      </c>
-      <c r="CX58" s="1">
-        <v>0</v>
-      </c>
-      <c r="CY58" s="1">
-        <v>0</v>
-      </c>
       <c r="CZ58" s="1">
-        <v>3</v>
-      </c>
-      <c r="DA58" s="1">
-        <v>0</v>
-      </c>
-      <c r="DB58" s="1">
-        <v>0</v>
-      </c>
-      <c r="DC58" s="1">
-        <v>3</v>
-      </c>
-      <c r="DD58" s="1">
-        <v>0</v>
-      </c>
-      <c r="DE58" s="1">
-        <v>0</v>
-      </c>
-      <c r="DF58" s="1">
-        <v>3</v>
-      </c>
-      <c r="DG58" s="1">
-        <v>0</v>
-      </c>
-      <c r="DH58" s="1">
-        <v>0</v>
-      </c>
-      <c r="DI58" s="1">
-        <v>3</v>
-      </c>
-      <c r="DJ58" s="1">
-        <v>0</v>
-      </c>
-      <c r="DK58" s="1">
-        <v>0</v>
-      </c>
-      <c r="DL58" s="1">
-        <v>3</v>
-      </c>
-      <c r="DM58" s="1">
-        <v>0</v>
-      </c>
-      <c r="DN58" s="1">
-        <v>0</v>
-      </c>
-      <c r="DO58" s="1">
-        <v>3</v>
-      </c>
-      <c r="DP58" s="1">
-        <v>0</v>
-      </c>
-      <c r="DQ58" s="1">
-        <v>0</v>
-      </c>
-      <c r="DR58" s="1">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="DA58" s="4">
+        <v>0</v>
+      </c>
+      <c r="DB58" s="4">
+        <v>0</v>
+      </c>
+      <c r="DC58" s="4">
+        <v>11</v>
+      </c>
+      <c r="DD58" s="4">
+        <v>0</v>
+      </c>
+      <c r="DE58" s="4">
+        <v>0</v>
+      </c>
+      <c r="DF58" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG58" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH58" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI58" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ58" s="4">
+        <v>0</v>
       </c>
       <c r="DS58" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY58" s="1">
         <v>4</v>
@@ -6686,19 +7376,124 @@
       <c r="BJ59" s="1">
         <v>0</v>
       </c>
-      <c r="BK59" s="1">
-        <v>0</v>
-      </c>
-      <c r="BL59" s="1">
-        <v>3</v>
-      </c>
-      <c r="BM59" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN59" s="1">
-        <v>0</v>
-      </c>
-      <c r="DM59" s="1">
+      <c r="BK59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY59" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC59" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD59" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE59" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF59" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG59" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK59" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL59" s="4">
+        <v>0</v>
+      </c>
+      <c r="CM59" s="4">
+        <v>0</v>
+      </c>
+      <c r="CN59" s="4">
+        <v>0</v>
+      </c>
+      <c r="CO59" s="4">
+        <v>0</v>
+      </c>
+      <c r="CS59" s="4">
+        <v>0</v>
+      </c>
+      <c r="CT59" s="4">
+        <v>0</v>
+      </c>
+      <c r="CU59" s="4">
+        <v>0</v>
+      </c>
+      <c r="CV59" s="4">
+        <v>0</v>
+      </c>
+      <c r="CW59" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA59" s="4">
+        <v>0</v>
+      </c>
+      <c r="DB59" s="4">
+        <v>0</v>
+      </c>
+      <c r="DC59" s="4">
+        <v>0</v>
+      </c>
+      <c r="DD59" s="4">
+        <v>0</v>
+      </c>
+      <c r="DE59" s="4">
+        <v>0</v>
+      </c>
+      <c r="DF59" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG59" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH59" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI59" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ59" s="4">
         <v>0</v>
       </c>
       <c r="DS59" s="1">
@@ -6808,14 +7603,131 @@
       <c r="AR60" s="4">
         <v>0</v>
       </c>
-      <c r="BI60" s="1">
-        <v>0</v>
-      </c>
-      <c r="DM60" s="1">
-        <v>4</v>
+      <c r="BJ60" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY60" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC60" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD60" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE60" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF60" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG60" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK60" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL60" s="4">
+        <v>0</v>
+      </c>
+      <c r="CM60" s="4">
+        <v>0</v>
+      </c>
+      <c r="CN60" s="4">
+        <v>0</v>
+      </c>
+      <c r="CO60" s="4">
+        <v>0</v>
+      </c>
+      <c r="CS60" s="4">
+        <v>0</v>
+      </c>
+      <c r="CT60" s="4">
+        <v>0</v>
+      </c>
+      <c r="CU60" s="4">
+        <v>0</v>
+      </c>
+      <c r="CV60" s="4">
+        <v>0</v>
+      </c>
+      <c r="CW60" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA60" s="4">
+        <v>0</v>
+      </c>
+      <c r="DB60" s="4">
+        <v>0</v>
+      </c>
+      <c r="DC60" s="4">
+        <v>0</v>
+      </c>
+      <c r="DD60" s="4">
+        <v>0</v>
+      </c>
+      <c r="DE60" s="4">
+        <v>0</v>
+      </c>
+      <c r="DF60" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG60" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH60" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI60" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ60" s="4">
+        <v>0</v>
       </c>
       <c r="DS60" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY60" s="1">
         <v>0</v>
@@ -6921,14 +7833,26 @@
       <c r="AR61" s="4">
         <v>0</v>
       </c>
-      <c r="BI61" s="1">
+      <c r="BJ61" s="1">
         <v>4</v>
       </c>
-      <c r="DM61" s="1">
+      <c r="DF61" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG61" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH61" s="4">
+        <v>11</v>
+      </c>
+      <c r="DI61" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ61" s="4">
         <v>0</v>
       </c>
       <c r="DS61" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY61" s="1">
         <v>4</v>
@@ -7019,10 +7943,22 @@
       <c r="AG62" s="1">
         <v>0</v>
       </c>
-      <c r="BI62" s="1">
-        <v>0</v>
-      </c>
-      <c r="DM62" s="1">
+      <c r="BJ62" s="1">
+        <v>0</v>
+      </c>
+      <c r="DF62" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG62" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH62" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI62" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ62" s="4">
         <v>0</v>
       </c>
       <c r="DS62" s="1">
@@ -7102,14 +8038,26 @@
       <c r="AG63" s="1">
         <v>0</v>
       </c>
-      <c r="BI63" s="1">
-        <v>0</v>
-      </c>
-      <c r="DM63" s="1">
-        <v>4</v>
+      <c r="BJ63" s="1">
+        <v>0</v>
+      </c>
+      <c r="DF63" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG63" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH63" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI63" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ63" s="4">
+        <v>0</v>
       </c>
       <c r="DS63" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY63" s="1">
         <v>0</v>
@@ -7185,14 +8133,26 @@
       <c r="AG64" s="1">
         <v>4</v>
       </c>
-      <c r="BI64" s="1">
+      <c r="BJ64" s="1">
         <v>4</v>
       </c>
-      <c r="DM64" s="1">
+      <c r="DF64" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG64" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH64" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI64" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ64" s="4">
         <v>0</v>
       </c>
       <c r="DS64" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY64" s="1">
         <v>4</v>
@@ -7268,10 +8228,22 @@
       <c r="AG65" s="1">
         <v>0</v>
       </c>
-      <c r="BI65" s="1">
-        <v>0</v>
-      </c>
-      <c r="DM65" s="1">
+      <c r="BJ65" s="1">
+        <v>0</v>
+      </c>
+      <c r="DF65" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG65" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH65" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI65" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ65" s="4">
         <v>0</v>
       </c>
       <c r="DS65" s="1">
@@ -7351,7 +8323,7 @@
       <c r="AG66" s="1">
         <v>0</v>
       </c>
-      <c r="BI66" s="1">
+      <c r="BJ66" s="1">
         <v>0</v>
       </c>
       <c r="BP66" s="3">
@@ -7414,11 +8386,35 @@
       <c r="CI66" s="3">
         <v>0</v>
       </c>
-      <c r="DM66" s="1">
-        <v>4</v>
-      </c>
-      <c r="DS66" s="1">
-        <v>4</v>
+      <c r="DF66" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG66" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH66" s="4">
+        <v>11</v>
+      </c>
+      <c r="DI66" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ66" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ66" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR66" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS66" s="4">
+        <v>0</v>
+      </c>
+      <c r="DT66" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU66" s="4">
+        <v>0</v>
       </c>
       <c r="DY66" s="1">
         <v>0</v>
@@ -7437,7 +8433,7 @@
       <c r="AG67" s="1">
         <v>4</v>
       </c>
-      <c r="BI67" s="1">
+      <c r="BJ67" s="1">
         <v>4</v>
       </c>
       <c r="BP67" s="3">
@@ -7500,10 +8496,34 @@
       <c r="CI67" s="3">
         <v>0</v>
       </c>
-      <c r="DM67" s="1">
-        <v>0</v>
-      </c>
-      <c r="DS67" s="1">
+      <c r="DF67" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG67" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH67" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI67" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ67" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ67" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR67" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS67" s="4">
+        <v>0</v>
+      </c>
+      <c r="DT67" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU67" s="4">
         <v>0</v>
       </c>
       <c r="DY67" s="1">
@@ -7523,7 +8543,7 @@
       <c r="AG68" s="1">
         <v>0</v>
       </c>
-      <c r="BI68" s="1">
+      <c r="BJ68" s="1">
         <v>0</v>
       </c>
       <c r="BP68" s="3">
@@ -7586,10 +8606,34 @@
       <c r="CI68" s="3">
         <v>0</v>
       </c>
-      <c r="DM68" s="1">
-        <v>0</v>
-      </c>
-      <c r="DS68" s="1">
+      <c r="DF68" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG68" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH68" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI68" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ68" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ68" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR68" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS68" s="4">
+        <v>11</v>
+      </c>
+      <c r="DT68" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU68" s="4">
         <v>0</v>
       </c>
       <c r="DY68" s="1">
@@ -7609,7 +8653,7 @@
       <c r="AG69" s="1">
         <v>0</v>
       </c>
-      <c r="BI69" s="1">
+      <c r="BJ69" s="1">
         <v>0</v>
       </c>
       <c r="BP69" s="3">
@@ -7672,11 +8716,23 @@
       <c r="CI69" s="3">
         <v>0</v>
       </c>
-      <c r="DM69" s="1">
-        <v>4</v>
-      </c>
-      <c r="DS69" s="1">
-        <v>4</v>
+      <c r="DH69" s="1">
+        <v>0</v>
+      </c>
+      <c r="DQ69" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR69" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS69" s="4">
+        <v>0</v>
+      </c>
+      <c r="DT69" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU69" s="4">
+        <v>0</v>
       </c>
       <c r="DY69" s="1">
         <v>0</v>
@@ -7695,7 +8751,7 @@
       <c r="AG70" s="1">
         <v>4</v>
       </c>
-      <c r="BI70" s="1">
+      <c r="BJ70" s="1">
         <v>4</v>
       </c>
       <c r="BP70" s="3">
@@ -7758,10 +8814,22 @@
       <c r="CI70" s="3">
         <v>0</v>
       </c>
-      <c r="DM70" s="1">
-        <v>0</v>
-      </c>
-      <c r="DS70" s="1">
+      <c r="DH70" s="1">
+        <v>4</v>
+      </c>
+      <c r="DQ70" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR70" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS70" s="4">
+        <v>0</v>
+      </c>
+      <c r="DT70" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU70" s="4">
         <v>0</v>
       </c>
       <c r="DY70" s="1">
@@ -7781,7 +8849,7 @@
       <c r="AG71" s="1">
         <v>0</v>
       </c>
-      <c r="BI71" s="1">
+      <c r="BJ71" s="1">
         <v>0</v>
       </c>
       <c r="BP71" s="3">
@@ -7842,6 +8910,15 @@
         <v>0</v>
       </c>
       <c r="CI71" s="3">
+        <v>0</v>
+      </c>
+      <c r="CP71" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ71" s="1">
+        <v>3</v>
+      </c>
+      <c r="CR71" s="1">
         <v>0</v>
       </c>
       <c r="CS71" s="1">
@@ -7890,21 +8967,6 @@
         <v>0</v>
       </c>
       <c r="DH71" s="1">
-        <v>0</v>
-      </c>
-      <c r="DI71" s="1">
-        <v>3</v>
-      </c>
-      <c r="DJ71" s="1">
-        <v>0</v>
-      </c>
-      <c r="DK71" s="1">
-        <v>0</v>
-      </c>
-      <c r="DL71" s="1">
-        <v>3</v>
-      </c>
-      <c r="DM71" s="1">
         <v>0</v>
       </c>
       <c r="DS71" s="1">
@@ -8474,7 +9536,34 @@
       <c r="CI77" s="3">
         <v>0</v>
       </c>
-      <c r="DS77" s="1">
+      <c r="CJ77" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK77" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL77" s="4">
+        <v>0</v>
+      </c>
+      <c r="CM77" s="4">
+        <v>0</v>
+      </c>
+      <c r="CN77" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ77" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR77" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS77" s="4">
+        <v>0</v>
+      </c>
+      <c r="DT77" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU77" s="4">
         <v>0</v>
       </c>
       <c r="DY77" s="1">
@@ -8602,8 +9691,35 @@
       <c r="CI78" s="3">
         <v>0</v>
       </c>
-      <c r="DS78" s="1">
-        <v>4</v>
+      <c r="CJ78" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK78" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL78" s="4">
+        <v>0</v>
+      </c>
+      <c r="CM78" s="4">
+        <v>0</v>
+      </c>
+      <c r="CN78" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ78" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR78" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS78" s="4">
+        <v>0</v>
+      </c>
+      <c r="DT78" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU78" s="4">
+        <v>0</v>
       </c>
       <c r="DY78" s="1">
         <v>0</v>
@@ -8706,7 +9822,97 @@
       <c r="CI79" s="3">
         <v>0</v>
       </c>
-      <c r="DS79" s="1">
+      <c r="CJ79" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK79" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL79" s="4">
+        <v>11</v>
+      </c>
+      <c r="CM79" s="4">
+        <v>0</v>
+      </c>
+      <c r="CN79" s="4">
+        <v>0</v>
+      </c>
+      <c r="CO79" s="1">
+        <v>0</v>
+      </c>
+      <c r="CP79" s="1">
+        <v>3</v>
+      </c>
+      <c r="CQ79" s="1">
+        <v>0</v>
+      </c>
+      <c r="CR79" s="5">
+        <v>0</v>
+      </c>
+      <c r="CS79" s="5">
+        <v>7</v>
+      </c>
+      <c r="CT79" s="5">
+        <v>0</v>
+      </c>
+      <c r="CU79" s="5">
+        <v>0</v>
+      </c>
+      <c r="CV79" s="5">
+        <v>7</v>
+      </c>
+      <c r="CW79" s="5">
+        <v>0</v>
+      </c>
+      <c r="CX79" s="1">
+        <v>0</v>
+      </c>
+      <c r="CY79" s="1">
+        <v>3</v>
+      </c>
+      <c r="CZ79" s="1">
+        <v>0</v>
+      </c>
+      <c r="DA79" s="1">
+        <v>0</v>
+      </c>
+      <c r="DB79" s="1">
+        <v>3</v>
+      </c>
+      <c r="DC79" s="1">
+        <v>0</v>
+      </c>
+      <c r="DD79" s="1">
+        <v>0</v>
+      </c>
+      <c r="DE79" s="1">
+        <v>3</v>
+      </c>
+      <c r="DF79" s="1">
+        <v>0</v>
+      </c>
+      <c r="DG79" s="1">
+        <v>0</v>
+      </c>
+      <c r="DH79" s="1">
+        <v>3</v>
+      </c>
+      <c r="DI79" s="1">
+        <v>0</v>
+      </c>
+      <c r="DQ79" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR79" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS79" s="4">
+        <v>11</v>
+      </c>
+      <c r="DT79" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU79" s="4">
         <v>0</v>
       </c>
       <c r="DY79" s="1">
@@ -8900,97 +10106,37 @@
       <c r="CI80" s="3">
         <v>0</v>
       </c>
-      <c r="CJ80" s="1">
-        <v>0</v>
-      </c>
-      <c r="CK80" s="1">
-        <v>3</v>
-      </c>
-      <c r="CL80" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM80" s="5">
-        <v>0</v>
-      </c>
-      <c r="CN80" s="5">
-        <v>7</v>
-      </c>
-      <c r="CO80" s="5">
-        <v>0</v>
-      </c>
-      <c r="CP80" s="5">
-        <v>0</v>
-      </c>
-      <c r="CQ80" s="5">
-        <v>7</v>
-      </c>
-      <c r="CR80" s="5">
-        <v>0</v>
-      </c>
-      <c r="CS80" s="1">
-        <v>0</v>
-      </c>
-      <c r="CT80" s="1">
-        <v>3</v>
-      </c>
-      <c r="CU80" s="1">
-        <v>0</v>
-      </c>
-      <c r="CV80" s="1">
-        <v>0</v>
-      </c>
-      <c r="CW80" s="1">
-        <v>3</v>
-      </c>
-      <c r="CX80" s="1">
-        <v>0</v>
-      </c>
-      <c r="CY80" s="1">
-        <v>0</v>
-      </c>
-      <c r="CZ80" s="1">
-        <v>3</v>
-      </c>
-      <c r="DA80" s="1">
-        <v>0</v>
-      </c>
-      <c r="DB80" s="1">
-        <v>0</v>
-      </c>
-      <c r="DC80" s="1">
-        <v>3</v>
-      </c>
-      <c r="DD80" s="1">
-        <v>0</v>
-      </c>
-      <c r="DE80" s="1">
-        <v>0</v>
-      </c>
-      <c r="DF80" s="1">
-        <v>3</v>
-      </c>
-      <c r="DG80" s="1">
+      <c r="CJ80" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK80" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL80" s="4">
+        <v>0</v>
+      </c>
+      <c r="CM80" s="4">
+        <v>0</v>
+      </c>
+      <c r="CN80" s="4">
         <v>0</v>
       </c>
       <c r="DH80" s="1">
         <v>0</v>
       </c>
-      <c r="DI80" s="1">
-        <v>3</v>
-      </c>
-      <c r="DJ80" s="1">
-        <v>0</v>
-      </c>
-      <c r="DK80" s="1">
-        <v>0</v>
-      </c>
-      <c r="DL80" s="1">
-        <v>3</v>
-      </c>
-      <c r="DM80" s="1">
-        <v>0</v>
-      </c>
-      <c r="DS80" s="1">
+      <c r="DQ80" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR80" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS80" s="4">
+        <v>0</v>
+      </c>
+      <c r="DT80" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU80" s="4">
         <v>0</v>
       </c>
       <c r="DY80" s="1">
@@ -9037,7 +10183,7 @@
       <c r="AG81" s="1">
         <v>0</v>
       </c>
-      <c r="BI81" s="1">
+      <c r="BJ81" s="1">
         <v>0</v>
       </c>
       <c r="BP81" s="3">
@@ -9100,14 +10246,38 @@
       <c r="CI81" s="3">
         <v>0</v>
       </c>
-      <c r="CJ81" s="1">
-        <v>0</v>
-      </c>
-      <c r="DM81" s="1">
-        <v>0</v>
-      </c>
-      <c r="DS81" s="1">
+      <c r="CJ81" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK81" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL81" s="4">
+        <v>0</v>
+      </c>
+      <c r="CM81" s="4">
+        <v>0</v>
+      </c>
+      <c r="CN81" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH81" s="1">
         <v>4</v>
+      </c>
+      <c r="DQ81" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR81" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS81" s="4">
+        <v>0</v>
+      </c>
+      <c r="DT81" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU81" s="4">
+        <v>0</v>
       </c>
       <c r="DY81" s="1">
         <v>0</v>
@@ -9138,7 +10308,7 @@
       <c r="AG82" s="1">
         <v>4</v>
       </c>
-      <c r="BI82" s="1">
+      <c r="BJ82" s="1">
         <v>4</v>
       </c>
       <c r="BP82" s="3">
@@ -9202,10 +10372,10 @@
         <v>0</v>
       </c>
       <c r="CJ82" s="1">
-        <v>4</v>
-      </c>
-      <c r="DM82" s="1">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="DH82" s="1">
+        <v>0</v>
       </c>
       <c r="DS82" s="1">
         <v>0</v>
@@ -9239,7 +10409,7 @@
       <c r="AG83" s="1">
         <v>0</v>
       </c>
-      <c r="BI83" s="1">
+      <c r="BJ83" s="1">
         <v>0</v>
       </c>
       <c r="BP83" s="3">
@@ -9303,13 +10473,25 @@
         <v>0</v>
       </c>
       <c r="CJ83" s="1">
-        <v>0</v>
-      </c>
-      <c r="DM83" s="1">
+        <v>4</v>
+      </c>
+      <c r="DF83" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG83" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH83" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI83" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ83" s="4">
         <v>0</v>
       </c>
       <c r="DS83" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY83" s="1">
         <v>0</v>
@@ -9325,7 +10507,7 @@
       <c r="AG84" s="1">
         <v>0</v>
       </c>
-      <c r="BI84" s="1">
+      <c r="BJ84" s="1">
         <v>0</v>
       </c>
       <c r="BP84" s="3">
@@ -9391,11 +10573,26 @@
       <c r="CJ84" s="1">
         <v>0</v>
       </c>
+      <c r="DF84" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG84" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH84" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI84" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ84" s="4">
+        <v>0</v>
+      </c>
       <c r="DM84" s="1">
         <v>0</v>
       </c>
       <c r="DS84" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY84" s="1">
         <v>0</v>
@@ -9411,7 +10608,7 @@
       <c r="AG85" s="1">
         <v>4</v>
       </c>
-      <c r="BI85" s="1">
+      <c r="BJ85" s="1">
         <v>4</v>
       </c>
       <c r="BP85" s="3">
@@ -9475,7 +10672,22 @@
         <v>0</v>
       </c>
       <c r="CJ85" s="1">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="DF85" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG85" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH85" s="4">
+        <v>11</v>
+      </c>
+      <c r="DI85" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ85" s="4">
+        <v>0</v>
       </c>
       <c r="DM85" s="1">
         <v>4</v>
@@ -9497,17 +10709,32 @@
       <c r="AG86" s="1">
         <v>0</v>
       </c>
-      <c r="BI86" s="1">
+      <c r="BJ86" s="1">
         <v>0</v>
       </c>
       <c r="CJ86" s="1">
+        <v>4</v>
+      </c>
+      <c r="DF86" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG86" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH86" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI86" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ86" s="4">
         <v>0</v>
       </c>
       <c r="DM86" s="1">
         <v>0</v>
       </c>
       <c r="DS86" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY86" s="1">
         <v>0</v>
@@ -9526,14 +10753,23 @@
       <c r="CJ87" s="1">
         <v>0</v>
       </c>
-      <c r="DM87" s="1">
-        <v>0</v>
-      </c>
-      <c r="DQ87" t="s">
+      <c r="DF87" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG87" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH87" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI87" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ87" s="4">
         <v>0</v>
       </c>
       <c r="DS87" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY87" s="1">
         <v>0</v>
@@ -9549,13 +10785,49 @@
       <c r="AG88" s="1">
         <v>4</v>
       </c>
-      <c r="CJ88" s="1">
-        <v>4</v>
-      </c>
-      <c r="DM88" s="1">
-        <v>4</v>
-      </c>
-      <c r="DS88" s="1">
+      <c r="CH88" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI88" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ88" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK88" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL88" s="4">
+        <v>0</v>
+      </c>
+      <c r="DF88" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG88" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH88" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI88" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ88" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ88" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR88" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS88" s="4">
+        <v>0</v>
+      </c>
+      <c r="DT88" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU88" s="4">
         <v>0</v>
       </c>
       <c r="DY88" s="1">
@@ -9587,13 +10859,49 @@
       <c r="AG89" s="1">
         <v>0</v>
       </c>
-      <c r="CJ89" s="1">
-        <v>0</v>
-      </c>
-      <c r="DM89" s="1">
-        <v>0</v>
-      </c>
-      <c r="DS89" s="1">
+      <c r="CH89" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI89" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ89" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK89" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL89" s="4">
+        <v>0</v>
+      </c>
+      <c r="DF89" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG89" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH89" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI89" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ89" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ89" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR89" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS89" s="4">
+        <v>0</v>
+      </c>
+      <c r="DT89" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU89" s="4">
         <v>0</v>
       </c>
       <c r="DY89" s="1">
@@ -9625,14 +10933,50 @@
       <c r="AG90" s="1">
         <v>0</v>
       </c>
-      <c r="CJ90" s="1">
-        <v>0</v>
-      </c>
-      <c r="DM90" s="1">
-        <v>0</v>
-      </c>
-      <c r="DS90" s="1">
-        <v>4</v>
+      <c r="CH90" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI90" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ90" s="4">
+        <v>11</v>
+      </c>
+      <c r="CK90" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL90" s="4">
+        <v>0</v>
+      </c>
+      <c r="DF90" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG90" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH90" s="4">
+        <v>11</v>
+      </c>
+      <c r="DI90" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ90" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ90" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR90" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS90" s="4">
+        <v>11</v>
+      </c>
+      <c r="DT90" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU90" s="4">
+        <v>0</v>
       </c>
       <c r="DY90" s="1">
         <v>0</v>
@@ -9663,13 +11007,49 @@
       <c r="AG91" s="1">
         <v>4</v>
       </c>
-      <c r="CJ91" s="1">
-        <v>4</v>
-      </c>
-      <c r="DM91" s="1">
-        <v>4</v>
-      </c>
-      <c r="DS91" s="1">
+      <c r="CH91" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI91" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ91" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK91" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL91" s="4">
+        <v>0</v>
+      </c>
+      <c r="DF91" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG91" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH91" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI91" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ91" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ91" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR91" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS91" s="4">
+        <v>0</v>
+      </c>
+      <c r="DT91" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU91" s="4">
         <v>0</v>
       </c>
       <c r="DY91" s="1">
@@ -9701,13 +11081,49 @@
       <c r="AG92" s="1">
         <v>0</v>
       </c>
-      <c r="CJ92" s="1">
-        <v>0</v>
-      </c>
-      <c r="DM92" s="1">
-        <v>0</v>
-      </c>
-      <c r="DS92" s="1">
+      <c r="CH92" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI92" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ92" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK92" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL92" s="4">
+        <v>0</v>
+      </c>
+      <c r="DF92" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG92" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH92" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI92" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ92" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ92" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR92" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS92" s="4">
+        <v>0</v>
+      </c>
+      <c r="DT92" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU92" s="4">
         <v>0</v>
       </c>
       <c r="DY92" s="1">
@@ -9739,98 +11155,68 @@
       <c r="AG93" s="1">
         <v>0</v>
       </c>
-      <c r="CJ93" s="1">
-        <v>0</v>
-      </c>
-      <c r="CK93" s="1">
-        <v>3</v>
-      </c>
-      <c r="CL93" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM93" s="1">
-        <v>0</v>
-      </c>
-      <c r="CN93" s="1">
-        <v>3</v>
-      </c>
-      <c r="CO93" s="1">
-        <v>0</v>
-      </c>
-      <c r="CP93" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ93" s="1">
-        <v>3</v>
-      </c>
-      <c r="CR93" s="1">
-        <v>0</v>
-      </c>
-      <c r="CS93" s="1">
-        <v>0</v>
-      </c>
-      <c r="CT93" s="1">
-        <v>3</v>
-      </c>
-      <c r="CU93" s="1">
-        <v>0</v>
-      </c>
-      <c r="CV93" s="1">
-        <v>0</v>
-      </c>
-      <c r="CW93" s="1">
-        <v>3</v>
-      </c>
-      <c r="CX93" s="1">
-        <v>0</v>
-      </c>
-      <c r="CY93" s="1">
-        <v>0</v>
-      </c>
-      <c r="CZ93" s="1">
-        <v>3</v>
-      </c>
-      <c r="DA93" s="1">
-        <v>0</v>
-      </c>
-      <c r="DB93" s="1">
-        <v>0</v>
-      </c>
-      <c r="DC93" s="1">
-        <v>3</v>
-      </c>
-      <c r="DD93" s="1">
-        <v>0</v>
-      </c>
-      <c r="DE93" s="1">
-        <v>0</v>
-      </c>
-      <c r="DF93" s="1">
-        <v>3</v>
-      </c>
-      <c r="DG93" s="1">
-        <v>0</v>
-      </c>
-      <c r="DH93" s="1">
-        <v>0</v>
-      </c>
-      <c r="DI93" s="1">
-        <v>3</v>
-      </c>
-      <c r="DJ93" s="1">
-        <v>0</v>
-      </c>
-      <c r="DK93" s="1">
-        <v>0</v>
-      </c>
-      <c r="DL93" s="1">
-        <v>3</v>
-      </c>
-      <c r="DM93" s="1">
+      <c r="CH93" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI93" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ93" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK93" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL93" s="4">
+        <v>0</v>
+      </c>
+      <c r="CP93" s="4">
+        <v>0</v>
+      </c>
+      <c r="CQ93" s="4">
+        <v>0</v>
+      </c>
+      <c r="CR93" s="4">
+        <v>0</v>
+      </c>
+      <c r="CS93" s="4">
+        <v>0</v>
+      </c>
+      <c r="CT93" s="4">
+        <v>0</v>
+      </c>
+      <c r="CX93" s="4">
+        <v>0</v>
+      </c>
+      <c r="CY93" s="4">
+        <v>0</v>
+      </c>
+      <c r="CZ93" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA93" s="4">
+        <v>0</v>
+      </c>
+      <c r="DB93" s="4">
+        <v>0</v>
+      </c>
+      <c r="DF93" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG93" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH93" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI93" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ93" s="4">
         <v>0</v>
       </c>
       <c r="DS93" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY93" s="1">
         <v>0</v>
@@ -9846,14 +11232,71 @@
       <c r="AG94" s="1">
         <v>4</v>
       </c>
-      <c r="BI94" s="1">
-        <v>0</v>
-      </c>
-      <c r="CJ94" s="1">
+      <c r="BJ94" s="1">
+        <v>0</v>
+      </c>
+      <c r="CH94" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI94" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ94" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK94" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL94" s="4">
+        <v>0</v>
+      </c>
+      <c r="CP94" s="4">
+        <v>0</v>
+      </c>
+      <c r="CQ94" s="4">
+        <v>0</v>
+      </c>
+      <c r="CR94" s="4">
+        <v>0</v>
+      </c>
+      <c r="CS94" s="4">
+        <v>0</v>
+      </c>
+      <c r="CT94" s="4">
+        <v>0</v>
+      </c>
+      <c r="CX94" s="4">
+        <v>0</v>
+      </c>
+      <c r="CY94" s="4">
+        <v>0</v>
+      </c>
+      <c r="CZ94" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA94" s="4">
+        <v>0</v>
+      </c>
+      <c r="DB94" s="4">
+        <v>0</v>
+      </c>
+      <c r="DF94" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG94" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH94" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI94" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ94" s="4">
         <v>0</v>
       </c>
       <c r="DS94" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY94" s="1">
         <v>4</v>
@@ -9869,13 +11312,94 @@
       <c r="AG95" s="1">
         <v>0</v>
       </c>
-      <c r="BI95" s="1">
+      <c r="BJ95" s="1">
         <v>4</v>
       </c>
-      <c r="CJ95" s="1">
-        <v>4</v>
-      </c>
-      <c r="DJ95" t="s">
+      <c r="CH95" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI95" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ95" s="4">
+        <v>11</v>
+      </c>
+      <c r="CK95" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL95" s="4">
+        <v>0</v>
+      </c>
+      <c r="CM95" s="1">
+        <v>0</v>
+      </c>
+      <c r="CN95" s="1">
+        <v>3</v>
+      </c>
+      <c r="CO95" s="1">
+        <v>0</v>
+      </c>
+      <c r="CP95" s="4">
+        <v>0</v>
+      </c>
+      <c r="CQ95" s="4">
+        <v>0</v>
+      </c>
+      <c r="CR95" s="4">
+        <v>11</v>
+      </c>
+      <c r="CS95" s="4">
+        <v>0</v>
+      </c>
+      <c r="CT95" s="4">
+        <v>0</v>
+      </c>
+      <c r="CU95" s="1">
+        <v>0</v>
+      </c>
+      <c r="CV95" s="1">
+        <v>3</v>
+      </c>
+      <c r="CW95" s="1">
+        <v>0</v>
+      </c>
+      <c r="CX95" s="4">
+        <v>0</v>
+      </c>
+      <c r="CY95" s="4">
+        <v>0</v>
+      </c>
+      <c r="CZ95" s="4">
+        <v>11</v>
+      </c>
+      <c r="DA95" s="4">
+        <v>0</v>
+      </c>
+      <c r="DB95" s="4">
+        <v>0</v>
+      </c>
+      <c r="DC95" s="1">
+        <v>0</v>
+      </c>
+      <c r="DD95" s="1">
+        <v>3</v>
+      </c>
+      <c r="DE95" s="1">
+        <v>0</v>
+      </c>
+      <c r="DF95" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG95" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH95" s="4">
+        <v>11</v>
+      </c>
+      <c r="DI95" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ95" s="4">
         <v>0</v>
       </c>
       <c r="DS95" s="1">
@@ -9895,14 +11419,71 @@
       <c r="AG96" s="1">
         <v>0</v>
       </c>
-      <c r="BI96" s="1">
-        <v>0</v>
-      </c>
-      <c r="CJ96" s="1">
+      <c r="BJ96" s="1">
+        <v>0</v>
+      </c>
+      <c r="CH96" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI96" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ96" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK96" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL96" s="4">
+        <v>0</v>
+      </c>
+      <c r="CP96" s="4">
+        <v>0</v>
+      </c>
+      <c r="CQ96" s="4">
+        <v>0</v>
+      </c>
+      <c r="CR96" s="4">
+        <v>0</v>
+      </c>
+      <c r="CS96" s="4">
+        <v>0</v>
+      </c>
+      <c r="CT96" s="4">
+        <v>0</v>
+      </c>
+      <c r="CX96" s="4">
+        <v>0</v>
+      </c>
+      <c r="CY96" s="4">
+        <v>0</v>
+      </c>
+      <c r="CZ96" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA96" s="4">
+        <v>0</v>
+      </c>
+      <c r="DB96" s="4">
+        <v>0</v>
+      </c>
+      <c r="DF96" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG96" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH96" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI96" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ96" s="4">
         <v>0</v>
       </c>
       <c r="DS96" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY96" s="1">
         <v>0</v>
@@ -9918,22 +11499,19 @@
       <c r="AG97" s="1">
         <v>4</v>
       </c>
-      <c r="BI97" s="1">
-        <v>0</v>
-      </c>
-      <c r="BM97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ97" s="4">
+      <c r="BH97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL97" s="4">
         <v>0</v>
       </c>
       <c r="CH97" s="4">
@@ -9951,8 +11529,53 @@
       <c r="CL97" s="4">
         <v>0</v>
       </c>
+      <c r="CP97" s="4">
+        <v>0</v>
+      </c>
+      <c r="CQ97" s="4">
+        <v>0</v>
+      </c>
+      <c r="CR97" s="4">
+        <v>0</v>
+      </c>
+      <c r="CS97" s="4">
+        <v>0</v>
+      </c>
+      <c r="CT97" s="4">
+        <v>0</v>
+      </c>
+      <c r="CX97" s="4">
+        <v>0</v>
+      </c>
+      <c r="CY97" s="4">
+        <v>0</v>
+      </c>
+      <c r="CZ97" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA97" s="4">
+        <v>0</v>
+      </c>
+      <c r="DB97" s="4">
+        <v>0</v>
+      </c>
+      <c r="DF97" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG97" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH97" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI97" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ97" s="4">
+        <v>0</v>
+      </c>
       <c r="DS97" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DY97" s="1">
         <v>4</v>
@@ -9968,22 +11591,19 @@
       <c r="AG98" s="1">
         <v>0</v>
       </c>
-      <c r="BI98" s="1">
-        <v>4</v>
-      </c>
-      <c r="BM98" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN98" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO98" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP98" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ98" s="4">
+      <c r="BH98" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI98" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ98" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK98" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL98" s="4">
         <v>0</v>
       </c>
       <c r="CH98" s="4">
@@ -10018,31 +11638,19 @@
       <c r="AG99" s="1">
         <v>0</v>
       </c>
-      <c r="BI99" s="1">
-        <v>0</v>
-      </c>
-      <c r="BJ99" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK99" s="1">
-        <v>3</v>
-      </c>
-      <c r="BL99" s="1">
-        <v>0</v>
-      </c>
-      <c r="BM99" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN99" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO99" s="4">
+      <c r="BH99" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI99" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ99" s="4">
         <v>11</v>
       </c>
-      <c r="BP99" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ99" s="4">
+      <c r="BK99" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL99" s="4">
         <v>0</v>
       </c>
       <c r="CH99" s="4">
@@ -10052,7 +11660,7 @@
         <v>0</v>
       </c>
       <c r="CJ99" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CK99" s="4">
         <v>0</v>
@@ -10060,8 +11668,20 @@
       <c r="CL99" s="4">
         <v>0</v>
       </c>
-      <c r="DS99" s="1">
-        <v>4</v>
+      <c r="DQ99" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR99" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS99" s="4">
+        <v>0</v>
+      </c>
+      <c r="DT99" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU99" s="4">
+        <v>0</v>
       </c>
       <c r="DY99" s="1">
         <v>0</v>
@@ -10092,19 +11712,19 @@
       <c r="AG100" s="1">
         <v>4</v>
       </c>
-      <c r="BM100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ100" s="4">
+      <c r="BH100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL100" s="4">
         <v>0</v>
       </c>
       <c r="CH100" s="4">
@@ -10114,7 +11734,7 @@
         <v>0</v>
       </c>
       <c r="CJ100" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CK100" s="4">
         <v>0</v>
@@ -10122,7 +11742,19 @@
       <c r="CL100" s="4">
         <v>0</v>
       </c>
-      <c r="DS100" s="1">
+      <c r="DQ100" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR100" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS100" s="4">
+        <v>0</v>
+      </c>
+      <c r="DT100" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU100" s="4">
         <v>0</v>
       </c>
       <c r="DY100" s="1">
@@ -10154,19 +11786,19 @@
       <c r="AG101" s="1">
         <v>0</v>
       </c>
-      <c r="BM101" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN101" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO101" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP101" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ101" s="4">
+      <c r="BH101" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI101" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ101" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK101" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL101" s="4">
         <v>0</v>
       </c>
       <c r="CH101" s="4">
@@ -10184,7 +11816,19 @@
       <c r="CL101" s="4">
         <v>0</v>
       </c>
-      <c r="DS101" s="1">
+      <c r="DQ101" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR101" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS101" s="4">
+        <v>11</v>
+      </c>
+      <c r="DT101" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU101" s="4">
         <v>0</v>
       </c>
       <c r="DY101" s="1">
@@ -10216,14 +11860,38 @@
       <c r="AG102" s="1">
         <v>0</v>
       </c>
-      <c r="BO102" s="1">
-        <v>0</v>
-      </c>
-      <c r="CJ102" s="1">
-        <v>0</v>
-      </c>
-      <c r="DS102" s="1">
-        <v>4</v>
+      <c r="BJ102" s="1">
+        <v>0</v>
+      </c>
+      <c r="CH102" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI102" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ102" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK102" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL102" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ102" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR102" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS102" s="4">
+        <v>0</v>
+      </c>
+      <c r="DT102" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU102" s="4">
+        <v>0</v>
       </c>
       <c r="DY102" s="1">
         <v>0</v>
@@ -10254,13 +11922,67 @@
       <c r="AG103" s="1">
         <v>4</v>
       </c>
-      <c r="BO103" s="1">
+      <c r="BJ103" s="1">
         <v>4</v>
       </c>
-      <c r="CJ103" s="1">
-        <v>4</v>
-      </c>
-      <c r="DS103" s="1">
+      <c r="BX103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ103" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA103" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB103" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC103" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD103" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE103" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF103" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG103" s="4">
+        <v>0</v>
+      </c>
+      <c r="CH103" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI103" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ103" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK103" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL103" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ103" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR103" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS103" s="4">
+        <v>0</v>
+      </c>
+      <c r="DT103" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU103" s="4">
         <v>0</v>
       </c>
       <c r="DY103" s="1">
@@ -10292,10 +12014,52 @@
       <c r="AG104" s="1">
         <v>0</v>
       </c>
-      <c r="BO104" s="1">
-        <v>0</v>
-      </c>
-      <c r="CJ104" s="1">
+      <c r="BJ104" s="1">
+        <v>0</v>
+      </c>
+      <c r="BX104" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY104" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ104" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA104" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB104" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC104" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD104" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE104" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF104" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG104" s="4">
+        <v>0</v>
+      </c>
+      <c r="CH104" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI104" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ104" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK104" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL104" s="4">
         <v>0</v>
       </c>
       <c r="DS104" s="1">
@@ -10408,112 +12172,106 @@
       <c r="AV105" s="1">
         <v>0</v>
       </c>
-      <c r="AW105" s="1">
+      <c r="BE105" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF105" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG105" s="1">
         <v>3</v>
       </c>
-      <c r="AX105" s="1">
-        <v>0</v>
-      </c>
-      <c r="BE105" s="1">
-        <v>0</v>
-      </c>
-      <c r="BF105" s="1">
+      <c r="BH105" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI105" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ105" s="1">
         <v>3</v>
       </c>
-      <c r="BG105" s="1">
-        <v>0</v>
-      </c>
-      <c r="BH105" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI105" s="1">
+      <c r="BK105" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL105" s="1">
+        <v>0</v>
+      </c>
+      <c r="BM105" s="1">
         <v>3</v>
       </c>
-      <c r="BJ105" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK105" s="1">
-        <v>0</v>
-      </c>
-      <c r="BL105" s="1">
+      <c r="BN105" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO105" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP105" s="1">
         <v>3</v>
       </c>
-      <c r="BM105" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN105" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO105" s="1">
+      <c r="BQ105" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR105" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS105" s="1">
         <v>3</v>
       </c>
-      <c r="BP105" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ105" s="1">
-        <v>0</v>
-      </c>
-      <c r="BR105" s="1">
+      <c r="BT105" s="1">
+        <v>0</v>
+      </c>
+      <c r="BU105" s="1">
+        <v>0</v>
+      </c>
+      <c r="BV105" s="1">
         <v>3</v>
       </c>
-      <c r="BS105" s="1">
-        <v>0</v>
-      </c>
-      <c r="BT105" s="1">
-        <v>0</v>
-      </c>
-      <c r="BU105" s="1">
-        <v>3</v>
-      </c>
-      <c r="BV105" s="1">
-        <v>0</v>
-      </c>
       <c r="BW105" s="1">
         <v>0</v>
       </c>
-      <c r="BX105" s="1">
-        <v>3</v>
-      </c>
-      <c r="BY105" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ105" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA105" s="1">
-        <v>3</v>
-      </c>
-      <c r="CB105" s="1">
-        <v>0</v>
-      </c>
-      <c r="CC105" s="1">
-        <v>0</v>
-      </c>
-      <c r="CD105" s="1">
-        <v>3</v>
-      </c>
-      <c r="CE105" s="1">
-        <v>0</v>
-      </c>
-      <c r="CF105" s="1">
-        <v>0</v>
-      </c>
-      <c r="CG105" s="1">
-        <v>3</v>
-      </c>
-      <c r="CH105" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI105" s="1">
-        <v>0</v>
-      </c>
-      <c r="CJ105" s="1">
-        <v>3</v>
-      </c>
-      <c r="CK105" s="1">
-        <v>0</v>
-      </c>
-      <c r="CL105" s="1">
+      <c r="BX105" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY105" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ105" s="4">
+        <v>11</v>
+      </c>
+      <c r="CA105" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB105" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC105" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD105" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE105" s="4">
+        <v>11</v>
+      </c>
+      <c r="CF105" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG105" s="4">
+        <v>0</v>
+      </c>
+      <c r="CH105" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI105" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ105" s="4">
+        <v>11</v>
+      </c>
+      <c r="CK105" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL105" s="4">
         <v>0</v>
       </c>
       <c r="CM105" s="1">
@@ -10629,13 +12387,55 @@
       <c r="Q106" s="1">
         <v>4</v>
       </c>
-      <c r="AX106" s="1">
-        <v>0</v>
+      <c r="AV106" s="1">
+        <v>4</v>
       </c>
       <c r="BE106" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ106" s="1">
+        <v>4</v>
+      </c>
+      <c r="BX106" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY106" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ106" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA106" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB106" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC106" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD106" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE106" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF106" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG106" s="4">
+        <v>0</v>
+      </c>
+      <c r="CH106" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI106" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ106" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK106" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL106" s="4">
         <v>0</v>
       </c>
       <c r="DS106" s="1">
@@ -10655,14 +12455,56 @@
       <c r="Q107" s="1">
         <v>0</v>
       </c>
-      <c r="AX107" s="1">
-        <v>4</v>
+      <c r="AV107" s="1">
+        <v>0</v>
       </c>
       <c r="BE107" s="1">
-        <v>4</v>
-      </c>
-      <c r="BZ107" s="1">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="BX107" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY107" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ107" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA107" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB107" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC107" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD107" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE107" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF107" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG107" s="4">
+        <v>0</v>
+      </c>
+      <c r="CH107" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI107" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ107" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK107" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL107" s="4">
+        <v>0</v>
       </c>
       <c r="DS107" s="1">
         <v>0</v>
@@ -10681,7 +12523,19 @@
       <c r="Q108" s="1">
         <v>0</v>
       </c>
-      <c r="AX108" s="1">
+      <c r="AT108" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU108" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV108" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW108" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX108" s="4">
         <v>0</v>
       </c>
       <c r="BE108" s="1">
@@ -10707,11 +12561,26 @@
       <c r="Q109" s="1">
         <v>4</v>
       </c>
-      <c r="AX109" s="1">
-        <v>0</v>
+      <c r="AT109" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU109" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV109" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW109" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX109" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE109" s="1">
+        <v>4</v>
       </c>
       <c r="BZ109" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DS109" s="1">
         <v>0</v>
@@ -10730,11 +12599,26 @@
       <c r="Q110" s="1">
         <v>0</v>
       </c>
-      <c r="AX110" s="1">
-        <v>4</v>
+      <c r="AT110" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU110" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV110" s="4">
+        <v>11</v>
+      </c>
+      <c r="AW110" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE110" s="1">
+        <v>0</v>
       </c>
       <c r="BZ110" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DS110" s="1">
         <v>0</v>
@@ -10780,10 +12664,34 @@
       <c r="S111" s="4">
         <v>0</v>
       </c>
-      <c r="AX111" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ111" s="1">
+      <c r="AT111" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU111" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV111" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW111" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX111" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX111" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY111" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ111" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA111" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB111" s="4">
         <v>0</v>
       </c>
       <c r="DS111" s="1">
@@ -10830,10 +12738,34 @@
       <c r="S112" s="4">
         <v>0</v>
       </c>
-      <c r="AX112" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ112" s="1">
+      <c r="AT112" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU112" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV112" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW112" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX112" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX112" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY112" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ112" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA112" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB112" s="4">
         <v>0</v>
       </c>
       <c r="DS112" s="1">
@@ -10889,11 +12821,23 @@
       <c r="S113" s="4">
         <v>0</v>
       </c>
-      <c r="AX113" s="1">
-        <v>4</v>
-      </c>
-      <c r="BZ113" s="1">
-        <v>4</v>
+      <c r="AV113" s="1">
+        <v>0</v>
+      </c>
+      <c r="BX113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ113" s="4">
+        <v>11</v>
+      </c>
+      <c r="CA113" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB113" s="4">
+        <v>0</v>
       </c>
       <c r="DS113" s="1">
         <v>0</v>
@@ -10939,13 +12883,22 @@
       <c r="S114" s="4">
         <v>0</v>
       </c>
-      <c r="AX114" s="1">
-        <v>0</v>
-      </c>
-      <c r="BE114" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ114" s="1">
+      <c r="AV114" s="1">
+        <v>4</v>
+      </c>
+      <c r="BX114" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY114" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ114" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA114" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB114" s="4">
         <v>0</v>
       </c>
       <c r="DS114" s="1">
@@ -10992,13 +12945,22 @@
       <c r="S115" s="4">
         <v>0</v>
       </c>
-      <c r="AX115" s="1">
-        <v>0</v>
-      </c>
-      <c r="BE115" s="1">
-        <v>4</v>
-      </c>
-      <c r="BZ115" s="1">
+      <c r="AV115" s="1">
+        <v>0</v>
+      </c>
+      <c r="BX115" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY115" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ115" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA115" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB115" s="4">
         <v>0</v>
       </c>
       <c r="CK115" s="3">
@@ -11081,14 +13043,65 @@
       <c r="Q116" s="1">
         <v>0</v>
       </c>
-      <c r="AX116" s="1">
-        <v>4</v>
-      </c>
-      <c r="BE116" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ116" s="1">
-        <v>4</v>
+      <c r="AA116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ116" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA116" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB116" s="4">
+        <v>0</v>
       </c>
       <c r="CK116" s="3">
         <v>0</v>
@@ -11170,13 +13183,67 @@
       <c r="Q117" s="1">
         <v>4</v>
       </c>
-      <c r="AX117" s="1">
+      <c r="AA117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX117" s="4">
         <v>0</v>
       </c>
       <c r="BE117" s="1">
         <v>0</v>
       </c>
-      <c r="BZ117" s="1">
+      <c r="BX117" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY117" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ117" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA117" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB117" s="4">
         <v>0</v>
       </c>
       <c r="CK117" s="3">
@@ -11259,13 +13326,94 @@
       <c r="Q118" s="1">
         <v>0</v>
       </c>
-      <c r="AX118" s="1">
+      <c r="AA118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC118" s="4">
+        <v>11</v>
+      </c>
+      <c r="AD118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH118" s="4">
+        <v>11</v>
+      </c>
+      <c r="AI118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AK118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL118" s="1">
+        <v>3</v>
+      </c>
+      <c r="AM118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO118" s="1">
+        <v>3</v>
+      </c>
+      <c r="AP118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR118" s="1">
+        <v>3</v>
+      </c>
+      <c r="AS118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV118" s="4">
+        <v>11</v>
+      </c>
+      <c r="AW118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX118" s="4">
         <v>0</v>
       </c>
       <c r="BE118" s="1">
         <v>4</v>
       </c>
-      <c r="BZ118" s="1">
+      <c r="BX118" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY118" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ118" s="4">
+        <v>11</v>
+      </c>
+      <c r="CA118" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB118" s="4">
         <v>0</v>
       </c>
       <c r="CK118" s="3">
@@ -11348,6 +13496,9 @@
       <c r="Q119" s="1">
         <v>0</v>
       </c>
+      <c r="AA119" s="4">
+        <v>0</v>
+      </c>
       <c r="AB119" s="4">
         <v>0</v>
       </c>
@@ -11363,29 +13514,50 @@
       <c r="AF119" s="4">
         <v>0</v>
       </c>
-      <c r="AM119" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN119" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO119" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP119" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ119" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX119" s="1">
-        <v>4</v>
+      <c r="AG119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX119" s="4">
+        <v>0</v>
       </c>
       <c r="BE119" s="1">
         <v>0</v>
       </c>
-      <c r="BZ119" s="1">
-        <v>4</v>
+      <c r="BX119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ119" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA119" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB119" s="4">
+        <v>0</v>
       </c>
       <c r="CK119" s="3">
         <v>0</v>
@@ -11467,6 +13639,9 @@
       <c r="Q120" s="1">
         <v>4</v>
       </c>
+      <c r="AA120" s="4">
+        <v>0</v>
+      </c>
       <c r="AB120" s="4">
         <v>0</v>
       </c>
@@ -11482,22 +13657,31 @@
       <c r="AF120" s="4">
         <v>0</v>
       </c>
-      <c r="AM120" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN120" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO120" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP120" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ120" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX120" s="1">
+      <c r="AG120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX120" s="4">
         <v>0</v>
       </c>
       <c r="BE120" s="1">
@@ -11509,10 +13693,19 @@
       <c r="BG120" s="1">
         <v>0</v>
       </c>
-      <c r="BZ120" s="1">
-        <v>0</v>
-      </c>
-      <c r="CJ120" s="1">
+      <c r="BX120" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY120" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ120" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA120" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB120" s="4">
         <v>0</v>
       </c>
       <c r="CK120" s="3">
@@ -11595,73 +13788,10 @@
       <c r="Q121" s="1">
         <v>0</v>
       </c>
-      <c r="AB121" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC121" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD121" s="4">
-        <v>11</v>
-      </c>
-      <c r="AE121" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF121" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG121" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH121" s="1">
-        <v>3</v>
-      </c>
-      <c r="AI121" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ121" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK121" s="1">
-        <v>3</v>
-      </c>
-      <c r="AL121" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM121" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN121" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO121" s="4">
-        <v>11</v>
-      </c>
-      <c r="AP121" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ121" s="4">
-        <v>0</v>
-      </c>
-      <c r="AR121" s="1">
-        <v>0</v>
-      </c>
-      <c r="AS121" s="1">
-        <v>3</v>
-      </c>
-      <c r="AT121" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU121" s="1">
+      <c r="AC121" s="1">
         <v>0</v>
       </c>
       <c r="AV121" s="1">
-        <v>3</v>
-      </c>
-      <c r="AW121" s="1">
-        <v>0</v>
-      </c>
-      <c r="AX121" s="1">
         <v>0</v>
       </c>
       <c r="BD121" s="1">
@@ -11670,11 +13800,20 @@
       <c r="BH121" s="1">
         <v>0</v>
       </c>
-      <c r="BZ121" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI121" s="1">
-        <v>5</v>
+      <c r="BX121" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY121" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ121" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA121" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB121" s="4">
+        <v>0</v>
       </c>
       <c r="CK121" s="3">
         <v>0</v>
@@ -11756,37 +13895,10 @@
       <c r="Q122" s="5">
         <v>0</v>
       </c>
-      <c r="AB122" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC122" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD122" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE122" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF122" s="4">
-        <v>0</v>
-      </c>
-      <c r="AM122" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN122" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO122" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP122" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ122" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX122" s="1">
+      <c r="AC122" s="1">
+        <v>4</v>
+      </c>
+      <c r="AV122" s="1">
         <v>4</v>
       </c>
       <c r="BC122" s="1">
@@ -11795,10 +13907,19 @@
       <c r="BI122" s="1">
         <v>6</v>
       </c>
-      <c r="BZ122" s="1">
-        <v>4</v>
-      </c>
-      <c r="CH122" s="1">
+      <c r="BX122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ122" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA122" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB122" s="4">
         <v>0</v>
       </c>
       <c r="CK122" s="3">
@@ -11881,37 +14002,10 @@
       <c r="Q123" s="5">
         <v>8</v>
       </c>
-      <c r="AB123" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC123" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD123" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE123" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF123" s="4">
-        <v>0</v>
-      </c>
-      <c r="AM123" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN123" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO123" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP123" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ123" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX123" s="1">
+      <c r="AC123" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV123" s="1">
         <v>0</v>
       </c>
       <c r="BB123" s="1">
@@ -11920,10 +14014,22 @@
       <c r="BJ123" s="1">
         <v>0</v>
       </c>
-      <c r="BZ123" s="1">
-        <v>0</v>
-      </c>
-      <c r="CG123" s="1">
+      <c r="BX123" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY123" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ123" s="4">
+        <v>11</v>
+      </c>
+      <c r="CA123" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB123" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ123" s="1">
         <v>0</v>
       </c>
       <c r="CK123" s="3">
@@ -12006,10 +14112,37 @@
       <c r="Q124" s="5">
         <v>0</v>
       </c>
-      <c r="AD124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AX124" s="1">
+      <c r="AC124" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL124" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM124" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN124" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO124" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP124" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT124" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU124" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV124" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW124" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX124" s="4">
         <v>0</v>
       </c>
       <c r="BA124" s="1">
@@ -12018,10 +14151,37 @@
       <c r="BK124" s="1">
         <v>0</v>
       </c>
-      <c r="BZ124" s="1">
-        <v>0</v>
-      </c>
-      <c r="CF124" s="1">
+      <c r="BN124" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO124" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP124" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ124" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR124" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX124" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY124" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ124" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA124" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB124" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI124" s="1">
         <v>5</v>
       </c>
       <c r="CK124" s="3">
@@ -12146,11 +14306,38 @@
       <c r="Q125" s="5">
         <v>0</v>
       </c>
-      <c r="AD125" s="1">
+      <c r="AC125" s="1">
         <v>4</v>
       </c>
-      <c r="AX125" s="1">
-        <v>4</v>
+      <c r="AL125" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM125" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN125" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO125" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP125" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT125" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU125" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV125" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW125" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX125" s="4">
+        <v>0</v>
       </c>
       <c r="AZ125" s="1">
         <v>5</v>
@@ -12158,10 +14345,37 @@
       <c r="BL125" s="1">
         <v>6</v>
       </c>
-      <c r="BZ125" s="1">
-        <v>4</v>
-      </c>
-      <c r="CE125" s="1">
+      <c r="BN125" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO125" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP125" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ125" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR125" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX125" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY125" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ125" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA125" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB125" s="4">
+        <v>0</v>
+      </c>
+      <c r="CH125" s="1">
         <v>0</v>
       </c>
       <c r="CK125" s="3">
@@ -12259,10 +14473,37 @@
       <c r="Q126" s="5">
         <v>8</v>
       </c>
-      <c r="AD126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AX126" s="1">
+      <c r="AC126" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL126" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM126" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN126" s="4">
+        <v>11</v>
+      </c>
+      <c r="AO126" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP126" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT126" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU126" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV126" s="4">
+        <v>11</v>
+      </c>
+      <c r="AW126" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX126" s="4">
         <v>0</v>
       </c>
       <c r="AY126" s="1">
@@ -12271,25 +14512,34 @@
       <c r="BM126" s="1">
         <v>0</v>
       </c>
-      <c r="BN126" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO126" s="1">
-        <v>3</v>
-      </c>
-      <c r="BP126" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ126" s="1">
-        <v>0</v>
-      </c>
-      <c r="BR126" s="1">
-        <v>3</v>
-      </c>
-      <c r="BS126" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ126" s="1">
+      <c r="BN126" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO126" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP126" s="4">
+        <v>11</v>
+      </c>
+      <c r="BQ126" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR126" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX126" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY126" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ126" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA126" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB126" s="4">
         <v>0</v>
       </c>
       <c r="CK126" s="3">
@@ -12387,10 +14637,67 @@
       <c r="Q127" s="5">
         <v>0</v>
       </c>
-      <c r="AD127" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ127" s="1">
+      <c r="AC127" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL127" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM127" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN127" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO127" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP127" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT127" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU127" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV127" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW127" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX127" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN127" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO127" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP127" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ127" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR127" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX127" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY127" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ127" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA127" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB127" s="4">
         <v>0</v>
       </c>
       <c r="CK127" s="3">
@@ -12488,9 +14795,39 @@
       <c r="Q128" s="1">
         <v>0</v>
       </c>
-      <c r="AD128" s="1">
+      <c r="AC128" s="1">
         <v>4</v>
       </c>
+      <c r="AL128" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM128" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN128" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO128" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP128" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT128" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU128" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV128" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW128" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX128" s="4">
+        <v>0</v>
+      </c>
       <c r="BD128" s="4">
         <v>0</v>
       </c>
@@ -12506,8 +14843,35 @@
       <c r="BH128" s="4">
         <v>0</v>
       </c>
-      <c r="BZ128" s="1">
-        <v>4</v>
+      <c r="BN128" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO128" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP128" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ128" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR128" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX128" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY128" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ128" s="4">
+        <v>11</v>
+      </c>
+      <c r="CA128" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB128" s="4">
+        <v>0</v>
       </c>
       <c r="CK128" s="3">
         <v>0</v>
@@ -12604,7 +14968,7 @@
       <c r="Q129" s="1">
         <v>4</v>
       </c>
-      <c r="AD129" s="1">
+      <c r="AC129" s="1">
         <v>0</v>
       </c>
       <c r="BD129" s="4">
@@ -12622,7 +14986,19 @@
       <c r="BH129" s="4">
         <v>0</v>
       </c>
-      <c r="BZ129" s="1">
+      <c r="BX129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ129" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA129" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB129" s="4">
         <v>0</v>
       </c>
       <c r="CK129" s="3">
@@ -12705,7 +15081,7 @@
       <c r="Q130" s="1">
         <v>0</v>
       </c>
-      <c r="AD130" s="1">
+      <c r="AC130" s="1">
         <v>0</v>
       </c>
       <c r="BD130" s="4">
@@ -12723,7 +15099,19 @@
       <c r="BH130" s="4">
         <v>0</v>
       </c>
-      <c r="BZ130" s="1">
+      <c r="BX130" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY130" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ130" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA130" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB130" s="4">
         <v>0</v>
       </c>
       <c r="CK130" s="3">
@@ -12830,7 +15218,7 @@
       <c r="S131" s="4">
         <v>0</v>
       </c>
-      <c r="AD131" s="1">
+      <c r="AC131" s="1">
         <v>4</v>
       </c>
       <c r="BD131" s="4">
@@ -12848,8 +15236,20 @@
       <c r="BH131" s="4">
         <v>0</v>
       </c>
-      <c r="BZ131" s="1">
-        <v>4</v>
+      <c r="BX131" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY131" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ131" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA131" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB131" s="4">
+        <v>0</v>
       </c>
       <c r="CK131" s="3">
         <v>0</v>
@@ -12955,7 +15355,7 @@
       <c r="S132" s="4">
         <v>0</v>
       </c>
-      <c r="AD132" s="1">
+      <c r="AC132" s="1">
         <v>0</v>
       </c>
       <c r="BD132" s="4">
@@ -12973,7 +15373,19 @@
       <c r="BH132" s="4">
         <v>0</v>
       </c>
-      <c r="BZ132" s="1">
+      <c r="BX132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ132" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA132" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB132" s="4">
         <v>0</v>
       </c>
       <c r="CK132" s="3">
@@ -13089,10 +15501,37 @@
       <c r="S133" s="4">
         <v>0</v>
       </c>
-      <c r="AD133" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ133" s="1">
+      <c r="AC133" s="1">
+        <v>0</v>
+      </c>
+      <c r="BN133" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO133" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP133" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ133" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR133" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX133" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY133" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ133" s="4">
+        <v>11</v>
+      </c>
+      <c r="CA133" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB133" s="4">
         <v>0</v>
       </c>
       <c r="CK133" s="3">
@@ -13199,13 +15638,52 @@
       <c r="S134" s="4">
         <v>0</v>
       </c>
-      <c r="AD134" s="1">
+      <c r="AC134" s="1">
         <v>4</v>
       </c>
-      <c r="BZ134" s="1">
-        <v>4</v>
-      </c>
-      <c r="CF134" s="1">
+      <c r="AT134" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU134" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV134" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW134" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX134" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN134" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO134" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP134" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ134" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR134" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX134" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY134" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ134" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA134" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB134" s="4">
         <v>0</v>
       </c>
       <c r="CK134" s="3">
@@ -13312,10 +15790,22 @@
       <c r="S135" s="4">
         <v>0</v>
       </c>
-      <c r="AD135" s="1">
-        <v>0</v>
-      </c>
-      <c r="AX135" s="1">
+      <c r="AC135" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT135" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU135" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV135" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW135" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX135" s="4">
         <v>0</v>
       </c>
       <c r="AY135" s="1">
@@ -13324,29 +15814,35 @@
       <c r="BM135" s="1">
         <v>0</v>
       </c>
-      <c r="BN135" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO135" s="1">
-        <v>3</v>
-      </c>
-      <c r="BP135" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ135" s="1">
-        <v>0</v>
-      </c>
-      <c r="BR135" s="1">
-        <v>3</v>
-      </c>
-      <c r="BS135" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ135" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE135" s="1">
-        <v>5</v>
+      <c r="BN135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP135" s="4">
+        <v>11</v>
+      </c>
+      <c r="BQ135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ135" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA135" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB135" s="4">
+        <v>0</v>
       </c>
       <c r="CS135" s="1">
         <v>0</v>
@@ -13365,6 +15861,9 @@
       <c r="A136" s="1">
         <v>0</v>
       </c>
+      <c r="AA136" s="4">
+        <v>0</v>
+      </c>
       <c r="AB136" s="4">
         <v>0</v>
       </c>
@@ -13377,11 +15876,20 @@
       <c r="AE136" s="4">
         <v>0</v>
       </c>
-      <c r="AF136" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX136" s="1">
-        <v>4</v>
+      <c r="AT136" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU136" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV136" s="4">
+        <v>11</v>
+      </c>
+      <c r="AW136" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX136" s="4">
+        <v>0</v>
       </c>
       <c r="AZ136" s="1">
         <v>6</v>
@@ -13389,10 +15897,37 @@
       <c r="BL136" s="1">
         <v>5</v>
       </c>
-      <c r="BZ136" s="1">
-        <v>0</v>
-      </c>
-      <c r="CD136" s="1">
+      <c r="BN136" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO136" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP136" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ136" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR136" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX136" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY136" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ136" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA136" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB136" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE136" s="1">
         <v>0</v>
       </c>
       <c r="CR136" s="1">
@@ -13412,6 +15947,9 @@
       <c r="A137" s="1">
         <v>0</v>
       </c>
+      <c r="AA137" s="4">
+        <v>0</v>
+      </c>
       <c r="AB137" s="4">
         <v>0</v>
       </c>
@@ -13424,7 +15962,10 @@
       <c r="AE137" s="4">
         <v>0</v>
       </c>
-      <c r="AF137" s="4">
+      <c r="AK137" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL137" s="4">
         <v>0</v>
       </c>
       <c r="AM137" s="4">
@@ -13436,13 +15977,19 @@
       <c r="AO137" s="4">
         <v>0</v>
       </c>
-      <c r="AP137" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ137" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX137" s="1">
+      <c r="AT137" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU137" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV137" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW137" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX137" s="4">
         <v>0</v>
       </c>
       <c r="BA137" s="1">
@@ -13451,11 +15998,38 @@
       <c r="BK137" s="1">
         <v>0</v>
       </c>
-      <c r="BZ137" s="1">
-        <v>4</v>
-      </c>
-      <c r="CC137" s="1">
-        <v>0</v>
+      <c r="BN137" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO137" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP137" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ137" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR137" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX137" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY137" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ137" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA137" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB137" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD137" s="1">
+        <v>5</v>
       </c>
       <c r="CQ137" s="1">
         <v>0</v>
@@ -13474,50 +16048,74 @@
       <c r="A138" s="1">
         <v>0</v>
       </c>
+      <c r="AA138" s="4">
+        <v>0</v>
+      </c>
       <c r="AB138" s="4">
         <v>0</v>
       </c>
       <c r="AC138" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD138" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE138" s="4">
+        <v>0</v>
+      </c>
+      <c r="AK138" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL138" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM138" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN138" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO138" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT138" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU138" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV138" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW138" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB138" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ138" s="1">
+        <v>0</v>
+      </c>
+      <c r="BX138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ138" s="4">
         <v>11</v>
       </c>
-      <c r="AE138" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF138" s="4">
-        <v>0</v>
-      </c>
-      <c r="AM138" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN138" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO138" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP138" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ138" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX138" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB138" s="1">
-        <v>0</v>
-      </c>
-      <c r="BJ138" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ138" s="1">
-        <v>0</v>
-      </c>
-      <c r="CB138" s="1">
-        <v>5</v>
+      <c r="CA138" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB138" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC138" s="1">
+        <v>0</v>
       </c>
       <c r="CP138" s="1">
         <v>0</v>
@@ -13536,6 +16134,9 @@
       <c r="A139" s="1">
         <v>0</v>
       </c>
+      <c r="AA139" s="4">
+        <v>0</v>
+      </c>
       <c r="AB139" s="4">
         <v>0</v>
       </c>
@@ -13548,26 +16149,23 @@
       <c r="AE139" s="4">
         <v>0</v>
       </c>
-      <c r="AF139" s="4">
+      <c r="AK139" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL139" s="4">
         <v>0</v>
       </c>
       <c r="AM139" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AN139" s="4">
         <v>0</v>
       </c>
       <c r="AO139" s="4">
-        <v>11</v>
-      </c>
-      <c r="AP139" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ139" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX139" s="1">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="AV139" s="1">
+        <v>0</v>
       </c>
       <c r="BC139" s="1">
         <v>6</v>
@@ -13575,10 +16173,19 @@
       <c r="BI139" s="1">
         <v>5</v>
       </c>
-      <c r="BZ139" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA139" s="1">
+      <c r="BX139" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY139" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ139" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA139" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB139" s="4">
         <v>0</v>
       </c>
       <c r="CO139" s="1">
@@ -13598,6 +16205,9 @@
       <c r="A140" s="1">
         <v>0</v>
       </c>
+      <c r="AA140" s="4">
+        <v>0</v>
+      </c>
       <c r="AB140" s="4">
         <v>0</v>
       </c>
@@ -13610,7 +16220,10 @@
       <c r="AE140" s="4">
         <v>0</v>
       </c>
-      <c r="AF140" s="4">
+      <c r="AK140" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL140" s="4">
         <v>0</v>
       </c>
       <c r="AM140" s="4">
@@ -13622,14 +16235,8 @@
       <c r="AO140" s="4">
         <v>0</v>
       </c>
-      <c r="AP140" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ140" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX140" s="1">
-        <v>0</v>
+      <c r="AV140" s="1">
+        <v>4</v>
       </c>
       <c r="BD140" s="1">
         <v>0</v>
@@ -13637,8 +16244,20 @@
       <c r="BH140" s="1">
         <v>0</v>
       </c>
-      <c r="BZ140" s="1">
-        <v>4</v>
+      <c r="BX140" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY140" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ140" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA140" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB140" s="4">
+        <v>0</v>
       </c>
       <c r="CN140" s="1">
         <v>0</v>
@@ -13657,7 +16276,13 @@
       <c r="A141" s="1">
         <v>0</v>
       </c>
-      <c r="AD141" s="1">
+      <c r="AC141" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK141" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL141" s="4">
         <v>0</v>
       </c>
       <c r="AM141" s="4">
@@ -13669,13 +16294,7 @@
       <c r="AO141" s="4">
         <v>0</v>
       </c>
-      <c r="AP141" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ141" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX141" s="1">
+      <c r="AV141" s="1">
         <v>0</v>
       </c>
       <c r="BE141" s="1">
@@ -13707,47 +16326,26 @@
       <c r="A142" s="1">
         <v>0</v>
       </c>
-      <c r="AD142" s="1">
+      <c r="AC142" s="1">
         <v>4</v>
       </c>
-      <c r="AX142" s="1">
+      <c r="AT142" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU142" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV142" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW142" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX142" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ142" s="1">
         <v>4</v>
-      </c>
-      <c r="BO142" s="1">
-        <v>0</v>
-      </c>
-      <c r="BP142" s="1">
-        <v>3</v>
-      </c>
-      <c r="BQ142" s="1">
-        <v>0</v>
-      </c>
-      <c r="BR142" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS142" s="1">
-        <v>3</v>
-      </c>
-      <c r="BT142" s="1">
-        <v>0</v>
-      </c>
-      <c r="BU142" s="1">
-        <v>0</v>
-      </c>
-      <c r="BV142" s="1">
-        <v>3</v>
-      </c>
-      <c r="BW142" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX142" s="1">
-        <v>0</v>
-      </c>
-      <c r="BY142" s="1">
-        <v>3</v>
-      </c>
-      <c r="BZ142" s="1">
-        <v>0</v>
       </c>
       <c r="CL142" s="1">
         <v>5</v>
@@ -13820,10 +16418,25 @@
       <c r="A143" s="1">
         <v>0</v>
       </c>
-      <c r="AD143" s="1">
-        <v>0</v>
-      </c>
-      <c r="AX143" s="1">
+      <c r="AC143" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT143" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU143" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV143" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW143" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX143" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ143" s="1">
         <v>0</v>
       </c>
       <c r="CK143" s="1">
@@ -13840,10 +16453,22 @@
       <c r="A144" s="1">
         <v>0</v>
       </c>
-      <c r="AD144" s="1">
-        <v>0</v>
-      </c>
-      <c r="AX144" s="1">
+      <c r="AC144" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT144" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU144" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV144" s="4">
+        <v>11</v>
+      </c>
+      <c r="AW144" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX144" s="4">
         <v>0</v>
       </c>
       <c r="CJ144" s="1">
@@ -13860,11 +16485,23 @@
       <c r="A145" s="1">
         <v>0</v>
       </c>
-      <c r="AD145" s="1">
+      <c r="AC145" s="1">
         <v>4</v>
       </c>
-      <c r="AX145" s="1">
-        <v>4</v>
+      <c r="AT145" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU145" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV145" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW145" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX145" s="4">
+        <v>0</v>
       </c>
       <c r="CI145" s="1">
         <v>5</v>
@@ -13880,10 +16517,22 @@
       <c r="B146" s="1">
         <v>6</v>
       </c>
-      <c r="AD146" s="1">
-        <v>0</v>
-      </c>
-      <c r="AX146" s="1">
+      <c r="AC146" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT146" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU146" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV146" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW146" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX146" s="4">
         <v>0</v>
       </c>
       <c r="CH146" s="1">
@@ -13900,10 +16549,10 @@
       <c r="C147" s="1">
         <v>0</v>
       </c>
-      <c r="AD147" s="1">
-        <v>0</v>
-      </c>
-      <c r="AX147" s="1">
+      <c r="AC147" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV147" s="1">
         <v>0</v>
       </c>
       <c r="CG147" s="1">
@@ -13920,10 +16569,10 @@
       <c r="D148" s="1">
         <v>0</v>
       </c>
-      <c r="AD148" s="1">
+      <c r="AC148" s="1">
         <v>4</v>
       </c>
-      <c r="AX148" s="1">
+      <c r="AV148" s="1">
         <v>4</v>
       </c>
       <c r="CF148" s="1">
@@ -13940,10 +16589,10 @@
       <c r="E149" s="1">
         <v>6</v>
       </c>
-      <c r="AD149" s="1">
-        <v>0</v>
-      </c>
-      <c r="AX149" s="1">
+      <c r="AC149" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV149" s="1">
         <v>0</v>
       </c>
       <c r="CE149" s="1">

--- a/media/Levels/Level_5.xlsx
+++ b/media/Levels/Level_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A74B9E7-4006-4234-81D7-6D01879E53C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4450CC44-ECD9-41C3-A7FD-6A8C9C34BD60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="72" windowWidth="15660" windowHeight="12168" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -1109,19 +1109,19 @@
       <c r="BT8" s="4">
         <v>0</v>
       </c>
-      <c r="BU8" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV8" s="4">
-        <v>0</v>
-      </c>
-      <c r="BW8" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX8" s="4">
-        <v>0</v>
-      </c>
       <c r="BY8" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ8" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA8" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB8" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC8" s="4">
         <v>0</v>
       </c>
       <c r="CW8" s="4">
@@ -1186,19 +1186,19 @@
       <c r="BT9" s="4">
         <v>0</v>
       </c>
-      <c r="BU9" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV9" s="4">
-        <v>0</v>
-      </c>
-      <c r="BW9" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX9" s="4">
-        <v>0</v>
-      </c>
       <c r="BY9" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ9" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA9" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB9" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC9" s="4">
         <v>0</v>
       </c>
       <c r="CW9" s="4">
@@ -1323,19 +1323,19 @@
       <c r="BT10" s="4">
         <v>0</v>
       </c>
-      <c r="BU10" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV10" s="4">
-        <v>0</v>
-      </c>
-      <c r="BW10" s="4">
+      <c r="BY10" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ10" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA10" s="4">
         <v>11</v>
       </c>
-      <c r="BX10" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY10" s="4">
+      <c r="CB10" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC10" s="4">
         <v>0</v>
       </c>
       <c r="CY10" s="1">
@@ -1448,19 +1448,19 @@
       <c r="BT11" s="4">
         <v>0</v>
       </c>
-      <c r="BU11" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV11" s="4">
-        <v>0</v>
-      </c>
-      <c r="BW11" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX11" s="4">
-        <v>0</v>
-      </c>
       <c r="BY11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ11" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA11" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB11" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC11" s="4">
         <v>0</v>
       </c>
       <c r="CY11" s="1">
@@ -1558,19 +1558,19 @@
       <c r="BT12" s="4">
         <v>0</v>
       </c>
-      <c r="BU12" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV12" s="4">
-        <v>0</v>
-      </c>
-      <c r="BW12" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX12" s="4">
-        <v>0</v>
-      </c>
       <c r="BY12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ12" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA12" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB12" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC12" s="4">
         <v>0</v>
       </c>
       <c r="CY12" s="1">
@@ -1653,19 +1653,7 @@
       <c r="BI13" s="3">
         <v>0</v>
       </c>
-      <c r="BP13" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ13" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR13" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS13" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT13" s="4">
+      <c r="BR13" s="1">
         <v>0</v>
       </c>
       <c r="CO13" s="3">
@@ -1805,20 +1793,8 @@
       <c r="BI14" s="3">
         <v>0</v>
       </c>
-      <c r="BP14" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ14" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR14" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS14" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT14" s="4">
-        <v>0</v>
+      <c r="BR14" s="1">
+        <v>4</v>
       </c>
       <c r="CO14" s="3">
         <v>0</v>
@@ -1972,19 +1948,7 @@
       <c r="BI15" s="3">
         <v>0</v>
       </c>
-      <c r="BP15" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ15" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR15" s="4">
-        <v>11</v>
-      </c>
-      <c r="BS15" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT15" s="4">
+      <c r="BR15" s="1">
         <v>0</v>
       </c>
       <c r="CO15" s="3">
@@ -2139,19 +2103,7 @@
       <c r="BI16" s="3">
         <v>0</v>
       </c>
-      <c r="BP16" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ16" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR16" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS16" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT16" s="4">
+      <c r="BR16" s="1">
         <v>0</v>
       </c>
       <c r="CO16" s="3">
@@ -2306,20 +2258,8 @@
       <c r="BI17" s="3">
         <v>0</v>
       </c>
-      <c r="BP17" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ17" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR17" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS17" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT17" s="4">
-        <v>0</v>
+      <c r="BR17" s="1">
+        <v>4</v>
       </c>
       <c r="CO17" s="3">
         <v>0</v>
@@ -2500,6 +2440,9 @@
       <c r="BI18" s="3">
         <v>0</v>
       </c>
+      <c r="BR18" s="1">
+        <v>0</v>
+      </c>
       <c r="CO18" s="3">
         <v>0</v>
       </c>
@@ -3413,21 +3356,6 @@
       <c r="BI23" s="3">
         <v>0</v>
       </c>
-      <c r="BP23" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ23" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR23" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS23" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT23" s="4">
-        <v>0</v>
-      </c>
       <c r="CD23" s="4">
         <v>0</v>
       </c>
@@ -3595,21 +3523,6 @@
       <c r="BI24" s="3">
         <v>0</v>
       </c>
-      <c r="BP24" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ24" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR24" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS24" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT24" s="4">
-        <v>0</v>
-      </c>
       <c r="CD24" s="4">
         <v>0</v>
       </c>
@@ -3786,19 +3699,7 @@
       <c r="BI25" s="3">
         <v>0</v>
       </c>
-      <c r="BP25" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ25" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR25" s="4">
-        <v>11</v>
-      </c>
-      <c r="BS25" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT25" s="4">
+      <c r="BR25" s="1">
         <v>0</v>
       </c>
       <c r="CD25" s="4">
@@ -3995,20 +3896,8 @@
       <c r="BI26" s="3">
         <v>0</v>
       </c>
-      <c r="BP26" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ26" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR26" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS26" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT26" s="4">
-        <v>0</v>
+      <c r="BR26" s="1">
+        <v>4</v>
       </c>
       <c r="CD26" s="4">
         <v>0</v>
@@ -4198,19 +4087,7 @@
       <c r="BI27" s="3">
         <v>0</v>
       </c>
-      <c r="BP27" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ27" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR27" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS27" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT27" s="4">
+      <c r="BR27" s="1">
         <v>0</v>
       </c>
       <c r="CF27" s="1">
@@ -5658,19 +5535,7 @@
       <c r="AG46" s="1">
         <v>4</v>
       </c>
-      <c r="BK46" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL46" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM46" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN46" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO46" s="4">
+      <c r="BM46" s="1">
         <v>0</v>
       </c>
       <c r="DY46" s="1">
@@ -5747,20 +5612,8 @@
       <c r="AG47" s="1">
         <v>0</v>
       </c>
-      <c r="BK47" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL47" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM47" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN47" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO47" s="4">
-        <v>0</v>
+      <c r="BM47" s="1">
+        <v>4</v>
       </c>
       <c r="DY47" s="1">
         <v>0</v>
@@ -5836,19 +5689,7 @@
       <c r="AG48" s="1">
         <v>0</v>
       </c>
-      <c r="BK48" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL48" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM48" s="4">
-        <v>11</v>
-      </c>
-      <c r="BN48" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO48" s="4">
+      <c r="BM48" s="1">
         <v>0</v>
       </c>
       <c r="DY48" s="1">
@@ -5925,19 +5766,7 @@
       <c r="AG49" s="1">
         <v>4</v>
       </c>
-      <c r="BK49" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL49" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM49" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN49" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO49" s="4">
+      <c r="BM49" s="1">
         <v>0</v>
       </c>
       <c r="DY49" s="1">
@@ -6014,20 +5843,8 @@
       <c r="AG50" s="1">
         <v>0</v>
       </c>
-      <c r="BK50" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL50" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM50" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN50" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO50" s="4">
-        <v>0</v>
+      <c r="BM50" s="1">
+        <v>4</v>
       </c>
       <c r="DY50" s="1">
         <v>0</v>
@@ -6103,19 +5920,7 @@
       <c r="AG51" s="1">
         <v>0</v>
       </c>
-      <c r="BK51" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL51" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM51" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN51" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO51" s="4">
+      <c r="BM51" s="1">
         <v>0</v>
       </c>
       <c r="DY51" s="1">
@@ -6192,19 +5997,7 @@
       <c r="AG52" s="1">
         <v>4</v>
       </c>
-      <c r="BK52" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL52" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM52" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN52" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO52" s="4">
+      <c r="BM52" s="1">
         <v>0</v>
       </c>
       <c r="DY52" s="1">
@@ -6281,20 +6074,8 @@
       <c r="AG53" s="1">
         <v>0</v>
       </c>
-      <c r="BK53" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL53" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM53" s="4">
-        <v>11</v>
-      </c>
-      <c r="BN53" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO53" s="4">
-        <v>0</v>
+      <c r="BM53" s="1">
+        <v>4</v>
       </c>
       <c r="DY53" s="1">
         <v>0</v>
@@ -6370,34 +6151,7 @@
       <c r="AG54" s="1">
         <v>0</v>
       </c>
-      <c r="BK54" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL54" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM54" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN54" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO54" s="4">
-        <v>0</v>
-      </c>
-      <c r="DF54" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG54" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH54" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI54" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ54" s="4">
+      <c r="BM54" s="1">
         <v>0</v>
       </c>
       <c r="DY54" s="1">
@@ -6474,34 +6228,7 @@
       <c r="AG55" s="1">
         <v>4</v>
       </c>
-      <c r="BK55" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL55" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM55" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN55" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO55" s="4">
-        <v>0</v>
-      </c>
-      <c r="DF55" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG55" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH55" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI55" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ55" s="4">
+      <c r="BM55" s="1">
         <v>0</v>
       </c>
       <c r="DY55" s="1">
@@ -6578,152 +6305,8 @@
       <c r="AG56" s="1">
         <v>0</v>
       </c>
-      <c r="BK56" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL56" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM56" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN56" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO56" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP56" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ56" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR56" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS56" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT56" s="4">
-        <v>0</v>
-      </c>
-      <c r="BU56" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV56" s="4">
-        <v>0</v>
-      </c>
-      <c r="BW56" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX56" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY56" s="4">
-        <v>0</v>
-      </c>
-      <c r="CC56" s="4">
-        <v>0</v>
-      </c>
-      <c r="CD56" s="4">
-        <v>0</v>
-      </c>
-      <c r="CE56" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF56" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG56" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK56" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL56" s="4">
-        <v>0</v>
-      </c>
-      <c r="CM56" s="4">
-        <v>0</v>
-      </c>
-      <c r="CN56" s="4">
-        <v>0</v>
-      </c>
-      <c r="CO56" s="4">
-        <v>0</v>
-      </c>
-      <c r="CS56" s="4">
-        <v>0</v>
-      </c>
-      <c r="CT56" s="4">
-        <v>0</v>
-      </c>
-      <c r="CU56" s="4">
-        <v>0</v>
-      </c>
-      <c r="CV56" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW56" s="4">
-        <v>0</v>
-      </c>
-      <c r="DA56" s="4">
-        <v>0</v>
-      </c>
-      <c r="DB56" s="4">
-        <v>0</v>
-      </c>
-      <c r="DC56" s="4">
-        <v>0</v>
-      </c>
-      <c r="DD56" s="4">
-        <v>0</v>
-      </c>
-      <c r="DE56" s="4">
-        <v>0</v>
-      </c>
-      <c r="DF56" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG56" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH56" s="4">
-        <v>11</v>
-      </c>
-      <c r="DI56" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ56" s="4">
-        <v>0</v>
-      </c>
-      <c r="DK56" s="1">
-        <v>0</v>
-      </c>
-      <c r="DL56" s="1">
-        <v>3</v>
-      </c>
-      <c r="DM56" s="1">
-        <v>0</v>
-      </c>
-      <c r="DN56" s="1">
-        <v>0</v>
-      </c>
-      <c r="DO56" s="1">
-        <v>3</v>
-      </c>
-      <c r="DP56" s="1">
-        <v>0</v>
-      </c>
-      <c r="DQ56" s="1">
-        <v>0</v>
-      </c>
-      <c r="DR56" s="1">
-        <v>3</v>
-      </c>
-      <c r="DS56" s="1">
-        <v>0</v>
+      <c r="BM56" s="1">
+        <v>4</v>
       </c>
       <c r="DY56" s="1">
         <v>0</v>
@@ -6832,127 +6415,10 @@
       <c r="AR57" s="4">
         <v>0</v>
       </c>
-      <c r="BK57" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL57" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM57" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN57" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO57" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP57" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ57" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR57" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS57" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT57" s="4">
-        <v>0</v>
-      </c>
-      <c r="BU57" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV57" s="4">
-        <v>0</v>
-      </c>
-      <c r="BW57" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX57" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY57" s="4">
-        <v>0</v>
-      </c>
-      <c r="CC57" s="4">
-        <v>0</v>
-      </c>
-      <c r="CD57" s="4">
-        <v>0</v>
-      </c>
-      <c r="CE57" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF57" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG57" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK57" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL57" s="4">
-        <v>0</v>
-      </c>
-      <c r="CM57" s="4">
-        <v>0</v>
-      </c>
-      <c r="CN57" s="4">
-        <v>0</v>
-      </c>
-      <c r="CO57" s="4">
-        <v>0</v>
-      </c>
-      <c r="CS57" s="4">
-        <v>0</v>
-      </c>
-      <c r="CT57" s="4">
-        <v>0</v>
-      </c>
-      <c r="CU57" s="4">
-        <v>0</v>
-      </c>
-      <c r="CV57" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW57" s="4">
-        <v>0</v>
-      </c>
-      <c r="DA57" s="4">
-        <v>0</v>
-      </c>
-      <c r="DB57" s="4">
-        <v>0</v>
-      </c>
-      <c r="DC57" s="4">
-        <v>0</v>
-      </c>
-      <c r="DD57" s="4">
-        <v>0</v>
-      </c>
-      <c r="DE57" s="4">
-        <v>0</v>
-      </c>
-      <c r="DF57" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG57" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH57" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI57" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ57" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS57" s="1">
+      <c r="BM57" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR57" s="1">
         <v>0</v>
       </c>
       <c r="DY57" s="1">
@@ -7059,73 +6525,76 @@
       <c r="AR58" s="4">
         <v>0</v>
       </c>
-      <c r="BK58" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL58" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM58" s="4">
-        <v>11</v>
-      </c>
-      <c r="BN58" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO58" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP58" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ58" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR58" s="4">
-        <v>11</v>
-      </c>
-      <c r="BS58" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT58" s="4">
-        <v>0</v>
-      </c>
-      <c r="BU58" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV58" s="4">
-        <v>0</v>
-      </c>
-      <c r="BW58" s="4">
-        <v>11</v>
-      </c>
-      <c r="BX58" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY58" s="4">
+      <c r="BJ58" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK58" s="1">
+        <v>3</v>
+      </c>
+      <c r="BL58" s="1">
+        <v>0</v>
+      </c>
+      <c r="BM58" s="1">
+        <v>0</v>
+      </c>
+      <c r="BN58" s="1">
+        <v>3</v>
+      </c>
+      <c r="BO58" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP58" s="1">
+        <v>0</v>
+      </c>
+      <c r="BQ58" s="1">
+        <v>3</v>
+      </c>
+      <c r="BR58" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS58" s="1">
+        <v>0</v>
+      </c>
+      <c r="BT58" s="1">
+        <v>3</v>
+      </c>
+      <c r="BU58" s="1">
+        <v>0</v>
+      </c>
+      <c r="BV58" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW58" s="1">
+        <v>3</v>
+      </c>
+      <c r="BX58" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY58" s="1">
         <v>0</v>
       </c>
       <c r="BZ58" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CA58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CB58" s="1">
         <v>0</v>
       </c>
-      <c r="CC58" s="4">
-        <v>0</v>
-      </c>
-      <c r="CD58" s="4">
-        <v>0</v>
-      </c>
-      <c r="CE58" s="4">
-        <v>11</v>
-      </c>
-      <c r="CF58" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG58" s="4">
+      <c r="CC58" s="1">
+        <v>3</v>
+      </c>
+      <c r="CD58" s="1">
+        <v>0</v>
+      </c>
+      <c r="CE58" s="1">
+        <v>0</v>
+      </c>
+      <c r="CF58" s="1">
+        <v>3</v>
+      </c>
+      <c r="CG58" s="1">
         <v>0</v>
       </c>
       <c r="CH58" s="1">
@@ -7137,85 +6606,106 @@
       <c r="CJ58" s="1">
         <v>0</v>
       </c>
-      <c r="CK58" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL58" s="4">
-        <v>0</v>
-      </c>
-      <c r="CM58" s="4">
-        <v>11</v>
-      </c>
-      <c r="CN58" s="4">
-        <v>0</v>
-      </c>
-      <c r="CO58" s="4">
-        <v>0</v>
+      <c r="CK58" s="1">
+        <v>0</v>
+      </c>
+      <c r="CL58" s="1">
+        <v>3</v>
+      </c>
+      <c r="CM58" s="1">
+        <v>0</v>
+      </c>
+      <c r="CN58" s="1">
+        <v>0</v>
+      </c>
+      <c r="CO58" s="1">
+        <v>3</v>
       </c>
       <c r="CP58" s="1">
         <v>0</v>
       </c>
       <c r="CQ58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CR58" s="1">
-        <v>0</v>
-      </c>
-      <c r="CS58" s="4">
-        <v>0</v>
-      </c>
-      <c r="CT58" s="4">
-        <v>0</v>
-      </c>
-      <c r="CU58" s="4">
-        <v>11</v>
-      </c>
-      <c r="CV58" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW58" s="4">
+        <v>3</v>
+      </c>
+      <c r="CS58" s="1">
+        <v>0</v>
+      </c>
+      <c r="CT58" s="1">
+        <v>0</v>
+      </c>
+      <c r="CU58" s="1">
+        <v>3</v>
+      </c>
+      <c r="CV58" s="1">
+        <v>0</v>
+      </c>
+      <c r="CW58" s="1">
         <v>0</v>
       </c>
       <c r="CX58" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CY58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CZ58" s="1">
         <v>0</v>
       </c>
-      <c r="DA58" s="4">
-        <v>0</v>
-      </c>
-      <c r="DB58" s="4">
-        <v>0</v>
-      </c>
-      <c r="DC58" s="4">
-        <v>11</v>
-      </c>
-      <c r="DD58" s="4">
-        <v>0</v>
-      </c>
-      <c r="DE58" s="4">
-        <v>0</v>
-      </c>
-      <c r="DF58" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG58" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH58" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI58" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ58" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS58" s="1">
+      <c r="DA58" s="1">
+        <v>3</v>
+      </c>
+      <c r="DB58" s="1">
+        <v>0</v>
+      </c>
+      <c r="DC58" s="1">
+        <v>0</v>
+      </c>
+      <c r="DD58" s="1">
+        <v>3</v>
+      </c>
+      <c r="DE58" s="1">
+        <v>0</v>
+      </c>
+      <c r="DF58" s="1">
+        <v>0</v>
+      </c>
+      <c r="DG58" s="1">
+        <v>3</v>
+      </c>
+      <c r="DH58" s="1">
+        <v>0</v>
+      </c>
+      <c r="DI58" s="1">
+        <v>0</v>
+      </c>
+      <c r="DJ58" s="1">
+        <v>3</v>
+      </c>
+      <c r="DK58" s="1">
+        <v>0</v>
+      </c>
+      <c r="DL58" s="1">
+        <v>0</v>
+      </c>
+      <c r="DM58" s="1">
+        <v>3</v>
+      </c>
+      <c r="DN58" s="1">
+        <v>0</v>
+      </c>
+      <c r="DO58" s="1">
+        <v>0</v>
+      </c>
+      <c r="DP58" s="1">
+        <v>3</v>
+      </c>
+      <c r="DQ58" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR58" s="1">
         <v>4</v>
       </c>
       <c r="DY58" s="1">
@@ -7376,127 +6866,10 @@
       <c r="BJ59" s="1">
         <v>0</v>
       </c>
-      <c r="BK59" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL59" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM59" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN59" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO59" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP59" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ59" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR59" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS59" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT59" s="4">
-        <v>0</v>
-      </c>
-      <c r="BU59" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV59" s="4">
-        <v>0</v>
-      </c>
-      <c r="BW59" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX59" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY59" s="4">
-        <v>0</v>
-      </c>
-      <c r="CC59" s="4">
-        <v>0</v>
-      </c>
-      <c r="CD59" s="4">
-        <v>0</v>
-      </c>
-      <c r="CE59" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF59" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG59" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK59" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL59" s="4">
-        <v>0</v>
-      </c>
-      <c r="CM59" s="4">
-        <v>0</v>
-      </c>
-      <c r="CN59" s="4">
-        <v>0</v>
-      </c>
-      <c r="CO59" s="4">
-        <v>0</v>
-      </c>
-      <c r="CS59" s="4">
-        <v>0</v>
-      </c>
-      <c r="CT59" s="4">
-        <v>0</v>
-      </c>
-      <c r="CU59" s="4">
-        <v>0</v>
-      </c>
-      <c r="CV59" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW59" s="4">
-        <v>0</v>
-      </c>
-      <c r="DA59" s="4">
-        <v>0</v>
-      </c>
-      <c r="DB59" s="4">
-        <v>0</v>
-      </c>
-      <c r="DC59" s="4">
-        <v>0</v>
-      </c>
-      <c r="DD59" s="4">
-        <v>0</v>
-      </c>
-      <c r="DE59" s="4">
-        <v>0</v>
-      </c>
-      <c r="DF59" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG59" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH59" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI59" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ59" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS59" s="1">
+      <c r="DJ59" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR59" s="1">
         <v>0</v>
       </c>
       <c r="DY59" s="1">
@@ -7606,127 +6979,10 @@
       <c r="BJ60" s="1">
         <v>0</v>
       </c>
-      <c r="BK60" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL60" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM60" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN60" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO60" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP60" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ60" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR60" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS60" s="4">
-        <v>0</v>
-      </c>
-      <c r="BT60" s="4">
-        <v>0</v>
-      </c>
-      <c r="BU60" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV60" s="4">
-        <v>0</v>
-      </c>
-      <c r="BW60" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX60" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY60" s="4">
-        <v>0</v>
-      </c>
-      <c r="CC60" s="4">
-        <v>0</v>
-      </c>
-      <c r="CD60" s="4">
-        <v>0</v>
-      </c>
-      <c r="CE60" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF60" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG60" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK60" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL60" s="4">
-        <v>0</v>
-      </c>
-      <c r="CM60" s="4">
-        <v>0</v>
-      </c>
-      <c r="CN60" s="4">
-        <v>0</v>
-      </c>
-      <c r="CO60" s="4">
-        <v>0</v>
-      </c>
-      <c r="CS60" s="4">
-        <v>0</v>
-      </c>
-      <c r="CT60" s="4">
-        <v>0</v>
-      </c>
-      <c r="CU60" s="4">
-        <v>0</v>
-      </c>
-      <c r="CV60" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW60" s="4">
-        <v>0</v>
-      </c>
-      <c r="DA60" s="4">
-        <v>0</v>
-      </c>
-      <c r="DB60" s="4">
-        <v>0</v>
-      </c>
-      <c r="DC60" s="4">
-        <v>0</v>
-      </c>
-      <c r="DD60" s="4">
-        <v>0</v>
-      </c>
-      <c r="DE60" s="4">
-        <v>0</v>
-      </c>
-      <c r="DF60" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG60" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH60" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI60" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ60" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS60" s="1">
+      <c r="DJ60" s="1">
+        <v>4</v>
+      </c>
+      <c r="DR60" s="1">
         <v>0</v>
       </c>
       <c r="DY60" s="1">
@@ -7836,22 +7092,10 @@
       <c r="BJ61" s="1">
         <v>4</v>
       </c>
-      <c r="DF61" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG61" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH61" s="4">
-        <v>11</v>
-      </c>
-      <c r="DI61" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ61" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS61" s="1">
+      <c r="DJ61" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR61" s="1">
         <v>4</v>
       </c>
       <c r="DY61" s="1">
@@ -7946,22 +7190,10 @@
       <c r="BJ62" s="1">
         <v>0</v>
       </c>
-      <c r="DF62" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG62" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH62" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI62" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ62" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS62" s="1">
+      <c r="DJ62" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR62" s="1">
         <v>0</v>
       </c>
       <c r="DY62" s="1">
@@ -8041,22 +7273,10 @@
       <c r="BJ63" s="1">
         <v>0</v>
       </c>
-      <c r="DF63" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG63" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH63" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI63" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ63" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS63" s="1">
+      <c r="DJ63" s="1">
+        <v>4</v>
+      </c>
+      <c r="DR63" s="1">
         <v>0</v>
       </c>
       <c r="DY63" s="1">
@@ -8136,22 +7356,10 @@
       <c r="BJ64" s="1">
         <v>4</v>
       </c>
-      <c r="DF64" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG64" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH64" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI64" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ64" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS64" s="1">
+      <c r="DJ64" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR64" s="1">
         <v>4</v>
       </c>
       <c r="DY64" s="1">
@@ -8231,22 +7439,10 @@
       <c r="BJ65" s="1">
         <v>0</v>
       </c>
-      <c r="DF65" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG65" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH65" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI65" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ65" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS65" s="1">
+      <c r="DJ65" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR65" s="1">
         <v>0</v>
       </c>
       <c r="DY65" s="1">
@@ -8386,34 +7582,10 @@
       <c r="CI66" s="3">
         <v>0</v>
       </c>
-      <c r="DF66" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG66" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH66" s="4">
-        <v>11</v>
-      </c>
-      <c r="DI66" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ66" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ66" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR66" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS66" s="4">
-        <v>0</v>
-      </c>
-      <c r="DT66" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU66" s="4">
+      <c r="DJ66" s="1">
+        <v>4</v>
+      </c>
+      <c r="DR66" s="1">
         <v>0</v>
       </c>
       <c r="DY66" s="1">
@@ -8496,35 +7668,11 @@
       <c r="CI67" s="3">
         <v>0</v>
       </c>
-      <c r="DF67" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG67" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH67" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI67" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ67" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ67" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR67" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS67" s="4">
-        <v>0</v>
-      </c>
-      <c r="DT67" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU67" s="4">
-        <v>0</v>
+      <c r="DJ67" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR67" s="1">
+        <v>4</v>
       </c>
       <c r="DY67" s="1">
         <v>4</v>
@@ -8606,34 +7754,10 @@
       <c r="CI68" s="3">
         <v>0</v>
       </c>
-      <c r="DF68" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG68" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH68" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI68" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ68" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ68" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR68" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS68" s="4">
-        <v>11</v>
-      </c>
-      <c r="DT68" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU68" s="4">
+      <c r="DJ68" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR68" s="1">
         <v>0</v>
       </c>
       <c r="DY68" s="1">
@@ -8716,22 +7840,10 @@
       <c r="CI69" s="3">
         <v>0</v>
       </c>
-      <c r="DH69" s="1">
-        <v>0</v>
-      </c>
-      <c r="DQ69" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR69" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS69" s="4">
-        <v>0</v>
-      </c>
-      <c r="DT69" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU69" s="4">
+      <c r="DJ69" s="1">
+        <v>4</v>
+      </c>
+      <c r="DR69" s="1">
         <v>0</v>
       </c>
       <c r="DY69" s="1">
@@ -8814,23 +7926,11 @@
       <c r="CI70" s="3">
         <v>0</v>
       </c>
-      <c r="DH70" s="1">
-        <v>4</v>
-      </c>
-      <c r="DQ70" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR70" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS70" s="4">
-        <v>0</v>
-      </c>
-      <c r="DT70" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU70" s="4">
-        <v>0</v>
+      <c r="DJ70" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR70" s="1">
+        <v>4</v>
       </c>
       <c r="DY70" s="1">
         <v>4</v>
@@ -8912,15 +8012,6 @@
       <c r="CI71" s="3">
         <v>0</v>
       </c>
-      <c r="CP71" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ71" s="1">
-        <v>3</v>
-      </c>
-      <c r="CR71" s="1">
-        <v>0</v>
-      </c>
       <c r="CS71" s="1">
         <v>0</v>
       </c>
@@ -8969,7 +8060,13 @@
       <c r="DH71" s="1">
         <v>0</v>
       </c>
-      <c r="DS71" s="1">
+      <c r="DI71" s="1">
+        <v>3</v>
+      </c>
+      <c r="DJ71" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR71" s="1">
         <v>0</v>
       </c>
       <c r="DY71" s="1">
@@ -9136,8 +8233,8 @@
       <c r="CI72" s="3">
         <v>0</v>
       </c>
-      <c r="DS72" s="1">
-        <v>4</v>
+      <c r="DR72" s="1">
+        <v>0</v>
       </c>
       <c r="DY72" s="1">
         <v>0</v>
@@ -9213,8 +8310,8 @@
       <c r="CI73" s="3">
         <v>0</v>
       </c>
-      <c r="DS73" s="1">
-        <v>0</v>
+      <c r="DR73" s="1">
+        <v>4</v>
       </c>
       <c r="DY73" s="1">
         <v>4</v>
@@ -9290,7 +8387,7 @@
       <c r="CI74" s="3">
         <v>0</v>
       </c>
-      <c r="DS74" s="1">
+      <c r="DR74" s="1">
         <v>0</v>
       </c>
       <c r="DY74" s="1">
@@ -9367,8 +8464,8 @@
       <c r="CI75" s="3">
         <v>0</v>
       </c>
-      <c r="DS75" s="1">
-        <v>4</v>
+      <c r="DR75" s="1">
+        <v>0</v>
       </c>
       <c r="DY75" s="1">
         <v>0</v>
@@ -9444,8 +8541,8 @@
       <c r="CI76" s="3">
         <v>0</v>
       </c>
-      <c r="DS76" s="1">
-        <v>0</v>
+      <c r="DR76" s="1">
+        <v>4</v>
       </c>
       <c r="DY76" s="1">
         <v>4</v>
@@ -9536,34 +8633,7 @@
       <c r="CI77" s="3">
         <v>0</v>
       </c>
-      <c r="CJ77" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK77" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL77" s="4">
-        <v>0</v>
-      </c>
-      <c r="CM77" s="4">
-        <v>0</v>
-      </c>
-      <c r="CN77" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ77" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR77" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS77" s="4">
-        <v>0</v>
-      </c>
-      <c r="DT77" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU77" s="4">
+      <c r="DR77" s="1">
         <v>0</v>
       </c>
       <c r="DY77" s="1">
@@ -9691,34 +8761,7 @@
       <c r="CI78" s="3">
         <v>0</v>
       </c>
-      <c r="CJ78" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK78" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL78" s="4">
-        <v>0</v>
-      </c>
-      <c r="CM78" s="4">
-        <v>0</v>
-      </c>
-      <c r="CN78" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ78" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR78" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS78" s="4">
-        <v>0</v>
-      </c>
-      <c r="DT78" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU78" s="4">
+      <c r="DR78" s="1">
         <v>0</v>
       </c>
       <c r="DY78" s="1">
@@ -9822,98 +8865,8 @@
       <c r="CI79" s="3">
         <v>0</v>
       </c>
-      <c r="CJ79" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK79" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL79" s="4">
-        <v>11</v>
-      </c>
-      <c r="CM79" s="4">
-        <v>0</v>
-      </c>
-      <c r="CN79" s="4">
-        <v>0</v>
-      </c>
-      <c r="CO79" s="1">
-        <v>0</v>
-      </c>
-      <c r="CP79" s="1">
-        <v>3</v>
-      </c>
-      <c r="CQ79" s="1">
-        <v>0</v>
-      </c>
-      <c r="CR79" s="5">
-        <v>0</v>
-      </c>
-      <c r="CS79" s="5">
-        <v>7</v>
-      </c>
-      <c r="CT79" s="5">
-        <v>0</v>
-      </c>
-      <c r="CU79" s="5">
-        <v>0</v>
-      </c>
-      <c r="CV79" s="5">
-        <v>7</v>
-      </c>
-      <c r="CW79" s="5">
-        <v>0</v>
-      </c>
-      <c r="CX79" s="1">
-        <v>0</v>
-      </c>
-      <c r="CY79" s="1">
-        <v>3</v>
-      </c>
-      <c r="CZ79" s="1">
-        <v>0</v>
-      </c>
-      <c r="DA79" s="1">
-        <v>0</v>
-      </c>
-      <c r="DB79" s="1">
-        <v>3</v>
-      </c>
-      <c r="DC79" s="1">
-        <v>0</v>
-      </c>
-      <c r="DD79" s="1">
-        <v>0</v>
-      </c>
-      <c r="DE79" s="1">
-        <v>3</v>
-      </c>
-      <c r="DF79" s="1">
-        <v>0</v>
-      </c>
-      <c r="DG79" s="1">
-        <v>0</v>
-      </c>
-      <c r="DH79" s="1">
-        <v>3</v>
-      </c>
-      <c r="DI79" s="1">
-        <v>0</v>
-      </c>
-      <c r="DQ79" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR79" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS79" s="4">
-        <v>11</v>
-      </c>
-      <c r="DT79" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU79" s="4">
-        <v>0</v>
+      <c r="DR79" s="1">
+        <v>4</v>
       </c>
       <c r="DY79" s="1">
         <v>4</v>
@@ -10106,37 +9059,76 @@
       <c r="CI80" s="3">
         <v>0</v>
       </c>
-      <c r="CJ80" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK80" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL80" s="4">
-        <v>0</v>
-      </c>
-      <c r="CM80" s="4">
-        <v>0</v>
-      </c>
-      <c r="CN80" s="4">
+      <c r="CJ80" s="1">
+        <v>0</v>
+      </c>
+      <c r="CK80" s="1">
+        <v>0</v>
+      </c>
+      <c r="CL80" s="1">
+        <v>3</v>
+      </c>
+      <c r="CM80" s="1">
+        <v>0</v>
+      </c>
+      <c r="CN80" s="1">
+        <v>0</v>
+      </c>
+      <c r="CO80" s="1">
+        <v>3</v>
+      </c>
+      <c r="CP80" s="1">
+        <v>0</v>
+      </c>
+      <c r="CU80" s="1">
+        <v>0</v>
+      </c>
+      <c r="CV80" s="1">
+        <v>3</v>
+      </c>
+      <c r="CW80" s="1">
+        <v>0</v>
+      </c>
+      <c r="CX80" s="1">
+        <v>0</v>
+      </c>
+      <c r="CY80" s="1">
+        <v>3</v>
+      </c>
+      <c r="CZ80" s="1">
+        <v>0</v>
+      </c>
+      <c r="DA80" s="1">
+        <v>0</v>
+      </c>
+      <c r="DB80" s="1">
+        <v>3</v>
+      </c>
+      <c r="DC80" s="1">
+        <v>0</v>
+      </c>
+      <c r="DD80" s="1">
+        <v>0</v>
+      </c>
+      <c r="DE80" s="1">
+        <v>3</v>
+      </c>
+      <c r="DF80" s="1">
+        <v>0</v>
+      </c>
+      <c r="DG80" s="1">
         <v>0</v>
       </c>
       <c r="DH80" s="1">
-        <v>0</v>
-      </c>
-      <c r="DQ80" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR80" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS80" s="4">
-        <v>0</v>
-      </c>
-      <c r="DT80" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU80" s="4">
+        <v>3</v>
+      </c>
+      <c r="DI80" s="1">
+        <v>0</v>
+      </c>
+      <c r="DJ80" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR80" s="1">
         <v>0</v>
       </c>
       <c r="DY80" s="1">
@@ -10246,37 +9238,13 @@
       <c r="CI81" s="3">
         <v>0</v>
       </c>
-      <c r="CJ81" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK81" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL81" s="4">
-        <v>0</v>
-      </c>
-      <c r="CM81" s="4">
-        <v>0</v>
-      </c>
-      <c r="CN81" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH81" s="1">
-        <v>4</v>
-      </c>
-      <c r="DQ81" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR81" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS81" s="4">
-        <v>0</v>
-      </c>
-      <c r="DT81" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU81" s="4">
+      <c r="CJ81" s="1">
+        <v>4</v>
+      </c>
+      <c r="DJ81" s="1">
+        <v>4</v>
+      </c>
+      <c r="DR81" s="1">
         <v>0</v>
       </c>
       <c r="DY81" s="1">
@@ -10374,11 +9342,11 @@
       <c r="CJ82" s="1">
         <v>0</v>
       </c>
-      <c r="DH82" s="1">
-        <v>0</v>
-      </c>
-      <c r="DS82" s="1">
-        <v>0</v>
+      <c r="DJ82" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR82" s="1">
+        <v>4</v>
       </c>
       <c r="DY82" s="1">
         <v>4</v>
@@ -10473,25 +9441,13 @@
         <v>0</v>
       </c>
       <c r="CJ83" s="1">
-        <v>4</v>
-      </c>
-      <c r="DF83" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG83" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH83" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI83" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ83" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS83" s="1">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="DJ83" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR83" s="1">
+        <v>0</v>
       </c>
       <c r="DY83" s="1">
         <v>0</v>
@@ -10571,27 +9527,12 @@
         <v>0</v>
       </c>
       <c r="CJ84" s="1">
-        <v>0</v>
-      </c>
-      <c r="DF84" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG84" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH84" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI84" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ84" s="4">
-        <v>0</v>
-      </c>
-      <c r="DM84" s="1">
-        <v>0</v>
-      </c>
-      <c r="DS84" s="1">
+        <v>4</v>
+      </c>
+      <c r="DJ84" s="1">
+        <v>4</v>
+      </c>
+      <c r="DR84" s="1">
         <v>0</v>
       </c>
       <c r="DY84" s="1">
@@ -10674,26 +9615,11 @@
       <c r="CJ85" s="1">
         <v>0</v>
       </c>
-      <c r="DF85" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG85" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH85" s="4">
-        <v>11</v>
-      </c>
-      <c r="DI85" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ85" s="4">
-        <v>0</v>
-      </c>
-      <c r="DM85" s="1">
-        <v>4</v>
-      </c>
-      <c r="DS85" s="1">
-        <v>0</v>
+      <c r="DJ85" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR85" s="1">
+        <v>4</v>
       </c>
       <c r="DY85" s="1">
         <v>4</v>
@@ -10713,28 +9639,13 @@
         <v>0</v>
       </c>
       <c r="CJ86" s="1">
-        <v>4</v>
-      </c>
-      <c r="DF86" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG86" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH86" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI86" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ86" s="4">
-        <v>0</v>
-      </c>
-      <c r="DM86" s="1">
-        <v>0</v>
-      </c>
-      <c r="DS86" s="1">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="DJ86" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR86" s="1">
+        <v>0</v>
       </c>
       <c r="DY86" s="1">
         <v>0</v>
@@ -10751,24 +9662,12 @@
         <v>0</v>
       </c>
       <c r="CJ87" s="1">
-        <v>0</v>
-      </c>
-      <c r="DF87" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG87" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH87" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI87" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ87" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS87" s="1">
+        <v>4</v>
+      </c>
+      <c r="DJ87" s="1">
+        <v>4</v>
+      </c>
+      <c r="DR87" s="1">
         <v>0</v>
       </c>
       <c r="DY87" s="1">
@@ -10785,50 +9684,14 @@
       <c r="AG88" s="1">
         <v>4</v>
       </c>
-      <c r="CH88" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI88" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ88" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK88" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL88" s="4">
-        <v>0</v>
-      </c>
-      <c r="DF88" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG88" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH88" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI88" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ88" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ88" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR88" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS88" s="4">
-        <v>0</v>
-      </c>
-      <c r="DT88" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU88" s="4">
-        <v>0</v>
+      <c r="CJ88" s="1">
+        <v>0</v>
+      </c>
+      <c r="DJ88" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR88" s="1">
+        <v>4</v>
       </c>
       <c r="DY88" s="1">
         <v>4</v>
@@ -10859,49 +9722,13 @@
       <c r="AG89" s="1">
         <v>0</v>
       </c>
-      <c r="CH89" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI89" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ89" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK89" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL89" s="4">
-        <v>0</v>
-      </c>
-      <c r="DF89" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG89" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH89" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI89" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ89" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ89" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR89" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS89" s="4">
-        <v>0</v>
-      </c>
-      <c r="DT89" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU89" s="4">
+      <c r="CJ89" s="1">
+        <v>0</v>
+      </c>
+      <c r="DJ89" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR89" s="1">
         <v>0</v>
       </c>
       <c r="DY89" s="1">
@@ -10933,49 +9760,13 @@
       <c r="AG90" s="1">
         <v>0</v>
       </c>
-      <c r="CH90" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI90" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ90" s="4">
-        <v>11</v>
-      </c>
-      <c r="CK90" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL90" s="4">
-        <v>0</v>
-      </c>
-      <c r="DF90" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG90" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH90" s="4">
-        <v>11</v>
-      </c>
-      <c r="DI90" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ90" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ90" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR90" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS90" s="4">
-        <v>11</v>
-      </c>
-      <c r="DT90" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU90" s="4">
+      <c r="CJ90" s="1">
+        <v>4</v>
+      </c>
+      <c r="DJ90" s="1">
+        <v>4</v>
+      </c>
+      <c r="DR90" s="1">
         <v>0</v>
       </c>
       <c r="DY90" s="1">
@@ -11007,50 +9798,14 @@
       <c r="AG91" s="1">
         <v>4</v>
       </c>
-      <c r="CH91" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI91" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ91" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK91" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL91" s="4">
-        <v>0</v>
-      </c>
-      <c r="DF91" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG91" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH91" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI91" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ91" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ91" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR91" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS91" s="4">
-        <v>0</v>
-      </c>
-      <c r="DT91" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU91" s="4">
-        <v>0</v>
+      <c r="CJ91" s="1">
+        <v>0</v>
+      </c>
+      <c r="DJ91" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR91" s="1">
+        <v>4</v>
       </c>
       <c r="DY91" s="1">
         <v>4</v>
@@ -11081,49 +9836,13 @@
       <c r="AG92" s="1">
         <v>0</v>
       </c>
-      <c r="CH92" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI92" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ92" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK92" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL92" s="4">
-        <v>0</v>
-      </c>
-      <c r="DF92" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG92" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH92" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI92" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ92" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ92" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR92" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS92" s="4">
-        <v>0</v>
-      </c>
-      <c r="DT92" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU92" s="4">
+      <c r="CJ92" s="1">
+        <v>0</v>
+      </c>
+      <c r="DJ92" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR92" s="1">
         <v>0</v>
       </c>
       <c r="DY92" s="1">
@@ -11155,67 +9874,13 @@
       <c r="AG93" s="1">
         <v>0</v>
       </c>
-      <c r="CH93" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI93" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ93" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK93" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL93" s="4">
-        <v>0</v>
-      </c>
-      <c r="CP93" s="4">
-        <v>0</v>
-      </c>
-      <c r="CQ93" s="4">
-        <v>0</v>
-      </c>
-      <c r="CR93" s="4">
-        <v>0</v>
-      </c>
-      <c r="CS93" s="4">
-        <v>0</v>
-      </c>
-      <c r="CT93" s="4">
-        <v>0</v>
-      </c>
-      <c r="CX93" s="4">
-        <v>0</v>
-      </c>
-      <c r="CY93" s="4">
-        <v>0</v>
-      </c>
-      <c r="CZ93" s="4">
-        <v>0</v>
-      </c>
-      <c r="DA93" s="4">
-        <v>0</v>
-      </c>
-      <c r="DB93" s="4">
-        <v>0</v>
-      </c>
-      <c r="DF93" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG93" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH93" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI93" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ93" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS93" s="1">
+      <c r="CJ93" s="1">
+        <v>4</v>
+      </c>
+      <c r="DJ93" s="1">
+        <v>4</v>
+      </c>
+      <c r="DR93" s="1">
         <v>0</v>
       </c>
       <c r="DY93" s="1">
@@ -11235,67 +9900,13 @@
       <c r="BJ94" s="1">
         <v>0</v>
       </c>
-      <c r="CH94" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI94" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ94" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK94" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL94" s="4">
-        <v>0</v>
-      </c>
-      <c r="CP94" s="4">
-        <v>0</v>
-      </c>
-      <c r="CQ94" s="4">
-        <v>0</v>
-      </c>
-      <c r="CR94" s="4">
-        <v>0</v>
-      </c>
-      <c r="CS94" s="4">
-        <v>0</v>
-      </c>
-      <c r="CT94" s="4">
-        <v>0</v>
-      </c>
-      <c r="CX94" s="4">
-        <v>0</v>
-      </c>
-      <c r="CY94" s="4">
-        <v>0</v>
-      </c>
-      <c r="CZ94" s="4">
-        <v>0</v>
-      </c>
-      <c r="DA94" s="4">
-        <v>0</v>
-      </c>
-      <c r="DB94" s="4">
-        <v>0</v>
-      </c>
-      <c r="DF94" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG94" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH94" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI94" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ94" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS94" s="1">
+      <c r="CJ94" s="1">
+        <v>0</v>
+      </c>
+      <c r="DJ94" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR94" s="1">
         <v>4</v>
       </c>
       <c r="DY94" s="1">
@@ -11315,19 +9926,13 @@
       <c r="BJ95" s="1">
         <v>4</v>
       </c>
-      <c r="CH95" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI95" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ95" s="4">
-        <v>11</v>
-      </c>
-      <c r="CK95" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL95" s="4">
+      <c r="CJ95" s="1">
+        <v>0</v>
+      </c>
+      <c r="CK95" s="1">
+        <v>3</v>
+      </c>
+      <c r="CL95" s="1">
         <v>0</v>
       </c>
       <c r="CM95" s="1">
@@ -11339,70 +9944,70 @@
       <c r="CO95" s="1">
         <v>0</v>
       </c>
-      <c r="CP95" s="4">
-        <v>0</v>
-      </c>
-      <c r="CQ95" s="4">
-        <v>0</v>
-      </c>
-      <c r="CR95" s="4">
-        <v>11</v>
-      </c>
-      <c r="CS95" s="4">
-        <v>0</v>
-      </c>
-      <c r="CT95" s="4">
-        <v>0</v>
+      <c r="CP95" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ95" s="1">
+        <v>3</v>
+      </c>
+      <c r="CR95" s="1">
+        <v>0</v>
+      </c>
+      <c r="CS95" s="1">
+        <v>0</v>
+      </c>
+      <c r="CT95" s="1">
+        <v>3</v>
       </c>
       <c r="CU95" s="1">
         <v>0</v>
       </c>
       <c r="CV95" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CW95" s="1">
-        <v>0</v>
-      </c>
-      <c r="CX95" s="4">
-        <v>0</v>
-      </c>
-      <c r="CY95" s="4">
-        <v>0</v>
-      </c>
-      <c r="CZ95" s="4">
-        <v>11</v>
-      </c>
-      <c r="DA95" s="4">
-        <v>0</v>
-      </c>
-      <c r="DB95" s="4">
+        <v>3</v>
+      </c>
+      <c r="CX95" s="1">
+        <v>0</v>
+      </c>
+      <c r="CY95" s="1">
+        <v>0</v>
+      </c>
+      <c r="CZ95" s="1">
+        <v>3</v>
+      </c>
+      <c r="DA95" s="1">
+        <v>0</v>
+      </c>
+      <c r="DB95" s="1">
         <v>0</v>
       </c>
       <c r="DC95" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DD95" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DE95" s="1">
         <v>0</v>
       </c>
-      <c r="DF95" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG95" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH95" s="4">
-        <v>11</v>
-      </c>
-      <c r="DI95" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ95" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS95" s="1">
+      <c r="DF95" s="1">
+        <v>3</v>
+      </c>
+      <c r="DG95" s="1">
+        <v>0</v>
+      </c>
+      <c r="DH95" s="1">
+        <v>0</v>
+      </c>
+      <c r="DI95" s="1">
+        <v>3</v>
+      </c>
+      <c r="DJ95" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR95" s="1">
         <v>0</v>
       </c>
       <c r="DY95" s="1">
@@ -11422,67 +10027,10 @@
       <c r="BJ96" s="1">
         <v>0</v>
       </c>
-      <c r="CH96" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI96" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ96" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK96" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL96" s="4">
-        <v>0</v>
-      </c>
-      <c r="CP96" s="4">
-        <v>0</v>
-      </c>
-      <c r="CQ96" s="4">
-        <v>0</v>
-      </c>
-      <c r="CR96" s="4">
-        <v>0</v>
-      </c>
-      <c r="CS96" s="4">
-        <v>0</v>
-      </c>
-      <c r="CT96" s="4">
-        <v>0</v>
-      </c>
-      <c r="CX96" s="4">
-        <v>0</v>
-      </c>
-      <c r="CY96" s="4">
-        <v>0</v>
-      </c>
-      <c r="CZ96" s="4">
-        <v>0</v>
-      </c>
-      <c r="DA96" s="4">
-        <v>0</v>
-      </c>
-      <c r="DB96" s="4">
-        <v>0</v>
-      </c>
-      <c r="DF96" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG96" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH96" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI96" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ96" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS96" s="1">
+      <c r="CJ96" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR96" s="1">
         <v>0</v>
       </c>
       <c r="DY96" s="1">
@@ -11514,67 +10062,10 @@
       <c r="BL97" s="4">
         <v>0</v>
       </c>
-      <c r="CH97" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI97" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ97" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK97" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL97" s="4">
-        <v>0</v>
-      </c>
-      <c r="CP97" s="4">
-        <v>0</v>
-      </c>
-      <c r="CQ97" s="4">
-        <v>0</v>
-      </c>
-      <c r="CR97" s="4">
-        <v>0</v>
-      </c>
-      <c r="CS97" s="4">
-        <v>0</v>
-      </c>
-      <c r="CT97" s="4">
-        <v>0</v>
-      </c>
-      <c r="CX97" s="4">
-        <v>0</v>
-      </c>
-      <c r="CY97" s="4">
-        <v>0</v>
-      </c>
-      <c r="CZ97" s="4">
-        <v>0</v>
-      </c>
-      <c r="DA97" s="4">
-        <v>0</v>
-      </c>
-      <c r="DB97" s="4">
-        <v>0</v>
-      </c>
-      <c r="DF97" s="4">
-        <v>0</v>
-      </c>
-      <c r="DG97" s="4">
-        <v>0</v>
-      </c>
-      <c r="DH97" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI97" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ97" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS97" s="1">
+      <c r="CJ97" s="1">
+        <v>4</v>
+      </c>
+      <c r="DR97" s="1">
         <v>4</v>
       </c>
       <c r="DY97" s="1">
@@ -11606,22 +10097,10 @@
       <c r="BL98" s="4">
         <v>0</v>
       </c>
-      <c r="CH98" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI98" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ98" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK98" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL98" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS98" s="1">
+      <c r="CJ98" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR98" s="1">
         <v>0</v>
       </c>
       <c r="DY98" s="1">
@@ -11653,34 +10132,10 @@
       <c r="BL99" s="4">
         <v>0</v>
       </c>
-      <c r="CH99" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI99" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ99" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK99" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL99" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ99" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR99" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS99" s="4">
-        <v>0</v>
-      </c>
-      <c r="DT99" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU99" s="4">
+      <c r="CJ99" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR99" s="1">
         <v>0</v>
       </c>
       <c r="DY99" s="1">
@@ -11727,35 +10182,11 @@
       <c r="BL100" s="4">
         <v>0</v>
       </c>
-      <c r="CH100" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI100" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ100" s="4">
-        <v>11</v>
-      </c>
-      <c r="CK100" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL100" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ100" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR100" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS100" s="4">
-        <v>0</v>
-      </c>
-      <c r="DT100" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU100" s="4">
-        <v>0</v>
+      <c r="CJ100" s="1">
+        <v>4</v>
+      </c>
+      <c r="DR100" s="1">
+        <v>4</v>
       </c>
       <c r="DY100" s="1">
         <v>4</v>
@@ -11801,34 +10232,10 @@
       <c r="BL101" s="4">
         <v>0</v>
       </c>
-      <c r="CH101" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI101" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ101" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK101" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL101" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ101" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR101" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS101" s="4">
-        <v>11</v>
-      </c>
-      <c r="DT101" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU101" s="4">
+      <c r="CJ101" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR101" s="1">
         <v>0</v>
       </c>
       <c r="DY101" s="1">
@@ -11863,34 +10270,10 @@
       <c r="BJ102" s="1">
         <v>0</v>
       </c>
-      <c r="CH102" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI102" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ102" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK102" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL102" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ102" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR102" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS102" s="4">
-        <v>0</v>
-      </c>
-      <c r="DT102" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU102" s="4">
+      <c r="CJ102" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR102" s="1">
         <v>0</v>
       </c>
       <c r="DY102" s="1">
@@ -11925,65 +10308,11 @@
       <c r="BJ103" s="1">
         <v>4</v>
       </c>
-      <c r="BX103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ103" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA103" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB103" s="4">
-        <v>0</v>
-      </c>
-      <c r="CC103" s="4">
-        <v>0</v>
-      </c>
-      <c r="CD103" s="4">
-        <v>0</v>
-      </c>
-      <c r="CE103" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF103" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG103" s="4">
-        <v>0</v>
-      </c>
-      <c r="CH103" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI103" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ103" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK103" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL103" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ103" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR103" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS103" s="4">
-        <v>0</v>
-      </c>
-      <c r="DT103" s="4">
-        <v>0</v>
-      </c>
-      <c r="DU103" s="4">
-        <v>0</v>
+      <c r="CJ103" s="1">
+        <v>4</v>
+      </c>
+      <c r="DR103" s="1">
+        <v>4</v>
       </c>
       <c r="DY103" s="1">
         <v>4</v>
@@ -12017,52 +10346,10 @@
       <c r="BJ104" s="1">
         <v>0</v>
       </c>
-      <c r="BX104" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY104" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ104" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA104" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB104" s="4">
-        <v>0</v>
-      </c>
-      <c r="CC104" s="4">
-        <v>0</v>
-      </c>
-      <c r="CD104" s="4">
-        <v>0</v>
-      </c>
-      <c r="CE104" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF104" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG104" s="4">
-        <v>0</v>
-      </c>
-      <c r="CH104" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI104" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ104" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK104" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL104" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS104" s="1">
+      <c r="CJ104" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR104" s="1">
         <v>0</v>
       </c>
       <c r="DY104" s="1">
@@ -12169,9 +10456,6 @@
       <c r="AU105" s="1">
         <v>0</v>
       </c>
-      <c r="AV105" s="1">
-        <v>0</v>
-      </c>
       <c r="BE105" s="1">
         <v>0</v>
       </c>
@@ -12229,49 +10513,49 @@
       <c r="BW105" s="1">
         <v>0</v>
       </c>
-      <c r="BX105" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY105" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ105" s="4">
-        <v>11</v>
-      </c>
-      <c r="CA105" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB105" s="4">
-        <v>0</v>
-      </c>
-      <c r="CC105" s="4">
-        <v>0</v>
-      </c>
-      <c r="CD105" s="4">
-        <v>0</v>
-      </c>
-      <c r="CE105" s="4">
-        <v>11</v>
-      </c>
-      <c r="CF105" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG105" s="4">
-        <v>0</v>
-      </c>
-      <c r="CH105" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI105" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ105" s="4">
-        <v>11</v>
-      </c>
-      <c r="CK105" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL105" s="4">
+      <c r="BX105" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY105" s="1">
+        <v>3</v>
+      </c>
+      <c r="BZ105" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA105" s="1">
+        <v>0</v>
+      </c>
+      <c r="CB105" s="1">
+        <v>3</v>
+      </c>
+      <c r="CC105" s="1">
+        <v>0</v>
+      </c>
+      <c r="CD105" s="1">
+        <v>0</v>
+      </c>
+      <c r="CE105" s="1">
+        <v>3</v>
+      </c>
+      <c r="CF105" s="1">
+        <v>0</v>
+      </c>
+      <c r="CG105" s="1">
+        <v>0</v>
+      </c>
+      <c r="CH105" s="1">
+        <v>3</v>
+      </c>
+      <c r="CI105" s="1">
+        <v>0</v>
+      </c>
+      <c r="CJ105" s="1">
+        <v>0</v>
+      </c>
+      <c r="CK105" s="1">
+        <v>3</v>
+      </c>
+      <c r="CL105" s="1">
         <v>0</v>
       </c>
       <c r="CM105" s="1">
@@ -12370,9 +10654,6 @@
       <c r="DR105" s="1">
         <v>0</v>
       </c>
-      <c r="DS105" s="1">
-        <v>4</v>
-      </c>
       <c r="DY105" s="1">
         <v>0</v>
       </c>
@@ -12388,57 +10669,15 @@
         <v>4</v>
       </c>
       <c r="AV106" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE106" s="1">
         <v>4</v>
       </c>
-      <c r="BX106" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY106" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ106" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA106" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB106" s="4">
-        <v>0</v>
-      </c>
-      <c r="CC106" s="4">
-        <v>0</v>
-      </c>
-      <c r="CD106" s="4">
-        <v>0</v>
-      </c>
-      <c r="CE106" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF106" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG106" s="4">
-        <v>0</v>
-      </c>
-      <c r="CH106" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI106" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ106" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK106" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL106" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS106" s="1">
+      <c r="BZ106" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR106" s="1">
         <v>0</v>
       </c>
       <c r="DY106" s="1">
@@ -12456,58 +10695,16 @@
         <v>0</v>
       </c>
       <c r="AV107" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE107" s="1">
         <v>0</v>
       </c>
-      <c r="BX107" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY107" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ107" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA107" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB107" s="4">
-        <v>0</v>
-      </c>
-      <c r="CC107" s="4">
-        <v>0</v>
-      </c>
-      <c r="CD107" s="4">
-        <v>0</v>
-      </c>
-      <c r="CE107" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF107" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG107" s="4">
-        <v>0</v>
-      </c>
-      <c r="CH107" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI107" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ107" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK107" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL107" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS107" s="1">
-        <v>0</v>
+      <c r="BZ107" s="1">
+        <v>4</v>
+      </c>
+      <c r="DR107" s="1">
+        <v>4</v>
       </c>
       <c r="DY107" s="1">
         <v>0</v>
@@ -12523,19 +10720,7 @@
       <c r="Q108" s="1">
         <v>0</v>
       </c>
-      <c r="AT108" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU108" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV108" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW108" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX108" s="4">
+      <c r="AV108" s="1">
         <v>0</v>
       </c>
       <c r="BE108" s="1">
@@ -12544,8 +10729,8 @@
       <c r="BZ108" s="1">
         <v>0</v>
       </c>
-      <c r="DS108" s="1">
-        <v>4</v>
+      <c r="DR108" s="1">
+        <v>0</v>
       </c>
       <c r="DY108" s="1">
         <v>0</v>
@@ -12561,28 +10746,16 @@
       <c r="Q109" s="1">
         <v>4</v>
       </c>
-      <c r="AT109" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU109" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV109" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW109" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX109" s="4">
+      <c r="AV109" s="1">
         <v>0</v>
       </c>
       <c r="BE109" s="1">
         <v>4</v>
       </c>
       <c r="BZ109" s="1">
-        <v>4</v>
-      </c>
-      <c r="DS109" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR109" s="1">
         <v>0</v>
       </c>
       <c r="DY109" s="1">
@@ -12599,29 +10772,17 @@
       <c r="Q110" s="1">
         <v>0</v>
       </c>
-      <c r="AT110" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU110" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV110" s="4">
-        <v>11</v>
-      </c>
-      <c r="AW110" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX110" s="4">
-        <v>0</v>
+      <c r="AV110" s="1">
+        <v>4</v>
       </c>
       <c r="BE110" s="1">
         <v>0</v>
       </c>
       <c r="BZ110" s="1">
-        <v>0</v>
-      </c>
-      <c r="DS110" s="1">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="DR110" s="1">
+        <v>4</v>
       </c>
       <c r="DY110" s="1">
         <v>0</v>
@@ -12664,38 +10825,14 @@
       <c r="S111" s="4">
         <v>0</v>
       </c>
-      <c r="AT111" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU111" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV111" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW111" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX111" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX111" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY111" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ111" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA111" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB111" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS111" s="1">
-        <v>4</v>
+      <c r="AV111" s="1">
+        <v>0</v>
+      </c>
+      <c r="BZ111" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR111" s="1">
+        <v>0</v>
       </c>
       <c r="DY111" s="1">
         <v>0</v>
@@ -12738,37 +10875,13 @@
       <c r="S112" s="4">
         <v>0</v>
       </c>
-      <c r="AT112" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU112" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV112" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW112" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX112" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX112" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY112" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ112" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA112" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB112" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS112" s="1">
+      <c r="AV112" s="1">
+        <v>0</v>
+      </c>
+      <c r="BZ112" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR112" s="1">
         <v>0</v>
       </c>
       <c r="DY112" s="1">
@@ -12822,25 +10935,13 @@
         <v>0</v>
       </c>
       <c r="AV113" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ113" s="4">
-        <v>11</v>
-      </c>
-      <c r="CA113" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB113" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS113" s="1">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="BZ113" s="1">
+        <v>4</v>
+      </c>
+      <c r="DR113" s="1">
+        <v>4</v>
       </c>
       <c r="DY113" s="1">
         <v>0</v>
@@ -12884,25 +10985,13 @@
         <v>0</v>
       </c>
       <c r="AV114" s="1">
-        <v>4</v>
-      </c>
-      <c r="BX114" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY114" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ114" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA114" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB114" s="4">
-        <v>0</v>
-      </c>
-      <c r="DS114" s="1">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="BZ114" s="1">
+        <v>0</v>
+      </c>
+      <c r="DR114" s="1">
+        <v>0</v>
       </c>
       <c r="DY114" s="1">
         <v>0</v>
@@ -12948,19 +11037,7 @@
       <c r="AV115" s="1">
         <v>0</v>
       </c>
-      <c r="BX115" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY115" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ115" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA115" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB115" s="4">
+      <c r="BZ115" s="1">
         <v>0</v>
       </c>
       <c r="CK115" s="3">
@@ -13023,7 +11100,7 @@
       <c r="DD115" s="3">
         <v>0</v>
       </c>
-      <c r="DS115" s="1">
+      <c r="DR115" s="1">
         <v>0</v>
       </c>
       <c r="DY115" s="1">
@@ -13058,50 +11135,41 @@
       <c r="AE116" s="4">
         <v>0</v>
       </c>
-      <c r="AF116" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG116" s="4">
-        <v>0</v>
-      </c>
-      <c r="AH116" s="4">
-        <v>0</v>
-      </c>
       <c r="AI116" s="4">
         <v>0</v>
       </c>
       <c r="AJ116" s="4">
         <v>0</v>
       </c>
+      <c r="AK116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR116" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS116" s="4">
+        <v>0</v>
+      </c>
       <c r="AT116" s="4">
         <v>0</v>
       </c>
       <c r="AU116" s="4">
         <v>0</v>
       </c>
-      <c r="AV116" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW116" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ116" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA116" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB116" s="4">
-        <v>0</v>
+      <c r="AV116" s="1">
+        <v>4</v>
+      </c>
+      <c r="BZ116" s="1">
+        <v>4</v>
       </c>
       <c r="CK116" s="3">
         <v>0</v>
@@ -13163,8 +11231,8 @@
       <c r="DD116" s="3">
         <v>0</v>
       </c>
-      <c r="DS116" s="1">
-        <v>0</v>
+      <c r="DR116" s="1">
+        <v>4</v>
       </c>
       <c r="DY116" s="1">
         <v>0</v>
@@ -13198,52 +11266,43 @@
       <c r="AE117" s="4">
         <v>0</v>
       </c>
-      <c r="AF117" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG117" s="4">
-        <v>0</v>
-      </c>
-      <c r="AH117" s="4">
-        <v>0</v>
-      </c>
       <c r="AI117" s="4">
         <v>0</v>
       </c>
       <c r="AJ117" s="4">
         <v>0</v>
       </c>
+      <c r="AK117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR117" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS117" s="4">
+        <v>0</v>
+      </c>
       <c r="AT117" s="4">
         <v>0</v>
       </c>
       <c r="AU117" s="4">
         <v>0</v>
       </c>
-      <c r="AV117" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW117" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX117" s="4">
+      <c r="AV117" s="1">
         <v>0</v>
       </c>
       <c r="BE117" s="1">
         <v>0</v>
       </c>
-      <c r="BX117" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY117" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ117" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA117" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB117" s="4">
+      <c r="BZ117" s="1">
         <v>0</v>
       </c>
       <c r="CK117" s="3">
@@ -13306,8 +11365,8 @@
       <c r="DD117" s="3">
         <v>0</v>
       </c>
-      <c r="DS117" s="1">
-        <v>4</v>
+      <c r="DR117" s="1">
+        <v>0</v>
       </c>
       <c r="DY117" s="1">
         <v>0</v>
@@ -13341,28 +11400,28 @@
       <c r="AE118" s="4">
         <v>0</v>
       </c>
-      <c r="AF118" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG118" s="4">
-        <v>0</v>
-      </c>
-      <c r="AH118" s="4">
+      <c r="AF118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG118" s="1">
+        <v>3</v>
+      </c>
+      <c r="AH118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AK118" s="4">
         <v>11</v>
       </c>
-      <c r="AI118" s="4">
-        <v>0</v>
-      </c>
-      <c r="AJ118" s="4">
-        <v>0</v>
-      </c>
-      <c r="AK118" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL118" s="1">
-        <v>3</v>
-      </c>
-      <c r="AM118" s="1">
+      <c r="AL118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM118" s="4">
         <v>0</v>
       </c>
       <c r="AN118" s="1">
@@ -13374,14 +11433,14 @@
       <c r="AP118" s="1">
         <v>0</v>
       </c>
-      <c r="AQ118" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR118" s="1">
-        <v>3</v>
-      </c>
-      <c r="AS118" s="1">
-        <v>0</v>
+      <c r="AQ118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR118" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS118" s="4">
+        <v>11</v>
       </c>
       <c r="AT118" s="4">
         <v>0</v>
@@ -13389,31 +11448,13 @@
       <c r="AU118" s="4">
         <v>0</v>
       </c>
-      <c r="AV118" s="4">
-        <v>11</v>
-      </c>
-      <c r="AW118" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX118" s="4">
+      <c r="AV118" s="1">
         <v>0</v>
       </c>
       <c r="BE118" s="1">
         <v>4</v>
       </c>
-      <c r="BX118" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY118" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ118" s="4">
-        <v>11</v>
-      </c>
-      <c r="CA118" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB118" s="4">
+      <c r="BZ118" s="1">
         <v>0</v>
       </c>
       <c r="CK118" s="3">
@@ -13476,7 +11517,7 @@
       <c r="DD118" s="3">
         <v>0</v>
       </c>
-      <c r="DS118" s="1">
+      <c r="DR118" s="1">
         <v>0</v>
       </c>
       <c r="DY118" s="1">
@@ -13511,53 +11552,44 @@
       <c r="AE119" s="4">
         <v>0</v>
       </c>
-      <c r="AF119" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG119" s="4">
-        <v>0</v>
-      </c>
-      <c r="AH119" s="4">
-        <v>0</v>
-      </c>
       <c r="AI119" s="4">
         <v>0</v>
       </c>
       <c r="AJ119" s="4">
         <v>0</v>
       </c>
+      <c r="AK119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR119" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS119" s="4">
+        <v>0</v>
+      </c>
       <c r="AT119" s="4">
         <v>0</v>
       </c>
       <c r="AU119" s="4">
         <v>0</v>
       </c>
-      <c r="AV119" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW119" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX119" s="4">
-        <v>0</v>
+      <c r="AV119" s="1">
+        <v>4</v>
       </c>
       <c r="BE119" s="1">
         <v>0</v>
       </c>
-      <c r="BX119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ119" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA119" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB119" s="4">
-        <v>0</v>
+      <c r="BZ119" s="1">
+        <v>4</v>
       </c>
       <c r="CK119" s="3">
         <v>0</v>
@@ -13619,8 +11651,8 @@
       <c r="DD119" s="3">
         <v>0</v>
       </c>
-      <c r="DS119" s="1">
-        <v>0</v>
+      <c r="DR119" s="1">
+        <v>4</v>
       </c>
       <c r="DY119" s="1">
         <v>0</v>
@@ -13654,34 +11686,37 @@
       <c r="AE120" s="4">
         <v>0</v>
       </c>
-      <c r="AF120" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG120" s="4">
-        <v>0</v>
-      </c>
-      <c r="AH120" s="4">
-        <v>0</v>
-      </c>
       <c r="AI120" s="4">
         <v>0</v>
       </c>
       <c r="AJ120" s="4">
         <v>0</v>
       </c>
+      <c r="AK120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR120" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS120" s="4">
+        <v>0</v>
+      </c>
       <c r="AT120" s="4">
         <v>0</v>
       </c>
       <c r="AU120" s="4">
         <v>0</v>
       </c>
-      <c r="AV120" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW120" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX120" s="4">
+      <c r="AV120" s="1">
         <v>0</v>
       </c>
       <c r="BE120" s="1">
@@ -13693,19 +11728,7 @@
       <c r="BG120" s="1">
         <v>0</v>
       </c>
-      <c r="BX120" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY120" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ120" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA120" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB120" s="4">
+      <c r="BZ120" s="1">
         <v>0</v>
       </c>
       <c r="CK120" s="3">
@@ -13768,8 +11791,8 @@
       <c r="DD120" s="3">
         <v>0</v>
       </c>
-      <c r="DS120" s="1">
-        <v>4</v>
+      <c r="DR120" s="1">
+        <v>0</v>
       </c>
       <c r="DY120" s="1">
         <v>0</v>
@@ -13800,19 +11823,7 @@
       <c r="BH121" s="1">
         <v>0</v>
       </c>
-      <c r="BX121" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY121" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ121" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA121" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB121" s="4">
+      <c r="BZ121" s="1">
         <v>0</v>
       </c>
       <c r="CK121" s="3">
@@ -13875,7 +11886,7 @@
       <c r="DD121" s="3">
         <v>0</v>
       </c>
-      <c r="DS121" s="1">
+      <c r="DR121" s="1">
         <v>0</v>
       </c>
       <c r="DY121" s="1">
@@ -13907,19 +11918,10 @@
       <c r="BI122" s="1">
         <v>6</v>
       </c>
-      <c r="BX122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ122" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA122" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB122" s="4">
+      <c r="BZ122" s="1">
+        <v>4</v>
+      </c>
+      <c r="CJ122" s="1">
         <v>0</v>
       </c>
       <c r="CK122" s="3">
@@ -13982,8 +11984,8 @@
       <c r="DD122" s="3">
         <v>0</v>
       </c>
-      <c r="DS122" s="1">
-        <v>0</v>
+      <c r="DR122" s="1">
+        <v>4</v>
       </c>
       <c r="DY122" s="1">
         <v>0</v>
@@ -14014,23 +12016,11 @@
       <c r="BJ123" s="1">
         <v>0</v>
       </c>
-      <c r="BX123" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY123" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ123" s="4">
-        <v>11</v>
-      </c>
-      <c r="CA123" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB123" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ123" s="1">
-        <v>0</v>
+      <c r="BZ123" s="1">
+        <v>0</v>
+      </c>
+      <c r="CI123" s="1">
+        <v>5</v>
       </c>
       <c r="CK123" s="3">
         <v>0</v>
@@ -14092,8 +12082,8 @@
       <c r="DD123" s="3">
         <v>0</v>
       </c>
-      <c r="DS123" s="1">
-        <v>4</v>
+      <c r="DR123" s="1">
+        <v>0</v>
       </c>
       <c r="DY123" s="1">
         <v>0</v>
@@ -14115,34 +12105,7 @@
       <c r="AC124" s="1">
         <v>0</v>
       </c>
-      <c r="AL124" s="4">
-        <v>0</v>
-      </c>
-      <c r="AM124" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN124" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO124" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP124" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT124" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU124" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV124" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW124" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX124" s="4">
+      <c r="AV124" s="1">
         <v>0</v>
       </c>
       <c r="BA124" s="1">
@@ -14151,38 +12114,11 @@
       <c r="BK124" s="1">
         <v>0</v>
       </c>
-      <c r="BN124" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO124" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP124" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ124" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR124" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX124" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY124" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ124" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA124" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB124" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI124" s="1">
-        <v>5</v>
+      <c r="BZ124" s="1">
+        <v>0</v>
+      </c>
+      <c r="CH124" s="1">
+        <v>0</v>
       </c>
       <c r="CK124" s="3">
         <v>0</v>
@@ -14271,7 +12207,7 @@
       <c r="DM124" s="1">
         <v>0</v>
       </c>
-      <c r="DS124" s="1">
+      <c r="DR124" s="1">
         <v>0</v>
       </c>
       <c r="DY124" s="1">
@@ -14309,35 +12245,8 @@
       <c r="AC125" s="1">
         <v>4</v>
       </c>
-      <c r="AL125" s="4">
-        <v>0</v>
-      </c>
-      <c r="AM125" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN125" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO125" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP125" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT125" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU125" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV125" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW125" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX125" s="4">
-        <v>0</v>
+      <c r="AV125" s="1">
+        <v>4</v>
       </c>
       <c r="AZ125" s="1">
         <v>5</v>
@@ -14345,38 +12254,8 @@
       <c r="BL125" s="1">
         <v>6</v>
       </c>
-      <c r="BN125" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO125" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP125" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ125" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR125" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX125" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY125" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ125" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA125" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB125" s="4">
-        <v>0</v>
-      </c>
-      <c r="CH125" s="1">
-        <v>0</v>
+      <c r="BZ125" s="1">
+        <v>4</v>
       </c>
       <c r="CK125" s="3">
         <v>0</v>
@@ -14438,8 +12317,8 @@
       <c r="DD125" s="3">
         <v>0</v>
       </c>
-      <c r="DS125" s="1">
-        <v>0</v>
+      <c r="DR125" s="1">
+        <v>4</v>
       </c>
       <c r="DY125" s="1">
         <v>0</v>
@@ -14476,34 +12355,7 @@
       <c r="AC126" s="1">
         <v>0</v>
       </c>
-      <c r="AL126" s="4">
-        <v>0</v>
-      </c>
-      <c r="AM126" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN126" s="4">
-        <v>11</v>
-      </c>
-      <c r="AO126" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP126" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT126" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU126" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV126" s="4">
-        <v>11</v>
-      </c>
-      <c r="AW126" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX126" s="4">
+      <c r="AV126" s="1">
         <v>0</v>
       </c>
       <c r="AY126" s="1">
@@ -14512,34 +12364,16 @@
       <c r="BM126" s="1">
         <v>0</v>
       </c>
-      <c r="BN126" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO126" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP126" s="4">
-        <v>11</v>
-      </c>
-      <c r="BQ126" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR126" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX126" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY126" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ126" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA126" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB126" s="4">
+      <c r="BN126" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO126" s="1">
+        <v>3</v>
+      </c>
+      <c r="BP126" s="1">
+        <v>0</v>
+      </c>
+      <c r="BZ126" s="1">
         <v>0</v>
       </c>
       <c r="CK126" s="3">
@@ -14602,8 +12436,8 @@
       <c r="DD126" s="3">
         <v>0</v>
       </c>
-      <c r="DS126" s="1">
-        <v>4</v>
+      <c r="DR126" s="1">
+        <v>0</v>
       </c>
       <c r="DY126" s="1">
         <v>0</v>
@@ -14640,64 +12474,16 @@
       <c r="AC127" s="1">
         <v>0</v>
       </c>
-      <c r="AL127" s="4">
-        <v>0</v>
-      </c>
-      <c r="AM127" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN127" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO127" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP127" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT127" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU127" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV127" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW127" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX127" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN127" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO127" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP127" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ127" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR127" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX127" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY127" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ127" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA127" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB127" s="4">
+      <c r="AV127" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW127" s="1">
+        <v>3</v>
+      </c>
+      <c r="AX127" s="1">
+        <v>0</v>
+      </c>
+      <c r="BZ127" s="1">
         <v>0</v>
       </c>
       <c r="CK127" s="3">
@@ -14760,7 +12546,7 @@
       <c r="DD127" s="3">
         <v>0</v>
       </c>
-      <c r="DS127" s="1">
+      <c r="DR127" s="1">
         <v>0</v>
       </c>
       <c r="DY127" s="1">
@@ -14813,21 +12599,6 @@
       <c r="AP128" s="4">
         <v>0</v>
       </c>
-      <c r="AT128" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU128" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV128" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW128" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX128" s="4">
-        <v>0</v>
-      </c>
       <c r="BD128" s="4">
         <v>0</v>
       </c>
@@ -14843,35 +12614,8 @@
       <c r="BH128" s="4">
         <v>0</v>
       </c>
-      <c r="BN128" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO128" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP128" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ128" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR128" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX128" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY128" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ128" s="4">
-        <v>11</v>
-      </c>
-      <c r="CA128" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB128" s="4">
-        <v>0</v>
+      <c r="BZ128" s="1">
+        <v>4</v>
       </c>
       <c r="CK128" s="3">
         <v>0</v>
@@ -14933,8 +12677,8 @@
       <c r="DD128" s="3">
         <v>0</v>
       </c>
-      <c r="DS128" s="1">
-        <v>0</v>
+      <c r="DR128" s="1">
+        <v>4</v>
       </c>
       <c r="DY128" s="1">
         <v>0</v>
@@ -14971,6 +12715,21 @@
       <c r="AC129" s="1">
         <v>0</v>
       </c>
+      <c r="AL129" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM129" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN129" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO129" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP129" s="4">
+        <v>0</v>
+      </c>
       <c r="BD129" s="4">
         <v>0</v>
       </c>
@@ -14986,19 +12745,7 @@
       <c r="BH129" s="4">
         <v>0</v>
       </c>
-      <c r="BX129" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY129" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ129" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA129" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB129" s="4">
+      <c r="BZ129" s="1">
         <v>0</v>
       </c>
       <c r="CK129" s="3">
@@ -15061,8 +12808,8 @@
       <c r="DD129" s="3">
         <v>0</v>
       </c>
-      <c r="DS129" s="1">
-        <v>4</v>
+      <c r="DR129" s="1">
+        <v>0</v>
       </c>
       <c r="DY129" s="1">
         <v>0</v>
@@ -15084,6 +12831,21 @@
       <c r="AC130" s="1">
         <v>0</v>
       </c>
+      <c r="AL130" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM130" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN130" s="4">
+        <v>11</v>
+      </c>
+      <c r="AO130" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP130" s="4">
+        <v>0</v>
+      </c>
       <c r="BD130" s="4">
         <v>0</v>
       </c>
@@ -15099,19 +12861,7 @@
       <c r="BH130" s="4">
         <v>0</v>
       </c>
-      <c r="BX130" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY130" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ130" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA130" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB130" s="4">
+      <c r="BZ130" s="1">
         <v>0</v>
       </c>
       <c r="CK130" s="3">
@@ -15174,7 +12924,7 @@
       <c r="DD130" s="3">
         <v>0</v>
       </c>
-      <c r="DS130" s="1">
+      <c r="DR130" s="1">
         <v>0</v>
       </c>
       <c r="DY130" s="1">
@@ -15221,6 +12971,21 @@
       <c r="AC131" s="1">
         <v>4</v>
       </c>
+      <c r="AL131" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM131" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN131" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO131" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP131" s="4">
+        <v>0</v>
+      </c>
       <c r="BD131" s="4">
         <v>0</v>
       </c>
@@ -15236,20 +13001,8 @@
       <c r="BH131" s="4">
         <v>0</v>
       </c>
-      <c r="BX131" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY131" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ131" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA131" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB131" s="4">
-        <v>0</v>
+      <c r="BZ131" s="1">
+        <v>4</v>
       </c>
       <c r="CK131" s="3">
         <v>0</v>
@@ -15311,8 +13064,8 @@
       <c r="DD131" s="3">
         <v>0</v>
       </c>
-      <c r="DS131" s="1">
-        <v>0</v>
+      <c r="DR131" s="1">
+        <v>4</v>
       </c>
       <c r="DY131" s="1">
         <v>0</v>
@@ -15358,6 +13111,21 @@
       <c r="AC132" s="1">
         <v>0</v>
       </c>
+      <c r="AL132" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM132" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN132" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO132" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP132" s="4">
+        <v>0</v>
+      </c>
       <c r="BD132" s="4">
         <v>0</v>
       </c>
@@ -15373,19 +13141,7 @@
       <c r="BH132" s="4">
         <v>0</v>
       </c>
-      <c r="BX132" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY132" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ132" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA132" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB132" s="4">
+      <c r="BZ132" s="1">
         <v>0</v>
       </c>
       <c r="CK132" s="3">
@@ -15448,8 +13204,8 @@
       <c r="DD132" s="3">
         <v>0</v>
       </c>
-      <c r="DS132" s="1">
-        <v>4</v>
+      <c r="DR132" s="1">
+        <v>0</v>
       </c>
       <c r="DY132" s="1">
         <v>0</v>
@@ -15504,34 +13260,7 @@
       <c r="AC133" s="1">
         <v>0</v>
       </c>
-      <c r="BN133" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO133" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP133" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ133" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR133" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX133" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY133" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ133" s="4">
-        <v>11</v>
-      </c>
-      <c r="CA133" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB133" s="4">
+      <c r="BZ133" s="1">
         <v>0</v>
       </c>
       <c r="CK133" s="3">
@@ -15594,7 +13323,7 @@
       <c r="DD133" s="3">
         <v>0</v>
       </c>
-      <c r="DS133" s="1">
+      <c r="DR133" s="1">
         <v>0</v>
       </c>
       <c r="DY133" s="1">
@@ -15641,50 +13370,17 @@
       <c r="AC134" s="1">
         <v>4</v>
       </c>
-      <c r="AT134" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU134" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV134" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW134" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX134" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN134" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO134" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP134" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ134" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR134" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX134" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY134" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ134" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA134" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB134" s="4">
-        <v>0</v>
+      <c r="AV134" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW134" s="1">
+        <v>3</v>
+      </c>
+      <c r="AX134" s="1">
+        <v>0</v>
+      </c>
+      <c r="BZ134" s="1">
+        <v>4</v>
       </c>
       <c r="CK134" s="3">
         <v>0</v>
@@ -15746,8 +13442,8 @@
       <c r="DD134" s="3">
         <v>0</v>
       </c>
-      <c r="DS134" s="1">
-        <v>0</v>
+      <c r="DR134" s="1">
+        <v>4</v>
       </c>
       <c r="DY134" s="1">
         <v>0</v>
@@ -15793,19 +13489,7 @@
       <c r="AC135" s="1">
         <v>0</v>
       </c>
-      <c r="AT135" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU135" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV135" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW135" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX135" s="4">
+      <c r="AV135" s="1">
         <v>0</v>
       </c>
       <c r="AY135" s="1">
@@ -15814,41 +13498,23 @@
       <c r="BM135" s="1">
         <v>0</v>
       </c>
-      <c r="BN135" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO135" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP135" s="4">
-        <v>11</v>
-      </c>
-      <c r="BQ135" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR135" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX135" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY135" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ135" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA135" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB135" s="4">
+      <c r="BN135" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO135" s="1">
+        <v>3</v>
+      </c>
+      <c r="BP135" s="1">
+        <v>0</v>
+      </c>
+      <c r="BZ135" s="1">
         <v>0</v>
       </c>
       <c r="CS135" s="1">
         <v>0</v>
       </c>
-      <c r="DS135" s="1">
-        <v>4</v>
+      <c r="DR135" s="1">
+        <v>0</v>
       </c>
       <c r="DY135" s="1">
         <v>0</v>
@@ -15876,20 +13542,8 @@
       <c r="AE136" s="4">
         <v>0</v>
       </c>
-      <c r="AT136" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU136" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV136" s="4">
-        <v>11</v>
-      </c>
-      <c r="AW136" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX136" s="4">
-        <v>0</v>
+      <c r="AV136" s="1">
+        <v>4</v>
       </c>
       <c r="AZ136" s="1">
         <v>6</v>
@@ -15897,21 +13551,6 @@
       <c r="BL136" s="1">
         <v>5</v>
       </c>
-      <c r="BN136" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO136" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP136" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ136" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR136" s="4">
-        <v>0</v>
-      </c>
       <c r="BX136" s="4">
         <v>0</v>
       </c>
@@ -15933,7 +13572,7 @@
       <c r="CR136" s="1">
         <v>5</v>
       </c>
-      <c r="DS136" s="1">
+      <c r="DR136" s="1">
         <v>0</v>
       </c>
       <c r="DY136" s="1">
@@ -15962,55 +13601,13 @@
       <c r="AE137" s="4">
         <v>0</v>
       </c>
-      <c r="AK137" s="4">
-        <v>0</v>
-      </c>
-      <c r="AL137" s="4">
-        <v>0</v>
-      </c>
-      <c r="AM137" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN137" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO137" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT137" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU137" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV137" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW137" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX137" s="4">
+      <c r="AV137" s="1">
         <v>0</v>
       </c>
       <c r="BA137" s="1">
         <v>0</v>
       </c>
       <c r="BK137" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN137" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO137" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP137" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ137" s="4">
-        <v>0</v>
-      </c>
-      <c r="BR137" s="4">
         <v>0</v>
       </c>
       <c r="BX137" s="4">
@@ -16034,8 +13631,8 @@
       <c r="CQ137" s="1">
         <v>0</v>
       </c>
-      <c r="DS137" s="1">
-        <v>0</v>
+      <c r="DR137" s="1">
+        <v>4</v>
       </c>
       <c r="DY137" s="1">
         <v>0</v>
@@ -16063,34 +13660,7 @@
       <c r="AE138" s="4">
         <v>0</v>
       </c>
-      <c r="AK138" s="4">
-        <v>0</v>
-      </c>
-      <c r="AL138" s="4">
-        <v>0</v>
-      </c>
-      <c r="AM138" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN138" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO138" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT138" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU138" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV138" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW138" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX138" s="4">
+      <c r="AV138" s="1">
         <v>0</v>
       </c>
       <c r="BB138" s="1">
@@ -16120,8 +13690,8 @@
       <c r="CP138" s="1">
         <v>0</v>
       </c>
-      <c r="DS138" s="1">
-        <v>4</v>
+      <c r="DR138" s="1">
+        <v>0</v>
       </c>
       <c r="DY138" s="1">
         <v>0</v>
@@ -16156,7 +13726,7 @@
         <v>0</v>
       </c>
       <c r="AM139" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AN139" s="4">
         <v>0</v>
@@ -16165,7 +13735,7 @@
         <v>0</v>
       </c>
       <c r="AV139" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC139" s="1">
         <v>6</v>
@@ -16191,7 +13761,7 @@
       <c r="CO139" s="1">
         <v>5</v>
       </c>
-      <c r="DS139" s="1">
+      <c r="DR139" s="1">
         <v>0</v>
       </c>
       <c r="DY139" s="1">
@@ -16236,7 +13806,7 @@
         <v>0</v>
       </c>
       <c r="AV140" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BD140" s="1">
         <v>0</v>
@@ -16262,8 +13832,8 @@
       <c r="CN140" s="1">
         <v>0</v>
       </c>
-      <c r="DS140" s="1">
-        <v>0</v>
+      <c r="DR140" s="1">
+        <v>4</v>
       </c>
       <c r="DY140" s="1">
         <v>0</v>
@@ -16286,7 +13856,7 @@
         <v>0</v>
       </c>
       <c r="AM141" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AN141" s="4">
         <v>0</v>
@@ -16312,8 +13882,8 @@
       <c r="CM141" s="1">
         <v>0</v>
       </c>
-      <c r="DS141" s="1">
-        <v>4</v>
+      <c r="DR141" s="1">
+        <v>0</v>
       </c>
       <c r="DY141" s="1">
         <v>0</v>
@@ -16329,20 +13899,23 @@
       <c r="AC142" s="1">
         <v>4</v>
       </c>
-      <c r="AT142" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU142" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV142" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW142" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX142" s="4">
-        <v>0</v>
+      <c r="AK142" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL142" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM142" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN142" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO142" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV142" s="1">
+        <v>4</v>
       </c>
       <c r="BZ142" s="1">
         <v>4</v>
@@ -16404,9 +13977,6 @@
       <c r="DR142" s="1">
         <v>0</v>
       </c>
-      <c r="DS142" s="1">
-        <v>0</v>
-      </c>
       <c r="DY142" s="1">
         <v>4</v>
       </c>
@@ -16421,19 +13991,22 @@
       <c r="AC143" s="1">
         <v>0</v>
       </c>
-      <c r="AT143" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU143" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV143" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW143" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX143" s="4">
+      <c r="AK143" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL143" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM143" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN143" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO143" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV143" s="1">
         <v>0</v>
       </c>
       <c r="BZ143" s="1">
@@ -16456,19 +14029,7 @@
       <c r="AC144" s="1">
         <v>0</v>
       </c>
-      <c r="AT144" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU144" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV144" s="4">
-        <v>11</v>
-      </c>
-      <c r="AW144" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX144" s="4">
+      <c r="AV144" s="1">
         <v>0</v>
       </c>
       <c r="CJ144" s="1">
@@ -16488,20 +14049,8 @@
       <c r="AC145" s="1">
         <v>4</v>
       </c>
-      <c r="AT145" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU145" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV145" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW145" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX145" s="4">
-        <v>0</v>
+      <c r="AV145" s="1">
+        <v>4</v>
       </c>
       <c r="CI145" s="1">
         <v>5</v>
@@ -16520,19 +14069,7 @@
       <c r="AC146" s="1">
         <v>0</v>
       </c>
-      <c r="AT146" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU146" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV146" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW146" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX146" s="4">
+      <c r="AV146" s="1">
         <v>0</v>
       </c>
       <c r="CH146" s="1">

--- a/media/Levels/Level_5.xlsx
+++ b/media/Levels/Level_5.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4450CC44-ECD9-41C3-A7FD-6A8C9C34BD60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E06CFDD-95E2-4315-8C04-371759B31B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="72" windowWidth="15660" windowHeight="12168" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Level_5" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2750,15 +2750,6 @@
       <c r="AI20" s="1">
         <v>0</v>
       </c>
-      <c r="AM20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN20" s="1">
-        <v>3</v>
-      </c>
-      <c r="AO20" s="1">
-        <v>0</v>
-      </c>
       <c r="AP20" s="3">
         <v>0</v>
       </c>
@@ -3538,15 +3529,6 @@
       <c r="CH24" s="4">
         <v>0</v>
       </c>
-      <c r="CL24" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM24" s="1">
-        <v>3</v>
-      </c>
-      <c r="CN24" s="1">
-        <v>0</v>
-      </c>
       <c r="CO24" s="3">
         <v>0</v>
       </c>
@@ -5539,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="DY46" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET46" s="1">
         <v>0</v>
@@ -5770,7 +5752,7 @@
         <v>0</v>
       </c>
       <c r="DY49" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET49" s="1">
         <v>0</v>
@@ -6001,7 +5983,7 @@
         <v>0</v>
       </c>
       <c r="DY52" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET52" s="1">
         <v>0</v>
@@ -6232,7 +6214,7 @@
         <v>0</v>
       </c>
       <c r="DY55" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET55" s="1">
         <v>0</v>
@@ -6529,7 +6511,7 @@
         <v>0</v>
       </c>
       <c r="BK58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BL58" s="1">
         <v>0</v>
@@ -6538,7 +6520,7 @@
         <v>0</v>
       </c>
       <c r="BN58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BO58" s="1">
         <v>0</v>
@@ -6547,7 +6529,7 @@
         <v>0</v>
       </c>
       <c r="BQ58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR58" s="1">
         <v>0</v>
@@ -6556,7 +6538,7 @@
         <v>0</v>
       </c>
       <c r="BT58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BU58" s="1">
         <v>0</v>
@@ -6565,7 +6547,7 @@
         <v>0</v>
       </c>
       <c r="BW58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BX58" s="1">
         <v>0</v>
@@ -6574,7 +6556,7 @@
         <v>0</v>
       </c>
       <c r="BZ58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CA58" s="1">
         <v>0</v>
@@ -6583,7 +6565,7 @@
         <v>0</v>
       </c>
       <c r="CC58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CD58" s="1">
         <v>0</v>
@@ -6592,7 +6574,7 @@
         <v>0</v>
       </c>
       <c r="CF58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CG58" s="1">
         <v>0</v>
@@ -6601,7 +6583,7 @@
         <v>0</v>
       </c>
       <c r="CI58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CJ58" s="1">
         <v>0</v>
@@ -6610,16 +6592,16 @@
         <v>0</v>
       </c>
       <c r="CL58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CM58" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="CN58" s="1">
         <v>0</v>
       </c>
       <c r="CO58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CP58" s="1">
         <v>0</v>
@@ -6628,7 +6610,7 @@
         <v>0</v>
       </c>
       <c r="CR58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CS58" s="1">
         <v>0</v>
@@ -6637,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="CU58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CV58" s="1">
         <v>0</v>
@@ -6646,7 +6628,7 @@
         <v>0</v>
       </c>
       <c r="CX58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CY58" s="1">
         <v>0</v>
@@ -6655,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="DA58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DB58" s="1">
         <v>0</v>
@@ -6664,7 +6646,7 @@
         <v>0</v>
       </c>
       <c r="DD58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DE58" s="1">
         <v>0</v>
@@ -6673,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="DG58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH58" s="1">
         <v>0</v>
@@ -6682,7 +6664,7 @@
         <v>0</v>
       </c>
       <c r="DJ58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DK58" s="1">
         <v>0</v>
@@ -6691,7 +6673,7 @@
         <v>0</v>
       </c>
       <c r="DM58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DN58" s="1">
         <v>0</v>
@@ -6700,16 +6682,16 @@
         <v>0</v>
       </c>
       <c r="DP58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DQ58" s="1">
         <v>0</v>
       </c>
       <c r="DR58" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY58" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="EJ58" s="4">
         <v>0</v>
@@ -7096,10 +7078,10 @@
         <v>0</v>
       </c>
       <c r="DR61" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY61" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="EJ61" s="4">
         <v>0</v>
@@ -7360,10 +7342,10 @@
         <v>0</v>
       </c>
       <c r="DR64" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY64" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET64" s="1">
         <v>0</v>
@@ -7672,10 +7654,10 @@
         <v>0</v>
       </c>
       <c r="DR67" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY67" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET67" s="1">
         <v>0</v>
@@ -7930,10 +7912,10 @@
         <v>0</v>
       </c>
       <c r="DR70" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY70" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET70" s="1">
         <v>0</v>
@@ -8012,57 +7994,6 @@
       <c r="CI71" s="3">
         <v>0</v>
       </c>
-      <c r="CS71" s="1">
-        <v>0</v>
-      </c>
-      <c r="CT71" s="1">
-        <v>3</v>
-      </c>
-      <c r="CU71" s="1">
-        <v>0</v>
-      </c>
-      <c r="CV71" s="1">
-        <v>0</v>
-      </c>
-      <c r="CW71" s="1">
-        <v>3</v>
-      </c>
-      <c r="CX71" s="1">
-        <v>0</v>
-      </c>
-      <c r="CY71" s="1">
-        <v>0</v>
-      </c>
-      <c r="CZ71" s="1">
-        <v>3</v>
-      </c>
-      <c r="DA71" s="1">
-        <v>0</v>
-      </c>
-      <c r="DB71" s="1">
-        <v>0</v>
-      </c>
-      <c r="DC71" s="1">
-        <v>3</v>
-      </c>
-      <c r="DD71" s="1">
-        <v>0</v>
-      </c>
-      <c r="DE71" s="1">
-        <v>0</v>
-      </c>
-      <c r="DF71" s="1">
-        <v>3</v>
-      </c>
-      <c r="DG71" s="1">
-        <v>0</v>
-      </c>
-      <c r="DH71" s="1">
-        <v>0</v>
-      </c>
-      <c r="DI71" s="1">
-        <v>3</v>
-      </c>
       <c r="DJ71" s="1">
         <v>0</v>
       </c>
@@ -8311,10 +8242,10 @@
         <v>0</v>
       </c>
       <c r="DR73" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY73" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET73" s="1">
         <v>0</v>
@@ -8542,10 +8473,10 @@
         <v>0</v>
       </c>
       <c r="DR76" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY76" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET76" s="1">
         <v>0</v>
@@ -8866,10 +8797,10 @@
         <v>0</v>
       </c>
       <c r="DR79" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY79" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="EB79" s="4">
         <v>0</v>
@@ -8972,33 +8903,6 @@
       <c r="BA80" s="1">
         <v>0</v>
       </c>
-      <c r="BB80" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC80" s="1">
-        <v>3</v>
-      </c>
-      <c r="BD80" s="1">
-        <v>0</v>
-      </c>
-      <c r="BE80" s="1">
-        <v>0</v>
-      </c>
-      <c r="BF80" s="1">
-        <v>3</v>
-      </c>
-      <c r="BG80" s="1">
-        <v>0</v>
-      </c>
-      <c r="BH80" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI80" s="1">
-        <v>3</v>
-      </c>
-      <c r="BJ80" s="1">
-        <v>0</v>
-      </c>
       <c r="BP80" s="3">
         <v>0</v>
       </c>
@@ -9080,15 +8984,6 @@
       <c r="CP80" s="1">
         <v>0</v>
       </c>
-      <c r="CU80" s="1">
-        <v>0</v>
-      </c>
-      <c r="CV80" s="1">
-        <v>3</v>
-      </c>
-      <c r="CW80" s="1">
-        <v>0</v>
-      </c>
       <c r="CX80" s="1">
         <v>0</v>
       </c>
@@ -9175,9 +9070,6 @@
       <c r="AG81" s="1">
         <v>0</v>
       </c>
-      <c r="BJ81" s="1">
-        <v>0</v>
-      </c>
       <c r="BP81" s="3">
         <v>0</v>
       </c>
@@ -9276,9 +9168,6 @@
       <c r="AG82" s="1">
         <v>4</v>
       </c>
-      <c r="BJ82" s="1">
-        <v>4</v>
-      </c>
       <c r="BP82" s="3">
         <v>0</v>
       </c>
@@ -9346,10 +9235,10 @@
         <v>0</v>
       </c>
       <c r="DR82" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY82" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="EB82" s="4">
         <v>0</v>
@@ -9377,9 +9266,6 @@
       <c r="AG83" s="1">
         <v>0</v>
       </c>
-      <c r="BJ83" s="1">
-        <v>0</v>
-      </c>
       <c r="BP83" s="3">
         <v>0</v>
       </c>
@@ -9463,9 +9349,6 @@
       <c r="AG84" s="1">
         <v>0</v>
       </c>
-      <c r="BJ84" s="1">
-        <v>0</v>
-      </c>
       <c r="BP84" s="3">
         <v>0</v>
       </c>
@@ -9549,9 +9432,6 @@
       <c r="AG85" s="1">
         <v>4</v>
       </c>
-      <c r="BJ85" s="1">
-        <v>4</v>
-      </c>
       <c r="BP85" s="3">
         <v>0</v>
       </c>
@@ -9619,10 +9499,10 @@
         <v>0</v>
       </c>
       <c r="DR85" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY85" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET85" s="1">
         <v>0</v>
@@ -9635,9 +9515,6 @@
       <c r="AG86" s="1">
         <v>0</v>
       </c>
-      <c r="BJ86" s="1">
-        <v>0</v>
-      </c>
       <c r="CJ86" s="1">
         <v>0</v>
       </c>
@@ -9691,10 +9568,10 @@
         <v>0</v>
       </c>
       <c r="DR88" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY88" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET88" s="1">
         <v>0</v>
@@ -9805,10 +9682,10 @@
         <v>0</v>
       </c>
       <c r="DR91" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY91" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET91" s="1">
         <v>0</v>
@@ -9897,9 +9774,6 @@
       <c r="AG94" s="1">
         <v>4</v>
       </c>
-      <c r="BJ94" s="1">
-        <v>0</v>
-      </c>
       <c r="CJ94" s="1">
         <v>0</v>
       </c>
@@ -9907,10 +9781,10 @@
         <v>0</v>
       </c>
       <c r="DR94" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY94" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET94" s="1">
         <v>0</v>
@@ -9923,9 +9797,6 @@
       <c r="AG95" s="1">
         <v>0</v>
       </c>
-      <c r="BJ95" s="1">
-        <v>4</v>
-      </c>
       <c r="CJ95" s="1">
         <v>0</v>
       </c>
@@ -10024,9 +9895,6 @@
       <c r="AG96" s="1">
         <v>0</v>
       </c>
-      <c r="BJ96" s="1">
-        <v>0</v>
-      </c>
       <c r="CJ96" s="1">
         <v>0</v>
       </c>
@@ -10047,29 +9915,14 @@
       <c r="AG97" s="1">
         <v>4</v>
       </c>
-      <c r="BH97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL97" s="4">
-        <v>0</v>
-      </c>
       <c r="CJ97" s="1">
         <v>4</v>
       </c>
       <c r="DR97" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY97" s="1">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="ET97" s="1">
         <v>0</v>
@@ -10082,21 +9935,6 @@
       <c r="AG98" s="1">
         <v>0</v>
       </c>
-      <c r="BH98" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI98" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ98" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK98" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL98" s="4">
-        <v>0</v>
-      </c>
       <c r="CJ98" s="1">
         <v>0</v>
       </c>
@@ -10117,26 +9955,11 @@
       <c r="AG99" s="1">
         <v>0</v>
       </c>
-      <c r="BH99" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI99" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ99" s="4">
-        <v>11</v>
-      </c>
-      <c r="BK99" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL99" s="4">
-        <v>0</v>
-      </c>
       <c r="CJ99" s="1">
         <v>0</v>
       </c>
       <c r="DR99" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="DY99" s="1">
         <v>0</v>
@@ -10167,29 +9990,14 @@
       <c r="AG100" s="1">
         <v>4</v>
       </c>
-      <c r="BH100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL100" s="4">
-        <v>0</v>
-      </c>
       <c r="CJ100" s="1">
         <v>4</v>
       </c>
       <c r="DR100" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY100" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="EK100" s="4">
         <v>0</v>
@@ -10217,21 +10025,6 @@
       <c r="AG101" s="1">
         <v>0</v>
       </c>
-      <c r="BH101" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI101" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ101" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK101" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL101" s="4">
-        <v>0</v>
-      </c>
       <c r="CJ101" s="1">
         <v>0</v>
       </c>
@@ -10267,9 +10060,6 @@
       <c r="AG102" s="1">
         <v>0</v>
       </c>
-      <c r="BJ102" s="1">
-        <v>0</v>
-      </c>
       <c r="CJ102" s="1">
         <v>0</v>
       </c>
@@ -10305,17 +10095,14 @@
       <c r="AG103" s="1">
         <v>4</v>
       </c>
-      <c r="BJ103" s="1">
-        <v>4</v>
-      </c>
       <c r="CJ103" s="1">
         <v>4</v>
       </c>
       <c r="DR103" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY103" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="EK103" s="4">
         <v>0</v>
@@ -10343,9 +10130,6 @@
       <c r="AG104" s="1">
         <v>0</v>
       </c>
-      <c r="BJ104" s="1">
-        <v>0</v>
-      </c>
       <c r="CJ104" s="1">
         <v>0</v>
       </c>
@@ -10463,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="BG105" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BH105" s="1">
         <v>0</v>
@@ -10472,7 +10256,7 @@
         <v>0</v>
       </c>
       <c r="BJ105" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BK105" s="1">
         <v>0</v>
@@ -10481,7 +10265,7 @@
         <v>0</v>
       </c>
       <c r="BM105" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BN105" s="1">
         <v>0</v>
@@ -10490,7 +10274,7 @@
         <v>0</v>
       </c>
       <c r="BP105" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BQ105" s="1">
         <v>0</v>
@@ -10499,7 +10283,7 @@
         <v>0</v>
       </c>
       <c r="BS105" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT105" s="1">
         <v>0</v>
@@ -10508,16 +10292,16 @@
         <v>0</v>
       </c>
       <c r="BV105" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BW105" s="1">
         <v>0</v>
       </c>
       <c r="BX105" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BY105" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BZ105" s="1">
         <v>0</v>
@@ -10526,7 +10310,7 @@
         <v>0</v>
       </c>
       <c r="CB105" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CC105" s="1">
         <v>0</v>
@@ -10535,7 +10319,7 @@
         <v>0</v>
       </c>
       <c r="CE105" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CF105" s="1">
         <v>0</v>
@@ -10544,7 +10328,7 @@
         <v>0</v>
       </c>
       <c r="CH105" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CI105" s="1">
         <v>0</v>
@@ -10553,13 +10337,13 @@
         <v>0</v>
       </c>
       <c r="CK105" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CL105" s="1">
         <v>0</v>
       </c>
       <c r="CM105" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CN105" s="1">
         <v>0</v>
@@ -10568,7 +10352,7 @@
         <v>0</v>
       </c>
       <c r="CP105" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CQ105" s="1">
         <v>0</v>
@@ -10672,7 +10456,7 @@
         <v>0</v>
       </c>
       <c r="BE106" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BZ106" s="1">
         <v>0</v>
@@ -10681,7 +10465,7 @@
         <v>0</v>
       </c>
       <c r="DY106" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET106" s="1">
         <v>0</v>
@@ -10698,13 +10482,13 @@
         <v>4</v>
       </c>
       <c r="BE107" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BZ107" s="1">
         <v>4</v>
       </c>
       <c r="DR107" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY107" s="1">
         <v>0</v>
@@ -10750,7 +10534,7 @@
         <v>0</v>
       </c>
       <c r="BE109" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BZ109" s="1">
         <v>0</v>
@@ -10759,7 +10543,7 @@
         <v>0</v>
       </c>
       <c r="DY109" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET109" s="1">
         <v>0</v>
@@ -10776,13 +10560,13 @@
         <v>4</v>
       </c>
       <c r="BE110" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BZ110" s="1">
         <v>4</v>
       </c>
       <c r="DR110" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY110" s="1">
         <v>0</v>
@@ -10828,6 +10612,9 @@
       <c r="AV111" s="1">
         <v>0</v>
       </c>
+      <c r="BE111" s="1">
+        <v>0</v>
+      </c>
       <c r="BZ111" s="1">
         <v>0</v>
       </c>
@@ -10885,7 +10672,7 @@
         <v>0</v>
       </c>
       <c r="DY112" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET112" s="1">
         <v>0</v>
@@ -10941,7 +10728,7 @@
         <v>4</v>
       </c>
       <c r="DR113" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY113" s="1">
         <v>0</v>
@@ -11104,7 +10891,7 @@
         <v>0</v>
       </c>
       <c r="DY115" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET115" s="1">
         <v>0</v>
@@ -11232,7 +11019,7 @@
         <v>0</v>
       </c>
       <c r="DR116" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY116" s="1">
         <v>0</v>
@@ -11299,9 +11086,6 @@
       <c r="AV117" s="1">
         <v>0</v>
       </c>
-      <c r="BE117" s="1">
-        <v>0</v>
-      </c>
       <c r="BZ117" s="1">
         <v>0</v>
       </c>
@@ -11451,9 +11235,6 @@
       <c r="AV118" s="1">
         <v>0</v>
       </c>
-      <c r="BE118" s="1">
-        <v>4</v>
-      </c>
       <c r="BZ118" s="1">
         <v>0</v>
       </c>
@@ -11521,7 +11302,7 @@
         <v>0</v>
       </c>
       <c r="DY118" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET118" s="1">
         <v>0</v>
@@ -11585,9 +11366,6 @@
       <c r="AV119" s="1">
         <v>4</v>
       </c>
-      <c r="BE119" s="1">
-        <v>0</v>
-      </c>
       <c r="BZ119" s="1">
         <v>4</v>
       </c>
@@ -11652,7 +11430,7 @@
         <v>0</v>
       </c>
       <c r="DR119" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY119" s="1">
         <v>0</v>
@@ -11890,7 +11668,7 @@
         <v>0</v>
       </c>
       <c r="DY121" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET121" s="1">
         <v>0</v>
@@ -11985,7 +11763,7 @@
         <v>0</v>
       </c>
       <c r="DR122" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY122" s="1">
         <v>0</v>
@@ -12211,7 +11989,7 @@
         <v>0</v>
       </c>
       <c r="DY124" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ED124" s="4">
         <v>0</v>
@@ -12318,7 +12096,7 @@
         <v>0</v>
       </c>
       <c r="DR125" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY125" s="1">
         <v>0</v>
@@ -12550,7 +12328,7 @@
         <v>0</v>
       </c>
       <c r="DY127" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ED127" s="4">
         <v>0</v>
@@ -12678,7 +12456,7 @@
         <v>0</v>
       </c>
       <c r="DR128" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY128" s="1">
         <v>0</v>
@@ -12928,7 +12706,7 @@
         <v>0</v>
       </c>
       <c r="DY130" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET130" s="1">
         <v>0</v>
@@ -13065,7 +12843,7 @@
         <v>0</v>
       </c>
       <c r="DR131" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY131" s="1">
         <v>0</v>
@@ -13327,7 +13105,7 @@
         <v>0</v>
       </c>
       <c r="DY133" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET133" s="1">
         <v>0</v>
@@ -13443,7 +13221,7 @@
         <v>0</v>
       </c>
       <c r="DR134" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY134" s="1">
         <v>0</v>
@@ -13576,7 +13354,7 @@
         <v>0</v>
       </c>
       <c r="DY136" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET136" s="1">
         <v>0</v>
@@ -13632,7 +13410,7 @@
         <v>0</v>
       </c>
       <c r="DR137" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY137" s="1">
         <v>0</v>
@@ -13765,7 +13543,7 @@
         <v>0</v>
       </c>
       <c r="DY139" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET139" s="1">
         <v>0</v>
@@ -13833,7 +13611,7 @@
         <v>0</v>
       </c>
       <c r="DR140" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DY140" s="1">
         <v>0</v>
@@ -13978,7 +13756,7 @@
         <v>0</v>
       </c>
       <c r="DY142" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET142" s="1">
         <v>0</v>
@@ -14056,7 +13834,7 @@
         <v>5</v>
       </c>
       <c r="DY145" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="ET145" s="1">
         <v>0</v>
@@ -14116,7 +13894,7 @@
         <v>5</v>
       </c>
       <c r="DY148" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="EQ148" s="1">
         <v>0</v>

--- a/media/Levels/Level_5.xlsx
+++ b/media/Levels/Level_5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuta\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\2024年３月特別授業\BaseCross64\DoctorRemote\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E06CFDD-95E2-4315-8C04-371759B31B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9763D425-5ED6-4674-B06F-B3DD199683D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -688,10 +688,10 @@
         <v>0</v>
       </c>
       <c r="BW1" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BY1" s="1">
         <v>0</v>
@@ -14129,10 +14129,10 @@
         <v>0</v>
       </c>
       <c r="BW150" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BY150" s="1">
         <v>0</v>
